--- a/規則庫.xlsx
+++ b/規則庫.xlsx
@@ -98,7 +98,7 @@
       <sz val="14"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -118,6 +118,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFE4B5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C8E6C9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E0F0E0"/>
       </patternFill>
     </fill>
   </fills>
@@ -148,7 +158,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -171,6 +181,13 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -12553,96 +12570,124 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
+  <dimension ref="A1:K2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="10" t="inlineStr">
         <is>
           <t>來源代號</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="10" t="inlineStr">
         <is>
           <t>審查意見檔名</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="10" t="inlineStr">
         <is>
           <t>技師姓名</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="10" t="inlineStr">
         <is>
           <t>技師證書字號</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="10" t="inlineStr">
         <is>
           <t>查核日期</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="10" t="inlineStr">
         <is>
           <t>簽證事業名稱</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="10" t="inlineStr">
         <is>
           <t>匯入日期</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="10" t="inlineStr">
         <is>
           <t>備註</t>
         </is>
       </c>
-    </row>
-    <row r="2" ht="31.5" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="I1" s="11" t="inlineStr">
+        <is>
+          <t>涵蓋槽體數</t>
+        </is>
+      </c>
+      <c r="J1" s="11" t="inlineStr">
+        <is>
+          <t>貢獻規則數</t>
+        </is>
+      </c>
+      <c r="K1" s="11" t="inlineStr">
+        <is>
+          <t>最後同步時間</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>S01</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>水污染業務查核缺失.pdf</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>(多位)</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>(見原文)</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>111-114</t>
         </is>
       </c>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>(多家)</t>
         </is>
       </c>
-      <c r="G2" s="4" t="n"/>
-      <c r="H2" s="4" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>環工技師查核缺失彙整,序1-14</t>
+        </is>
+      </c>
+      <c r="I2" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="J2" s="12" t="n">
+        <v>299</v>
+      </c>
+      <c r="K2" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-03 16:58:38</t>
         </is>
       </c>
     </row>

--- a/規則庫.xlsx
+++ b/規則庫.xlsx
@@ -10,31 +10,32 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_來源清單" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_槽體對照表" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_審查紀錄" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pH調整槽" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="廢水調整池" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="慢混池" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="沉澱池" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中和池" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="放流池" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="現場設備類" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="文件類" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="活性碳吸附裝置" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批次反應槽" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="(文件類)" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="脫水機" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="砂濾塔" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="(現場設備類)" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="快混槽" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="活性碳吸附塔" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="氧化池" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="離子交換樹脂塔" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="暫存槽" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="污泥儲槽" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="曝氣槽" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="貯留槽" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="濃縮槽" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="調勻池" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="廢水收集池" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_同義字" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pH調整槽" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="廢水調整池" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="慢混池" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="沉澱池" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="中和池" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="放流池" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="現場設備類" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="文件類" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="活性碳吸附裝置" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="批次反應槽" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="(文件類)" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="脫水機" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="砂濾塔" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="(現場設備類)" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="快混槽" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="活性碳吸附塔" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="氧化池" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="離子交換樹脂塔" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="暫存槽" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="污泥儲槽" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="曝氣槽" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="貯留槽" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="濃縮槽" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="調勻池" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="廢水收集池" sheetId="30" state="visible" r:id="rId30"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -44,7 +45,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="新細明體"/>
       <family val="2"/>
@@ -97,8 +98,12 @@
       <b val="1"/>
       <sz val="14"/>
     </font>
+    <font>
+      <b val="1"/>
+      <i val="1"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -130,6 +135,11 @@
         <fgColor rgb="00E0F0E0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E0E0E0"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -158,7 +168,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -188,6 +198,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
@@ -1521,6 +1537,208 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:L3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>缺失ID</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>來源</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>原文缺失</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>檢查類型</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>對照項目</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>規則(萃取/可比對判斷式)</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>比對位置(依標題,非頁碼)</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>判定邏輯(條件→結論)</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>技師姓名</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>序號</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>原始槽體代號</t>
+        </is>
+      </c>
+      <c r="L1" s="9" t="inlineStr">
+        <is>
+          <t>狀態</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="63" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>D008</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>S01 水污染業務查核缺失.pdf</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>(8)許可證T01–04中和槽之操作參數包含pH，惟加藥未包含硫酸不合理，且功能測試報告之廢（污）水處理設施處理程序及操作條件之添加藥品量有登載中和槽有添加硫酸。</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>文件一致性</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>硫酸加藥</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>許可證登載加藥種類需與功能測試報告一致</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>廢(污)水(前)處理設施資料表/加藥參數</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>若 功測報告有加藥 且 許可證未登載 → 標記:加藥不一致</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>方天志</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>序1 方天志技師 (8)</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>T01-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="47.25" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>D197a</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>S01 水污染業務查核缺失.pdf</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>(4)P23. T01-03 pH中和槽 pH控制值5~9 後接T01-04活性污泥槽1，生物處理單元的pH值偏低，不利微生物成長。</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>操作條件</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>pH操作範圍</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>銜接生物處理前之調整池pH下限必須滿足微生物生長需求(通常&gt;6)</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>廢(污)水(前)處理設施資料表/操作參數</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>若 進水pH設定過低 → 標記:pH值偏低不利微生物成長</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>徐振利</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>序12 徐振利技師 (4)</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>T01-03</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:L6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
@@ -1880,77 +2098,6 @@
       <c r="K6" s="4" t="inlineStr">
         <is>
           <t>T01-16</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>缺失ID</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>來源</t>
-        </is>
-      </c>
-      <c r="C1" s="5" t="inlineStr">
-        <is>
-          <t>原文缺失</t>
-        </is>
-      </c>
-      <c r="D1" s="5" t="inlineStr">
-        <is>
-          <t>檢查類型</t>
-        </is>
-      </c>
-      <c r="E1" s="5" t="inlineStr">
-        <is>
-          <t>對照項目</t>
-        </is>
-      </c>
-      <c r="F1" s="5" t="inlineStr">
-        <is>
-          <t>規則(萃取/可比對判斷式)</t>
-        </is>
-      </c>
-      <c r="G1" s="5" t="inlineStr">
-        <is>
-          <t>比對位置(依標題,非頁碼)</t>
-        </is>
-      </c>
-      <c r="H1" s="5" t="inlineStr">
-        <is>
-          <t>判定邏輯(條件→結論)</t>
-        </is>
-      </c>
-      <c r="I1" s="9" t="inlineStr">
-        <is>
-          <t>狀態</t>
         </is>
       </c>
     </row>
@@ -2036,6 +2183,77 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>缺失ID</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>來源</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>原文缺失</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>檢查類型</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>對照項目</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>規則(萃取/可比對判斷式)</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>比對位置(依標題,非頁碼)</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>判定邏輯(條件→結論)</t>
+        </is>
+      </c>
+      <c r="I1" s="9" t="inlineStr">
+        <is>
+          <t>狀態</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:L13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
   <cols>
@@ -2802,7 +3020,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3118,7 +3336,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6227,7 +6445,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7113,7 +7331,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7657,7 +7875,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11670,892 +11888,6 @@
       <c r="K70" s="4" t="inlineStr">
         <is>
           <t>T01-05</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="36" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>缺失ID</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>來源</t>
-        </is>
-      </c>
-      <c r="C1" s="5" t="inlineStr">
-        <is>
-          <t>原文缺失</t>
-        </is>
-      </c>
-      <c r="D1" s="5" t="inlineStr">
-        <is>
-          <t>檢查類型</t>
-        </is>
-      </c>
-      <c r="E1" s="5" t="inlineStr">
-        <is>
-          <t>對照項目</t>
-        </is>
-      </c>
-      <c r="F1" s="5" t="inlineStr">
-        <is>
-          <t>規則(萃取/可比對判斷式)</t>
-        </is>
-      </c>
-      <c r="G1" s="5" t="inlineStr">
-        <is>
-          <t>比對位置(依標題,非頁碼)</t>
-        </is>
-      </c>
-      <c r="H1" s="5" t="inlineStr">
-        <is>
-          <t>判定邏輯(條件→結論)</t>
-        </is>
-      </c>
-      <c r="I1" s="5" t="inlineStr">
-        <is>
-          <t>技師姓名</t>
-        </is>
-      </c>
-      <c r="J1" s="5" t="inlineStr">
-        <is>
-          <t>序號</t>
-        </is>
-      </c>
-      <c r="K1" s="5" t="inlineStr">
-        <is>
-          <t>原始槽體代號</t>
-        </is>
-      </c>
-      <c r="L1" s="9" t="inlineStr">
-        <is>
-          <t>狀態</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="47.25" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>D019</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>S01 水污染業務查核缺失.pdf</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>(7)快混池（T01–09）尺寸設計1.21 M，有效水深1.17 M，出水高度僅0.04 M，設計參數不符合環工學理。</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>設計參數</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>出水高度</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>槽體出水高度（乾舷）應留有足夠安全空間，符合環工學理</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>廢(污)水(前)處理設施資料表/容量計算</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>若 出水高度過低 → 標記:設計參數不符學理</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr">
-        <is>
-          <t>張子健</t>
-        </is>
-      </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>序2 張子健技師 (7)</t>
-        </is>
-      </c>
-      <c r="K2" s="4" t="inlineStr">
-        <is>
-          <t>T01-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="47.25" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>D026a</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>S01 水污染業務查核缺失.pdf</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>(14)附件八–2，三個快混池之間流向標示不應該為雙向，應該為“單向”，慢混池有相同標示錯誤問題。</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>流向示意圖</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>流向標示</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>各處理池槽間之廢水流向應為單向流動，不可標示為雙向</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>廠區平面及流向配置圖</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>若 處理池間流向為雙向 → 標記:標示錯誤應為單向</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>張子健</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>序2 張子健技師 (14)</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>(無)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="47.25" customHeight="1">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>D034a</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>S01 水污染業務查核缺失.pdf</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>(4)T02快混、慢混1、慢混3及待過濾池之pH分別顯示為8.15、6.72、6.83及7.58，就pH變化及去除重金屬而言，較不合理</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>操作條件</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="inlineStr">
-        <is>
-          <t>pH變化</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>各連續處理單元之pH變化應符合去除重金屬之沉降學理</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="inlineStr">
-        <is>
-          <t>現場操作參數比對</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>若 相鄰處理槽之pH變化不符合學理 → 標記:pH變化不合理</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>施紹揚</t>
-        </is>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>序3 施紹揚技師 (4)</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>T02</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="47.25" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>D041a</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>S01 水污染業務查核缺失.pdf</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>(11)頁次47~50/95：T02-02快混池停留時間與T02-03慢混池相同，有違一般設計原理</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>設計參數</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>停留時間</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>快混與慢混槽之水力停留時間應有區隔，符合學理設計</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr">
-        <is>
-          <t>廢(污)水(前)處理設施資料表</t>
-        </is>
-      </c>
-      <c r="H5" s="4" t="inlineStr">
-        <is>
-          <t>若 快混停留時間 == 慢混停留時間 → 標記:有違設計原理</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>施紹揚</t>
-        </is>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>序3 施紹揚技師 (11)</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>T02-02</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="110.25" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>D054</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>S01 水污染業務查核缺失.pdf</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>(7)張維欽老師：第9/42頁水質資料表T01-05 pH調整兼快混槽，顯示重金屬鋅由1500 mg/L降至4.5 mg/L，該重金屬鋅非指溶解性，應於化學沈澱池展現其去除效能。洪瑞敏技師：P.9/42，水污染防治措施資料/水質水量平衡示意圖中T01-05 pH調整兼快混槽尚未經過沉澱單元，應該不具有重金屬鋅的去除效果。</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>質量平衡</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>鋅濃度</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>未經沉澱單元前不應表現懸浮重金屬之去除效能</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr">
-        <is>
-          <t>水質水量平衡示意圖</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>若 單元無沉澱功能 且 表現出重金屬去除 → 標記:不具有去除效果</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>彭文良</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>序4 彭文良技師 (7)</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>T01-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="110.25" customHeight="1">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>D055</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>S01 水污染業務查核缺失.pdf</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>(8)張維欽老師：第18/42頁T01-05 pH調整兼快混槽設施資料表，本化混程序擬去除重金屬，控制之pH為6~9，其低限值過低，非適宜去除重金屬之pH範圍。洪瑞敏技師：P.18/42，T01-05 pH 調整兼快混槽的量測操作參數pH 值設定範圍為6~9，則如何確保其重金屬鋅(pH=9.5~10.5)的去除效率?</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>操作條件</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>pH範圍</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>去除特定重金屬之pH應符合該金屬之最佳沉降範圍</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr">
-        <is>
-          <t>廢(污)水(前)處理設施資料表/操作參數</t>
-        </is>
-      </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>若 設定pH範圍不符重金屬沉澱所需 → 標記:pH低限值過低</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>彭文良</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>序4 彭文良技師 (8)</t>
-        </is>
-      </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>T01-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="47.25" customHeight="1">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>D070</t>
-        </is>
-      </c>
-      <c r="B8" s="4" t="inlineStr">
-        <is>
-          <t>S01 水污染業務查核缺失.pdf</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>(3)快混轉速過慢，與常用參數不同。</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>設計參數</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>轉速</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>快混機具轉速應符合學理常見範圍</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="inlineStr">
-        <is>
-          <t>廢(污)水(前)處理設施資料表/操作參數</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>若 轉速 &lt; 學理常用範圍 → 標記:轉速過慢</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>劉暐廷</t>
-        </is>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>序6 劉暐廷技師 (3)</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>(無)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="47.25" customHeight="1">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>D090a</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>S01 水污染業務查核缺失.pdf</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>(2)T01-08快混池，攪拌機如無變頻調整，轉速應為固定，非為80~120rpm。T01-09、T01-15、T01-16，問題同T01-08。</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>操作條件</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>轉速參數</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>無變頻之攪拌機其轉速參數應為固定值而非範圍值</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="inlineStr">
-        <is>
-          <t>廢(污)水(前)處理設施資料表/操作參數</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>若 無變頻器 且 轉速為區間值 → 標記:轉速應為固定</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>陳映嘉</t>
-        </is>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>序7 陳映嘉技師 (2)</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>T01-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="47.25" customHeight="1">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>D099</t>
-        </is>
-      </c>
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t>S01 水污染業務查核缺失.pdf</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>(11)P27_T01-08快混槽1，有效水深標示11公尺，與槽體尺寸不相符。</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>設計參數</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>有效水深</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>有效水深不應超過槽體總高度或不符比例</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="inlineStr">
-        <is>
-          <t>廢(污)水(前)處理設施資料表</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>若 水深 &gt; 槽體尺寸或不合邏輯 → 標記:與尺寸不相符</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>陳映嘉</t>
-        </is>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>序7 陳映嘉技師 (11)</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>T01-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="47.25" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>D107</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>S01 水污染業務查核缺失.pdf</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>(19)T01-18大量汙泥回流至T01-15快混池之設計考量。</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>設計參數</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>污泥迴流設計</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>特殊之污泥迴流設計應有明確之學理考量與說明</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="inlineStr">
-        <is>
-          <t>設計參數評估</t>
-        </is>
-      </c>
-      <c r="H11" s="4" t="inlineStr">
-        <is>
-          <t>若 特殊迴流無說明 → 標記:迴流之設計考量不明</t>
-        </is>
-      </c>
-      <c r="I11" s="4" t="inlineStr">
-        <is>
-          <t>陳映嘉</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>序7 陳映嘉技師 (19)</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="inlineStr">
-        <is>
-          <t>T01-18;T01-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="63" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>D146</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t>S01 水污染業務查核缺失.pdf</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>(4)頁次28/52及頁次115：本案重金屬廢水以鎳濃度相對較高，T01-08快混槽pH操作參數控制在8~12，pH=8的下限值偏低(pH為8時，鎳之解離濃度可超過1.0mg/L以上)。</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>操作條件</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>pH下限設定</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>高濃度鎳廢水之pH操作下限必須足以維持有效之沉降效果</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>廢(污)水(前)處理設施資料表/操作參數</t>
-        </is>
-      </c>
-      <c r="H12" s="4" t="inlineStr">
-        <is>
-          <t>若 pH下限不足以沉澱目標重金屬 → 標記:下限值偏低</t>
-        </is>
-      </c>
-      <c r="I12" s="4" t="inlineStr">
-        <is>
-          <t>汪正倫</t>
-        </is>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>序9 汪正倫技師 (4)</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="inlineStr">
-        <is>
-          <t>T01-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="47.25" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>D154</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>S01 水污染業務查核缺失.pdf</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>(12)T01-08快混槽之污泥迴流比為0.018%，約為0.074CMD，唯現場操作遠大於迴流比例。</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>操作條件</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>污泥迴流比</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>現場實際污泥迴流操作量必須與許可登載比例相符</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>現場操作查核</t>
-        </is>
-      </c>
-      <c r="H13" s="4" t="inlineStr">
-        <is>
-          <t>若 現場迴流量 &gt; 許可設計迴流比 → 標記:現場操作遠大於迴流比例</t>
-        </is>
-      </c>
-      <c r="I13" s="4" t="inlineStr">
-        <is>
-          <t>汪正倫</t>
-        </is>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>序9 汪正倫技師 (12)</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="inlineStr">
-        <is>
-          <t>T01-08</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="47.25" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>D178a</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>S01 水污染業務查核缺失.pdf</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>(3)由P7. 得知廢水貯池有緊急應變管線，在SS大於400mg/L時排至T01-01混凝池；而P39. T01-30廢水貯池卻無相關量測參數與設施，該如何判斷？</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>設計參數</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>緊急應變量測設施</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>設有水質條件啟動之緊急管線，其前端必須配備對應之量測參數與設施</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>廢(污)水(前)處理設施資料表</t>
-        </is>
-      </c>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>若 有水質觸發條件 且 無量測設施 → 標記:無相關量測參數與設施該如何判斷</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>周志豪</t>
-        </is>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>序11 周志豪技師 (3)</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="inlineStr">
-        <is>
-          <t>T01-01</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="47.25" customHeight="1">
-      <c r="A15" s="4" t="inlineStr">
-        <is>
-          <t>D187</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>S01 水污染業務查核缺失.pdf</t>
-        </is>
-      </c>
-      <c r="C15" s="4" t="inlineStr">
-        <is>
-          <t>(12)P10. T01-01混凝池進出流SS質量未平衡，請提供計算過程的相關佐證資料。</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr">
-        <is>
-          <t>質量平衡</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>SS質量平衡</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
-          <t>混凝池之進流出流及產出固體物之SS質量必須達成平衡</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="inlineStr">
-        <is>
-          <t>水質水量平衡圖/計算書</t>
-        </is>
-      </c>
-      <c r="H15" s="4" t="inlineStr">
-        <is>
-          <t>若 質量計算不平衡 → 標記:進出流SS質量未平衡請提供計算</t>
-        </is>
-      </c>
-      <c r="I15" s="4" t="inlineStr">
-        <is>
-          <t>周志豪</t>
-        </is>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>序11 周志豪技師 (12)</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="inlineStr">
-        <is>
-          <t>T01-01</t>
         </is>
       </c>
     </row>
@@ -12687,7 +12019,7 @@
       </c>
       <c r="K2" s="12" t="inlineStr">
         <is>
-          <t>2026-06-03 16:58:38</t>
+          <t>2026-06-04 09:02:22</t>
         </is>
       </c>
     </row>
@@ -12697,6 +12029,892 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>缺失ID</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>來源</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>原文缺失</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>檢查類型</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>對照項目</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>規則(萃取/可比對判斷式)</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>比對位置(依標題,非頁碼)</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>判定邏輯(條件→結論)</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>技師姓名</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>序號</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>原始槽體代號</t>
+        </is>
+      </c>
+      <c r="L1" s="9" t="inlineStr">
+        <is>
+          <t>狀態</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="47.25" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>D019</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>S01 水污染業務查核缺失.pdf</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>(7)快混池（T01–09）尺寸設計1.21 M，有效水深1.17 M，出水高度僅0.04 M，設計參數不符合環工學理。</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>設計參數</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>出水高度</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>槽體出水高度（乾舷）應留有足夠安全空間，符合環工學理</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>廢(污)水(前)處理設施資料表/容量計算</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>若 出水高度過低 → 標記:設計參數不符學理</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>張子健</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>序2 張子健技師 (7)</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>T01-09</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="47.25" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>D026a</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>S01 水污染業務查核缺失.pdf</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>(14)附件八–2，三個快混池之間流向標示不應該為雙向，應該為“單向”，慢混池有相同標示錯誤問題。</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>流向示意圖</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>流向標示</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>各處理池槽間之廢水流向應為單向流動，不可標示為雙向</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>廠區平面及流向配置圖</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>若 處理池間流向為雙向 → 標記:標示錯誤應為單向</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>張子健</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>序2 張子健技師 (14)</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>(無)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="47.25" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>D034a</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>S01 水污染業務查核缺失.pdf</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>(4)T02快混、慢混1、慢混3及待過濾池之pH分別顯示為8.15、6.72、6.83及7.58，就pH變化及去除重金屬而言，較不合理</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>操作條件</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>pH變化</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>各連續處理單元之pH變化應符合去除重金屬之沉降學理</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>現場操作參數比對</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>若 相鄰處理槽之pH變化不符合學理 → 標記:pH變化不合理</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>施紹揚</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>序3 施紹揚技師 (4)</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>T02</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="47.25" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>D041a</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>S01 水污染業務查核缺失.pdf</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>(11)頁次47~50/95：T02-02快混池停留時間與T02-03慢混池相同，有違一般設計原理</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>設計參數</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>停留時間</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>快混與慢混槽之水力停留時間應有區隔，符合學理設計</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>廢(污)水(前)處理設施資料表</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>若 快混停留時間 == 慢混停留時間 → 標記:有違設計原理</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>施紹揚</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>序3 施紹揚技師 (11)</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>T02-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="110.25" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>D054</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>S01 水污染業務查核缺失.pdf</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>(7)張維欽老師：第9/42頁水質資料表T01-05 pH調整兼快混槽，顯示重金屬鋅由1500 mg/L降至4.5 mg/L，該重金屬鋅非指溶解性，應於化學沈澱池展現其去除效能。洪瑞敏技師：P.9/42，水污染防治措施資料/水質水量平衡示意圖中T01-05 pH調整兼快混槽尚未經過沉澱單元，應該不具有重金屬鋅的去除效果。</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>質量平衡</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>鋅濃度</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>未經沉澱單元前不應表現懸浮重金屬之去除效能</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>水質水量平衡示意圖</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>若 單元無沉澱功能 且 表現出重金屬去除 → 標記:不具有去除效果</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>彭文良</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>序4 彭文良技師 (7)</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>T01-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="110.25" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>D055</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>S01 水污染業務查核缺失.pdf</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>(8)張維欽老師：第18/42頁T01-05 pH調整兼快混槽設施資料表，本化混程序擬去除重金屬，控制之pH為6~9，其低限值過低，非適宜去除重金屬之pH範圍。洪瑞敏技師：P.18/42，T01-05 pH 調整兼快混槽的量測操作參數pH 值設定範圍為6~9，則如何確保其重金屬鋅(pH=9.5~10.5)的去除效率?</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>操作條件</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>pH範圍</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>去除特定重金屬之pH應符合該金屬之最佳沉降範圍</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>廢(污)水(前)處理設施資料表/操作參數</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>若 設定pH範圍不符重金屬沉澱所需 → 標記:pH低限值過低</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>彭文良</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>序4 彭文良技師 (8)</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>T01-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="47.25" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>D070</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>S01 水污染業務查核缺失.pdf</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>(3)快混轉速過慢，與常用參數不同。</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>設計參數</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>轉速</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>快混機具轉速應符合學理常見範圍</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>廢(污)水(前)處理設施資料表/操作參數</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>若 轉速 &lt; 學理常用範圍 → 標記:轉速過慢</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>劉暐廷</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>序6 劉暐廷技師 (3)</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>(無)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="47.25" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>D090a</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>S01 水污染業務查核缺失.pdf</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>(2)T01-08快混池，攪拌機如無變頻調整，轉速應為固定，非為80~120rpm。T01-09、T01-15、T01-16，問題同T01-08。</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>操作條件</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>轉速參數</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>無變頻之攪拌機其轉速參數應為固定值而非範圍值</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>廢(污)水(前)處理設施資料表/操作參數</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>若 無變頻器 且 轉速為區間值 → 標記:轉速應為固定</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>陳映嘉</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>序7 陳映嘉技師 (2)</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>T01-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="47.25" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>D099</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>S01 水污染業務查核缺失.pdf</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>(11)P27_T01-08快混槽1，有效水深標示11公尺，與槽體尺寸不相符。</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>設計參數</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>有效水深</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>有效水深不應超過槽體總高度或不符比例</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>廢(污)水(前)處理設施資料表</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>若 水深 &gt; 槽體尺寸或不合邏輯 → 標記:與尺寸不相符</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>陳映嘉</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>序7 陳映嘉技師 (11)</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>T01-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="47.25" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>D107</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>S01 水污染業務查核缺失.pdf</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>(19)T01-18大量汙泥回流至T01-15快混池之設計考量。</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>設計參數</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>污泥迴流設計</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>特殊之污泥迴流設計應有明確之學理考量與說明</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>設計參數評估</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>若 特殊迴流無說明 → 標記:迴流之設計考量不明</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>陳映嘉</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>序7 陳映嘉技師 (19)</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>T01-18;T01-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="63" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>D146</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>S01 水污染業務查核缺失.pdf</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>(4)頁次28/52及頁次115：本案重金屬廢水以鎳濃度相對較高，T01-08快混槽pH操作參數控制在8~12，pH=8的下限值偏低(pH為8時，鎳之解離濃度可超過1.0mg/L以上)。</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>操作條件</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>pH下限設定</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>高濃度鎳廢水之pH操作下限必須足以維持有效之沉降效果</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>廢(污)水(前)處理設施資料表/操作參數</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>若 pH下限不足以沉澱目標重金屬 → 標記:下限值偏低</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>汪正倫</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>序9 汪正倫技師 (4)</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>T01-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="47.25" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>D154</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>S01 水污染業務查核缺失.pdf</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>(12)T01-08快混槽之污泥迴流比為0.018%，約為0.074CMD，唯現場操作遠大於迴流比例。</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>操作條件</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>污泥迴流比</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>現場實際污泥迴流操作量必須與許可登載比例相符</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>現場操作查核</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>若 現場迴流量 &gt; 許可設計迴流比 → 標記:現場操作遠大於迴流比例</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>汪正倫</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>序9 汪正倫技師 (12)</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>T01-08</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="47.25" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>D178a</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>S01 水污染業務查核缺失.pdf</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>(3)由P7. 得知廢水貯池有緊急應變管線，在SS大於400mg/L時排至T01-01混凝池；而P39. T01-30廢水貯池卻無相關量測參數與設施，該如何判斷？</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>設計參數</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>緊急應變量測設施</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>設有水質條件啟動之緊急管線，其前端必須配備對應之量測參數與設施</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>廢(污)水(前)處理設施資料表</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>若 有水質觸發條件 且 無量測設施 → 標記:無相關量測參數與設施該如何判斷</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>周志豪</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>序11 周志豪技師 (3)</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>T01-01</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="47.25" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>D187</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>S01 水污染業務查核缺失.pdf</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>(12)P10. T01-01混凝池進出流SS質量未平衡，請提供計算過程的相關佐證資料。</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>質量平衡</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>SS質量平衡</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>混凝池之進流出流及產出固體物之SS質量必須達成平衡</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>水質水量平衡圖/計算書</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>若 質量計算不平衡 → 標記:進出流SS質量未平衡請提供計算</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>周志豪</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>序11 周志豪技師 (12)</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>T01-01</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12898,7 +13116,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13670,7 +13888,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13815,7 +14033,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14473,7 +14691,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14960,7 +15178,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16587,7 +16805,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -16846,7 +17064,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -17040,151 +17258,6 @@
       <c r="K3" s="4" t="inlineStr">
         <is>
           <t>T01-53</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="36" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>缺失ID</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>來源</t>
-        </is>
-      </c>
-      <c r="C1" s="5" t="inlineStr">
-        <is>
-          <t>原文缺失</t>
-        </is>
-      </c>
-      <c r="D1" s="5" t="inlineStr">
-        <is>
-          <t>檢查類型</t>
-        </is>
-      </c>
-      <c r="E1" s="5" t="inlineStr">
-        <is>
-          <t>對照項目</t>
-        </is>
-      </c>
-      <c r="F1" s="5" t="inlineStr">
-        <is>
-          <t>規則(萃取/可比對判斷式)</t>
-        </is>
-      </c>
-      <c r="G1" s="5" t="inlineStr">
-        <is>
-          <t>比對位置(依標題,非頁碼)</t>
-        </is>
-      </c>
-      <c r="H1" s="5" t="inlineStr">
-        <is>
-          <t>判定邏輯(條件→結論)</t>
-        </is>
-      </c>
-      <c r="I1" s="5" t="inlineStr">
-        <is>
-          <t>技師姓名</t>
-        </is>
-      </c>
-      <c r="J1" s="5" t="inlineStr">
-        <is>
-          <t>序號</t>
-        </is>
-      </c>
-      <c r="K1" s="5" t="inlineStr">
-        <is>
-          <t>原始槽體代號</t>
-        </is>
-      </c>
-      <c r="L1" s="9" t="inlineStr">
-        <is>
-          <t>狀態</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="94.5" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>D188a</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>S01 水污染業務查核缺失.pdf</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>(13)P8. T01-19污泥調勻槽進流污泥量為何不等於T01-18污泥儲槽出流污泥量，請提供計算過程。另T01-19污泥調勻槽進流乾污泥量238423.97kg/d、T01-21螺旋式脫水機出流乾污泥量108482.91kg/d，離心式與螺旋式脫水機固體物捕抓率是否偏低？</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>質量平衡</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>單元間污泥量移轉</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>上下游銜接之污泥量必須相等，且脫水機之固體捕捉率應合理</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>污泥流向資料表</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>若 上下游污泥量不相等或捕捉率異常偏低 → 標記:進出流污泥量不等於及捕抓率是否偏低</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr">
-        <is>
-          <t>周志豪</t>
-        </is>
-      </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>序11 周志豪技師 (13)</t>
-        </is>
-      </c>
-      <c r="K2" s="4" t="inlineStr">
-        <is>
-          <t>T01-19</t>
         </is>
       </c>
     </row>
@@ -17276,10 +17349,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="78.75" customHeight="1">
+    <row r="2" ht="94.5" customHeight="1">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>D228</t>
+          <t>D188a</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
@@ -17289,47 +17362,47 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>(3)P29/37採樣位置示意圖原廢水 採樣點設置於收集池(T01- 01)，未符合水污染防治措施及檢 測申報管理辦法第九十一條規定 原廢(污)水水質應於調勻設施採 樣，故本廠原廢水水質依規定應 於調勻池(T01-03)採樣。</t>
+          <t>(13)P8. T01-19污泥調勻槽進流污泥量為何不等於T01-18污泥儲槽出流污泥量，請提供計算過程。另T01-19污泥調勻槽進流乾污泥量238423.97kg/d、T01-21螺旋式脫水機出流乾污泥量108482.91kg/d，離心式與螺旋式脫水機固體物捕抓率是否偏低？</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>操作條件</t>
+          <t>質量平衡</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>採樣位置</t>
+          <t>單元間污泥量移轉</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>原廢水採樣位置應依法規設置於調勻池而非收集池</t>
+          <t>上下游銜接之污泥量必須相等，且脫水機之固體捕捉率應合理</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
         <is>
-          <t>採樣位置示意圖</t>
+          <t>污泥流向資料表</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>若 採樣點未設於調勻設施 → 標記:未符合規定應於調勻池採樣</t>
+          <t>若 上下游污泥量不相等或捕捉率異常偏低 → 標記:進出流污泥量不等於及捕抓率是否偏低</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
-          <t>徐永郎</t>
+          <t>周志豪</t>
         </is>
       </c>
       <c r="J2" s="4" t="inlineStr">
         <is>
-          <t>序14 徐永郎技師 (3)</t>
+          <t>序11 周志豪技師 (13)</t>
         </is>
       </c>
       <c r="K2" s="4" t="inlineStr">
         <is>
-          <t>T01-01;T01-03</t>
+          <t>T01-19</t>
         </is>
       </c>
     </row>
@@ -19798,6 +19871,151 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
+  <cols>
+    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="36" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>缺失ID</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>來源</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>原文缺失</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>檢查類型</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>對照項目</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>規則(萃取/可比對判斷式)</t>
+        </is>
+      </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>比對位置(依標題,非頁碼)</t>
+        </is>
+      </c>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>判定邏輯(條件→結論)</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="inlineStr">
+        <is>
+          <t>技師姓名</t>
+        </is>
+      </c>
+      <c r="J1" s="5" t="inlineStr">
+        <is>
+          <t>序號</t>
+        </is>
+      </c>
+      <c r="K1" s="5" t="inlineStr">
+        <is>
+          <t>原始槽體代號</t>
+        </is>
+      </c>
+      <c r="L1" s="9" t="inlineStr">
+        <is>
+          <t>狀態</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="78.75" customHeight="1">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>D228</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>S01 水污染業務查核缺失.pdf</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>(3)P29/37採樣位置示意圖原廢水 採樣點設置於收集池(T01- 01)，未符合水污染防治措施及檢 測申報管理辦法第九十一條規定 原廢(污)水水質應於調勻設施採 樣，故本廠原廢水水質依規定應 於調勻池(T01-03)採樣。</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>操作條件</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>採樣位置</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>原廢水採樣位置應依法規設置於調勻池而非收集池</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>採樣位置示意圖</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>若 採樣點未設於調勻設施 → 標記:未符合規定應於調勻池採樣</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>徐永郎</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>序14 徐永郎技師 (3)</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>T01-01;T01-03</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -19933,6 +20151,683 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C54"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>標準詞</t>
+        </is>
+      </c>
+      <c r="B1" s="10" t="inlineStr">
+        <is>
+          <t>別名 (用 / 分隔)</t>
+        </is>
+      </c>
+      <c r="C1" s="10" t="inlineStr">
+        <is>
+          <t>說明</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>── 槽體尺寸 ──</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr"/>
+      <c r="C2" s="13" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>出水高度</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>液面到槽頂距離 / 自由水面高度 / 餘裕高度 / 乾舷 / freeboard</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>有效容量</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>有效體積 / 有效水量 / operating volume / 工作容積</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>有效水深</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>有效深度 / 操作水深 / operating depth</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>槽體尺寸</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>槽體規格 / tank dimension</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>── 操作參數 ──</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr"/>
+      <c r="C7" s="13" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>滯留時間</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>停留時間 / HRT / 水力停留時間 / 接觸時間 / 反應時間</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>曝氣量</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>風量 / 曝氣風量 / 供氣量 / air flow</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>迴流比</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>污泥迴流率 / 迴流污泥比 / RAS</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>MLSS</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>混合液懸浮固體 / 活性污泥濃度</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>DO</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>溶氧 / 溶氧濃度 / dissolved oxygen</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>SVI</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>污泥容積指數 / 沉降比</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>F/M</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>食微比 / BOD 負荷率</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>── 機具設施 ──</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr"/>
+      <c r="C15" s="13" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>液位計</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>水位計 / 液面計 / level transmitter / LT / level sensor</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>pH計</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>pH meter / 酸鹼度計 / pH 計 / pH 感測器</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>DO計</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>溶氧計 / dissolved oxygen meter / DO 計</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>流量計</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>FT / flow meter / 流速計 / flowmeter</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>攪拌機</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>攪拌器 / 攪拌槳 / agitator / mixer / 攪拌設備</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>曝氣機</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>鼓風機 / blower / 氣泵 / air blower</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>加藥泵</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>藥劑泵 / 投藥泵 / dosing pump / 計量泵</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>刮泥機</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>刮砂機 / scraper / sludge scraper</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>污泥泵</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>污泥輸送泵 / sludge pump</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>── 化學處理 ──</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr"/>
+      <c r="C25" s="13" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>反洗水</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>反沖洗水 / 回沖洗 / backwash / 逆洗水</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>加藥</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>投藥 / 添加藥品 / dosing / 藥品投加</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>中和</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>pH 調整 / 酸鹼中和 / neutralization</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>混凝</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>膠凝 / coagulation</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>膠凝</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>絮凝 / flocculation</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="13" t="inlineStr">
+        <is>
+          <t>── 水質參數 ──</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="inlineStr"/>
+      <c r="C31" s="13" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>BOD</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>生化需氧量 / BOD5 / biochemical oxygen demand</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>COD</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>化學需氧量 / chemical oxygen demand</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>懸浮固體 / 懸浮物 / suspended solids</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>TKN</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>總凱氏氮 / total Kjeldahl nitrogen</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>總磷 / total phosphorus</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>TN</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>總氮 / total nitrogen</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>── 流向 ──</t>
+        </is>
+      </c>
+      <c r="B38" s="13" t="inlineStr"/>
+      <c r="C38" s="13" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>進流水</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>入流水 / 進水 / influent / 原水</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>出流水</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>放流水 / 排水 / effluent / 出水</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>原廢水</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>原始廢水 / raw wastewater / 原廢</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>放流口</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>排放口 / outlet / discharge point</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="13" t="inlineStr">
+        <is>
+          <t>── 污泥處理 ──</t>
+        </is>
+      </c>
+      <c r="B43" s="13" t="inlineStr"/>
+      <c r="C43" s="13" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>污泥含水率</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>含水率 / moisture content / 水含量</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>脫水</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>污泥脫水 / dewatering</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>濃縮</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>污泥濃縮 / thickening</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr"/>
+      <c r="C47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="14" t="inlineStr">
+        <is>
+          <t>── 使用說明 ──</t>
+        </is>
+      </c>
+      <c r="B48" s="14" t="inlineStr"/>
+      <c r="C48" s="14" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>標準詞</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>系統內部使用的標準詞彙</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>別名</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>技師可能用的不同寫法 (用 / 分隔, 大小寫不分)</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>系統會自動把別名比對到標準詞</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>範例</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>「液面到槽頂距離」會自動對應到「出水高度」</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>新增</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>在最下方加新列就行, 不用刻意分類</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>系統下次同步時自動更新</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -20191,7 +21086,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -20678,7 +21573,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -21450,7 +22345,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -23246,206 +24141,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15.75"/>
-  <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="36" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
-    <col width="36" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>缺失ID</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>來源</t>
-        </is>
-      </c>
-      <c r="C1" s="5" t="inlineStr">
-        <is>
-          <t>原文缺失</t>
-        </is>
-      </c>
-      <c r="D1" s="5" t="inlineStr">
-        <is>
-          <t>檢查類型</t>
-        </is>
-      </c>
-      <c r="E1" s="5" t="inlineStr">
-        <is>
-          <t>對照項目</t>
-        </is>
-      </c>
-      <c r="F1" s="5" t="inlineStr">
-        <is>
-          <t>規則(萃取/可比對判斷式)</t>
-        </is>
-      </c>
-      <c r="G1" s="5" t="inlineStr">
-        <is>
-          <t>比對位置(依標題,非頁碼)</t>
-        </is>
-      </c>
-      <c r="H1" s="5" t="inlineStr">
-        <is>
-          <t>判定邏輯(條件→結論)</t>
-        </is>
-      </c>
-      <c r="I1" s="5" t="inlineStr">
-        <is>
-          <t>技師姓名</t>
-        </is>
-      </c>
-      <c r="J1" s="5" t="inlineStr">
-        <is>
-          <t>序號</t>
-        </is>
-      </c>
-      <c r="K1" s="5" t="inlineStr">
-        <is>
-          <t>原始槽體代號</t>
-        </is>
-      </c>
-      <c r="L1" s="9" t="inlineStr">
-        <is>
-          <t>狀態</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="63" customHeight="1">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>D008</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>S01 水污染業務查核缺失.pdf</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>(8)許可證T01–04中和槽之操作參數包含pH，惟加藥未包含硫酸不合理，且功能測試報告之廢（污）水處理設施處理程序及操作條件之添加藥品量有登載中和槽有添加硫酸。</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>文件一致性</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>硫酸加藥</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>許可證登載加藥種類需與功能測試報告一致</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr">
-        <is>
-          <t>廢(污)水(前)處理設施資料表/加藥參數</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr">
-        <is>
-          <t>若 功測報告有加藥 且 許可證未登載 → 標記:加藥不一致</t>
-        </is>
-      </c>
-      <c r="I2" s="4" t="inlineStr">
-        <is>
-          <t>方天志</t>
-        </is>
-      </c>
-      <c r="J2" s="4" t="inlineStr">
-        <is>
-          <t>序1 方天志技師 (8)</t>
-        </is>
-      </c>
-      <c r="K2" s="4" t="inlineStr">
-        <is>
-          <t>T01-04</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="47.25" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>D197a</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>S01 水污染業務查核缺失.pdf</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>(4)P23. T01-03 pH中和槽 pH控制值5~9 後接T01-04活性污泥槽1，生物處理單元的pH值偏低，不利微生物成長。</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>操作條件</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>pH操作範圍</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>銜接生物處理前之調整池pH下限必須滿足微生物生長需求(通常&gt;6)</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr">
-        <is>
-          <t>廢(污)水(前)處理設施資料表/操作參數</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>若 進水pH設定過低 → 標記:pH值偏低不利微生物成長</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>徐振利</t>
-        </is>
-      </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>序12 徐振利技師 (4)</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>T01-03</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/規則庫.xlsx
+++ b/規則庫.xlsx
@@ -35,6 +35,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="調勻池" sheetId="26" state="visible" r:id="rId26"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="廢水收集池" sheetId="27" state="visible" r:id="rId27"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_同義字" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_槽體學理" sheetId="29" state="visible" r:id="rId29"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -44,7 +45,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,16 +53,27 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002F5496"/>
+        <bgColor rgb="002F5496"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -69,12 +81,32 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00CCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="00CCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="00CCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00CCCCCC"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -12983,7 +13015,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-06-05 10:08:27</t>
+          <t>2026-06-05 12:36:20</t>
         </is>
       </c>
     </row>
@@ -17169,6 +17201,1152 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="8" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>標準槽體</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>加藥類型</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>應變動項目</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>不應變動項目</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>容忍度(%)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>違反嚴重度</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>學理說明</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>狀態</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>pH調整槽</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>酸/鹼</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>pH, 水溫</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>不合理</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>純 pH 調整槽只加酸/鹼, 無分離機制, 其他水質應守恆</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>pH調整池</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>酸/鹼</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>pH, 水溫</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>不合理</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>同 pH 調整槽 (申請文件命名變體)</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>中和池</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>酸/鹼</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>pH, 水溫</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>不合理</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>加酸鹼中和廢水, 學理上同純 pH 調整槽</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>pH調整暨快混池</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>酸鹼 + 混凝劑</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>pH, 水溫, SS</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>不合理</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>加酸鹼 + 混凝劑, 混凝劑本身為固體故 SS 增加合理, 但無分離機制, 重金屬/COD/BOD 須後端沉澱才能去除</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>pH調整池暨快混池</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>酸鹼 + 混凝劑</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>pH, 水溫, SS</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>不合理</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>同 pH 調整暨快混池 (申請文件命名變體)</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>快混槽</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>混凝劑</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>SS, 水溫</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>不合理</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>加 PAC/明礬/FeCl₃ 混凝, SS 增加合理, 但無沉降, 重金屬/COD/BOD 不該減少</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>慢混池</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>助凝劑</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>SS, 水溫</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>不合理</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>加助凝劑 (PAM) 形成大絮凝體, SS 可微增, 仍無沉降, 重金屬/COD/BOD 不該減少</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>沉澱池</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>無 (重力沉降)</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>SS, 重金屬, 濁度, COD, BOD</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>pH, 氨氮, 硼, 氯, 硝酸鹽</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>不合理</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>重力沉降, 固體+附著重金屬下沉, 但溶解性離子 (氨氮/硼/Cl⁻/NO₃⁻) 不應改變</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>沉降池</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>無 (重力沉降)</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>SS, 重金屬, 濁度, COD, BOD</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>pH, 氨氮, 硼, 氯, 硝酸鹽</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>不合理</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>同沉澱池</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>浮除槽</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>氣浮 (DAF)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>SS, 油脂</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>pH, 重金屬, 離子</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>不合理</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>加壓溶氣浮除油脂與輕質懸浮物, 重金屬與溶解性物質不應改變</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>砂濾塔</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>無 (物理過濾)</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>pH, 重金屬, 離子, 氨氮</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>不合理</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>物理截留懸浮固體, 對溶解物無作用 (COD/重金屬僅微減)</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>活性碳吸附塔</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>活性碳</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>COD, BOD, 有機物</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>pH, 離子, 氨氮, 硝酸鹽</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>不合理</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>活性碳吸附有機物與部分重金屬, 對溶解性離子無效</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>活性碳吸附裝置</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>活性碳</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>COD, BOD, 有機物</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>pH, 離子, 氨氮, 硝酸鹽</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>不合理</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>同活性碳吸附塔</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>離子交換樹脂塔</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>離子交換樹脂</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>指定離子 (Ca, Mg, Na, NO₃, 重金屬)</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>pH, COD, BOD, SS</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待人工</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>依樹脂類型 (陽/陰/螯合) 只去除特定離子, 對有機物/SS 無作用; 需人工判斷樹脂類型與目標離子是否相符</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>曝氣槽</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>供氧 + 微生物</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>BOD, COD, 氨氮, DO</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>pH, 重金屬, 氯, 硼</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>不合理</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>好氧微生物代謝有機物 + 硝化, 重金屬不應自行減少, Cl⁻/硼為保守物質不該變</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>氧化池</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>氧化 (供氧 / 加氧化劑)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>COD, BOD, 真色色度</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>pH, 重金屬, 離子</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>不合理</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>氧化有機物與色度, 但對重金屬 (除非還原型 Cr⁶⁺) 不應顯著去除</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>厭氧池</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>厭氧菌</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>BOD, COD</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>pH, 重金屬, 離子</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>不合理</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>厭氧菌代謝有機物, 重金屬不應減少</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>脫水機</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>脫水助劑</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>含水率</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待人工</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>物理脫水, 濃度暴升合理但污染物質量應守恆; 系統會用質量基準檢查</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>濃縮槽</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>無 (重力濃縮)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>含水率</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待人工</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>重力濃縮污泥, 同脫水機原則</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>污泥儲槽</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>無 (儲存)</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>含水率</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待人工</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>暫存污泥, 質量應守恆</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>暫存槽</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>無 (均化)</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>重金屬, 離子</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待人工</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>均化多股廢水, 進出水質可變動但污染物質量應大致守恆; 若大幅減少需確認是否誤填</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>貯留槽</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>無 (均化)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>重金屬, 離子</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待人工</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>同暫存槽</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>調勻池</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>無 (均化)</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>重金屬, 離子</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待人工</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>同暫存槽</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>廢水調整池</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>無 (均化)</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>重金屬, 離子</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待人工</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>均化多股廢水穩定後端進流, 重金屬等不應自行減少</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>廢水收集池</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>無 (均化)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>重金屬, 離子</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待人工</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>同廢水調整池</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>批次反應槽</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>視製程而定</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>視批次而定</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>視批次而定</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待人工</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>依批次操作條件不同, 規則難以一概而論, 須人工判讀</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>放流池</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>無 (儲存)</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>(不應變動)</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>不合理</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>放流前的暫存, 水質應與前端處理出流完全一致</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -19570,7 +20748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19951,6 +21129,100 @@
       <c r="J8" t="inlineStr">
         <is>
           <t>2026-06-04 4:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>水污染業務查核缺失.pdf</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>合格(自動)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2026-06-05 11:32:34</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2026-06-05 11:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>申請文件(秋棠)(1150519).pdf</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>不合理 13 項</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2026-06-05 11:35:43</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>2026-06-05 11:19</t>
         </is>
       </c>
     </row>
@@ -21333,7 +22605,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>(10)T01-25慢混槽2混合效果不佳，進出流有短流現象。</t>
+          <t>(10)T01-25慢混槽2混合效果不佳，進出流有短流現象。/待討論/</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -21374,6 +22646,11 @@
       <c r="K11" t="inlineStr">
         <is>
           <t>T01-25</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>?</t>
         </is>
       </c>
     </row>
@@ -21623,6 +22900,11 @@
           <t>T01-11</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NICK從去除率驗證</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -22093,7 +23375,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>(1)P37_T01-18快沉槽，設計參數表面溢流率未以斜板水平投影面積核算。T01-10沉澱池，停留時間僅有0.38hr，表面負荷高達83.1 m/d；T01-18，停留時間僅有0.2hr，表面負荷高達433m/d，設計處理負荷不足。</t>
+          <t>(1)P37_T01-18快沉槽，設計參數表面溢流率未以斜板水平投影面積核算。T01-10沉澱池，停留時間僅有0.38hr，表面負荷高達83.1 m/d；T01-18，停留時間僅有0.2hr，表面負荷高達433m/d，設計處理負荷不足。/待討論/就是槽體面積?</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -22134,6 +23416,11 @@
       <c r="K11" t="inlineStr">
         <is>
           <t>T01-10</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>?</t>
         </is>
       </c>
     </row>
@@ -23409,6 +24696,11 @@
           <t>T01-04</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -23464,6 +24756,11 @@
       <c r="K3" t="inlineStr">
         <is>
           <t>T01-03</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>V</t>
         </is>
       </c>
     </row>

--- a/規則庫.xlsx
+++ b/規則庫.xlsx
@@ -17207,7 +17207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:M30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -17218,6 +17218,11 @@
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -17261,6 +17266,31 @@
           <t>狀態</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>HRT_min (hr)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>HRT_max (hr)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>SOR_max (m³/m²·d)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>G_min (1/s)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>G_max (1/s)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -17301,6 +17331,15 @@
           <t>V</t>
         </is>
       </c>
+      <c r="I2" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr"/>
+      <c r="M2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -17341,6 +17380,15 @@
           <t>V</t>
         </is>
       </c>
+      <c r="I3" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K3" s="2" t="inlineStr"/>
+      <c r="L3" s="2" t="inlineStr"/>
+      <c r="M3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -17381,6 +17429,15 @@
           <t>V</t>
         </is>
       </c>
+      <c r="I4" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K4" s="2" t="inlineStr"/>
+      <c r="L4" s="2" t="inlineStr"/>
+      <c r="M4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -17421,6 +17478,19 @@
           <t>V</t>
         </is>
       </c>
+      <c r="I5" s="2" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K5" s="2" t="inlineStr"/>
+      <c r="L5" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="M5" s="2" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -17461,6 +17531,19 @@
           <t>V</t>
         </is>
       </c>
+      <c r="I6" s="2" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -17501,16 +17584,29 @@
           <t>V</t>
         </is>
       </c>
+      <c r="I7" s="2" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>慢混池</t>
+          <t>快混池</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>助凝劑</t>
+          <t>混凝劑</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -17533,114 +17629,153 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>加助凝劑 (PAM) 形成大絮凝體, SS 可微增, 仍無沉降, 重金屬/COD/BOD 不該減少</t>
+          <t>同快混槽 (命名變體)</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
           <t>V</t>
         </is>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="n">
+        <v>300</v>
+      </c>
+      <c r="M8" s="2" t="n">
+        <v>1000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>沉澱池</t>
+          <t>慢混池</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>無 (重力沉降)</t>
+          <t>助凝劑</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>SS, 重金屬, 濁度, COD, BOD</t>
+          <t>SS, 水溫</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>pH, 氨氮, 硼, 氯, 硝酸鹽</t>
+          <t>*</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>不合理</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>加助凝劑 (PAM) 形成大絮凝體, SS 可微增, 仍無沉降, 重金屬/COD/BOD 不該減少</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>不合理</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>重力沉降, 固體+附著重金屬下沉, 但溶解性離子 (氨氮/硼/Cl⁻/NO₃⁻) 不應改變</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
+      <c r="M9" s="2" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>沉降池</t>
+          <t>慢混槽</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>無 (重力沉降)</t>
+          <t>助凝劑</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>SS, 重金屬, 濁度, COD, BOD</t>
+          <t>SS, 水溫</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>pH, 氨氮, 硼, 氯, 硝酸鹽</t>
+          <t>*</t>
         </is>
       </c>
       <c r="E10" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>不合理</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>同慢混池</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>不合理</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>同沉澱池</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
+      <c r="M10" s="2" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>浮除槽</t>
+          <t>沉澱池</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>氣浮 (DAF)</t>
+          <t>無 (重力沉降)</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>SS, 油脂</t>
+          <t>SS, 重金屬, 濁度, COD, BOD</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>pH, 重金屬, 離子</t>
+          <t>pH, 氨氮, 硼, 氯, 硝酸鹽</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
@@ -17653,7 +17788,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>加壓溶氣浮除油脂與輕質懸浮物, 重金屬與溶解性物質不應改變</t>
+          <t>重力沉降, 固體+附著重金屬下沉, 但溶解性離子 (氨氮/硼/Cl⁻/NO₃⁻) 不應改變</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -17661,26 +17796,37 @@
           <t>V</t>
         </is>
       </c>
+      <c r="I11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="L11" s="2" t="inlineStr"/>
+      <c r="M11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>砂濾塔</t>
+          <t>沉降池</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>無 (物理過濾)</t>
+          <t>無 (重力沉降)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>SS</t>
+          <t>SS, 重金屬, 濁度, COD, BOD</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>pH, 重金屬, 離子, 氨氮</t>
+          <t>pH, 氨氮, 硼, 氯, 硝酸鹽</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
@@ -17693,7 +17839,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>物理截留懸浮固體, 對溶解物無作用 (COD/重金屬僅微減)</t>
+          <t>同沉澱池</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -17701,30 +17847,41 @@
           <t>V</t>
         </is>
       </c>
+      <c r="I12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>活性碳吸附塔</t>
+          <t>浮除槽</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>活性碳</t>
+          <t>氣浮 (DAF)</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COD, BOD, 有機物</t>
+          <t>SS, 油脂</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>pH, 離子, 氨氮, 硝酸鹽</t>
+          <t>pH, 重金屬, 離子</t>
         </is>
       </c>
       <c r="E13" s="2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -17733,7 +17890,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>活性碳吸附有機物與部分重金屬, 對溶解性離子無效</t>
+          <t>加壓溶氣浮除油脂與輕質懸浮物, 重金屬與溶解性物質不應改變</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -17741,30 +17898,39 @@
           <t>V</t>
         </is>
       </c>
+      <c r="I13" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr"/>
+      <c r="M13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>活性碳吸附裝置</t>
+          <t>砂濾塔</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>活性碳</t>
+          <t>無 (物理過濾)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COD, BOD, 有機物</t>
+          <t>SS</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>pH, 離子, 氨氮, 硝酸鹽</t>
+          <t>pH, 重金屬, 離子, 氨氮</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -17773,7 +17939,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>同活性碳吸附塔</t>
+          <t>物理截留懸浮固體, 對溶解物無作用 (COD/重金屬僅微減)</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -17781,39 +17947,44 @@
           <t>V</t>
         </is>
       </c>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>離子交換樹脂塔</t>
+          <t>活性碳吸附塔</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>離子交換樹脂</t>
+          <t>活性碳</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>指定離子 (Ca, Mg, Na, NO₃, 重金屬)</t>
+          <t>COD, BOD, 有機物</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>pH, COD, BOD, SS</t>
+          <t>pH, 離子, 氨氮, 硝酸鹽</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>待人工</t>
+          <t>不合理</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>依樹脂類型 (陽/陰/螯合) 只去除特定離子, 對有機物/SS 無作用; 需人工判斷樹脂類型與目標離子是否相符</t>
+          <t>活性碳吸附有機物與部分重金屬, 對溶解性離子無效</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -17821,26 +17992,31 @@
           <t>V</t>
         </is>
       </c>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr"/>
+      <c r="M15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>曝氣槽</t>
+          <t>活性碳吸附裝置</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>供氧 + 微生物</t>
+          <t>活性碳</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>BOD, COD, 氨氮, DO</t>
+          <t>COD, BOD, 有機物</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>pH, 重金屬, 氯, 硼</t>
+          <t>pH, 離子, 氨氮, 硝酸鹽</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
@@ -17853,7 +18029,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>好氧微生物代謝有機物 + 硝化, 重金屬不應自行減少, Cl⁻/硼為保守物質不該變</t>
+          <t>同活性碳吸附塔</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -17861,39 +18037,44 @@
           <t>V</t>
         </is>
       </c>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr"/>
+      <c r="M16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>氧化池</t>
+          <t>離子交換樹脂塔</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>氧化 (供氧 / 加氧化劑)</t>
+          <t>離子交換樹脂</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COD, BOD, 真色色度</t>
+          <t>指定離子 (Ca, Mg, Na, NO₃, 重金屬)</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>pH, 重金屬, 離子</t>
+          <t>pH, COD, BOD, SS</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>不合理</t>
+          <t>待人工</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>氧化有機物與色度, 但對重金屬 (除非還原型 Cr⁶⁺) 不應顯著去除</t>
+          <t>依樹脂類型 (陽/陰/螯合) 只去除特定離子, 對有機物/SS 無作用; 需人工判斷樹脂類型與目標離子是否相符</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -17901,26 +18082,31 @@
           <t>V</t>
         </is>
       </c>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr"/>
+      <c r="M17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>厭氧池</t>
+          <t>曝氣槽</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>厭氧菌</t>
+          <t>供氧 + 微生物</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>BOD, COD</t>
+          <t>BOD, COD, 氨氮, DO</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>pH, 重金屬, 離子</t>
+          <t>pH, 重金屬, 氯, 硼</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
@@ -17933,7 +18119,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>厭氧菌代謝有機物, 重金屬不應減少</t>
+          <t>好氧微生物代謝有機物 + 硝化, 重金屬不應自行減少, Cl⁻/硼為保守物質不該變</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -17941,39 +18127,48 @@
           <t>V</t>
         </is>
       </c>
+      <c r="I18" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr"/>
+      <c r="M18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>脫水機</t>
+          <t>氧化池</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>脫水助劑</t>
+          <t>氧化 (供氧 / 加氧化劑)</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>含水率</t>
+          <t>COD, BOD, 真色色度</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>pH, 重金屬, 離子</t>
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>待人工</t>
+          <t>不合理</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>物理脫水, 濃度暴升合理但污染物質量應守恆; 系統會用質量基準檢查</t>
+          <t>氧化有機物與色度, 但對重金屬 (除非還原型 Cr⁶⁺) 不應顯著去除</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -17981,39 +18176,48 @@
           <t>V</t>
         </is>
       </c>
+      <c r="I19" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr"/>
+      <c r="M19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>濃縮槽</t>
+          <t>厭氧池</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>無 (重力濃縮)</t>
+          <t>厭氧菌</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>含水率</t>
+          <t>BOD, COD</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>*</t>
+          <t>pH, 重金屬, 離子</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>待人工</t>
+          <t>不合理</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>重力濃縮污泥, 同脫水機原則</t>
+          <t>厭氧菌代謝有機物, 重金屬不應減少</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -18021,16 +18225,25 @@
           <t>V</t>
         </is>
       </c>
+      <c r="I20" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr"/>
+      <c r="M20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>污泥儲槽</t>
+          <t>脫水機</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>無 (儲存)</t>
+          <t>脫水助劑</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -18044,7 +18257,7 @@
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -18053,7 +18266,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>暫存污泥, 質量應守恆</t>
+          <t>物理脫水, 濃度暴升合理但污染物質量應守恆; 系統會用質量基準檢查</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -18061,30 +18274,35 @@
           <t>V</t>
         </is>
       </c>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>暫存槽</t>
+          <t>濃縮槽</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>無 (均化)</t>
+          <t>無 (重力濃縮)</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>含水率</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>*</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>重金屬, 離子</t>
-        </is>
-      </c>
       <c r="E22" s="2" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -18093,7 +18311,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>均化多股廢水, 進出水質可變動但污染物質量應大致守恆; 若大幅減少需確認是否誤填</t>
+          <t>重力濃縮污泥, 同脫水機原則</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -18101,30 +18319,37 @@
           <t>V</t>
         </is>
       </c>
+      <c r="I22" s="2" t="inlineStr"/>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="L22" s="2" t="inlineStr"/>
+      <c r="M22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>貯留槽</t>
+          <t>污泥儲槽</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>無 (均化)</t>
+          <t>無 (儲存)</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>含水率</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
           <t>*</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>重金屬, 離子</t>
-        </is>
-      </c>
       <c r="E23" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -18133,7 +18358,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>同暫存槽</t>
+          <t>暫存污泥, 質量應守恆</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -18141,11 +18366,16 @@
           <t>V</t>
         </is>
       </c>
+      <c r="I23" s="2" t="inlineStr"/>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr"/>
+      <c r="M23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>調勻池</t>
+          <t>暫存槽</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -18173,7 +18403,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>同暫存槽</t>
+          <t>均化多股廢水, 進出水質可變動但污染物質量應大致守恆; 若大幅減少需確認是否誤填</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -18181,11 +18411,20 @@
           <t>V</t>
         </is>
       </c>
+      <c r="I24" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr"/>
+      <c r="M24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>廢水調整池</t>
+          <t>貯留槽</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -18213,7 +18452,7 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>均化多股廢水穩定後端進流, 重金屬等不應自行減少</t>
+          <t>同暫存槽</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -18221,11 +18460,20 @@
           <t>V</t>
         </is>
       </c>
+      <c r="I25" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr"/>
+      <c r="M25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>廢水收集池</t>
+          <t>調勻池</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -18253,7 +18501,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>同廢水調整池</t>
+          <t>同暫存槽</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -18261,30 +18509,39 @@
           <t>V</t>
         </is>
       </c>
+      <c r="I26" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr"/>
+      <c r="M26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>批次反應槽</t>
+          <t>廢水調整池</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>視製程而定</t>
+          <t>無 (均化)</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>視批次而定</t>
+          <t>*</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>視批次而定</t>
+          <t>重金屬, 離子</t>
         </is>
       </c>
       <c r="E27" s="2" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -18293,7 +18550,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>依批次操作條件不同, 規則難以一概而論, 須人工判讀</t>
+          <t>均化多股廢水穩定後端進流, 重金屬等不應自行減少</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -18301,46 +18558,152 @@
           <t>V</t>
         </is>
       </c>
+      <c r="I27" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr"/>
+      <c r="M27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>廢水收集池</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>無 (均化)</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>重金屬, 離子</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待人工</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>同廢水調整池</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr"/>
+      <c r="J28" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr"/>
+      <c r="M28" s="2" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>批次反應槽</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>視製程而定</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>視批次而定</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>視批次而定</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待人工</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>依批次操作條件不同, 規則難以一概而論, 須人工判讀</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>V</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
           <t>放流池</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>無 (儲存)</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
         <is>
           <t>(不應變動)</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>*</t>
         </is>
       </c>
-      <c r="E28" s="2" t="n">
+      <c r="E30" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>不合理</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>放流前的暫存, 水質應與前端處理出流完全一致</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>V</t>
         </is>
       </c>
+      <c r="I30" s="2" t="inlineStr"/>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr"/>
+      <c r="M30" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/規則庫.xlsx
+++ b/規則庫.xlsx
@@ -17207,7 +17207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M30"/>
+  <dimension ref="A1:N30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -17291,6 +17291,11 @@
           <t>G_max (1/s)</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>類型</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -17340,6 +17345,11 @@
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr"/>
       <c r="M2" s="2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>反應</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -17389,6 +17399,11 @@
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr"/>
       <c r="M3" s="2" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>儲存</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -17438,6 +17453,11 @@
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr"/>
       <c r="M4" s="2" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>反應</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -17491,6 +17511,11 @@
       <c r="M5" s="2" t="n">
         <v>1000</v>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>反應</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -17544,6 +17569,11 @@
       <c r="M6" s="2" t="n">
         <v>1000</v>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>反應</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -17597,6 +17627,11 @@
       <c r="M7" s="2" t="n">
         <v>1000</v>
       </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>反應</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -17650,6 +17685,11 @@
       <c r="M8" s="2" t="n">
         <v>1000</v>
       </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>反應</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -17703,6 +17743,11 @@
       <c r="M9" s="2" t="n">
         <v>50</v>
       </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>反應</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -17756,6 +17801,11 @@
       <c r="M10" s="2" t="n">
         <v>50</v>
       </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>反應</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -17807,6 +17857,11 @@
       </c>
       <c r="L11" s="2" t="inlineStr"/>
       <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>分離</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -17858,6 +17913,11 @@
       </c>
       <c r="L12" s="2" t="inlineStr"/>
       <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>分離</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -17907,6 +17967,11 @@
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr"/>
       <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>分離</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -17952,6 +18017,11 @@
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr"/>
       <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>分離</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -17997,6 +18067,11 @@
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr"/>
       <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>分離</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -18042,6 +18117,11 @@
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr"/>
       <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>分離</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -18087,6 +18167,11 @@
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>分離</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -18136,6 +18221,11 @@
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr"/>
       <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>生物</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -18185,6 +18275,11 @@
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr"/>
       <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>反應</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -18234,6 +18329,11 @@
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr"/>
       <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>生物</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -18279,6 +18379,11 @@
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr"/>
       <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>分離</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -18326,6 +18431,11 @@
       </c>
       <c r="L22" s="2" t="inlineStr"/>
       <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>分離</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -18371,6 +18481,11 @@
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr"/>
       <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>儲存</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -18420,6 +18535,11 @@
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr"/>
       <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>儲存</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -18469,6 +18589,11 @@
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>儲存</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -18518,6 +18643,11 @@
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr"/>
       <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>儲存</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -18567,6 +18697,11 @@
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr"/>
       <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>儲存</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -18614,6 +18749,11 @@
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr"/>
       <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>儲存</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -18659,6 +18799,11 @@
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr"/>
       <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>反應</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -18704,6 +18849,11 @@
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr"/>
       <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>儲存</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/規則庫.xlsx
+++ b/規則庫.xlsx
@@ -32,6 +32,9 @@
     <sheet state="visible" name="廢水收集池" sheetId="27" r:id="rId31"/>
     <sheet state="visible" name="_同義字" sheetId="28" r:id="rId32"/>
     <sheet state="visible" name="_槽體學理" sheetId="29" r:id="rId33"/>
+    <sheet state="visible" name="_加藥規則" sheetId="30" r:id="rId34"/>
+    <sheet state="visible" name="_官方代碼表" sheetId="31" r:id="rId35"/>
+    <sheet state="visible" name="_官方參數規範" sheetId="32" r:id="rId36"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -41,11 +44,21 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={715435ca-42fd-465c-9146-cbaf2bc2a093}</author>
-    <author>tc={df0aefa8-16e6-4b27-a70c-ee6eecd15893}</author>
+    <author>tc={5aaed787-bfd2-4c77-9119-dfe99fb76b81}</author>
+    <author>tc={d91dee48-4ad6-4c1f-9fc0-9da73d9045b3}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{715435ca-42fd-465c-9146-cbaf2bc2a093}" ref="C2">
+    <comment authorId="0" xr:uid="{5aaed787-bfd2-4c77-9119-dfe99fb76b81}" ref="C10">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	公式為：G=(P/ (μ*V))^1/2     計算是直接把馬達功率 P(ex. P= 370 W、槽體有效容積 V = 1.17 m³、水的粘滯係數 μ = 0.001 N⋅s/m² 直接代入。
+學理標準範圍10~50S^-1
+</t>
+      </text>
+    </comment>
+    <comment authorId="1" xr:uid="{d91dee48-4ad6-4c1f-9fc0-9da73d9045b3}" ref="C2">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -62,22 +75,12 @@
 </t>
       </text>
     </comment>
-    <comment authorId="1" xr:uid="{df0aefa8-16e6-4b27-a70c-ee6eecd15893}" ref="C10">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	公式為：G=(P/ (μ*V))^1/2     計算是直接把馬達功率 P(ex. P= 370 W、槽體有效容積 V = 1.17 m³、水的粘滯係數 μ = 0.001 N⋅s/m² 直接代入。
-學理標準範圍10~50S^-1
-</t>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5352" uniqueCount="2032">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6530" uniqueCount="2445">
   <si>
     <t>水措審查系統 — 規則庫 使用說明 (v2)</t>
   </si>
@@ -6360,6 +6363,1245 @@
   <si>
     <t>放流前的暫存, 水質應與前端處理出流完全一致</t>
   </si>
+  <si>
+    <t>編號</t>
+  </si>
+  <si>
+    <t>分流系統</t>
+  </si>
+  <si>
+    <t>槽體類別</t>
+  </si>
+  <si>
+    <t>藥劑</t>
+  </si>
+  <si>
+    <t>加藥角色</t>
+  </si>
+  <si>
+    <t>配比 min (kg/ton)</t>
+  </si>
+  <si>
+    <t>配比 max (kg/ton)</t>
+  </si>
+  <si>
+    <t>商品濃度 min (%)</t>
+  </si>
+  <si>
+    <t>商品濃度 max (%)</t>
+  </si>
+  <si>
+    <t>pH min</t>
+  </si>
+  <si>
+    <t>pH max</t>
+  </si>
+  <si>
+    <t>學理對應水質</t>
+  </si>
+  <si>
+    <t>污泥代碼</t>
+  </si>
+  <si>
+    <t>別名/說明</t>
+  </si>
+  <si>
+    <t>D-DOSE-001</t>
+  </si>
+  <si>
+    <t>鎳系</t>
+  </si>
+  <si>
+    <t>NaOH</t>
+  </si>
+  <si>
+    <t>應加</t>
+  </si>
+  <si>
+    <t>Ni²⁺ → Ni(OH)₂</t>
+  </si>
+  <si>
+    <t>D-1101 有害</t>
+  </si>
+  <si>
+    <t>別名: 聶系/鎳水洗/化學鎳/鍍鎳/化銅. 鎳系廢水高 Ni²⁺ 需大量 NaOH 拉 pH 10.5~11 沉澱. 1 mg/L Ni 約需 2.7 mg/L NaOH.</t>
+  </si>
+  <si>
+    <t>D-DOSE-002</t>
+  </si>
+  <si>
+    <t>Ca(OH)2</t>
+  </si>
+  <si>
+    <t>替代 NaOH;改善污泥脫水性;1 mg/L Ni 約需 1.3 mg/L Ca(OH)₂.</t>
+  </si>
+  <si>
+    <t>D-DOSE-003</t>
+  </si>
+  <si>
+    <t>禁加</t>
+  </si>
+  <si>
+    <t>鎳系沒鹼前先加 PAC 沒效果 (Ni 還沒沉澱). 應先 NaOH 沉鎳, 後段才需混凝.</t>
+  </si>
+  <si>
+    <t>D-DOSE-004</t>
+  </si>
+  <si>
+    <t>Polymer</t>
+  </si>
+  <si>
+    <t>同上, 鎳系前段不需助凝.</t>
+  </si>
+  <si>
+    <t>D-DOSE-005</t>
+  </si>
+  <si>
+    <t>輕系</t>
+  </si>
+  <si>
+    <t>酸性原水中和</t>
+  </si>
+  <si>
+    <t>D-2299</t>
+  </si>
+  <si>
+    <t>別名: 輕細/輕研磨/輕污染/酸鹼廢水. 中和到 pH 6~8.</t>
+  </si>
+  <si>
+    <t>D-DOSE-006</t>
+  </si>
+  <si>
+    <t>H2SO4</t>
+  </si>
+  <si>
+    <t>鹼性原水中和</t>
+  </si>
+  <si>
+    <t>鹼性原水中和到 pH 6~8.</t>
+  </si>
+  <si>
+    <t>D-DOSE-007</t>
+  </si>
+  <si>
+    <t>HCl</t>
+  </si>
+  <si>
+    <t>D-DOSE-008</t>
+  </si>
+  <si>
+    <t>輕系污染輕、水量大, 加 PAC 是浪費 (污染物濃度不夠形成絮羽).</t>
+  </si>
+  <si>
+    <t>D-DOSE-009</t>
+  </si>
+  <si>
+    <t>SS/重金屬膠羽形成</t>
+  </si>
+  <si>
+    <t>別名: 綜合/混合廢水/總匯/總混. 商品濃度 5~10%, 投藥配比 50~500 ppm.</t>
+  </si>
+  <si>
+    <t>D-DOSE-010</t>
+  </si>
+  <si>
+    <t>Polymer (PAM)</t>
+  </si>
+  <si>
+    <t>助凝形成大絮羽</t>
+  </si>
+  <si>
+    <t>商品濃度 0.1~0.5% (現場稀釋), 投藥配比 0.5~5 ppm.</t>
+  </si>
+  <si>
+    <t>D-DOSE-011</t>
+  </si>
+  <si>
+    <t>混凝池</t>
+  </si>
+  <si>
+    <t>FeCl3</t>
+  </si>
+  <si>
+    <t>鐵系混凝替代 PAC</t>
+  </si>
+  <si>
+    <t>硫化物廢水或磷去除常用.</t>
+  </si>
+  <si>
+    <t>D-DOSE-012</t>
+  </si>
+  <si>
+    <t>氰系</t>
+  </si>
+  <si>
+    <t>NaOCl</t>
+  </si>
+  <si>
+    <t>CN⁻ → CNO⁻ → CO₂+N₂</t>
+  </si>
+  <si>
+    <t>別名: 含氰廢水/破氰. 兩段氧化第一段;1 mg/L CN 需 6.8 mg/L NaOCl.</t>
+  </si>
+  <si>
+    <t>D-DOSE-013</t>
+  </si>
+  <si>
+    <t>H2O2</t>
+  </si>
+  <si>
+    <t>CN⁻ → CNO⁻</t>
+  </si>
+  <si>
+    <t>替代 NaOCl;1 mg/L CN 需 4.4 mg/L H₂O₂.</t>
+  </si>
+  <si>
+    <t>D-DOSE-014</t>
+  </si>
+  <si>
+    <t>鉻系</t>
+  </si>
+  <si>
+    <t>還原池</t>
+  </si>
+  <si>
+    <t>NaHSO3</t>
+  </si>
+  <si>
+    <t>Cr⁶⁺ → Cr³⁺</t>
+  </si>
+  <si>
+    <t>別名: 六價鉻/Cr6+. 酸性還原 (pH 2~3);1 mg/L Cr⁶⁺ 需 3.2 mg/L NaHSO₃.</t>
+  </si>
+  <si>
+    <t>D-DOSE-015</t>
+  </si>
+  <si>
+    <t>Na2S</t>
+  </si>
+  <si>
+    <t>替代 NaHSO₃;1 mg/L Cr⁶⁺ 需 2.2 mg/L Na₂S.</t>
+  </si>
+  <si>
+    <t>D-DOSE-016</t>
+  </si>
+  <si>
+    <t>通用</t>
+  </si>
+  <si>
+    <t>硫化物沉澱池</t>
+  </si>
+  <si>
+    <t>重金屬硫化物沉澱</t>
+  </si>
+  <si>
+    <t>1 mg/L Cu²⁺ 需 1.2 mg/L Na₂S. 殘留 S²⁻ 需後處理.</t>
+  </si>
+  <si>
+    <t>D-DOSE-017</t>
+  </si>
+  <si>
+    <t>消毒池</t>
+  </si>
+  <si>
+    <t>餘氯 0.5~2 mg/L</t>
+  </si>
+  <si>
+    <t>放流前消毒.</t>
+  </si>
+  <si>
+    <t>D-DOSE-018</t>
+  </si>
+  <si>
+    <t>視原水 pH 跟緩衝量</t>
+  </si>
+  <si>
+    <t>一般 pH 調整 (非鎳系).</t>
+  </si>
+  <si>
+    <t>代碼</t>
+  </si>
+  <si>
+    <t>處理單元</t>
+  </si>
+  <si>
+    <t>大類</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>攔污柵</t>
+  </si>
+  <si>
+    <t>一級</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>流量量測裝置</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>水平流沉砂池</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>曝氣沉砂池</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>抽水站</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>調勻站(廢水調整池)</t>
+  </si>
+  <si>
+    <t>107</t>
+  </si>
+  <si>
+    <t>pH調整池(槽)</t>
+  </si>
+  <si>
+    <t>108</t>
+  </si>
+  <si>
+    <t>混凝膠凝池(槽)</t>
+  </si>
+  <si>
+    <t>109</t>
+  </si>
+  <si>
+    <t>初級沉澱池</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>浮除槽(池)</t>
+  </si>
+  <si>
+    <t>111</t>
+  </si>
+  <si>
+    <t>除油井(除油池)</t>
+  </si>
+  <si>
+    <t>112</t>
+  </si>
+  <si>
+    <t>撇除槽</t>
+  </si>
+  <si>
+    <t>113</t>
+  </si>
+  <si>
+    <t>固液分離裝置</t>
+  </si>
+  <si>
+    <t>114</t>
+  </si>
+  <si>
+    <t>化糞池</t>
+  </si>
+  <si>
+    <t>115</t>
+  </si>
+  <si>
+    <t>破鏈機</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>貯存池(槽)</t>
+  </si>
+  <si>
+    <t>117</t>
+  </si>
+  <si>
+    <t>沉砂池</t>
+  </si>
+  <si>
+    <t>118</t>
+  </si>
+  <si>
+    <t>油脂分離槽</t>
+  </si>
+  <si>
+    <t>119</t>
+  </si>
+  <si>
+    <t>預處理池</t>
+  </si>
+  <si>
+    <t>120</t>
+  </si>
+  <si>
+    <t>中和池(槽)</t>
+  </si>
+  <si>
+    <t>121</t>
+  </si>
+  <si>
+    <t>加藥池(槽)</t>
+  </si>
+  <si>
+    <t>122</t>
+  </si>
+  <si>
+    <t>混凝沉澱池(槽)</t>
+  </si>
+  <si>
+    <t>123</t>
+  </si>
+  <si>
+    <t>過濾池(槽)</t>
+  </si>
+  <si>
+    <t>124</t>
+  </si>
+  <si>
+    <t>慢濾池(槽)</t>
+  </si>
+  <si>
+    <t>125</t>
+  </si>
+  <si>
+    <t>快濾池(槽)</t>
+  </si>
+  <si>
+    <t>126</t>
+  </si>
+  <si>
+    <t>氯接觸槽(池)</t>
+  </si>
+  <si>
+    <t>127</t>
+  </si>
+  <si>
+    <t>快混池(槽)</t>
+  </si>
+  <si>
+    <t>128</t>
+  </si>
+  <si>
+    <t>慢混池(槽)</t>
+  </si>
+  <si>
+    <t>199</t>
+  </si>
+  <si>
+    <t>其他一級處理單元</t>
+  </si>
+  <si>
+    <t>201</t>
+  </si>
+  <si>
+    <t>旋轉生物圓盤</t>
+  </si>
+  <si>
+    <t>二級</t>
+  </si>
+  <si>
+    <t>202</t>
+  </si>
+  <si>
+    <t>滴濾池(槽)</t>
+  </si>
+  <si>
+    <t>203</t>
+  </si>
+  <si>
+    <t>氧化渠(氧化深渠)</t>
+  </si>
+  <si>
+    <t>204</t>
+  </si>
+  <si>
+    <t>接觸氧化池(槽)</t>
+  </si>
+  <si>
+    <t>205</t>
+  </si>
+  <si>
+    <t>流動床(喜氣流體床)</t>
+  </si>
+  <si>
+    <t>206</t>
+  </si>
+  <si>
+    <t>生物濾床(生物塔)</t>
+  </si>
+  <si>
+    <t>207</t>
+  </si>
+  <si>
+    <t>喜氣塘/曝氣氧化塘</t>
+  </si>
+  <si>
+    <t>208</t>
+  </si>
+  <si>
+    <t>活性污泥池(活性污泥曝氣池)</t>
+  </si>
+  <si>
+    <t>209</t>
+  </si>
+  <si>
+    <t>生物膜</t>
+  </si>
+  <si>
+    <t>210</t>
+  </si>
+  <si>
+    <t>兼氣污水塘(兼氣塘)</t>
+  </si>
+  <si>
+    <t>211</t>
+  </si>
+  <si>
+    <t>傳統厭氣池</t>
+  </si>
+  <si>
+    <t>212</t>
+  </si>
+  <si>
+    <t>厭氣污泥床(上流式厭氣污泥床UASB)</t>
+  </si>
+  <si>
+    <t>213</t>
+  </si>
+  <si>
+    <t>厭氣固定濾床(厭氣濾床)</t>
+  </si>
+  <si>
+    <t>214</t>
+  </si>
+  <si>
+    <t>厭氣流動床(厭氣流體化床)</t>
+  </si>
+  <si>
+    <t>215</t>
+  </si>
+  <si>
+    <t>厭氣塘</t>
+  </si>
+  <si>
+    <t>216</t>
+  </si>
+  <si>
+    <t>高率滴濾池</t>
+  </si>
+  <si>
+    <t>217</t>
+  </si>
+  <si>
+    <t>氧化池(槽)</t>
+  </si>
+  <si>
+    <t>218</t>
+  </si>
+  <si>
+    <t>曝氣池(槽)</t>
+  </si>
+  <si>
+    <t>219</t>
+  </si>
+  <si>
+    <t>高率曝氣沉澱池(槽)</t>
+  </si>
+  <si>
+    <t>220</t>
+  </si>
+  <si>
+    <t>曝氣污水塘</t>
+  </si>
+  <si>
+    <t>221</t>
+  </si>
+  <si>
+    <t>再曝氣池(槽)</t>
+  </si>
+  <si>
+    <t>222</t>
+  </si>
+  <si>
+    <t>生物養生池(槽)</t>
+  </si>
+  <si>
+    <t>223</t>
+  </si>
+  <si>
+    <t>迴流池</t>
+  </si>
+  <si>
+    <t>224</t>
+  </si>
+  <si>
+    <t>穩定池</t>
+  </si>
+  <si>
+    <t>225</t>
+  </si>
+  <si>
+    <t>第一消化池(槽)</t>
+  </si>
+  <si>
+    <t>226</t>
+  </si>
+  <si>
+    <t>第二消化池(槽)</t>
+  </si>
+  <si>
+    <t>227</t>
+  </si>
+  <si>
+    <t>醱酵池</t>
+  </si>
+  <si>
+    <t>228</t>
+  </si>
+  <si>
+    <t>厭氧接觸濾池</t>
+  </si>
+  <si>
+    <t>229</t>
+  </si>
+  <si>
+    <t>氰系第一氧化槽</t>
+  </si>
+  <si>
+    <t>二級_氰系</t>
+  </si>
+  <si>
+    <t>230</t>
+  </si>
+  <si>
+    <t>氰系第二氧化槽</t>
+  </si>
+  <si>
+    <t>231</t>
+  </si>
+  <si>
+    <t>鉻系還原槽</t>
+  </si>
+  <si>
+    <t>二級_鉻系</t>
+  </si>
+  <si>
+    <t>232</t>
+  </si>
+  <si>
+    <t>氰系滯留槽</t>
+  </si>
+  <si>
+    <t>233</t>
+  </si>
+  <si>
+    <t>鉻系滯留槽</t>
+  </si>
+  <si>
+    <t>234</t>
+  </si>
+  <si>
+    <t>鎳系廢水回收機</t>
+  </si>
+  <si>
+    <t>二級_鎳系</t>
+  </si>
+  <si>
+    <t>235</t>
+  </si>
+  <si>
+    <t>生物沉澱池(槽)</t>
+  </si>
+  <si>
+    <t>236</t>
+  </si>
+  <si>
+    <t>化學沉澱池(槽)</t>
+  </si>
+  <si>
+    <t>237</t>
+  </si>
+  <si>
+    <t>喜氣流體化床</t>
+  </si>
+  <si>
+    <t>238</t>
+  </si>
+  <si>
+    <t>氰系氧化槽(二段式鹼氯法)</t>
+  </si>
+  <si>
+    <t>239</t>
+  </si>
+  <si>
+    <t>低率滴濾池</t>
+  </si>
+  <si>
+    <t>240</t>
+  </si>
+  <si>
+    <t>分水槽</t>
+  </si>
+  <si>
+    <t>241</t>
+  </si>
+  <si>
+    <t>薄膜生物反應器(MBR)</t>
+  </si>
+  <si>
+    <t>242</t>
+  </si>
+  <si>
+    <t>活性碳污泥法加濕式氧化再生系統(PACT-WAR)</t>
+  </si>
+  <si>
+    <t>243</t>
+  </si>
+  <si>
+    <t>二級沉澱池</t>
+  </si>
+  <si>
+    <t>其他二級處理單元</t>
+  </si>
+  <si>
+    <t>301</t>
+  </si>
+  <si>
+    <t>離子交換裝置</t>
+  </si>
+  <si>
+    <t>三級</t>
+  </si>
+  <si>
+    <t>302</t>
+  </si>
+  <si>
+    <t>303</t>
+  </si>
+  <si>
+    <t>消毒裝置</t>
+  </si>
+  <si>
+    <t>304</t>
+  </si>
+  <si>
+    <t>砂濾器</t>
+  </si>
+  <si>
+    <t>305</t>
+  </si>
+  <si>
+    <t>透析裝置</t>
+  </si>
+  <si>
+    <t>306</t>
+  </si>
+  <si>
+    <t>電透析裝置</t>
+  </si>
+  <si>
+    <t>307</t>
+  </si>
+  <si>
+    <t>蒸餾裝置</t>
+  </si>
+  <si>
+    <t>308</t>
+  </si>
+  <si>
+    <t>逆滲透裝置</t>
+  </si>
+  <si>
+    <t>309</t>
+  </si>
+  <si>
+    <t>超過濾裝置</t>
+  </si>
+  <si>
+    <t>310</t>
+  </si>
+  <si>
+    <t>氯提裝置</t>
+  </si>
+  <si>
+    <t>311</t>
+  </si>
+  <si>
+    <t>萃取裝置</t>
+  </si>
+  <si>
+    <t>312</t>
+  </si>
+  <si>
+    <t>冰凍裝置</t>
+  </si>
+  <si>
+    <t>313</t>
+  </si>
+  <si>
+    <t>三級沉澱池</t>
+  </si>
+  <si>
+    <t>314</t>
+  </si>
+  <si>
+    <t>纖維快濾裝置</t>
+  </si>
+  <si>
+    <t>315</t>
+  </si>
+  <si>
+    <t>微過濾裝置</t>
+  </si>
+  <si>
+    <t>399</t>
+  </si>
+  <si>
+    <t>其他三級處理單元</t>
+  </si>
+  <si>
+    <t>401</t>
+  </si>
+  <si>
+    <t>重力式濃縮池</t>
+  </si>
+  <si>
+    <t>402</t>
+  </si>
+  <si>
+    <t>溶解空氣浮除池</t>
+  </si>
+  <si>
+    <t>403</t>
+  </si>
+  <si>
+    <t>好氧消化池(污泥)</t>
+  </si>
+  <si>
+    <t>其他_污泥</t>
+  </si>
+  <si>
+    <t>404</t>
+  </si>
+  <si>
+    <t>厭氧消化池(污泥)</t>
+  </si>
+  <si>
+    <t>405</t>
+  </si>
+  <si>
+    <t>最終沉澱池</t>
+  </si>
+  <si>
+    <t>406</t>
+  </si>
+  <si>
+    <t>冷卻塔</t>
+  </si>
+  <si>
+    <t>407</t>
+  </si>
+  <si>
+    <t>深井注入裝置</t>
+  </si>
+  <si>
+    <t>408</t>
+  </si>
+  <si>
+    <t>沼氣收集槽</t>
+  </si>
+  <si>
+    <t>409</t>
+  </si>
+  <si>
+    <t>堆肥舍</t>
+  </si>
+  <si>
+    <t>410</t>
+  </si>
+  <si>
+    <t>貯水池</t>
+  </si>
+  <si>
+    <t>411</t>
+  </si>
+  <si>
+    <t>洗砂廢水槽</t>
+  </si>
+  <si>
+    <t>412</t>
+  </si>
+  <si>
+    <t>洗砂水塔</t>
+  </si>
+  <si>
+    <t>413</t>
+  </si>
+  <si>
+    <t>清水池</t>
+  </si>
+  <si>
+    <t>414</t>
+  </si>
+  <si>
+    <t>廢水池</t>
+  </si>
+  <si>
+    <t>415</t>
+  </si>
+  <si>
+    <t>加氯機</t>
+  </si>
+  <si>
+    <t>416</t>
+  </si>
+  <si>
+    <t>會合井</t>
+  </si>
+  <si>
+    <t>417</t>
+  </si>
+  <si>
+    <t>放流槽</t>
+  </si>
+  <si>
+    <t>418</t>
+  </si>
+  <si>
+    <t>凝集裝置</t>
+  </si>
+  <si>
+    <t>419</t>
+  </si>
+  <si>
+    <t>澄清液槽</t>
+  </si>
+  <si>
+    <t>499</t>
+  </si>
+  <si>
+    <t>其他無法歸類裝置單元</t>
+  </si>
+  <si>
+    <t>501</t>
+  </si>
+  <si>
+    <t>污泥掏洗</t>
+  </si>
+  <si>
+    <t>污泥</t>
+  </si>
+  <si>
+    <t>502</t>
+  </si>
+  <si>
+    <t>污泥熱處理</t>
+  </si>
+  <si>
+    <t>503</t>
+  </si>
+  <si>
+    <t>污泥真空過濾脫水機</t>
+  </si>
+  <si>
+    <t>504</t>
+  </si>
+  <si>
+    <t>污泥離心式脫水機</t>
+  </si>
+  <si>
+    <t>505</t>
+  </si>
+  <si>
+    <t>污泥壓濾式脫水機</t>
+  </si>
+  <si>
+    <t>506</t>
+  </si>
+  <si>
+    <t>污泥帶濾式脫水機</t>
+  </si>
+  <si>
+    <t>507</t>
+  </si>
+  <si>
+    <t>污泥曬乾床</t>
+  </si>
+  <si>
+    <t>508</t>
+  </si>
+  <si>
+    <t>污泥加熱乾燥(加熱乾燥機)</t>
+  </si>
+  <si>
+    <t>509</t>
+  </si>
+  <si>
+    <t>濕法燃燒(濕式燃燒)</t>
+  </si>
+  <si>
+    <t>510</t>
+  </si>
+  <si>
+    <t>污泥濃縮設施</t>
+  </si>
+  <si>
+    <t>599</t>
+  </si>
+  <si>
+    <t>污泥之其他處理</t>
+  </si>
+  <si>
+    <t>量測或計算方式</t>
+  </si>
+  <si>
+    <t>類型(設計/量測)</t>
+  </si>
+  <si>
+    <t>流速 (m/s)</t>
+  </si>
+  <si>
+    <t>(流量Q) ÷ (開孔面積A)</t>
+  </si>
+  <si>
+    <t>設計</t>
+  </si>
+  <si>
+    <t>表面溢流率 (m³/m²·d)</t>
+  </si>
+  <si>
+    <t>(流量Q) ÷ (池表面積A)</t>
+  </si>
+  <si>
+    <t>(流量Q) ÷ (槽體或槽內格板總面積A)</t>
+  </si>
+  <si>
+    <t>水力停留時間 (d)</t>
+  </si>
+  <si>
+    <t>(有效容積V) ÷ (流量Q)</t>
+  </si>
+  <si>
+    <t>堰負荷 (m³/m·d)</t>
+  </si>
+  <si>
+    <t>(流量Q) ÷ 堰總長度</t>
+  </si>
+  <si>
+    <t>排泥頻率 (d)</t>
+  </si>
+  <si>
+    <t>--</t>
+  </si>
+  <si>
+    <t>量測</t>
+  </si>
+  <si>
+    <t>排泥量 (m³/d)</t>
+  </si>
+  <si>
+    <t>氣固比 (kg/kg)</t>
+  </si>
+  <si>
+    <t>(加壓空氣量) ÷ (SS進流濃度)</t>
+  </si>
+  <si>
+    <t>固體負荷 (kg/m²·d)</t>
+  </si>
+  <si>
+    <t>(SS進流量) ÷ (池表面積A)</t>
+  </si>
+  <si>
+    <t>加藥量 (mg/L)</t>
+  </si>
+  <si>
+    <t>迴流率 (%)</t>
+  </si>
+  <si>
+    <t>溶氣槽壓力 (Pa 或 kg/cm²)</t>
+  </si>
+  <si>
+    <t>pH值</t>
+  </si>
+  <si>
+    <t>設計空氣量 (m³/d)</t>
+  </si>
+  <si>
+    <t>壓降 (Pa)</t>
+  </si>
+  <si>
+    <t>污泥停留時間/污泥齡 (d)</t>
+  </si>
+  <si>
+    <t>【(曝氣槽容積V) × (混合液懸浮固體濃度MLSS)】 ÷ 日排泥量</t>
+  </si>
+  <si>
+    <t>體積負荷 (kg BOD/m³·d)</t>
+  </si>
+  <si>
+    <t>【(流量Q) × (濃度C)】 ÷ (曝氣槽容積V)</t>
+  </si>
+  <si>
+    <t>污泥迴流比 (%)</t>
+  </si>
+  <si>
+    <t>(迴流污泥量Qr) ÷ (廢水進流流量Q)</t>
+  </si>
+  <si>
+    <t>廢棄污泥量 (m³/d)</t>
+  </si>
+  <si>
+    <t>MLSS值 (mg/L)</t>
+  </si>
+  <si>
+    <t>食微比 F/M (kgBOD/kgMLVSS·d)</t>
+  </si>
+  <si>
+    <t>【(流量Q) × (濃度C)】 ÷ 【(曝氣槽容積V × MLVSS)】 (註: MLVSS ÷ MLSS ≈ 0.6~0.8)</t>
+  </si>
+  <si>
+    <t>溶氧 (mg/L 或飽和溶解度百分比)</t>
+  </si>
+  <si>
+    <t>SVI (mL/g)</t>
+  </si>
+  <si>
+    <t>(1公升圓筒中30分鐘沉降污泥體積SV) ÷ (混合液懸浮固體濃度MLSS)</t>
+  </si>
+  <si>
+    <t>【(流量Q) × (濃度C)】 ÷ (槽體容積V)</t>
+  </si>
+  <si>
+    <t>面積負荷 (kg COD/m²·d)</t>
+  </si>
+  <si>
+    <t>【(流量Q) × (濃度C)】 ÷ (濾材面積A)</t>
+  </si>
+  <si>
+    <t>溶氧 (mg/L)</t>
+  </si>
+  <si>
+    <t>厭氣污泥床(UASB)</t>
+  </si>
+  <si>
+    <t>體積負荷 (kg COD/m³·d)</t>
+  </si>
+  <si>
+    <t>沉澱速度</t>
+  </si>
+  <si>
+    <t>旋轉生物圓盤法(RBC)</t>
+  </si>
+  <si>
+    <t>生物盤轉速 (rpm)</t>
+  </si>
+  <si>
+    <t>BOD5圓板面積負荷 (gBOD/m²·d)</t>
+  </si>
+  <si>
+    <t>(流量Q) × (濃度C) ÷ 圓盤面積A</t>
+  </si>
+  <si>
+    <t>【(曝氣槽容積V) × (MLSS)】 ÷ 日排泥量</t>
+  </si>
+  <si>
+    <t>濾速 (m³/m²·hr)</t>
+  </si>
+  <si>
+    <t>(流量Q) ÷ (面積A)</t>
+  </si>
+  <si>
+    <t>薄膜反洗週期 (min)</t>
+  </si>
+  <si>
+    <t>食微比 F/M (kg BOD/kg MLVSS·d)</t>
+  </si>
+  <si>
+    <t>【(流量Q) × (濃度C)】 ÷ 【(曝氣槽容積V × MLVSS)】</t>
+  </si>
+  <si>
+    <t>(1公升圓筒中30分鐘沉降污泥體積SV) ÷ (MLSS)</t>
+  </si>
+  <si>
+    <t>污泥停留時間 (d)</t>
+  </si>
+  <si>
+    <t>固體濃度 (mg/L)</t>
+  </si>
+  <si>
+    <t>灰分 (%)</t>
+  </si>
+  <si>
+    <t>速度坡降 G (1/s)</t>
+  </si>
+  <si>
+    <t>【動力 / (體體積 × 黏滯度)】^(1/2)</t>
+  </si>
+  <si>
+    <t>攪拌機轉速</t>
+  </si>
+  <si>
+    <t>濾速 (m³/m²·d)</t>
+  </si>
+  <si>
+    <t>(流量Q) ÷ (過濾面積A)</t>
+  </si>
+  <si>
+    <t>反洗週期 (d)</t>
+  </si>
+  <si>
+    <t>接觸時間 (hr)</t>
+  </si>
+  <si>
+    <t>更換頻率 (d)</t>
+  </si>
+  <si>
+    <t>(污泥量Q) ÷ (表面積A)</t>
+  </si>
+  <si>
+    <t>含水率 (%)</t>
+  </si>
+  <si>
+    <t>(有效容積V) ÷ (污泥量Q)</t>
+  </si>
+  <si>
+    <t>曝氣量 (m³/d)</t>
+  </si>
+  <si>
+    <t>消化污泥之固體物量</t>
+  </si>
+  <si>
+    <t>污泥之有機成分比 (%)</t>
+  </si>
+  <si>
+    <t>biogas生產量</t>
+  </si>
+  <si>
+    <t>(污泥量Q) ÷ (濾帶寬度)</t>
+  </si>
+  <si>
+    <t>(污泥量Q) ÷ (濾布總面積)</t>
+  </si>
+  <si>
+    <t>污泥螺旋式脫水機</t>
+  </si>
+  <si>
+    <t>處理量 (kg SS/hr)</t>
+  </si>
 </sst>
 </file>
 
@@ -6402,7 +7644,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="16">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -6431,11 +7673,29 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf quotePrefix="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="6">
     <dxf>
       <font/>
       <fill>
@@ -6446,7 +7706,80 @@
       </fill>
       <border/>
     </dxf>
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF356854"/>
+          <bgColor rgb="FF356854"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF6F8F9"/>
+          <bgColor rgb="FFF6F8F9"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF356854"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF356854"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF356854"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF356854"/>
+        </bottom>
+      </border>
+    </dxf>
   </dxfs>
+  <tableStyles count="3">
+    <tableStyle count="4" pivot="0" name="_加藥規則-style">
+      <tableStyleElement dxfId="2" type="headerRow"/>
+      <tableStyleElement dxfId="3" type="firstRowStripe"/>
+      <tableStyleElement dxfId="4" type="secondRowStripe"/>
+      <tableStyleElement dxfId="5" size="0" type="wholeTable"/>
+    </tableStyle>
+    <tableStyle count="4" pivot="0" name="_官方代碼表-style">
+      <tableStyleElement dxfId="2" type="headerRow"/>
+      <tableStyleElement dxfId="3" type="firstRowStripe"/>
+      <tableStyleElement dxfId="4" type="secondRowStripe"/>
+      <tableStyleElement dxfId="5" size="0" type="wholeTable"/>
+    </tableStyle>
+    <tableStyle count="4" pivot="0" name="_官方參數規範-style">
+      <tableStyleElement dxfId="2" type="headerRow"/>
+      <tableStyleElement dxfId="3" type="firstRowStripe"/>
+      <tableStyleElement dxfId="4" type="secondRowStripe"/>
+      <tableStyleElement dxfId="5" size="0" type="wholeTable"/>
+    </tableStyle>
+  </tableStyles>
 </styleSheet>
 </file>
 
@@ -6546,6 +7879,18 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
+<file path=xl/drawings/drawing30.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing31.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing32.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
@@ -6572,8 +7917,55 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <x18tc:person displayName="Faye Tsai" id="{3abc9c29-67a2-4543-ba9f-b7daebb67bfe}" providerId="google-sheets"/>
+  <x18tc:person displayName="Faye Tsai" id="{dcafed0d-9573-4718-9329-e83cbb91b281}" providerId="google-sheets"/>
 </x18tc:personList>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:N19" displayName="表_3" name="表_3" id="1">
+  <tableColumns count="14">
+    <tableColumn name="編號" id="1"/>
+    <tableColumn name="分流系統" id="2"/>
+    <tableColumn name="槽體類別" id="3"/>
+    <tableColumn name="藥劑" id="4"/>
+    <tableColumn name="加藥角色" id="5"/>
+    <tableColumn name="配比 min (kg/ton)" id="6"/>
+    <tableColumn name="配比 max (kg/ton)" id="7"/>
+    <tableColumn name="商品濃度 min (%)" id="8"/>
+    <tableColumn name="商品濃度 max (%)" id="9"/>
+    <tableColumn name="pH min" id="10"/>
+    <tableColumn name="pH max" id="11"/>
+    <tableColumn name="學理對應水質" id="12"/>
+    <tableColumn name="污泥代碼" id="13"/>
+    <tableColumn name="別名/說明" id="14"/>
+  </tableColumns>
+  <tableStyleInfo name="_加藥規則-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:D121" displayName="表_1" name="表_1" id="2">
+  <tableColumns count="4">
+    <tableColumn name="代碼" id="1"/>
+    <tableColumn name="處理單元" id="2"/>
+    <tableColumn name="大類" id="3"/>
+    <tableColumn name="備註" id="4"/>
+  </tableColumns>
+  <tableStyleInfo name="_官方代碼表-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:E102" displayName="表_2" name="表_2" id="3">
+  <tableColumns count="5">
+    <tableColumn name="大類" id="1"/>
+    <tableColumn name="處理單元" id="2"/>
+    <tableColumn name="操作參數" id="3"/>
+    <tableColumn name="量測或計算方式" id="4"/>
+    <tableColumn name="類型(設計/量測)" id="5"/>
+  </tableColumns>
+  <tableStyleInfo name="_官方參數規範-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -6772,11 +8164,11 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="C10" dT="2026-06-04T08:43:26.00" personId="{3abc9c29-67a2-4543-ba9f-b7daebb67bfe}" id="{df0aefa8-16e6-4b27-a70c-ee6eecd15893}" done="1">
+  <x18tc:threadedComment ref="C10" dT="2026-06-04T08:43:26.00" personId="{dcafed0d-9573-4718-9329-e83cbb91b281}" id="{5aaed787-bfd2-4c77-9119-dfe99fb76b81}" done="1">
     <x18tc:text xml:space="preserve">公式為：G=(P/ (μ*V))^1/2     計算是直接把馬達功率 P(ex. P= 370 W、槽體有效容積 V = 1.17 m³、水的粘滯係數 μ = 0.001 N⋅s/m² 直接代入。
 學理標準範圍10~50S^-1</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="C2" dT="2026-06-04T07:39:16.00" personId="{3abc9c29-67a2-4543-ba9f-b7daebb67bfe}" id="{715435ca-42fd-465c-9146-cbaf2bc2a093}" done="0">
+  <x18tc:threadedComment ref="C2" dT="2026-06-04T07:39:16.00" personId="{dcafed0d-9573-4718-9329-e83cbb91b281}" id="{d91dee48-4ad6-4c1f-9fc0-9da73d9045b3}" done="0">
     <x18tc:text xml:space="preserve">項目	常見設計去除率
 SS	80~95%
 銅(Cu)	90~99%
@@ -29656,6 +31048,8310 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="2" max="2" width="12.38"/>
+    <col customWidth="1" min="3" max="3" width="10.5"/>
+    <col customWidth="1" min="4" max="4" width="12.75"/>
+    <col customWidth="1" min="5" max="5" width="15.25"/>
+    <col customWidth="1" min="6" max="6" width="12.75"/>
+    <col customWidth="1" min="7" max="7" width="14.38"/>
+    <col customWidth="1" min="8" max="8" width="12.88"/>
+    <col customWidth="1" min="9" max="9" width="14.0"/>
+    <col customWidth="1" min="10" max="11" width="10.13"/>
+    <col customWidth="1" min="12" max="12" width="19.0"/>
+    <col customWidth="1" min="13" max="13" width="14.63"/>
+    <col customWidth="1" min="14" max="14" width="90.88"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22.5" customHeight="1">
+      <c r="A1" s="10" t="s">
+        <v>2032</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>2033</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>2034</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>2035</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>2036</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>2037</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>2038</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>2039</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>2040</v>
+      </c>
+      <c r="J1" s="10" t="s">
+        <v>2041</v>
+      </c>
+      <c r="K1" s="10" t="s">
+        <v>2042</v>
+      </c>
+      <c r="L1" s="10" t="s">
+        <v>2043</v>
+      </c>
+      <c r="M1" s="10" t="s">
+        <v>2044</v>
+      </c>
+      <c r="N1" s="10" t="s">
+        <v>2045</v>
+      </c>
+    </row>
+    <row r="2" ht="22.5" customHeight="1">
+      <c r="A2" s="11" t="s">
+        <v>2046</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>2047</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>1955</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F2" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="G2" s="13">
+        <v>10.0</v>
+      </c>
+      <c r="H2" s="13">
+        <v>25.0</v>
+      </c>
+      <c r="I2" s="13">
+        <v>50.0</v>
+      </c>
+      <c r="J2" s="13">
+        <v>10.5</v>
+      </c>
+      <c r="K2" s="13">
+        <v>11.0</v>
+      </c>
+      <c r="L2" s="11" t="s">
+        <v>2050</v>
+      </c>
+      <c r="M2" s="12" t="s">
+        <v>2051</v>
+      </c>
+      <c r="N2" s="11" t="s">
+        <v>2052</v>
+      </c>
+    </row>
+    <row r="3" ht="22.5" customHeight="1">
+      <c r="A3" s="11" t="s">
+        <v>2053</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>2047</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>1955</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>2054</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F3" s="13">
+        <v>2.0</v>
+      </c>
+      <c r="G3" s="13">
+        <v>8.0</v>
+      </c>
+      <c r="H3" s="13">
+        <v>8.0</v>
+      </c>
+      <c r="I3" s="13">
+        <v>20.0</v>
+      </c>
+      <c r="J3" s="13">
+        <v>10.5</v>
+      </c>
+      <c r="K3" s="13">
+        <v>11.0</v>
+      </c>
+      <c r="L3" s="11" t="s">
+        <v>2050</v>
+      </c>
+      <c r="M3" s="12" t="s">
+        <v>2051</v>
+      </c>
+      <c r="N3" s="11" t="s">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="4" ht="22.5" customHeight="1">
+      <c r="A4" s="11" t="s">
+        <v>2056</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>2047</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>1955</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>440</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="K4" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="L4" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="M4" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="N4" s="11" t="s">
+        <v>2058</v>
+      </c>
+    </row>
+    <row r="5" ht="22.5" customHeight="1">
+      <c r="A5" s="11" t="s">
+        <v>2059</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>2047</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>1955</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>2060</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="H5" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="J5" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="K5" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="L5" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="M5" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="N5" s="11" t="s">
+        <v>2061</v>
+      </c>
+    </row>
+    <row r="6" ht="22.5" customHeight="1">
+      <c r="A6" s="11" t="s">
+        <v>2062</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>2063</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F6" s="13">
+        <v>0.1</v>
+      </c>
+      <c r="G6" s="13">
+        <v>2.0</v>
+      </c>
+      <c r="H6" s="13">
+        <v>25.0</v>
+      </c>
+      <c r="I6" s="13">
+        <v>50.0</v>
+      </c>
+      <c r="J6" s="13">
+        <v>6.0</v>
+      </c>
+      <c r="K6" s="13">
+        <v>8.0</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>2064</v>
+      </c>
+      <c r="M6" s="12" t="s">
+        <v>2065</v>
+      </c>
+      <c r="N6" s="11" t="s">
+        <v>2066</v>
+      </c>
+    </row>
+    <row r="7" ht="22.5" customHeight="1">
+      <c r="A7" s="11" t="s">
+        <v>2067</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>2063</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>2068</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F7" s="13">
+        <v>0.1</v>
+      </c>
+      <c r="G7" s="13">
+        <v>2.0</v>
+      </c>
+      <c r="H7" s="13">
+        <v>50.0</v>
+      </c>
+      <c r="I7" s="13">
+        <v>98.0</v>
+      </c>
+      <c r="J7" s="13">
+        <v>6.0</v>
+      </c>
+      <c r="K7" s="13">
+        <v>8.0</v>
+      </c>
+      <c r="L7" s="11" t="s">
+        <v>2069</v>
+      </c>
+      <c r="M7" s="12" t="s">
+        <v>2065</v>
+      </c>
+      <c r="N7" s="11" t="s">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="8" ht="22.5" customHeight="1">
+      <c r="A8" s="11" t="s">
+        <v>2071</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>2063</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>2072</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F8" s="13">
+        <v>0.1</v>
+      </c>
+      <c r="G8" s="13">
+        <v>2.0</v>
+      </c>
+      <c r="H8" s="13">
+        <v>25.0</v>
+      </c>
+      <c r="I8" s="13">
+        <v>37.0</v>
+      </c>
+      <c r="J8" s="13">
+        <v>6.0</v>
+      </c>
+      <c r="K8" s="13">
+        <v>8.0</v>
+      </c>
+      <c r="L8" s="11" t="s">
+        <v>2069</v>
+      </c>
+      <c r="M8" s="12" t="s">
+        <v>2065</v>
+      </c>
+      <c r="N8" s="11" t="s">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="9" ht="22.5" customHeight="1">
+      <c r="A9" s="11" t="s">
+        <v>2073</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>2063</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>440</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>2057</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="H9" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="J9" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="K9" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="L9" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="M9" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="N9" s="11" t="s">
+        <v>2074</v>
+      </c>
+    </row>
+    <row r="10" ht="22.5" customHeight="1">
+      <c r="A10" s="11" t="s">
+        <v>2075</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>439</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>1968</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>440</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F10" s="13">
+        <v>0.05</v>
+      </c>
+      <c r="G10" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="H10" s="13">
+        <v>5.0</v>
+      </c>
+      <c r="I10" s="13">
+        <v>10.0</v>
+      </c>
+      <c r="J10" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="K10" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="L10" s="11" t="s">
+        <v>2076</v>
+      </c>
+      <c r="M10" s="12" t="s">
+        <v>2065</v>
+      </c>
+      <c r="N10" s="11" t="s">
+        <v>2077</v>
+      </c>
+    </row>
+    <row r="11" ht="22.5" customHeight="1">
+      <c r="A11" s="11" t="s">
+        <v>2078</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>439</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>2079</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F11" s="13">
+        <v>5.0E-4</v>
+      </c>
+      <c r="G11" s="13">
+        <v>0.005</v>
+      </c>
+      <c r="H11" s="13">
+        <v>0.1</v>
+      </c>
+      <c r="I11" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="L11" s="11" t="s">
+        <v>2080</v>
+      </c>
+      <c r="M11" s="12" t="s">
+        <v>2065</v>
+      </c>
+      <c r="N11" s="11" t="s">
+        <v>2081</v>
+      </c>
+    </row>
+    <row r="12" ht="22.5" customHeight="1">
+      <c r="A12" s="11" t="s">
+        <v>2082</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>439</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>2083</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>2084</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F12" s="13">
+        <v>0.05</v>
+      </c>
+      <c r="G12" s="13">
+        <v>0.4</v>
+      </c>
+      <c r="H12" s="13">
+        <v>10.0</v>
+      </c>
+      <c r="I12" s="13">
+        <v>45.0</v>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="K12" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="L12" s="11" t="s">
+        <v>2085</v>
+      </c>
+      <c r="M12" s="12" t="s">
+        <v>2065</v>
+      </c>
+      <c r="N12" s="11" t="s">
+        <v>2086</v>
+      </c>
+    </row>
+    <row r="13" ht="22.5" customHeight="1">
+      <c r="A13" s="11" t="s">
+        <v>2087</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>2089</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F13" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="G13" s="13">
+        <v>5.0</v>
+      </c>
+      <c r="H13" s="13">
+        <v>10.0</v>
+      </c>
+      <c r="I13" s="13">
+        <v>12.0</v>
+      </c>
+      <c r="J13" s="13">
+        <v>10.0</v>
+      </c>
+      <c r="K13" s="13">
+        <v>11.0</v>
+      </c>
+      <c r="L13" s="11" t="s">
+        <v>2090</v>
+      </c>
+      <c r="M13" s="12" t="s">
+        <v>2065</v>
+      </c>
+      <c r="N13" s="11" t="s">
+        <v>2091</v>
+      </c>
+    </row>
+    <row r="14" ht="22.5" customHeight="1">
+      <c r="A14" s="11" t="s">
+        <v>2092</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>2088</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>2093</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F14" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="G14" s="13">
+        <v>3.0</v>
+      </c>
+      <c r="H14" s="13">
+        <v>30.0</v>
+      </c>
+      <c r="I14" s="13">
+        <v>50.0</v>
+      </c>
+      <c r="J14" s="13">
+        <v>10.0</v>
+      </c>
+      <c r="K14" s="13">
+        <v>11.0</v>
+      </c>
+      <c r="L14" s="11" t="s">
+        <v>2094</v>
+      </c>
+      <c r="M14" s="12" t="s">
+        <v>2065</v>
+      </c>
+      <c r="N14" s="11" t="s">
+        <v>2095</v>
+      </c>
+    </row>
+    <row r="15" ht="22.5" customHeight="1">
+      <c r="A15" s="11" t="s">
+        <v>2096</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>2097</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>2098</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>2099</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F15" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="G15" s="13">
+        <v>5.0</v>
+      </c>
+      <c r="H15" s="13">
+        <v>30.0</v>
+      </c>
+      <c r="I15" s="13">
+        <v>38.0</v>
+      </c>
+      <c r="J15" s="13">
+        <v>2.0</v>
+      </c>
+      <c r="K15" s="13">
+        <v>3.0</v>
+      </c>
+      <c r="L15" s="11" t="s">
+        <v>2100</v>
+      </c>
+      <c r="M15" s="12" t="s">
+        <v>2065</v>
+      </c>
+      <c r="N15" s="11" t="s">
+        <v>2101</v>
+      </c>
+    </row>
+    <row r="16" ht="22.5" customHeight="1">
+      <c r="A16" s="11" t="s">
+        <v>2102</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>2097</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>2098</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>2103</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F16" s="13">
+        <v>1.0</v>
+      </c>
+      <c r="G16" s="13">
+        <v>4.0</v>
+      </c>
+      <c r="H16" s="13">
+        <v>5.0</v>
+      </c>
+      <c r="I16" s="13">
+        <v>60.0</v>
+      </c>
+      <c r="J16" s="13">
+        <v>2.0</v>
+      </c>
+      <c r="K16" s="13">
+        <v>3.0</v>
+      </c>
+      <c r="L16" s="11" t="s">
+        <v>2100</v>
+      </c>
+      <c r="M16" s="12" t="s">
+        <v>2065</v>
+      </c>
+      <c r="N16" s="11" t="s">
+        <v>2104</v>
+      </c>
+    </row>
+    <row r="17" ht="22.5" customHeight="1">
+      <c r="A17" s="11" t="s">
+        <v>2105</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>2106</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>2107</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>2103</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F17" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="G17" s="13">
+        <v>3.0</v>
+      </c>
+      <c r="H17" s="13">
+        <v>5.0</v>
+      </c>
+      <c r="I17" s="13">
+        <v>60.0</v>
+      </c>
+      <c r="J17" s="13">
+        <v>8.0</v>
+      </c>
+      <c r="K17" s="13">
+        <v>10.0</v>
+      </c>
+      <c r="L17" s="11" t="s">
+        <v>2108</v>
+      </c>
+      <c r="M17" s="12" t="s">
+        <v>2051</v>
+      </c>
+      <c r="N17" s="11" t="s">
+        <v>2109</v>
+      </c>
+    </row>
+    <row r="18" ht="22.5" customHeight="1">
+      <c r="A18" s="11" t="s">
+        <v>2110</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>2106</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>2111</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>2089</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F18" s="13">
+        <v>0.01</v>
+      </c>
+      <c r="G18" s="13">
+        <v>0.05</v>
+      </c>
+      <c r="H18" s="13">
+        <v>10.0</v>
+      </c>
+      <c r="I18" s="13">
+        <v>12.0</v>
+      </c>
+      <c r="J18" s="13">
+        <v>6.0</v>
+      </c>
+      <c r="K18" s="13">
+        <v>8.0</v>
+      </c>
+      <c r="L18" s="11" t="s">
+        <v>2112</v>
+      </c>
+      <c r="M18" s="12" t="s">
+        <v>2065</v>
+      </c>
+      <c r="N18" s="11" t="s">
+        <v>2113</v>
+      </c>
+    </row>
+    <row r="19" ht="22.5" customHeight="1">
+      <c r="A19" s="11" t="s">
+        <v>2114</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>2106</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>1955</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>2048</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>2049</v>
+      </c>
+      <c r="F19" s="13">
+        <v>0.5</v>
+      </c>
+      <c r="G19" s="13">
+        <v>3.0</v>
+      </c>
+      <c r="H19" s="13">
+        <v>25.0</v>
+      </c>
+      <c r="I19" s="13">
+        <v>50.0</v>
+      </c>
+      <c r="J19" s="13">
+        <v>6.0</v>
+      </c>
+      <c r="K19" s="13">
+        <v>8.0</v>
+      </c>
+      <c r="L19" s="11" t="s">
+        <v>2115</v>
+      </c>
+      <c r="M19" s="12" t="s">
+        <v>2065</v>
+      </c>
+      <c r="N19" s="11" t="s">
+        <v>2116</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="7"/>
+      <c r="E20" s="7"/>
+    </row>
+    <row r="21">
+      <c r="B21" s="7"/>
+      <c r="E21" s="7"/>
+    </row>
+    <row r="22">
+      <c r="B22" s="7"/>
+      <c r="E22" s="7"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="7"/>
+      <c r="E23" s="7"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="7"/>
+      <c r="E24" s="7"/>
+    </row>
+    <row r="25">
+      <c r="B25" s="7"/>
+      <c r="E25" s="7"/>
+    </row>
+    <row r="26">
+      <c r="B26" s="7"/>
+      <c r="E26" s="7"/>
+    </row>
+    <row r="27">
+      <c r="B27" s="7"/>
+      <c r="E27" s="7"/>
+    </row>
+    <row r="28">
+      <c r="B28" s="7"/>
+      <c r="E28" s="7"/>
+    </row>
+    <row r="29">
+      <c r="B29" s="7"/>
+      <c r="E29" s="7"/>
+    </row>
+    <row r="30">
+      <c r="B30" s="7"/>
+      <c r="E30" s="7"/>
+    </row>
+    <row r="31">
+      <c r="B31" s="7"/>
+      <c r="E31" s="7"/>
+    </row>
+    <row r="32">
+      <c r="B32" s="7"/>
+      <c r="E32" s="7"/>
+    </row>
+    <row r="33">
+      <c r="B33" s="7"/>
+      <c r="E33" s="7"/>
+    </row>
+    <row r="34">
+      <c r="B34" s="7"/>
+      <c r="E34" s="7"/>
+    </row>
+    <row r="35">
+      <c r="B35" s="7"/>
+      <c r="E35" s="7"/>
+    </row>
+    <row r="36">
+      <c r="B36" s="7"/>
+      <c r="E36" s="7"/>
+    </row>
+    <row r="37">
+      <c r="B37" s="7"/>
+      <c r="E37" s="7"/>
+    </row>
+    <row r="38">
+      <c r="B38" s="7"/>
+      <c r="E38" s="7"/>
+    </row>
+    <row r="39">
+      <c r="B39" s="7"/>
+      <c r="E39" s="7"/>
+    </row>
+    <row r="40">
+      <c r="B40" s="7"/>
+      <c r="E40" s="7"/>
+    </row>
+    <row r="41">
+      <c r="B41" s="7"/>
+      <c r="E41" s="7"/>
+    </row>
+    <row r="42">
+      <c r="B42" s="7"/>
+      <c r="E42" s="7"/>
+    </row>
+    <row r="43">
+      <c r="B43" s="7"/>
+      <c r="E43" s="7"/>
+    </row>
+    <row r="44">
+      <c r="B44" s="7"/>
+      <c r="E44" s="7"/>
+    </row>
+    <row r="45">
+      <c r="B45" s="7"/>
+      <c r="E45" s="7"/>
+    </row>
+    <row r="46">
+      <c r="B46" s="7"/>
+      <c r="E46" s="7"/>
+    </row>
+    <row r="47">
+      <c r="B47" s="7"/>
+      <c r="E47" s="7"/>
+    </row>
+    <row r="48">
+      <c r="B48" s="7"/>
+      <c r="E48" s="7"/>
+    </row>
+    <row r="49">
+      <c r="B49" s="7"/>
+      <c r="E49" s="7"/>
+    </row>
+    <row r="50">
+      <c r="B50" s="7"/>
+      <c r="E50" s="7"/>
+    </row>
+    <row r="51">
+      <c r="B51" s="7"/>
+      <c r="E51" s="7"/>
+    </row>
+    <row r="52">
+      <c r="B52" s="7"/>
+      <c r="E52" s="7"/>
+    </row>
+    <row r="53">
+      <c r="B53" s="7"/>
+      <c r="E53" s="7"/>
+    </row>
+    <row r="54">
+      <c r="B54" s="7"/>
+      <c r="E54" s="7"/>
+    </row>
+    <row r="55">
+      <c r="B55" s="7"/>
+      <c r="E55" s="7"/>
+    </row>
+    <row r="56">
+      <c r="B56" s="7"/>
+      <c r="E56" s="7"/>
+    </row>
+    <row r="57">
+      <c r="B57" s="7"/>
+      <c r="E57" s="7"/>
+    </row>
+    <row r="58">
+      <c r="B58" s="7"/>
+      <c r="E58" s="7"/>
+    </row>
+    <row r="59">
+      <c r="B59" s="7"/>
+      <c r="E59" s="7"/>
+    </row>
+    <row r="60">
+      <c r="B60" s="7"/>
+      <c r="E60" s="7"/>
+    </row>
+    <row r="61">
+      <c r="B61" s="7"/>
+      <c r="E61" s="7"/>
+    </row>
+    <row r="62">
+      <c r="B62" s="7"/>
+      <c r="E62" s="7"/>
+    </row>
+    <row r="63">
+      <c r="B63" s="7"/>
+      <c r="E63" s="7"/>
+    </row>
+    <row r="64">
+      <c r="B64" s="7"/>
+      <c r="E64" s="7"/>
+    </row>
+    <row r="65">
+      <c r="B65" s="7"/>
+      <c r="E65" s="7"/>
+    </row>
+    <row r="66">
+      <c r="B66" s="7"/>
+      <c r="E66" s="7"/>
+    </row>
+    <row r="67">
+      <c r="B67" s="7"/>
+      <c r="E67" s="7"/>
+    </row>
+    <row r="68">
+      <c r="B68" s="7"/>
+      <c r="E68" s="7"/>
+    </row>
+    <row r="69">
+      <c r="B69" s="7"/>
+      <c r="E69" s="7"/>
+    </row>
+    <row r="70">
+      <c r="B70" s="7"/>
+      <c r="E70" s="7"/>
+    </row>
+    <row r="71">
+      <c r="B71" s="7"/>
+      <c r="E71" s="7"/>
+    </row>
+    <row r="72">
+      <c r="B72" s="7"/>
+      <c r="E72" s="7"/>
+    </row>
+    <row r="73">
+      <c r="B73" s="7"/>
+      <c r="E73" s="7"/>
+    </row>
+    <row r="74">
+      <c r="B74" s="7"/>
+      <c r="E74" s="7"/>
+    </row>
+    <row r="75">
+      <c r="B75" s="7"/>
+      <c r="E75" s="7"/>
+    </row>
+    <row r="76">
+      <c r="B76" s="7"/>
+      <c r="E76" s="7"/>
+    </row>
+    <row r="77">
+      <c r="B77" s="7"/>
+      <c r="E77" s="7"/>
+    </row>
+    <row r="78">
+      <c r="B78" s="7"/>
+      <c r="E78" s="7"/>
+    </row>
+    <row r="79">
+      <c r="B79" s="7"/>
+      <c r="E79" s="7"/>
+    </row>
+    <row r="80">
+      <c r="B80" s="7"/>
+      <c r="E80" s="7"/>
+    </row>
+    <row r="81">
+      <c r="B81" s="7"/>
+      <c r="E81" s="7"/>
+    </row>
+    <row r="82">
+      <c r="B82" s="7"/>
+      <c r="E82" s="7"/>
+    </row>
+    <row r="83">
+      <c r="B83" s="7"/>
+      <c r="E83" s="7"/>
+    </row>
+    <row r="84">
+      <c r="B84" s="7"/>
+      <c r="E84" s="7"/>
+    </row>
+    <row r="85">
+      <c r="B85" s="7"/>
+      <c r="E85" s="7"/>
+    </row>
+    <row r="86">
+      <c r="B86" s="7"/>
+      <c r="E86" s="7"/>
+    </row>
+    <row r="87">
+      <c r="B87" s="7"/>
+      <c r="E87" s="7"/>
+    </row>
+    <row r="88">
+      <c r="B88" s="7"/>
+      <c r="E88" s="7"/>
+    </row>
+    <row r="89">
+      <c r="B89" s="7"/>
+      <c r="E89" s="7"/>
+    </row>
+    <row r="90">
+      <c r="B90" s="7"/>
+      <c r="E90" s="7"/>
+    </row>
+    <row r="91">
+      <c r="B91" s="7"/>
+      <c r="E91" s="7"/>
+    </row>
+    <row r="92">
+      <c r="B92" s="7"/>
+      <c r="E92" s="7"/>
+    </row>
+    <row r="93">
+      <c r="B93" s="7"/>
+      <c r="E93" s="7"/>
+    </row>
+    <row r="94">
+      <c r="B94" s="7"/>
+      <c r="E94" s="7"/>
+    </row>
+    <row r="95">
+      <c r="B95" s="7"/>
+      <c r="E95" s="7"/>
+    </row>
+    <row r="96">
+      <c r="B96" s="7"/>
+      <c r="E96" s="7"/>
+    </row>
+    <row r="97">
+      <c r="B97" s="7"/>
+      <c r="E97" s="7"/>
+    </row>
+    <row r="98">
+      <c r="B98" s="7"/>
+      <c r="E98" s="7"/>
+    </row>
+    <row r="99">
+      <c r="B99" s="7"/>
+      <c r="E99" s="7"/>
+    </row>
+    <row r="100">
+      <c r="B100" s="7"/>
+      <c r="E100" s="7"/>
+    </row>
+    <row r="101">
+      <c r="B101" s="7"/>
+      <c r="E101" s="7"/>
+    </row>
+    <row r="102">
+      <c r="B102" s="7"/>
+      <c r="E102" s="7"/>
+    </row>
+    <row r="103">
+      <c r="B103" s="7"/>
+      <c r="E103" s="7"/>
+    </row>
+    <row r="104">
+      <c r="B104" s="7"/>
+      <c r="E104" s="7"/>
+    </row>
+    <row r="105">
+      <c r="B105" s="7"/>
+      <c r="E105" s="7"/>
+    </row>
+    <row r="106">
+      <c r="B106" s="7"/>
+      <c r="E106" s="7"/>
+    </row>
+    <row r="107">
+      <c r="B107" s="7"/>
+      <c r="E107" s="7"/>
+    </row>
+    <row r="108">
+      <c r="B108" s="7"/>
+      <c r="E108" s="7"/>
+    </row>
+    <row r="109">
+      <c r="B109" s="7"/>
+      <c r="E109" s="7"/>
+    </row>
+    <row r="110">
+      <c r="B110" s="7"/>
+      <c r="E110" s="7"/>
+    </row>
+    <row r="111">
+      <c r="B111" s="7"/>
+      <c r="E111" s="7"/>
+    </row>
+    <row r="112">
+      <c r="B112" s="7"/>
+      <c r="E112" s="7"/>
+    </row>
+    <row r="113">
+      <c r="B113" s="7"/>
+      <c r="E113" s="7"/>
+    </row>
+    <row r="114">
+      <c r="B114" s="7"/>
+      <c r="E114" s="7"/>
+    </row>
+    <row r="115">
+      <c r="B115" s="7"/>
+      <c r="E115" s="7"/>
+    </row>
+    <row r="116">
+      <c r="B116" s="7"/>
+      <c r="E116" s="7"/>
+    </row>
+    <row r="117">
+      <c r="B117" s="7"/>
+      <c r="E117" s="7"/>
+    </row>
+    <row r="118">
+      <c r="B118" s="7"/>
+      <c r="E118" s="7"/>
+    </row>
+    <row r="119">
+      <c r="B119" s="7"/>
+      <c r="E119" s="7"/>
+    </row>
+    <row r="120">
+      <c r="B120" s="7"/>
+      <c r="E120" s="7"/>
+    </row>
+    <row r="121">
+      <c r="B121" s="7"/>
+      <c r="E121" s="7"/>
+    </row>
+    <row r="122">
+      <c r="B122" s="7"/>
+      <c r="E122" s="7"/>
+    </row>
+    <row r="123">
+      <c r="B123" s="7"/>
+      <c r="E123" s="7"/>
+    </row>
+    <row r="124">
+      <c r="B124" s="7"/>
+      <c r="E124" s="7"/>
+    </row>
+    <row r="125">
+      <c r="B125" s="7"/>
+      <c r="E125" s="7"/>
+    </row>
+    <row r="126">
+      <c r="B126" s="7"/>
+      <c r="E126" s="7"/>
+    </row>
+    <row r="127">
+      <c r="B127" s="7"/>
+      <c r="E127" s="7"/>
+    </row>
+    <row r="128">
+      <c r="B128" s="7"/>
+      <c r="E128" s="7"/>
+    </row>
+    <row r="129">
+      <c r="B129" s="7"/>
+      <c r="E129" s="7"/>
+    </row>
+    <row r="130">
+      <c r="B130" s="7"/>
+      <c r="E130" s="7"/>
+    </row>
+    <row r="131">
+      <c r="B131" s="7"/>
+      <c r="E131" s="7"/>
+    </row>
+    <row r="132">
+      <c r="B132" s="7"/>
+      <c r="E132" s="7"/>
+    </row>
+    <row r="133">
+      <c r="B133" s="7"/>
+      <c r="E133" s="7"/>
+    </row>
+    <row r="134">
+      <c r="B134" s="7"/>
+      <c r="E134" s="7"/>
+    </row>
+    <row r="135">
+      <c r="B135" s="7"/>
+      <c r="E135" s="7"/>
+    </row>
+    <row r="136">
+      <c r="B136" s="7"/>
+      <c r="E136" s="7"/>
+    </row>
+    <row r="137">
+      <c r="B137" s="7"/>
+      <c r="E137" s="7"/>
+    </row>
+    <row r="138">
+      <c r="B138" s="7"/>
+      <c r="E138" s="7"/>
+    </row>
+    <row r="139">
+      <c r="B139" s="7"/>
+      <c r="E139" s="7"/>
+    </row>
+    <row r="140">
+      <c r="B140" s="7"/>
+      <c r="E140" s="7"/>
+    </row>
+    <row r="141">
+      <c r="B141" s="7"/>
+      <c r="E141" s="7"/>
+    </row>
+    <row r="142">
+      <c r="B142" s="7"/>
+      <c r="E142" s="7"/>
+    </row>
+    <row r="143">
+      <c r="B143" s="7"/>
+      <c r="E143" s="7"/>
+    </row>
+    <row r="144">
+      <c r="B144" s="7"/>
+      <c r="E144" s="7"/>
+    </row>
+    <row r="145">
+      <c r="B145" s="7"/>
+      <c r="E145" s="7"/>
+    </row>
+    <row r="146">
+      <c r="B146" s="7"/>
+      <c r="E146" s="7"/>
+    </row>
+    <row r="147">
+      <c r="B147" s="7"/>
+      <c r="E147" s="7"/>
+    </row>
+    <row r="148">
+      <c r="B148" s="7"/>
+      <c r="E148" s="7"/>
+    </row>
+    <row r="149">
+      <c r="B149" s="7"/>
+      <c r="E149" s="7"/>
+    </row>
+    <row r="150">
+      <c r="B150" s="7"/>
+      <c r="E150" s="7"/>
+    </row>
+    <row r="151">
+      <c r="B151" s="7"/>
+      <c r="E151" s="7"/>
+    </row>
+    <row r="152">
+      <c r="B152" s="7"/>
+      <c r="E152" s="7"/>
+    </row>
+    <row r="153">
+      <c r="B153" s="7"/>
+      <c r="E153" s="7"/>
+    </row>
+    <row r="154">
+      <c r="B154" s="7"/>
+      <c r="E154" s="7"/>
+    </row>
+    <row r="155">
+      <c r="B155" s="7"/>
+      <c r="E155" s="7"/>
+    </row>
+    <row r="156">
+      <c r="B156" s="7"/>
+      <c r="E156" s="7"/>
+    </row>
+    <row r="157">
+      <c r="B157" s="7"/>
+      <c r="E157" s="7"/>
+    </row>
+    <row r="158">
+      <c r="B158" s="7"/>
+      <c r="E158" s="7"/>
+    </row>
+    <row r="159">
+      <c r="B159" s="7"/>
+      <c r="E159" s="7"/>
+    </row>
+    <row r="160">
+      <c r="B160" s="7"/>
+      <c r="E160" s="7"/>
+    </row>
+    <row r="161">
+      <c r="B161" s="7"/>
+      <c r="E161" s="7"/>
+    </row>
+    <row r="162">
+      <c r="B162" s="7"/>
+      <c r="E162" s="7"/>
+    </row>
+    <row r="163">
+      <c r="B163" s="7"/>
+      <c r="E163" s="7"/>
+    </row>
+    <row r="164">
+      <c r="B164" s="7"/>
+      <c r="E164" s="7"/>
+    </row>
+    <row r="165">
+      <c r="B165" s="7"/>
+      <c r="E165" s="7"/>
+    </row>
+    <row r="166">
+      <c r="B166" s="7"/>
+      <c r="E166" s="7"/>
+    </row>
+    <row r="167">
+      <c r="B167" s="7"/>
+      <c r="E167" s="7"/>
+    </row>
+    <row r="168">
+      <c r="B168" s="7"/>
+      <c r="E168" s="7"/>
+    </row>
+    <row r="169">
+      <c r="B169" s="7"/>
+      <c r="E169" s="7"/>
+    </row>
+    <row r="170">
+      <c r="B170" s="7"/>
+      <c r="E170" s="7"/>
+    </row>
+    <row r="171">
+      <c r="B171" s="7"/>
+      <c r="E171" s="7"/>
+    </row>
+    <row r="172">
+      <c r="B172" s="7"/>
+      <c r="E172" s="7"/>
+    </row>
+    <row r="173">
+      <c r="B173" s="7"/>
+      <c r="E173" s="7"/>
+    </row>
+    <row r="174">
+      <c r="B174" s="7"/>
+      <c r="E174" s="7"/>
+    </row>
+    <row r="175">
+      <c r="B175" s="7"/>
+      <c r="E175" s="7"/>
+    </row>
+    <row r="176">
+      <c r="B176" s="7"/>
+      <c r="E176" s="7"/>
+    </row>
+    <row r="177">
+      <c r="B177" s="7"/>
+      <c r="E177" s="7"/>
+    </row>
+    <row r="178">
+      <c r="B178" s="7"/>
+      <c r="E178" s="7"/>
+    </row>
+    <row r="179">
+      <c r="B179" s="7"/>
+      <c r="E179" s="7"/>
+    </row>
+    <row r="180">
+      <c r="B180" s="7"/>
+      <c r="E180" s="7"/>
+    </row>
+    <row r="181">
+      <c r="B181" s="7"/>
+      <c r="E181" s="7"/>
+    </row>
+    <row r="182">
+      <c r="B182" s="7"/>
+      <c r="E182" s="7"/>
+    </row>
+    <row r="183">
+      <c r="B183" s="7"/>
+      <c r="E183" s="7"/>
+    </row>
+    <row r="184">
+      <c r="B184" s="7"/>
+      <c r="E184" s="7"/>
+    </row>
+    <row r="185">
+      <c r="B185" s="7"/>
+      <c r="E185" s="7"/>
+    </row>
+    <row r="186">
+      <c r="B186" s="7"/>
+      <c r="E186" s="7"/>
+    </row>
+    <row r="187">
+      <c r="B187" s="7"/>
+      <c r="E187" s="7"/>
+    </row>
+    <row r="188">
+      <c r="B188" s="7"/>
+      <c r="E188" s="7"/>
+    </row>
+    <row r="189">
+      <c r="B189" s="7"/>
+      <c r="E189" s="7"/>
+    </row>
+    <row r="190">
+      <c r="B190" s="7"/>
+      <c r="E190" s="7"/>
+    </row>
+    <row r="191">
+      <c r="B191" s="7"/>
+      <c r="E191" s="7"/>
+    </row>
+    <row r="192">
+      <c r="B192" s="7"/>
+      <c r="E192" s="7"/>
+    </row>
+    <row r="193">
+      <c r="B193" s="7"/>
+      <c r="E193" s="7"/>
+    </row>
+    <row r="194">
+      <c r="B194" s="7"/>
+      <c r="E194" s="7"/>
+    </row>
+    <row r="195">
+      <c r="B195" s="7"/>
+      <c r="E195" s="7"/>
+    </row>
+    <row r="196">
+      <c r="B196" s="7"/>
+      <c r="E196" s="7"/>
+    </row>
+    <row r="197">
+      <c r="B197" s="7"/>
+      <c r="E197" s="7"/>
+    </row>
+    <row r="198">
+      <c r="B198" s="7"/>
+      <c r="E198" s="7"/>
+    </row>
+    <row r="199">
+      <c r="B199" s="7"/>
+      <c r="E199" s="7"/>
+    </row>
+    <row r="200">
+      <c r="B200" s="7"/>
+      <c r="E200" s="7"/>
+    </row>
+    <row r="201">
+      <c r="B201" s="7"/>
+      <c r="E201" s="7"/>
+    </row>
+    <row r="202">
+      <c r="B202" s="7"/>
+      <c r="E202" s="7"/>
+    </row>
+    <row r="203">
+      <c r="B203" s="7"/>
+      <c r="E203" s="7"/>
+    </row>
+    <row r="204">
+      <c r="B204" s="7"/>
+      <c r="E204" s="7"/>
+    </row>
+    <row r="205">
+      <c r="B205" s="7"/>
+      <c r="E205" s="7"/>
+    </row>
+    <row r="206">
+      <c r="B206" s="7"/>
+      <c r="E206" s="7"/>
+    </row>
+    <row r="207">
+      <c r="B207" s="7"/>
+      <c r="E207" s="7"/>
+    </row>
+    <row r="208">
+      <c r="B208" s="7"/>
+      <c r="E208" s="7"/>
+    </row>
+    <row r="209">
+      <c r="B209" s="7"/>
+      <c r="E209" s="7"/>
+    </row>
+    <row r="210">
+      <c r="B210" s="7"/>
+      <c r="E210" s="7"/>
+    </row>
+    <row r="211">
+      <c r="B211" s="7"/>
+      <c r="E211" s="7"/>
+    </row>
+    <row r="212">
+      <c r="B212" s="7"/>
+      <c r="E212" s="7"/>
+    </row>
+    <row r="213">
+      <c r="B213" s="7"/>
+      <c r="E213" s="7"/>
+    </row>
+    <row r="214">
+      <c r="B214" s="7"/>
+      <c r="E214" s="7"/>
+    </row>
+    <row r="215">
+      <c r="B215" s="7"/>
+      <c r="E215" s="7"/>
+    </row>
+    <row r="216">
+      <c r="B216" s="7"/>
+      <c r="E216" s="7"/>
+    </row>
+    <row r="217">
+      <c r="B217" s="7"/>
+      <c r="E217" s="7"/>
+    </row>
+    <row r="218">
+      <c r="B218" s="7"/>
+      <c r="E218" s="7"/>
+    </row>
+    <row r="219">
+      <c r="B219" s="7"/>
+      <c r="E219" s="7"/>
+    </row>
+    <row r="220">
+      <c r="B220" s="7"/>
+      <c r="E220" s="7"/>
+    </row>
+    <row r="221">
+      <c r="B221" s="7"/>
+      <c r="E221" s="7"/>
+    </row>
+    <row r="222">
+      <c r="B222" s="7"/>
+      <c r="E222" s="7"/>
+    </row>
+    <row r="223">
+      <c r="B223" s="7"/>
+      <c r="E223" s="7"/>
+    </row>
+    <row r="224">
+      <c r="B224" s="7"/>
+      <c r="E224" s="7"/>
+    </row>
+    <row r="225">
+      <c r="B225" s="7"/>
+      <c r="E225" s="7"/>
+    </row>
+    <row r="226">
+      <c r="B226" s="7"/>
+      <c r="E226" s="7"/>
+    </row>
+    <row r="227">
+      <c r="B227" s="7"/>
+      <c r="E227" s="7"/>
+    </row>
+    <row r="228">
+      <c r="B228" s="7"/>
+      <c r="E228" s="7"/>
+    </row>
+    <row r="229">
+      <c r="B229" s="7"/>
+      <c r="E229" s="7"/>
+    </row>
+    <row r="230">
+      <c r="B230" s="7"/>
+      <c r="E230" s="7"/>
+    </row>
+    <row r="231">
+      <c r="B231" s="7"/>
+      <c r="E231" s="7"/>
+    </row>
+    <row r="232">
+      <c r="B232" s="7"/>
+      <c r="E232" s="7"/>
+    </row>
+    <row r="233">
+      <c r="B233" s="7"/>
+      <c r="E233" s="7"/>
+    </row>
+    <row r="234">
+      <c r="B234" s="7"/>
+      <c r="E234" s="7"/>
+    </row>
+    <row r="235">
+      <c r="B235" s="7"/>
+      <c r="E235" s="7"/>
+    </row>
+    <row r="236">
+      <c r="B236" s="7"/>
+      <c r="E236" s="7"/>
+    </row>
+    <row r="237">
+      <c r="B237" s="7"/>
+      <c r="E237" s="7"/>
+    </row>
+    <row r="238">
+      <c r="B238" s="7"/>
+      <c r="E238" s="7"/>
+    </row>
+    <row r="239">
+      <c r="B239" s="7"/>
+      <c r="E239" s="7"/>
+    </row>
+    <row r="240">
+      <c r="B240" s="7"/>
+      <c r="E240" s="7"/>
+    </row>
+    <row r="241">
+      <c r="B241" s="7"/>
+      <c r="E241" s="7"/>
+    </row>
+    <row r="242">
+      <c r="B242" s="7"/>
+      <c r="E242" s="7"/>
+    </row>
+    <row r="243">
+      <c r="B243" s="7"/>
+      <c r="E243" s="7"/>
+    </row>
+    <row r="244">
+      <c r="B244" s="7"/>
+      <c r="E244" s="7"/>
+    </row>
+    <row r="245">
+      <c r="B245" s="7"/>
+      <c r="E245" s="7"/>
+    </row>
+    <row r="246">
+      <c r="B246" s="7"/>
+      <c r="E246" s="7"/>
+    </row>
+    <row r="247">
+      <c r="B247" s="7"/>
+      <c r="E247" s="7"/>
+    </row>
+    <row r="248">
+      <c r="B248" s="7"/>
+      <c r="E248" s="7"/>
+    </row>
+    <row r="249">
+      <c r="B249" s="7"/>
+      <c r="E249" s="7"/>
+    </row>
+    <row r="250">
+      <c r="B250" s="7"/>
+      <c r="E250" s="7"/>
+    </row>
+    <row r="251">
+      <c r="B251" s="7"/>
+      <c r="E251" s="7"/>
+    </row>
+    <row r="252">
+      <c r="B252" s="7"/>
+      <c r="E252" s="7"/>
+    </row>
+    <row r="253">
+      <c r="B253" s="7"/>
+      <c r="E253" s="7"/>
+    </row>
+    <row r="254">
+      <c r="B254" s="7"/>
+      <c r="E254" s="7"/>
+    </row>
+    <row r="255">
+      <c r="B255" s="7"/>
+      <c r="E255" s="7"/>
+    </row>
+    <row r="256">
+      <c r="B256" s="7"/>
+      <c r="E256" s="7"/>
+    </row>
+    <row r="257">
+      <c r="B257" s="7"/>
+      <c r="E257" s="7"/>
+    </row>
+    <row r="258">
+      <c r="B258" s="7"/>
+      <c r="E258" s="7"/>
+    </row>
+    <row r="259">
+      <c r="B259" s="7"/>
+      <c r="E259" s="7"/>
+    </row>
+    <row r="260">
+      <c r="B260" s="7"/>
+      <c r="E260" s="7"/>
+    </row>
+    <row r="261">
+      <c r="B261" s="7"/>
+      <c r="E261" s="7"/>
+    </row>
+    <row r="262">
+      <c r="B262" s="7"/>
+      <c r="E262" s="7"/>
+    </row>
+    <row r="263">
+      <c r="B263" s="7"/>
+      <c r="E263" s="7"/>
+    </row>
+    <row r="264">
+      <c r="B264" s="7"/>
+      <c r="E264" s="7"/>
+    </row>
+    <row r="265">
+      <c r="B265" s="7"/>
+      <c r="E265" s="7"/>
+    </row>
+    <row r="266">
+      <c r="B266" s="7"/>
+      <c r="E266" s="7"/>
+    </row>
+    <row r="267">
+      <c r="B267" s="7"/>
+      <c r="E267" s="7"/>
+    </row>
+    <row r="268">
+      <c r="B268" s="7"/>
+      <c r="E268" s="7"/>
+    </row>
+    <row r="269">
+      <c r="B269" s="7"/>
+      <c r="E269" s="7"/>
+    </row>
+    <row r="270">
+      <c r="B270" s="7"/>
+      <c r="E270" s="7"/>
+    </row>
+    <row r="271">
+      <c r="B271" s="7"/>
+      <c r="E271" s="7"/>
+    </row>
+    <row r="272">
+      <c r="B272" s="7"/>
+      <c r="E272" s="7"/>
+    </row>
+    <row r="273">
+      <c r="B273" s="7"/>
+      <c r="E273" s="7"/>
+    </row>
+    <row r="274">
+      <c r="B274" s="7"/>
+      <c r="E274" s="7"/>
+    </row>
+    <row r="275">
+      <c r="B275" s="7"/>
+      <c r="E275" s="7"/>
+    </row>
+    <row r="276">
+      <c r="B276" s="7"/>
+      <c r="E276" s="7"/>
+    </row>
+    <row r="277">
+      <c r="B277" s="7"/>
+      <c r="E277" s="7"/>
+    </row>
+    <row r="278">
+      <c r="B278" s="7"/>
+      <c r="E278" s="7"/>
+    </row>
+    <row r="279">
+      <c r="B279" s="7"/>
+      <c r="E279" s="7"/>
+    </row>
+    <row r="280">
+      <c r="B280" s="7"/>
+      <c r="E280" s="7"/>
+    </row>
+    <row r="281">
+      <c r="B281" s="7"/>
+      <c r="E281" s="7"/>
+    </row>
+    <row r="282">
+      <c r="B282" s="7"/>
+      <c r="E282" s="7"/>
+    </row>
+    <row r="283">
+      <c r="B283" s="7"/>
+      <c r="E283" s="7"/>
+    </row>
+    <row r="284">
+      <c r="B284" s="7"/>
+      <c r="E284" s="7"/>
+    </row>
+    <row r="285">
+      <c r="B285" s="7"/>
+      <c r="E285" s="7"/>
+    </row>
+    <row r="286">
+      <c r="B286" s="7"/>
+      <c r="E286" s="7"/>
+    </row>
+    <row r="287">
+      <c r="B287" s="7"/>
+      <c r="E287" s="7"/>
+    </row>
+    <row r="288">
+      <c r="B288" s="7"/>
+      <c r="E288" s="7"/>
+    </row>
+    <row r="289">
+      <c r="B289" s="7"/>
+      <c r="E289" s="7"/>
+    </row>
+    <row r="290">
+      <c r="B290" s="7"/>
+      <c r="E290" s="7"/>
+    </row>
+    <row r="291">
+      <c r="B291" s="7"/>
+      <c r="E291" s="7"/>
+    </row>
+    <row r="292">
+      <c r="B292" s="7"/>
+      <c r="E292" s="7"/>
+    </row>
+    <row r="293">
+      <c r="B293" s="7"/>
+      <c r="E293" s="7"/>
+    </row>
+    <row r="294">
+      <c r="B294" s="7"/>
+      <c r="E294" s="7"/>
+    </row>
+    <row r="295">
+      <c r="B295" s="7"/>
+      <c r="E295" s="7"/>
+    </row>
+    <row r="296">
+      <c r="B296" s="7"/>
+      <c r="E296" s="7"/>
+    </row>
+    <row r="297">
+      <c r="B297" s="7"/>
+      <c r="E297" s="7"/>
+    </row>
+    <row r="298">
+      <c r="B298" s="7"/>
+      <c r="E298" s="7"/>
+    </row>
+    <row r="299">
+      <c r="B299" s="7"/>
+      <c r="E299" s="7"/>
+    </row>
+    <row r="300">
+      <c r="B300" s="7"/>
+      <c r="E300" s="7"/>
+    </row>
+    <row r="301">
+      <c r="B301" s="7"/>
+      <c r="E301" s="7"/>
+    </row>
+    <row r="302">
+      <c r="B302" s="7"/>
+      <c r="E302" s="7"/>
+    </row>
+    <row r="303">
+      <c r="B303" s="7"/>
+      <c r="E303" s="7"/>
+    </row>
+    <row r="304">
+      <c r="B304" s="7"/>
+      <c r="E304" s="7"/>
+    </row>
+    <row r="305">
+      <c r="B305" s="7"/>
+      <c r="E305" s="7"/>
+    </row>
+    <row r="306">
+      <c r="B306" s="7"/>
+      <c r="E306" s="7"/>
+    </row>
+    <row r="307">
+      <c r="B307" s="7"/>
+      <c r="E307" s="7"/>
+    </row>
+    <row r="308">
+      <c r="B308" s="7"/>
+      <c r="E308" s="7"/>
+    </row>
+    <row r="309">
+      <c r="B309" s="7"/>
+      <c r="E309" s="7"/>
+    </row>
+    <row r="310">
+      <c r="B310" s="7"/>
+      <c r="E310" s="7"/>
+    </row>
+    <row r="311">
+      <c r="B311" s="7"/>
+      <c r="E311" s="7"/>
+    </row>
+    <row r="312">
+      <c r="B312" s="7"/>
+      <c r="E312" s="7"/>
+    </row>
+    <row r="313">
+      <c r="B313" s="7"/>
+      <c r="E313" s="7"/>
+    </row>
+    <row r="314">
+      <c r="B314" s="7"/>
+      <c r="E314" s="7"/>
+    </row>
+    <row r="315">
+      <c r="B315" s="7"/>
+      <c r="E315" s="7"/>
+    </row>
+    <row r="316">
+      <c r="B316" s="7"/>
+      <c r="E316" s="7"/>
+    </row>
+    <row r="317">
+      <c r="B317" s="7"/>
+      <c r="E317" s="7"/>
+    </row>
+    <row r="318">
+      <c r="B318" s="7"/>
+      <c r="E318" s="7"/>
+    </row>
+    <row r="319">
+      <c r="B319" s="7"/>
+      <c r="E319" s="7"/>
+    </row>
+    <row r="320">
+      <c r="B320" s="7"/>
+      <c r="E320" s="7"/>
+    </row>
+    <row r="321">
+      <c r="B321" s="7"/>
+      <c r="E321" s="7"/>
+    </row>
+    <row r="322">
+      <c r="B322" s="7"/>
+      <c r="E322" s="7"/>
+    </row>
+    <row r="323">
+      <c r="B323" s="7"/>
+      <c r="E323" s="7"/>
+    </row>
+    <row r="324">
+      <c r="B324" s="7"/>
+      <c r="E324" s="7"/>
+    </row>
+    <row r="325">
+      <c r="B325" s="7"/>
+      <c r="E325" s="7"/>
+    </row>
+    <row r="326">
+      <c r="B326" s="7"/>
+      <c r="E326" s="7"/>
+    </row>
+    <row r="327">
+      <c r="B327" s="7"/>
+      <c r="E327" s="7"/>
+    </row>
+    <row r="328">
+      <c r="B328" s="7"/>
+      <c r="E328" s="7"/>
+    </row>
+    <row r="329">
+      <c r="B329" s="7"/>
+      <c r="E329" s="7"/>
+    </row>
+    <row r="330">
+      <c r="B330" s="7"/>
+      <c r="E330" s="7"/>
+    </row>
+    <row r="331">
+      <c r="B331" s="7"/>
+      <c r="E331" s="7"/>
+    </row>
+    <row r="332">
+      <c r="B332" s="7"/>
+      <c r="E332" s="7"/>
+    </row>
+    <row r="333">
+      <c r="B333" s="7"/>
+      <c r="E333" s="7"/>
+    </row>
+    <row r="334">
+      <c r="B334" s="7"/>
+      <c r="E334" s="7"/>
+    </row>
+    <row r="335">
+      <c r="B335" s="7"/>
+      <c r="E335" s="7"/>
+    </row>
+    <row r="336">
+      <c r="B336" s="7"/>
+      <c r="E336" s="7"/>
+    </row>
+    <row r="337">
+      <c r="B337" s="7"/>
+      <c r="E337" s="7"/>
+    </row>
+    <row r="338">
+      <c r="B338" s="7"/>
+      <c r="E338" s="7"/>
+    </row>
+    <row r="339">
+      <c r="B339" s="7"/>
+      <c r="E339" s="7"/>
+    </row>
+    <row r="340">
+      <c r="B340" s="7"/>
+      <c r="E340" s="7"/>
+    </row>
+    <row r="341">
+      <c r="B341" s="7"/>
+      <c r="E341" s="7"/>
+    </row>
+    <row r="342">
+      <c r="B342" s="7"/>
+      <c r="E342" s="7"/>
+    </row>
+    <row r="343">
+      <c r="B343" s="7"/>
+      <c r="E343" s="7"/>
+    </row>
+    <row r="344">
+      <c r="B344" s="7"/>
+      <c r="E344" s="7"/>
+    </row>
+    <row r="345">
+      <c r="B345" s="7"/>
+      <c r="E345" s="7"/>
+    </row>
+    <row r="346">
+      <c r="B346" s="7"/>
+      <c r="E346" s="7"/>
+    </row>
+    <row r="347">
+      <c r="B347" s="7"/>
+      <c r="E347" s="7"/>
+    </row>
+    <row r="348">
+      <c r="B348" s="7"/>
+      <c r="E348" s="7"/>
+    </row>
+    <row r="349">
+      <c r="B349" s="7"/>
+      <c r="E349" s="7"/>
+    </row>
+    <row r="350">
+      <c r="B350" s="7"/>
+      <c r="E350" s="7"/>
+    </row>
+    <row r="351">
+      <c r="B351" s="7"/>
+      <c r="E351" s="7"/>
+    </row>
+    <row r="352">
+      <c r="B352" s="7"/>
+      <c r="E352" s="7"/>
+    </row>
+    <row r="353">
+      <c r="B353" s="7"/>
+      <c r="E353" s="7"/>
+    </row>
+    <row r="354">
+      <c r="B354" s="7"/>
+      <c r="E354" s="7"/>
+    </row>
+    <row r="355">
+      <c r="B355" s="7"/>
+      <c r="E355" s="7"/>
+    </row>
+    <row r="356">
+      <c r="B356" s="7"/>
+      <c r="E356" s="7"/>
+    </row>
+    <row r="357">
+      <c r="B357" s="7"/>
+      <c r="E357" s="7"/>
+    </row>
+    <row r="358">
+      <c r="B358" s="7"/>
+      <c r="E358" s="7"/>
+    </row>
+    <row r="359">
+      <c r="B359" s="7"/>
+      <c r="E359" s="7"/>
+    </row>
+    <row r="360">
+      <c r="B360" s="7"/>
+      <c r="E360" s="7"/>
+    </row>
+    <row r="361">
+      <c r="B361" s="7"/>
+      <c r="E361" s="7"/>
+    </row>
+    <row r="362">
+      <c r="B362" s="7"/>
+      <c r="E362" s="7"/>
+    </row>
+    <row r="363">
+      <c r="B363" s="7"/>
+      <c r="E363" s="7"/>
+    </row>
+    <row r="364">
+      <c r="B364" s="7"/>
+      <c r="E364" s="7"/>
+    </row>
+    <row r="365">
+      <c r="B365" s="7"/>
+      <c r="E365" s="7"/>
+    </row>
+    <row r="366">
+      <c r="B366" s="7"/>
+      <c r="E366" s="7"/>
+    </row>
+    <row r="367">
+      <c r="B367" s="7"/>
+      <c r="E367" s="7"/>
+    </row>
+    <row r="368">
+      <c r="B368" s="7"/>
+      <c r="E368" s="7"/>
+    </row>
+    <row r="369">
+      <c r="B369" s="7"/>
+      <c r="E369" s="7"/>
+    </row>
+    <row r="370">
+      <c r="B370" s="7"/>
+      <c r="E370" s="7"/>
+    </row>
+    <row r="371">
+      <c r="B371" s="7"/>
+      <c r="E371" s="7"/>
+    </row>
+    <row r="372">
+      <c r="B372" s="7"/>
+      <c r="E372" s="7"/>
+    </row>
+    <row r="373">
+      <c r="B373" s="7"/>
+      <c r="E373" s="7"/>
+    </row>
+    <row r="374">
+      <c r="B374" s="7"/>
+      <c r="E374" s="7"/>
+    </row>
+    <row r="375">
+      <c r="B375" s="7"/>
+      <c r="E375" s="7"/>
+    </row>
+    <row r="376">
+      <c r="B376" s="7"/>
+      <c r="E376" s="7"/>
+    </row>
+    <row r="377">
+      <c r="B377" s="7"/>
+      <c r="E377" s="7"/>
+    </row>
+    <row r="378">
+      <c r="B378" s="7"/>
+      <c r="E378" s="7"/>
+    </row>
+    <row r="379">
+      <c r="B379" s="7"/>
+      <c r="E379" s="7"/>
+    </row>
+    <row r="380">
+      <c r="B380" s="7"/>
+      <c r="E380" s="7"/>
+    </row>
+    <row r="381">
+      <c r="B381" s="7"/>
+      <c r="E381" s="7"/>
+    </row>
+    <row r="382">
+      <c r="B382" s="7"/>
+      <c r="E382" s="7"/>
+    </row>
+    <row r="383">
+      <c r="B383" s="7"/>
+      <c r="E383" s="7"/>
+    </row>
+    <row r="384">
+      <c r="B384" s="7"/>
+      <c r="E384" s="7"/>
+    </row>
+    <row r="385">
+      <c r="B385" s="7"/>
+      <c r="E385" s="7"/>
+    </row>
+    <row r="386">
+      <c r="B386" s="7"/>
+      <c r="E386" s="7"/>
+    </row>
+    <row r="387">
+      <c r="B387" s="7"/>
+      <c r="E387" s="7"/>
+    </row>
+    <row r="388">
+      <c r="B388" s="7"/>
+      <c r="E388" s="7"/>
+    </row>
+    <row r="389">
+      <c r="B389" s="7"/>
+      <c r="E389" s="7"/>
+    </row>
+    <row r="390">
+      <c r="B390" s="7"/>
+      <c r="E390" s="7"/>
+    </row>
+    <row r="391">
+      <c r="B391" s="7"/>
+      <c r="E391" s="7"/>
+    </row>
+    <row r="392">
+      <c r="B392" s="7"/>
+      <c r="E392" s="7"/>
+    </row>
+    <row r="393">
+      <c r="B393" s="7"/>
+      <c r="E393" s="7"/>
+    </row>
+    <row r="394">
+      <c r="B394" s="7"/>
+      <c r="E394" s="7"/>
+    </row>
+    <row r="395">
+      <c r="B395" s="7"/>
+      <c r="E395" s="7"/>
+    </row>
+    <row r="396">
+      <c r="B396" s="7"/>
+      <c r="E396" s="7"/>
+    </row>
+    <row r="397">
+      <c r="B397" s="7"/>
+      <c r="E397" s="7"/>
+    </row>
+    <row r="398">
+      <c r="B398" s="7"/>
+      <c r="E398" s="7"/>
+    </row>
+    <row r="399">
+      <c r="B399" s="7"/>
+      <c r="E399" s="7"/>
+    </row>
+    <row r="400">
+      <c r="B400" s="7"/>
+      <c r="E400" s="7"/>
+    </row>
+    <row r="401">
+      <c r="B401" s="7"/>
+      <c r="E401" s="7"/>
+    </row>
+    <row r="402">
+      <c r="B402" s="7"/>
+      <c r="E402" s="7"/>
+    </row>
+    <row r="403">
+      <c r="B403" s="7"/>
+      <c r="E403" s="7"/>
+    </row>
+    <row r="404">
+      <c r="B404" s="7"/>
+      <c r="E404" s="7"/>
+    </row>
+    <row r="405">
+      <c r="B405" s="7"/>
+      <c r="E405" s="7"/>
+    </row>
+    <row r="406">
+      <c r="B406" s="7"/>
+      <c r="E406" s="7"/>
+    </row>
+    <row r="407">
+      <c r="B407" s="7"/>
+      <c r="E407" s="7"/>
+    </row>
+    <row r="408">
+      <c r="B408" s="7"/>
+      <c r="E408" s="7"/>
+    </row>
+    <row r="409">
+      <c r="B409" s="7"/>
+      <c r="E409" s="7"/>
+    </row>
+    <row r="410">
+      <c r="B410" s="7"/>
+      <c r="E410" s="7"/>
+    </row>
+    <row r="411">
+      <c r="B411" s="7"/>
+      <c r="E411" s="7"/>
+    </row>
+    <row r="412">
+      <c r="B412" s="7"/>
+      <c r="E412" s="7"/>
+    </row>
+    <row r="413">
+      <c r="B413" s="7"/>
+      <c r="E413" s="7"/>
+    </row>
+    <row r="414">
+      <c r="B414" s="7"/>
+      <c r="E414" s="7"/>
+    </row>
+    <row r="415">
+      <c r="B415" s="7"/>
+      <c r="E415" s="7"/>
+    </row>
+    <row r="416">
+      <c r="B416" s="7"/>
+      <c r="E416" s="7"/>
+    </row>
+    <row r="417">
+      <c r="B417" s="7"/>
+      <c r="E417" s="7"/>
+    </row>
+    <row r="418">
+      <c r="B418" s="7"/>
+      <c r="E418" s="7"/>
+    </row>
+    <row r="419">
+      <c r="B419" s="7"/>
+      <c r="E419" s="7"/>
+    </row>
+    <row r="420">
+      <c r="B420" s="7"/>
+      <c r="E420" s="7"/>
+    </row>
+    <row r="421">
+      <c r="B421" s="7"/>
+      <c r="E421" s="7"/>
+    </row>
+    <row r="422">
+      <c r="B422" s="7"/>
+      <c r="E422" s="7"/>
+    </row>
+    <row r="423">
+      <c r="B423" s="7"/>
+      <c r="E423" s="7"/>
+    </row>
+    <row r="424">
+      <c r="B424" s="7"/>
+      <c r="E424" s="7"/>
+    </row>
+    <row r="425">
+      <c r="B425" s="7"/>
+      <c r="E425" s="7"/>
+    </row>
+    <row r="426">
+      <c r="B426" s="7"/>
+      <c r="E426" s="7"/>
+    </row>
+    <row r="427">
+      <c r="B427" s="7"/>
+      <c r="E427" s="7"/>
+    </row>
+    <row r="428">
+      <c r="B428" s="7"/>
+      <c r="E428" s="7"/>
+    </row>
+    <row r="429">
+      <c r="B429" s="7"/>
+      <c r="E429" s="7"/>
+    </row>
+    <row r="430">
+      <c r="B430" s="7"/>
+      <c r="E430" s="7"/>
+    </row>
+    <row r="431">
+      <c r="B431" s="7"/>
+      <c r="E431" s="7"/>
+    </row>
+    <row r="432">
+      <c r="B432" s="7"/>
+      <c r="E432" s="7"/>
+    </row>
+    <row r="433">
+      <c r="B433" s="7"/>
+      <c r="E433" s="7"/>
+    </row>
+    <row r="434">
+      <c r="B434" s="7"/>
+      <c r="E434" s="7"/>
+    </row>
+    <row r="435">
+      <c r="B435" s="7"/>
+      <c r="E435" s="7"/>
+    </row>
+    <row r="436">
+      <c r="B436" s="7"/>
+      <c r="E436" s="7"/>
+    </row>
+    <row r="437">
+      <c r="B437" s="7"/>
+      <c r="E437" s="7"/>
+    </row>
+    <row r="438">
+      <c r="B438" s="7"/>
+      <c r="E438" s="7"/>
+    </row>
+    <row r="439">
+      <c r="B439" s="7"/>
+      <c r="E439" s="7"/>
+    </row>
+    <row r="440">
+      <c r="B440" s="7"/>
+      <c r="E440" s="7"/>
+    </row>
+    <row r="441">
+      <c r="B441" s="7"/>
+      <c r="E441" s="7"/>
+    </row>
+    <row r="442">
+      <c r="B442" s="7"/>
+      <c r="E442" s="7"/>
+    </row>
+    <row r="443">
+      <c r="B443" s="7"/>
+      <c r="E443" s="7"/>
+    </row>
+    <row r="444">
+      <c r="B444" s="7"/>
+      <c r="E444" s="7"/>
+    </row>
+    <row r="445">
+      <c r="B445" s="7"/>
+      <c r="E445" s="7"/>
+    </row>
+    <row r="446">
+      <c r="B446" s="7"/>
+      <c r="E446" s="7"/>
+    </row>
+    <row r="447">
+      <c r="B447" s="7"/>
+      <c r="E447" s="7"/>
+    </row>
+    <row r="448">
+      <c r="B448" s="7"/>
+      <c r="E448" s="7"/>
+    </row>
+    <row r="449">
+      <c r="B449" s="7"/>
+      <c r="E449" s="7"/>
+    </row>
+    <row r="450">
+      <c r="B450" s="7"/>
+      <c r="E450" s="7"/>
+    </row>
+    <row r="451">
+      <c r="B451" s="7"/>
+      <c r="E451" s="7"/>
+    </row>
+    <row r="452">
+      <c r="B452" s="7"/>
+      <c r="E452" s="7"/>
+    </row>
+    <row r="453">
+      <c r="B453" s="7"/>
+      <c r="E453" s="7"/>
+    </row>
+    <row r="454">
+      <c r="B454" s="7"/>
+      <c r="E454" s="7"/>
+    </row>
+    <row r="455">
+      <c r="B455" s="7"/>
+      <c r="E455" s="7"/>
+    </row>
+    <row r="456">
+      <c r="B456" s="7"/>
+      <c r="E456" s="7"/>
+    </row>
+    <row r="457">
+      <c r="B457" s="7"/>
+      <c r="E457" s="7"/>
+    </row>
+    <row r="458">
+      <c r="B458" s="7"/>
+      <c r="E458" s="7"/>
+    </row>
+    <row r="459">
+      <c r="B459" s="7"/>
+      <c r="E459" s="7"/>
+    </row>
+    <row r="460">
+      <c r="B460" s="7"/>
+      <c r="E460" s="7"/>
+    </row>
+    <row r="461">
+      <c r="B461" s="7"/>
+      <c r="E461" s="7"/>
+    </row>
+    <row r="462">
+      <c r="B462" s="7"/>
+      <c r="E462" s="7"/>
+    </row>
+    <row r="463">
+      <c r="B463" s="7"/>
+      <c r="E463" s="7"/>
+    </row>
+    <row r="464">
+      <c r="B464" s="7"/>
+      <c r="E464" s="7"/>
+    </row>
+    <row r="465">
+      <c r="B465" s="7"/>
+      <c r="E465" s="7"/>
+    </row>
+    <row r="466">
+      <c r="B466" s="7"/>
+      <c r="E466" s="7"/>
+    </row>
+    <row r="467">
+      <c r="B467" s="7"/>
+      <c r="E467" s="7"/>
+    </row>
+    <row r="468">
+      <c r="B468" s="7"/>
+      <c r="E468" s="7"/>
+    </row>
+    <row r="469">
+      <c r="B469" s="7"/>
+      <c r="E469" s="7"/>
+    </row>
+    <row r="470">
+      <c r="B470" s="7"/>
+      <c r="E470" s="7"/>
+    </row>
+    <row r="471">
+      <c r="B471" s="7"/>
+      <c r="E471" s="7"/>
+    </row>
+    <row r="472">
+      <c r="B472" s="7"/>
+      <c r="E472" s="7"/>
+    </row>
+    <row r="473">
+      <c r="B473" s="7"/>
+      <c r="E473" s="7"/>
+    </row>
+    <row r="474">
+      <c r="B474" s="7"/>
+      <c r="E474" s="7"/>
+    </row>
+    <row r="475">
+      <c r="B475" s="7"/>
+      <c r="E475" s="7"/>
+    </row>
+    <row r="476">
+      <c r="B476" s="7"/>
+      <c r="E476" s="7"/>
+    </row>
+    <row r="477">
+      <c r="B477" s="7"/>
+      <c r="E477" s="7"/>
+    </row>
+    <row r="478">
+      <c r="B478" s="7"/>
+      <c r="E478" s="7"/>
+    </row>
+    <row r="479">
+      <c r="B479" s="7"/>
+      <c r="E479" s="7"/>
+    </row>
+    <row r="480">
+      <c r="B480" s="7"/>
+      <c r="E480" s="7"/>
+    </row>
+    <row r="481">
+      <c r="B481" s="7"/>
+      <c r="E481" s="7"/>
+    </row>
+    <row r="482">
+      <c r="B482" s="7"/>
+      <c r="E482" s="7"/>
+    </row>
+    <row r="483">
+      <c r="B483" s="7"/>
+      <c r="E483" s="7"/>
+    </row>
+    <row r="484">
+      <c r="B484" s="7"/>
+      <c r="E484" s="7"/>
+    </row>
+    <row r="485">
+      <c r="B485" s="7"/>
+      <c r="E485" s="7"/>
+    </row>
+    <row r="486">
+      <c r="B486" s="7"/>
+      <c r="E486" s="7"/>
+    </row>
+    <row r="487">
+      <c r="B487" s="7"/>
+      <c r="E487" s="7"/>
+    </row>
+    <row r="488">
+      <c r="B488" s="7"/>
+      <c r="E488" s="7"/>
+    </row>
+    <row r="489">
+      <c r="B489" s="7"/>
+      <c r="E489" s="7"/>
+    </row>
+    <row r="490">
+      <c r="B490" s="7"/>
+      <c r="E490" s="7"/>
+    </row>
+    <row r="491">
+      <c r="B491" s="7"/>
+      <c r="E491" s="7"/>
+    </row>
+    <row r="492">
+      <c r="B492" s="7"/>
+      <c r="E492" s="7"/>
+    </row>
+    <row r="493">
+      <c r="B493" s="7"/>
+      <c r="E493" s="7"/>
+    </row>
+    <row r="494">
+      <c r="B494" s="7"/>
+      <c r="E494" s="7"/>
+    </row>
+    <row r="495">
+      <c r="B495" s="7"/>
+      <c r="E495" s="7"/>
+    </row>
+    <row r="496">
+      <c r="B496" s="7"/>
+      <c r="E496" s="7"/>
+    </row>
+    <row r="497">
+      <c r="B497" s="7"/>
+      <c r="E497" s="7"/>
+    </row>
+    <row r="498">
+      <c r="B498" s="7"/>
+      <c r="E498" s="7"/>
+    </row>
+    <row r="499">
+      <c r="B499" s="7"/>
+      <c r="E499" s="7"/>
+    </row>
+    <row r="500">
+      <c r="B500" s="7"/>
+      <c r="E500" s="7"/>
+    </row>
+    <row r="501">
+      <c r="B501" s="7"/>
+      <c r="E501" s="7"/>
+    </row>
+    <row r="502">
+      <c r="B502" s="7"/>
+      <c r="E502" s="7"/>
+    </row>
+    <row r="503">
+      <c r="B503" s="7"/>
+      <c r="E503" s="7"/>
+    </row>
+    <row r="504">
+      <c r="B504" s="7"/>
+      <c r="E504" s="7"/>
+    </row>
+    <row r="505">
+      <c r="B505" s="7"/>
+      <c r="E505" s="7"/>
+    </row>
+    <row r="506">
+      <c r="B506" s="7"/>
+      <c r="E506" s="7"/>
+    </row>
+    <row r="507">
+      <c r="B507" s="7"/>
+      <c r="E507" s="7"/>
+    </row>
+    <row r="508">
+      <c r="B508" s="7"/>
+      <c r="E508" s="7"/>
+    </row>
+    <row r="509">
+      <c r="B509" s="7"/>
+      <c r="E509" s="7"/>
+    </row>
+    <row r="510">
+      <c r="B510" s="7"/>
+      <c r="E510" s="7"/>
+    </row>
+    <row r="511">
+      <c r="B511" s="7"/>
+      <c r="E511" s="7"/>
+    </row>
+    <row r="512">
+      <c r="B512" s="7"/>
+      <c r="E512" s="7"/>
+    </row>
+    <row r="513">
+      <c r="B513" s="7"/>
+      <c r="E513" s="7"/>
+    </row>
+    <row r="514">
+      <c r="B514" s="7"/>
+      <c r="E514" s="7"/>
+    </row>
+    <row r="515">
+      <c r="B515" s="7"/>
+      <c r="E515" s="7"/>
+    </row>
+    <row r="516">
+      <c r="B516" s="7"/>
+      <c r="E516" s="7"/>
+    </row>
+    <row r="517">
+      <c r="B517" s="7"/>
+      <c r="E517" s="7"/>
+    </row>
+    <row r="518">
+      <c r="B518" s="7"/>
+      <c r="E518" s="7"/>
+    </row>
+    <row r="519">
+      <c r="B519" s="7"/>
+      <c r="E519" s="7"/>
+    </row>
+    <row r="520">
+      <c r="B520" s="7"/>
+      <c r="E520" s="7"/>
+    </row>
+    <row r="521">
+      <c r="B521" s="7"/>
+      <c r="E521" s="7"/>
+    </row>
+    <row r="522">
+      <c r="B522" s="7"/>
+      <c r="E522" s="7"/>
+    </row>
+    <row r="523">
+      <c r="B523" s="7"/>
+      <c r="E523" s="7"/>
+    </row>
+    <row r="524">
+      <c r="B524" s="7"/>
+      <c r="E524" s="7"/>
+    </row>
+    <row r="525">
+      <c r="B525" s="7"/>
+      <c r="E525" s="7"/>
+    </row>
+    <row r="526">
+      <c r="B526" s="7"/>
+      <c r="E526" s="7"/>
+    </row>
+    <row r="527">
+      <c r="B527" s="7"/>
+      <c r="E527" s="7"/>
+    </row>
+    <row r="528">
+      <c r="B528" s="7"/>
+      <c r="E528" s="7"/>
+    </row>
+    <row r="529">
+      <c r="B529" s="7"/>
+      <c r="E529" s="7"/>
+    </row>
+    <row r="530">
+      <c r="B530" s="7"/>
+      <c r="E530" s="7"/>
+    </row>
+    <row r="531">
+      <c r="B531" s="7"/>
+      <c r="E531" s="7"/>
+    </row>
+    <row r="532">
+      <c r="B532" s="7"/>
+      <c r="E532" s="7"/>
+    </row>
+    <row r="533">
+      <c r="B533" s="7"/>
+      <c r="E533" s="7"/>
+    </row>
+    <row r="534">
+      <c r="B534" s="7"/>
+      <c r="E534" s="7"/>
+    </row>
+    <row r="535">
+      <c r="B535" s="7"/>
+      <c r="E535" s="7"/>
+    </row>
+    <row r="536">
+      <c r="B536" s="7"/>
+      <c r="E536" s="7"/>
+    </row>
+    <row r="537">
+      <c r="B537" s="7"/>
+      <c r="E537" s="7"/>
+    </row>
+    <row r="538">
+      <c r="B538" s="7"/>
+      <c r="E538" s="7"/>
+    </row>
+    <row r="539">
+      <c r="B539" s="7"/>
+      <c r="E539" s="7"/>
+    </row>
+    <row r="540">
+      <c r="B540" s="7"/>
+      <c r="E540" s="7"/>
+    </row>
+    <row r="541">
+      <c r="B541" s="7"/>
+      <c r="E541" s="7"/>
+    </row>
+    <row r="542">
+      <c r="B542" s="7"/>
+      <c r="E542" s="7"/>
+    </row>
+    <row r="543">
+      <c r="B543" s="7"/>
+      <c r="E543" s="7"/>
+    </row>
+    <row r="544">
+      <c r="B544" s="7"/>
+      <c r="E544" s="7"/>
+    </row>
+    <row r="545">
+      <c r="B545" s="7"/>
+      <c r="E545" s="7"/>
+    </row>
+    <row r="546">
+      <c r="B546" s="7"/>
+      <c r="E546" s="7"/>
+    </row>
+    <row r="547">
+      <c r="B547" s="7"/>
+      <c r="E547" s="7"/>
+    </row>
+    <row r="548">
+      <c r="B548" s="7"/>
+      <c r="E548" s="7"/>
+    </row>
+    <row r="549">
+      <c r="B549" s="7"/>
+      <c r="E549" s="7"/>
+    </row>
+    <row r="550">
+      <c r="B550" s="7"/>
+      <c r="E550" s="7"/>
+    </row>
+    <row r="551">
+      <c r="B551" s="7"/>
+      <c r="E551" s="7"/>
+    </row>
+    <row r="552">
+      <c r="B552" s="7"/>
+      <c r="E552" s="7"/>
+    </row>
+    <row r="553">
+      <c r="B553" s="7"/>
+      <c r="E553" s="7"/>
+    </row>
+    <row r="554">
+      <c r="B554" s="7"/>
+      <c r="E554" s="7"/>
+    </row>
+    <row r="555">
+      <c r="B555" s="7"/>
+      <c r="E555" s="7"/>
+    </row>
+    <row r="556">
+      <c r="B556" s="7"/>
+      <c r="E556" s="7"/>
+    </row>
+    <row r="557">
+      <c r="B557" s="7"/>
+      <c r="E557" s="7"/>
+    </row>
+    <row r="558">
+      <c r="B558" s="7"/>
+      <c r="E558" s="7"/>
+    </row>
+    <row r="559">
+      <c r="B559" s="7"/>
+      <c r="E559" s="7"/>
+    </row>
+    <row r="560">
+      <c r="B560" s="7"/>
+      <c r="E560" s="7"/>
+    </row>
+    <row r="561">
+      <c r="B561" s="7"/>
+      <c r="E561" s="7"/>
+    </row>
+    <row r="562">
+      <c r="B562" s="7"/>
+      <c r="E562" s="7"/>
+    </row>
+    <row r="563">
+      <c r="B563" s="7"/>
+      <c r="E563" s="7"/>
+    </row>
+    <row r="564">
+      <c r="B564" s="7"/>
+      <c r="E564" s="7"/>
+    </row>
+    <row r="565">
+      <c r="B565" s="7"/>
+      <c r="E565" s="7"/>
+    </row>
+    <row r="566">
+      <c r="B566" s="7"/>
+      <c r="E566" s="7"/>
+    </row>
+    <row r="567">
+      <c r="B567" s="7"/>
+      <c r="E567" s="7"/>
+    </row>
+    <row r="568">
+      <c r="B568" s="7"/>
+      <c r="E568" s="7"/>
+    </row>
+    <row r="569">
+      <c r="B569" s="7"/>
+      <c r="E569" s="7"/>
+    </row>
+    <row r="570">
+      <c r="B570" s="7"/>
+      <c r="E570" s="7"/>
+    </row>
+    <row r="571">
+      <c r="B571" s="7"/>
+      <c r="E571" s="7"/>
+    </row>
+    <row r="572">
+      <c r="B572" s="7"/>
+      <c r="E572" s="7"/>
+    </row>
+    <row r="573">
+      <c r="B573" s="7"/>
+      <c r="E573" s="7"/>
+    </row>
+    <row r="574">
+      <c r="B574" s="7"/>
+      <c r="E574" s="7"/>
+    </row>
+    <row r="575">
+      <c r="B575" s="7"/>
+      <c r="E575" s="7"/>
+    </row>
+    <row r="576">
+      <c r="B576" s="7"/>
+      <c r="E576" s="7"/>
+    </row>
+    <row r="577">
+      <c r="B577" s="7"/>
+      <c r="E577" s="7"/>
+    </row>
+    <row r="578">
+      <c r="B578" s="7"/>
+      <c r="E578" s="7"/>
+    </row>
+    <row r="579">
+      <c r="B579" s="7"/>
+      <c r="E579" s="7"/>
+    </row>
+    <row r="580">
+      <c r="B580" s="7"/>
+      <c r="E580" s="7"/>
+    </row>
+    <row r="581">
+      <c r="B581" s="7"/>
+      <c r="E581" s="7"/>
+    </row>
+    <row r="582">
+      <c r="B582" s="7"/>
+      <c r="E582" s="7"/>
+    </row>
+    <row r="583">
+      <c r="B583" s="7"/>
+      <c r="E583" s="7"/>
+    </row>
+    <row r="584">
+      <c r="B584" s="7"/>
+      <c r="E584" s="7"/>
+    </row>
+    <row r="585">
+      <c r="B585" s="7"/>
+      <c r="E585" s="7"/>
+    </row>
+    <row r="586">
+      <c r="B586" s="7"/>
+      <c r="E586" s="7"/>
+    </row>
+    <row r="587">
+      <c r="B587" s="7"/>
+      <c r="E587" s="7"/>
+    </row>
+    <row r="588">
+      <c r="B588" s="7"/>
+      <c r="E588" s="7"/>
+    </row>
+    <row r="589">
+      <c r="B589" s="7"/>
+      <c r="E589" s="7"/>
+    </row>
+    <row r="590">
+      <c r="B590" s="7"/>
+      <c r="E590" s="7"/>
+    </row>
+    <row r="591">
+      <c r="B591" s="7"/>
+      <c r="E591" s="7"/>
+    </row>
+    <row r="592">
+      <c r="B592" s="7"/>
+      <c r="E592" s="7"/>
+    </row>
+    <row r="593">
+      <c r="B593" s="7"/>
+      <c r="E593" s="7"/>
+    </row>
+    <row r="594">
+      <c r="B594" s="7"/>
+      <c r="E594" s="7"/>
+    </row>
+    <row r="595">
+      <c r="B595" s="7"/>
+      <c r="E595" s="7"/>
+    </row>
+    <row r="596">
+      <c r="B596" s="7"/>
+      <c r="E596" s="7"/>
+    </row>
+    <row r="597">
+      <c r="B597" s="7"/>
+      <c r="E597" s="7"/>
+    </row>
+    <row r="598">
+      <c r="B598" s="7"/>
+      <c r="E598" s="7"/>
+    </row>
+    <row r="599">
+      <c r="B599" s="7"/>
+      <c r="E599" s="7"/>
+    </row>
+    <row r="600">
+      <c r="B600" s="7"/>
+      <c r="E600" s="7"/>
+    </row>
+    <row r="601">
+      <c r="B601" s="7"/>
+      <c r="E601" s="7"/>
+    </row>
+    <row r="602">
+      <c r="B602" s="7"/>
+      <c r="E602" s="7"/>
+    </row>
+    <row r="603">
+      <c r="B603" s="7"/>
+      <c r="E603" s="7"/>
+    </row>
+    <row r="604">
+      <c r="B604" s="7"/>
+      <c r="E604" s="7"/>
+    </row>
+    <row r="605">
+      <c r="B605" s="7"/>
+      <c r="E605" s="7"/>
+    </row>
+    <row r="606">
+      <c r="B606" s="7"/>
+      <c r="E606" s="7"/>
+    </row>
+    <row r="607">
+      <c r="B607" s="7"/>
+      <c r="E607" s="7"/>
+    </row>
+    <row r="608">
+      <c r="B608" s="7"/>
+      <c r="E608" s="7"/>
+    </row>
+    <row r="609">
+      <c r="B609" s="7"/>
+      <c r="E609" s="7"/>
+    </row>
+    <row r="610">
+      <c r="B610" s="7"/>
+      <c r="E610" s="7"/>
+    </row>
+    <row r="611">
+      <c r="B611" s="7"/>
+      <c r="E611" s="7"/>
+    </row>
+    <row r="612">
+      <c r="B612" s="7"/>
+      <c r="E612" s="7"/>
+    </row>
+    <row r="613">
+      <c r="B613" s="7"/>
+      <c r="E613" s="7"/>
+    </row>
+    <row r="614">
+      <c r="B614" s="7"/>
+      <c r="E614" s="7"/>
+    </row>
+    <row r="615">
+      <c r="B615" s="7"/>
+      <c r="E615" s="7"/>
+    </row>
+    <row r="616">
+      <c r="B616" s="7"/>
+      <c r="E616" s="7"/>
+    </row>
+    <row r="617">
+      <c r="B617" s="7"/>
+      <c r="E617" s="7"/>
+    </row>
+    <row r="618">
+      <c r="B618" s="7"/>
+      <c r="E618" s="7"/>
+    </row>
+    <row r="619">
+      <c r="B619" s="7"/>
+      <c r="E619" s="7"/>
+    </row>
+    <row r="620">
+      <c r="B620" s="7"/>
+      <c r="E620" s="7"/>
+    </row>
+    <row r="621">
+      <c r="B621" s="7"/>
+      <c r="E621" s="7"/>
+    </row>
+    <row r="622">
+      <c r="B622" s="7"/>
+      <c r="E622" s="7"/>
+    </row>
+    <row r="623">
+      <c r="B623" s="7"/>
+      <c r="E623" s="7"/>
+    </row>
+    <row r="624">
+      <c r="B624" s="7"/>
+      <c r="E624" s="7"/>
+    </row>
+    <row r="625">
+      <c r="B625" s="7"/>
+      <c r="E625" s="7"/>
+    </row>
+    <row r="626">
+      <c r="B626" s="7"/>
+      <c r="E626" s="7"/>
+    </row>
+    <row r="627">
+      <c r="B627" s="7"/>
+      <c r="E627" s="7"/>
+    </row>
+    <row r="628">
+      <c r="B628" s="7"/>
+      <c r="E628" s="7"/>
+    </row>
+    <row r="629">
+      <c r="B629" s="7"/>
+      <c r="E629" s="7"/>
+    </row>
+    <row r="630">
+      <c r="B630" s="7"/>
+      <c r="E630" s="7"/>
+    </row>
+    <row r="631">
+      <c r="B631" s="7"/>
+      <c r="E631" s="7"/>
+    </row>
+    <row r="632">
+      <c r="B632" s="7"/>
+      <c r="E632" s="7"/>
+    </row>
+    <row r="633">
+      <c r="B633" s="7"/>
+      <c r="E633" s="7"/>
+    </row>
+    <row r="634">
+      <c r="B634" s="7"/>
+      <c r="E634" s="7"/>
+    </row>
+    <row r="635">
+      <c r="B635" s="7"/>
+      <c r="E635" s="7"/>
+    </row>
+    <row r="636">
+      <c r="B636" s="7"/>
+      <c r="E636" s="7"/>
+    </row>
+    <row r="637">
+      <c r="B637" s="7"/>
+      <c r="E637" s="7"/>
+    </row>
+    <row r="638">
+      <c r="B638" s="7"/>
+      <c r="E638" s="7"/>
+    </row>
+    <row r="639">
+      <c r="B639" s="7"/>
+      <c r="E639" s="7"/>
+    </row>
+    <row r="640">
+      <c r="B640" s="7"/>
+      <c r="E640" s="7"/>
+    </row>
+    <row r="641">
+      <c r="B641" s="7"/>
+      <c r="E641" s="7"/>
+    </row>
+    <row r="642">
+      <c r="B642" s="7"/>
+      <c r="E642" s="7"/>
+    </row>
+    <row r="643">
+      <c r="B643" s="7"/>
+      <c r="E643" s="7"/>
+    </row>
+    <row r="644">
+      <c r="B644" s="7"/>
+      <c r="E644" s="7"/>
+    </row>
+    <row r="645">
+      <c r="B645" s="7"/>
+      <c r="E645" s="7"/>
+    </row>
+    <row r="646">
+      <c r="B646" s="7"/>
+      <c r="E646" s="7"/>
+    </row>
+    <row r="647">
+      <c r="B647" s="7"/>
+      <c r="E647" s="7"/>
+    </row>
+    <row r="648">
+      <c r="B648" s="7"/>
+      <c r="E648" s="7"/>
+    </row>
+    <row r="649">
+      <c r="B649" s="7"/>
+      <c r="E649" s="7"/>
+    </row>
+    <row r="650">
+      <c r="B650" s="7"/>
+      <c r="E650" s="7"/>
+    </row>
+    <row r="651">
+      <c r="B651" s="7"/>
+      <c r="E651" s="7"/>
+    </row>
+    <row r="652">
+      <c r="B652" s="7"/>
+      <c r="E652" s="7"/>
+    </row>
+    <row r="653">
+      <c r="B653" s="7"/>
+      <c r="E653" s="7"/>
+    </row>
+    <row r="654">
+      <c r="B654" s="7"/>
+      <c r="E654" s="7"/>
+    </row>
+    <row r="655">
+      <c r="B655" s="7"/>
+      <c r="E655" s="7"/>
+    </row>
+    <row r="656">
+      <c r="B656" s="7"/>
+      <c r="E656" s="7"/>
+    </row>
+    <row r="657">
+      <c r="B657" s="7"/>
+      <c r="E657" s="7"/>
+    </row>
+    <row r="658">
+      <c r="B658" s="7"/>
+      <c r="E658" s="7"/>
+    </row>
+    <row r="659">
+      <c r="B659" s="7"/>
+      <c r="E659" s="7"/>
+    </row>
+    <row r="660">
+      <c r="B660" s="7"/>
+      <c r="E660" s="7"/>
+    </row>
+    <row r="661">
+      <c r="B661" s="7"/>
+      <c r="E661" s="7"/>
+    </row>
+    <row r="662">
+      <c r="B662" s="7"/>
+      <c r="E662" s="7"/>
+    </row>
+    <row r="663">
+      <c r="B663" s="7"/>
+      <c r="E663" s="7"/>
+    </row>
+    <row r="664">
+      <c r="B664" s="7"/>
+      <c r="E664" s="7"/>
+    </row>
+    <row r="665">
+      <c r="B665" s="7"/>
+      <c r="E665" s="7"/>
+    </row>
+    <row r="666">
+      <c r="B666" s="7"/>
+      <c r="E666" s="7"/>
+    </row>
+    <row r="667">
+      <c r="B667" s="7"/>
+      <c r="E667" s="7"/>
+    </row>
+    <row r="668">
+      <c r="B668" s="7"/>
+      <c r="E668" s="7"/>
+    </row>
+    <row r="669">
+      <c r="B669" s="7"/>
+      <c r="E669" s="7"/>
+    </row>
+    <row r="670">
+      <c r="B670" s="7"/>
+      <c r="E670" s="7"/>
+    </row>
+    <row r="671">
+      <c r="B671" s="7"/>
+      <c r="E671" s="7"/>
+    </row>
+    <row r="672">
+      <c r="B672" s="7"/>
+      <c r="E672" s="7"/>
+    </row>
+    <row r="673">
+      <c r="B673" s="7"/>
+      <c r="E673" s="7"/>
+    </row>
+    <row r="674">
+      <c r="B674" s="7"/>
+      <c r="E674" s="7"/>
+    </row>
+    <row r="675">
+      <c r="B675" s="7"/>
+      <c r="E675" s="7"/>
+    </row>
+    <row r="676">
+      <c r="B676" s="7"/>
+      <c r="E676" s="7"/>
+    </row>
+    <row r="677">
+      <c r="B677" s="7"/>
+      <c r="E677" s="7"/>
+    </row>
+    <row r="678">
+      <c r="B678" s="7"/>
+      <c r="E678" s="7"/>
+    </row>
+    <row r="679">
+      <c r="B679" s="7"/>
+      <c r="E679" s="7"/>
+    </row>
+    <row r="680">
+      <c r="B680" s="7"/>
+      <c r="E680" s="7"/>
+    </row>
+    <row r="681">
+      <c r="B681" s="7"/>
+      <c r="E681" s="7"/>
+    </row>
+    <row r="682">
+      <c r="B682" s="7"/>
+      <c r="E682" s="7"/>
+    </row>
+    <row r="683">
+      <c r="B683" s="7"/>
+      <c r="E683" s="7"/>
+    </row>
+    <row r="684">
+      <c r="B684" s="7"/>
+      <c r="E684" s="7"/>
+    </row>
+    <row r="685">
+      <c r="B685" s="7"/>
+      <c r="E685" s="7"/>
+    </row>
+    <row r="686">
+      <c r="B686" s="7"/>
+      <c r="E686" s="7"/>
+    </row>
+    <row r="687">
+      <c r="B687" s="7"/>
+      <c r="E687" s="7"/>
+    </row>
+    <row r="688">
+      <c r="B688" s="7"/>
+      <c r="E688" s="7"/>
+    </row>
+    <row r="689">
+      <c r="B689" s="7"/>
+      <c r="E689" s="7"/>
+    </row>
+    <row r="690">
+      <c r="B690" s="7"/>
+      <c r="E690" s="7"/>
+    </row>
+    <row r="691">
+      <c r="B691" s="7"/>
+      <c r="E691" s="7"/>
+    </row>
+    <row r="692">
+      <c r="B692" s="7"/>
+      <c r="E692" s="7"/>
+    </row>
+    <row r="693">
+      <c r="B693" s="7"/>
+      <c r="E693" s="7"/>
+    </row>
+    <row r="694">
+      <c r="B694" s="7"/>
+      <c r="E694" s="7"/>
+    </row>
+    <row r="695">
+      <c r="B695" s="7"/>
+      <c r="E695" s="7"/>
+    </row>
+    <row r="696">
+      <c r="B696" s="7"/>
+      <c r="E696" s="7"/>
+    </row>
+    <row r="697">
+      <c r="B697" s="7"/>
+      <c r="E697" s="7"/>
+    </row>
+    <row r="698">
+      <c r="B698" s="7"/>
+      <c r="E698" s="7"/>
+    </row>
+    <row r="699">
+      <c r="B699" s="7"/>
+      <c r="E699" s="7"/>
+    </row>
+    <row r="700">
+      <c r="B700" s="7"/>
+      <c r="E700" s="7"/>
+    </row>
+    <row r="701">
+      <c r="B701" s="7"/>
+      <c r="E701" s="7"/>
+    </row>
+    <row r="702">
+      <c r="B702" s="7"/>
+      <c r="E702" s="7"/>
+    </row>
+    <row r="703">
+      <c r="B703" s="7"/>
+      <c r="E703" s="7"/>
+    </row>
+    <row r="704">
+      <c r="B704" s="7"/>
+      <c r="E704" s="7"/>
+    </row>
+    <row r="705">
+      <c r="B705" s="7"/>
+      <c r="E705" s="7"/>
+    </row>
+    <row r="706">
+      <c r="B706" s="7"/>
+      <c r="E706" s="7"/>
+    </row>
+    <row r="707">
+      <c r="B707" s="7"/>
+      <c r="E707" s="7"/>
+    </row>
+    <row r="708">
+      <c r="B708" s="7"/>
+      <c r="E708" s="7"/>
+    </row>
+    <row r="709">
+      <c r="B709" s="7"/>
+      <c r="E709" s="7"/>
+    </row>
+    <row r="710">
+      <c r="B710" s="7"/>
+      <c r="E710" s="7"/>
+    </row>
+    <row r="711">
+      <c r="B711" s="7"/>
+      <c r="E711" s="7"/>
+    </row>
+    <row r="712">
+      <c r="B712" s="7"/>
+      <c r="E712" s="7"/>
+    </row>
+    <row r="713">
+      <c r="B713" s="7"/>
+      <c r="E713" s="7"/>
+    </row>
+    <row r="714">
+      <c r="B714" s="7"/>
+      <c r="E714" s="7"/>
+    </row>
+    <row r="715">
+      <c r="B715" s="7"/>
+      <c r="E715" s="7"/>
+    </row>
+    <row r="716">
+      <c r="B716" s="7"/>
+      <c r="E716" s="7"/>
+    </row>
+    <row r="717">
+      <c r="B717" s="7"/>
+      <c r="E717" s="7"/>
+    </row>
+    <row r="718">
+      <c r="B718" s="7"/>
+      <c r="E718" s="7"/>
+    </row>
+    <row r="719">
+      <c r="B719" s="7"/>
+      <c r="E719" s="7"/>
+    </row>
+    <row r="720">
+      <c r="B720" s="7"/>
+      <c r="E720" s="7"/>
+    </row>
+    <row r="721">
+      <c r="B721" s="7"/>
+      <c r="E721" s="7"/>
+    </row>
+    <row r="722">
+      <c r="B722" s="7"/>
+      <c r="E722" s="7"/>
+    </row>
+    <row r="723">
+      <c r="B723" s="7"/>
+      <c r="E723" s="7"/>
+    </row>
+    <row r="724">
+      <c r="B724" s="7"/>
+      <c r="E724" s="7"/>
+    </row>
+    <row r="725">
+      <c r="B725" s="7"/>
+      <c r="E725" s="7"/>
+    </row>
+    <row r="726">
+      <c r="B726" s="7"/>
+      <c r="E726" s="7"/>
+    </row>
+    <row r="727">
+      <c r="B727" s="7"/>
+      <c r="E727" s="7"/>
+    </row>
+    <row r="728">
+      <c r="B728" s="7"/>
+      <c r="E728" s="7"/>
+    </row>
+    <row r="729">
+      <c r="B729" s="7"/>
+      <c r="E729" s="7"/>
+    </row>
+    <row r="730">
+      <c r="B730" s="7"/>
+      <c r="E730" s="7"/>
+    </row>
+    <row r="731">
+      <c r="B731" s="7"/>
+      <c r="E731" s="7"/>
+    </row>
+    <row r="732">
+      <c r="B732" s="7"/>
+      <c r="E732" s="7"/>
+    </row>
+    <row r="733">
+      <c r="B733" s="7"/>
+      <c r="E733" s="7"/>
+    </row>
+    <row r="734">
+      <c r="B734" s="7"/>
+      <c r="E734" s="7"/>
+    </row>
+    <row r="735">
+      <c r="B735" s="7"/>
+      <c r="E735" s="7"/>
+    </row>
+    <row r="736">
+      <c r="B736" s="7"/>
+      <c r="E736" s="7"/>
+    </row>
+    <row r="737">
+      <c r="B737" s="7"/>
+      <c r="E737" s="7"/>
+    </row>
+    <row r="738">
+      <c r="B738" s="7"/>
+      <c r="E738" s="7"/>
+    </row>
+    <row r="739">
+      <c r="B739" s="7"/>
+      <c r="E739" s="7"/>
+    </row>
+    <row r="740">
+      <c r="B740" s="7"/>
+      <c r="E740" s="7"/>
+    </row>
+    <row r="741">
+      <c r="B741" s="7"/>
+      <c r="E741" s="7"/>
+    </row>
+    <row r="742">
+      <c r="B742" s="7"/>
+      <c r="E742" s="7"/>
+    </row>
+    <row r="743">
+      <c r="B743" s="7"/>
+      <c r="E743" s="7"/>
+    </row>
+    <row r="744">
+      <c r="B744" s="7"/>
+      <c r="E744" s="7"/>
+    </row>
+    <row r="745">
+      <c r="B745" s="7"/>
+      <c r="E745" s="7"/>
+    </row>
+    <row r="746">
+      <c r="B746" s="7"/>
+      <c r="E746" s="7"/>
+    </row>
+    <row r="747">
+      <c r="B747" s="7"/>
+      <c r="E747" s="7"/>
+    </row>
+    <row r="748">
+      <c r="B748" s="7"/>
+      <c r="E748" s="7"/>
+    </row>
+    <row r="749">
+      <c r="B749" s="7"/>
+      <c r="E749" s="7"/>
+    </row>
+    <row r="750">
+      <c r="B750" s="7"/>
+      <c r="E750" s="7"/>
+    </row>
+    <row r="751">
+      <c r="B751" s="7"/>
+      <c r="E751" s="7"/>
+    </row>
+    <row r="752">
+      <c r="B752" s="7"/>
+      <c r="E752" s="7"/>
+    </row>
+    <row r="753">
+      <c r="B753" s="7"/>
+      <c r="E753" s="7"/>
+    </row>
+    <row r="754">
+      <c r="B754" s="7"/>
+      <c r="E754" s="7"/>
+    </row>
+    <row r="755">
+      <c r="B755" s="7"/>
+      <c r="E755" s="7"/>
+    </row>
+    <row r="756">
+      <c r="B756" s="7"/>
+      <c r="E756" s="7"/>
+    </row>
+    <row r="757">
+      <c r="B757" s="7"/>
+      <c r="E757" s="7"/>
+    </row>
+    <row r="758">
+      <c r="B758" s="7"/>
+      <c r="E758" s="7"/>
+    </row>
+    <row r="759">
+      <c r="B759" s="7"/>
+      <c r="E759" s="7"/>
+    </row>
+    <row r="760">
+      <c r="B760" s="7"/>
+      <c r="E760" s="7"/>
+    </row>
+    <row r="761">
+      <c r="B761" s="7"/>
+      <c r="E761" s="7"/>
+    </row>
+    <row r="762">
+      <c r="B762" s="7"/>
+      <c r="E762" s="7"/>
+    </row>
+    <row r="763">
+      <c r="B763" s="7"/>
+      <c r="E763" s="7"/>
+    </row>
+    <row r="764">
+      <c r="B764" s="7"/>
+      <c r="E764" s="7"/>
+    </row>
+    <row r="765">
+      <c r="B765" s="7"/>
+      <c r="E765" s="7"/>
+    </row>
+    <row r="766">
+      <c r="B766" s="7"/>
+      <c r="E766" s="7"/>
+    </row>
+    <row r="767">
+      <c r="B767" s="7"/>
+      <c r="E767" s="7"/>
+    </row>
+    <row r="768">
+      <c r="B768" s="7"/>
+      <c r="E768" s="7"/>
+    </row>
+    <row r="769">
+      <c r="B769" s="7"/>
+      <c r="E769" s="7"/>
+    </row>
+    <row r="770">
+      <c r="B770" s="7"/>
+      <c r="E770" s="7"/>
+    </row>
+    <row r="771">
+      <c r="B771" s="7"/>
+      <c r="E771" s="7"/>
+    </row>
+    <row r="772">
+      <c r="B772" s="7"/>
+      <c r="E772" s="7"/>
+    </row>
+    <row r="773">
+      <c r="B773" s="7"/>
+      <c r="E773" s="7"/>
+    </row>
+    <row r="774">
+      <c r="B774" s="7"/>
+      <c r="E774" s="7"/>
+    </row>
+    <row r="775">
+      <c r="B775" s="7"/>
+      <c r="E775" s="7"/>
+    </row>
+    <row r="776">
+      <c r="B776" s="7"/>
+      <c r="E776" s="7"/>
+    </row>
+    <row r="777">
+      <c r="B777" s="7"/>
+      <c r="E777" s="7"/>
+    </row>
+    <row r="778">
+      <c r="B778" s="7"/>
+      <c r="E778" s="7"/>
+    </row>
+    <row r="779">
+      <c r="B779" s="7"/>
+      <c r="E779" s="7"/>
+    </row>
+    <row r="780">
+      <c r="B780" s="7"/>
+      <c r="E780" s="7"/>
+    </row>
+    <row r="781">
+      <c r="B781" s="7"/>
+      <c r="E781" s="7"/>
+    </row>
+    <row r="782">
+      <c r="B782" s="7"/>
+      <c r="E782" s="7"/>
+    </row>
+    <row r="783">
+      <c r="B783" s="7"/>
+      <c r="E783" s="7"/>
+    </row>
+    <row r="784">
+      <c r="B784" s="7"/>
+      <c r="E784" s="7"/>
+    </row>
+    <row r="785">
+      <c r="B785" s="7"/>
+      <c r="E785" s="7"/>
+    </row>
+    <row r="786">
+      <c r="B786" s="7"/>
+      <c r="E786" s="7"/>
+    </row>
+    <row r="787">
+      <c r="B787" s="7"/>
+      <c r="E787" s="7"/>
+    </row>
+    <row r="788">
+      <c r="B788" s="7"/>
+      <c r="E788" s="7"/>
+    </row>
+    <row r="789">
+      <c r="B789" s="7"/>
+      <c r="E789" s="7"/>
+    </row>
+    <row r="790">
+      <c r="B790" s="7"/>
+      <c r="E790" s="7"/>
+    </row>
+    <row r="791">
+      <c r="B791" s="7"/>
+      <c r="E791" s="7"/>
+    </row>
+    <row r="792">
+      <c r="B792" s="7"/>
+      <c r="E792" s="7"/>
+    </row>
+    <row r="793">
+      <c r="B793" s="7"/>
+      <c r="E793" s="7"/>
+    </row>
+    <row r="794">
+      <c r="B794" s="7"/>
+      <c r="E794" s="7"/>
+    </row>
+    <row r="795">
+      <c r="B795" s="7"/>
+      <c r="E795" s="7"/>
+    </row>
+    <row r="796">
+      <c r="B796" s="7"/>
+      <c r="E796" s="7"/>
+    </row>
+    <row r="797">
+      <c r="B797" s="7"/>
+      <c r="E797" s="7"/>
+    </row>
+    <row r="798">
+      <c r="B798" s="7"/>
+      <c r="E798" s="7"/>
+    </row>
+    <row r="799">
+      <c r="B799" s="7"/>
+      <c r="E799" s="7"/>
+    </row>
+    <row r="800">
+      <c r="B800" s="7"/>
+      <c r="E800" s="7"/>
+    </row>
+    <row r="801">
+      <c r="B801" s="7"/>
+      <c r="E801" s="7"/>
+    </row>
+    <row r="802">
+      <c r="B802" s="7"/>
+      <c r="E802" s="7"/>
+    </row>
+    <row r="803">
+      <c r="B803" s="7"/>
+      <c r="E803" s="7"/>
+    </row>
+    <row r="804">
+      <c r="B804" s="7"/>
+      <c r="E804" s="7"/>
+    </row>
+    <row r="805">
+      <c r="B805" s="7"/>
+      <c r="E805" s="7"/>
+    </row>
+    <row r="806">
+      <c r="B806" s="7"/>
+      <c r="E806" s="7"/>
+    </row>
+    <row r="807">
+      <c r="B807" s="7"/>
+      <c r="E807" s="7"/>
+    </row>
+    <row r="808">
+      <c r="B808" s="7"/>
+      <c r="E808" s="7"/>
+    </row>
+    <row r="809">
+      <c r="B809" s="7"/>
+      <c r="E809" s="7"/>
+    </row>
+    <row r="810">
+      <c r="B810" s="7"/>
+      <c r="E810" s="7"/>
+    </row>
+    <row r="811">
+      <c r="B811" s="7"/>
+      <c r="E811" s="7"/>
+    </row>
+    <row r="812">
+      <c r="B812" s="7"/>
+      <c r="E812" s="7"/>
+    </row>
+    <row r="813">
+      <c r="B813" s="7"/>
+      <c r="E813" s="7"/>
+    </row>
+    <row r="814">
+      <c r="B814" s="7"/>
+      <c r="E814" s="7"/>
+    </row>
+    <row r="815">
+      <c r="B815" s="7"/>
+      <c r="E815" s="7"/>
+    </row>
+    <row r="816">
+      <c r="B816" s="7"/>
+      <c r="E816" s="7"/>
+    </row>
+    <row r="817">
+      <c r="B817" s="7"/>
+      <c r="E817" s="7"/>
+    </row>
+    <row r="818">
+      <c r="B818" s="7"/>
+      <c r="E818" s="7"/>
+    </row>
+    <row r="819">
+      <c r="B819" s="7"/>
+      <c r="E819" s="7"/>
+    </row>
+    <row r="820">
+      <c r="B820" s="7"/>
+      <c r="E820" s="7"/>
+    </row>
+    <row r="821">
+      <c r="B821" s="7"/>
+      <c r="E821" s="7"/>
+    </row>
+    <row r="822">
+      <c r="B822" s="7"/>
+      <c r="E822" s="7"/>
+    </row>
+    <row r="823">
+      <c r="B823" s="7"/>
+      <c r="E823" s="7"/>
+    </row>
+    <row r="824">
+      <c r="B824" s="7"/>
+      <c r="E824" s="7"/>
+    </row>
+    <row r="825">
+      <c r="B825" s="7"/>
+      <c r="E825" s="7"/>
+    </row>
+    <row r="826">
+      <c r="B826" s="7"/>
+      <c r="E826" s="7"/>
+    </row>
+    <row r="827">
+      <c r="B827" s="7"/>
+      <c r="E827" s="7"/>
+    </row>
+    <row r="828">
+      <c r="B828" s="7"/>
+      <c r="E828" s="7"/>
+    </row>
+    <row r="829">
+      <c r="B829" s="7"/>
+      <c r="E829" s="7"/>
+    </row>
+    <row r="830">
+      <c r="B830" s="7"/>
+      <c r="E830" s="7"/>
+    </row>
+    <row r="831">
+      <c r="B831" s="7"/>
+      <c r="E831" s="7"/>
+    </row>
+    <row r="832">
+      <c r="B832" s="7"/>
+      <c r="E832" s="7"/>
+    </row>
+    <row r="833">
+      <c r="B833" s="7"/>
+      <c r="E833" s="7"/>
+    </row>
+    <row r="834">
+      <c r="B834" s="7"/>
+      <c r="E834" s="7"/>
+    </row>
+    <row r="835">
+      <c r="B835" s="7"/>
+      <c r="E835" s="7"/>
+    </row>
+    <row r="836">
+      <c r="B836" s="7"/>
+      <c r="E836" s="7"/>
+    </row>
+    <row r="837">
+      <c r="B837" s="7"/>
+      <c r="E837" s="7"/>
+    </row>
+    <row r="838">
+      <c r="B838" s="7"/>
+      <c r="E838" s="7"/>
+    </row>
+    <row r="839">
+      <c r="B839" s="7"/>
+      <c r="E839" s="7"/>
+    </row>
+    <row r="840">
+      <c r="B840" s="7"/>
+      <c r="E840" s="7"/>
+    </row>
+    <row r="841">
+      <c r="B841" s="7"/>
+      <c r="E841" s="7"/>
+    </row>
+    <row r="842">
+      <c r="B842" s="7"/>
+      <c r="E842" s="7"/>
+    </row>
+    <row r="843">
+      <c r="B843" s="7"/>
+      <c r="E843" s="7"/>
+    </row>
+    <row r="844">
+      <c r="B844" s="7"/>
+      <c r="E844" s="7"/>
+    </row>
+    <row r="845">
+      <c r="B845" s="7"/>
+      <c r="E845" s="7"/>
+    </row>
+    <row r="846">
+      <c r="B846" s="7"/>
+      <c r="E846" s="7"/>
+    </row>
+    <row r="847">
+      <c r="B847" s="7"/>
+      <c r="E847" s="7"/>
+    </row>
+    <row r="848">
+      <c r="B848" s="7"/>
+      <c r="E848" s="7"/>
+    </row>
+    <row r="849">
+      <c r="B849" s="7"/>
+      <c r="E849" s="7"/>
+    </row>
+    <row r="850">
+      <c r="B850" s="7"/>
+      <c r="E850" s="7"/>
+    </row>
+    <row r="851">
+      <c r="B851" s="7"/>
+      <c r="E851" s="7"/>
+    </row>
+    <row r="852">
+      <c r="B852" s="7"/>
+      <c r="E852" s="7"/>
+    </row>
+    <row r="853">
+      <c r="B853" s="7"/>
+      <c r="E853" s="7"/>
+    </row>
+    <row r="854">
+      <c r="B854" s="7"/>
+      <c r="E854" s="7"/>
+    </row>
+    <row r="855">
+      <c r="B855" s="7"/>
+      <c r="E855" s="7"/>
+    </row>
+    <row r="856">
+      <c r="B856" s="7"/>
+      <c r="E856" s="7"/>
+    </row>
+    <row r="857">
+      <c r="B857" s="7"/>
+      <c r="E857" s="7"/>
+    </row>
+    <row r="858">
+      <c r="B858" s="7"/>
+      <c r="E858" s="7"/>
+    </row>
+    <row r="859">
+      <c r="B859" s="7"/>
+      <c r="E859" s="7"/>
+    </row>
+    <row r="860">
+      <c r="B860" s="7"/>
+      <c r="E860" s="7"/>
+    </row>
+    <row r="861">
+      <c r="B861" s="7"/>
+      <c r="E861" s="7"/>
+    </row>
+    <row r="862">
+      <c r="B862" s="7"/>
+      <c r="E862" s="7"/>
+    </row>
+    <row r="863">
+      <c r="B863" s="7"/>
+      <c r="E863" s="7"/>
+    </row>
+    <row r="864">
+      <c r="B864" s="7"/>
+      <c r="E864" s="7"/>
+    </row>
+    <row r="865">
+      <c r="B865" s="7"/>
+      <c r="E865" s="7"/>
+    </row>
+    <row r="866">
+      <c r="B866" s="7"/>
+      <c r="E866" s="7"/>
+    </row>
+    <row r="867">
+      <c r="B867" s="7"/>
+      <c r="E867" s="7"/>
+    </row>
+    <row r="868">
+      <c r="B868" s="7"/>
+      <c r="E868" s="7"/>
+    </row>
+    <row r="869">
+      <c r="B869" s="7"/>
+      <c r="E869" s="7"/>
+    </row>
+    <row r="870">
+      <c r="B870" s="7"/>
+      <c r="E870" s="7"/>
+    </row>
+    <row r="871">
+      <c r="B871" s="7"/>
+      <c r="E871" s="7"/>
+    </row>
+    <row r="872">
+      <c r="B872" s="7"/>
+      <c r="E872" s="7"/>
+    </row>
+    <row r="873">
+      <c r="B873" s="7"/>
+      <c r="E873" s="7"/>
+    </row>
+    <row r="874">
+      <c r="B874" s="7"/>
+      <c r="E874" s="7"/>
+    </row>
+    <row r="875">
+      <c r="B875" s="7"/>
+      <c r="E875" s="7"/>
+    </row>
+    <row r="876">
+      <c r="B876" s="7"/>
+      <c r="E876" s="7"/>
+    </row>
+    <row r="877">
+      <c r="B877" s="7"/>
+      <c r="E877" s="7"/>
+    </row>
+    <row r="878">
+      <c r="B878" s="7"/>
+      <c r="E878" s="7"/>
+    </row>
+    <row r="879">
+      <c r="B879" s="7"/>
+      <c r="E879" s="7"/>
+    </row>
+    <row r="880">
+      <c r="B880" s="7"/>
+      <c r="E880" s="7"/>
+    </row>
+    <row r="881">
+      <c r="B881" s="7"/>
+      <c r="E881" s="7"/>
+    </row>
+    <row r="882">
+      <c r="B882" s="7"/>
+      <c r="E882" s="7"/>
+    </row>
+    <row r="883">
+      <c r="B883" s="7"/>
+      <c r="E883" s="7"/>
+    </row>
+    <row r="884">
+      <c r="B884" s="7"/>
+      <c r="E884" s="7"/>
+    </row>
+    <row r="885">
+      <c r="B885" s="7"/>
+      <c r="E885" s="7"/>
+    </row>
+    <row r="886">
+      <c r="B886" s="7"/>
+      <c r="E886" s="7"/>
+    </row>
+    <row r="887">
+      <c r="B887" s="7"/>
+      <c r="E887" s="7"/>
+    </row>
+    <row r="888">
+      <c r="B888" s="7"/>
+      <c r="E888" s="7"/>
+    </row>
+    <row r="889">
+      <c r="B889" s="7"/>
+      <c r="E889" s="7"/>
+    </row>
+    <row r="890">
+      <c r="B890" s="7"/>
+      <c r="E890" s="7"/>
+    </row>
+    <row r="891">
+      <c r="B891" s="7"/>
+      <c r="E891" s="7"/>
+    </row>
+    <row r="892">
+      <c r="B892" s="7"/>
+      <c r="E892" s="7"/>
+    </row>
+    <row r="893">
+      <c r="B893" s="7"/>
+      <c r="E893" s="7"/>
+    </row>
+    <row r="894">
+      <c r="B894" s="7"/>
+      <c r="E894" s="7"/>
+    </row>
+    <row r="895">
+      <c r="B895" s="7"/>
+      <c r="E895" s="7"/>
+    </row>
+    <row r="896">
+      <c r="B896" s="7"/>
+      <c r="E896" s="7"/>
+    </row>
+    <row r="897">
+      <c r="B897" s="7"/>
+      <c r="E897" s="7"/>
+    </row>
+    <row r="898">
+      <c r="B898" s="7"/>
+      <c r="E898" s="7"/>
+    </row>
+    <row r="899">
+      <c r="B899" s="7"/>
+      <c r="E899" s="7"/>
+    </row>
+    <row r="900">
+      <c r="B900" s="7"/>
+      <c r="E900" s="7"/>
+    </row>
+    <row r="901">
+      <c r="B901" s="7"/>
+      <c r="E901" s="7"/>
+    </row>
+    <row r="902">
+      <c r="B902" s="7"/>
+      <c r="E902" s="7"/>
+    </row>
+    <row r="903">
+      <c r="B903" s="7"/>
+      <c r="E903" s="7"/>
+    </row>
+    <row r="904">
+      <c r="B904" s="7"/>
+      <c r="E904" s="7"/>
+    </row>
+    <row r="905">
+      <c r="B905" s="7"/>
+      <c r="E905" s="7"/>
+    </row>
+    <row r="906">
+      <c r="B906" s="7"/>
+      <c r="E906" s="7"/>
+    </row>
+    <row r="907">
+      <c r="B907" s="7"/>
+      <c r="E907" s="7"/>
+    </row>
+    <row r="908">
+      <c r="B908" s="7"/>
+      <c r="E908" s="7"/>
+    </row>
+    <row r="909">
+      <c r="B909" s="7"/>
+      <c r="E909" s="7"/>
+    </row>
+    <row r="910">
+      <c r="B910" s="7"/>
+      <c r="E910" s="7"/>
+    </row>
+    <row r="911">
+      <c r="B911" s="7"/>
+      <c r="E911" s="7"/>
+    </row>
+    <row r="912">
+      <c r="B912" s="7"/>
+      <c r="E912" s="7"/>
+    </row>
+    <row r="913">
+      <c r="B913" s="7"/>
+      <c r="E913" s="7"/>
+    </row>
+    <row r="914">
+      <c r="B914" s="7"/>
+      <c r="E914" s="7"/>
+    </row>
+    <row r="915">
+      <c r="B915" s="7"/>
+      <c r="E915" s="7"/>
+    </row>
+    <row r="916">
+      <c r="B916" s="7"/>
+      <c r="E916" s="7"/>
+    </row>
+    <row r="917">
+      <c r="B917" s="7"/>
+      <c r="E917" s="7"/>
+    </row>
+    <row r="918">
+      <c r="B918" s="7"/>
+      <c r="E918" s="7"/>
+    </row>
+    <row r="919">
+      <c r="B919" s="7"/>
+      <c r="E919" s="7"/>
+    </row>
+    <row r="920">
+      <c r="B920" s="7"/>
+      <c r="E920" s="7"/>
+    </row>
+    <row r="921">
+      <c r="B921" s="7"/>
+      <c r="E921" s="7"/>
+    </row>
+    <row r="922">
+      <c r="B922" s="7"/>
+      <c r="E922" s="7"/>
+    </row>
+    <row r="923">
+      <c r="B923" s="7"/>
+      <c r="E923" s="7"/>
+    </row>
+    <row r="924">
+      <c r="B924" s="7"/>
+      <c r="E924" s="7"/>
+    </row>
+    <row r="925">
+      <c r="B925" s="7"/>
+      <c r="E925" s="7"/>
+    </row>
+    <row r="926">
+      <c r="B926" s="7"/>
+      <c r="E926" s="7"/>
+    </row>
+    <row r="927">
+      <c r="B927" s="7"/>
+      <c r="E927" s="7"/>
+    </row>
+    <row r="928">
+      <c r="B928" s="7"/>
+      <c r="E928" s="7"/>
+    </row>
+    <row r="929">
+      <c r="B929" s="7"/>
+      <c r="E929" s="7"/>
+    </row>
+    <row r="930">
+      <c r="B930" s="7"/>
+      <c r="E930" s="7"/>
+    </row>
+    <row r="931">
+      <c r="B931" s="7"/>
+      <c r="E931" s="7"/>
+    </row>
+    <row r="932">
+      <c r="B932" s="7"/>
+      <c r="E932" s="7"/>
+    </row>
+    <row r="933">
+      <c r="B933" s="7"/>
+      <c r="E933" s="7"/>
+    </row>
+    <row r="934">
+      <c r="B934" s="7"/>
+      <c r="E934" s="7"/>
+    </row>
+    <row r="935">
+      <c r="B935" s="7"/>
+      <c r="E935" s="7"/>
+    </row>
+    <row r="936">
+      <c r="B936" s="7"/>
+      <c r="E936" s="7"/>
+    </row>
+    <row r="937">
+      <c r="B937" s="7"/>
+      <c r="E937" s="7"/>
+    </row>
+    <row r="938">
+      <c r="B938" s="7"/>
+      <c r="E938" s="7"/>
+    </row>
+    <row r="939">
+      <c r="B939" s="7"/>
+      <c r="E939" s="7"/>
+    </row>
+    <row r="940">
+      <c r="B940" s="7"/>
+      <c r="E940" s="7"/>
+    </row>
+    <row r="941">
+      <c r="B941" s="7"/>
+      <c r="E941" s="7"/>
+    </row>
+    <row r="942">
+      <c r="B942" s="7"/>
+      <c r="E942" s="7"/>
+    </row>
+    <row r="943">
+      <c r="B943" s="7"/>
+      <c r="E943" s="7"/>
+    </row>
+    <row r="944">
+      <c r="B944" s="7"/>
+      <c r="E944" s="7"/>
+    </row>
+    <row r="945">
+      <c r="B945" s="7"/>
+      <c r="E945" s="7"/>
+    </row>
+    <row r="946">
+      <c r="B946" s="7"/>
+      <c r="E946" s="7"/>
+    </row>
+    <row r="947">
+      <c r="B947" s="7"/>
+      <c r="E947" s="7"/>
+    </row>
+    <row r="948">
+      <c r="B948" s="7"/>
+      <c r="E948" s="7"/>
+    </row>
+    <row r="949">
+      <c r="B949" s="7"/>
+      <c r="E949" s="7"/>
+    </row>
+    <row r="950">
+      <c r="B950" s="7"/>
+      <c r="E950" s="7"/>
+    </row>
+    <row r="951">
+      <c r="B951" s="7"/>
+      <c r="E951" s="7"/>
+    </row>
+    <row r="952">
+      <c r="B952" s="7"/>
+      <c r="E952" s="7"/>
+    </row>
+    <row r="953">
+      <c r="B953" s="7"/>
+      <c r="E953" s="7"/>
+    </row>
+    <row r="954">
+      <c r="B954" s="7"/>
+      <c r="E954" s="7"/>
+    </row>
+    <row r="955">
+      <c r="B955" s="7"/>
+      <c r="E955" s="7"/>
+    </row>
+    <row r="956">
+      <c r="B956" s="7"/>
+      <c r="E956" s="7"/>
+    </row>
+    <row r="957">
+      <c r="B957" s="7"/>
+      <c r="E957" s="7"/>
+    </row>
+    <row r="958">
+      <c r="B958" s="7"/>
+      <c r="E958" s="7"/>
+    </row>
+    <row r="959">
+      <c r="B959" s="7"/>
+      <c r="E959" s="7"/>
+    </row>
+    <row r="960">
+      <c r="B960" s="7"/>
+      <c r="E960" s="7"/>
+    </row>
+    <row r="961">
+      <c r="B961" s="7"/>
+      <c r="E961" s="7"/>
+    </row>
+    <row r="962">
+      <c r="B962" s="7"/>
+      <c r="E962" s="7"/>
+    </row>
+    <row r="963">
+      <c r="B963" s="7"/>
+      <c r="E963" s="7"/>
+    </row>
+    <row r="964">
+      <c r="B964" s="7"/>
+      <c r="E964" s="7"/>
+    </row>
+    <row r="965">
+      <c r="B965" s="7"/>
+      <c r="E965" s="7"/>
+    </row>
+    <row r="966">
+      <c r="B966" s="7"/>
+      <c r="E966" s="7"/>
+    </row>
+    <row r="967">
+      <c r="B967" s="7"/>
+      <c r="E967" s="7"/>
+    </row>
+    <row r="968">
+      <c r="B968" s="7"/>
+      <c r="E968" s="7"/>
+    </row>
+    <row r="969">
+      <c r="B969" s="7"/>
+      <c r="E969" s="7"/>
+    </row>
+    <row r="970">
+      <c r="B970" s="7"/>
+      <c r="E970" s="7"/>
+    </row>
+    <row r="971">
+      <c r="B971" s="7"/>
+      <c r="E971" s="7"/>
+    </row>
+    <row r="972">
+      <c r="B972" s="7"/>
+      <c r="E972" s="7"/>
+    </row>
+    <row r="973">
+      <c r="B973" s="7"/>
+      <c r="E973" s="7"/>
+    </row>
+    <row r="974">
+      <c r="B974" s="7"/>
+      <c r="E974" s="7"/>
+    </row>
+    <row r="975">
+      <c r="B975" s="7"/>
+      <c r="E975" s="7"/>
+    </row>
+    <row r="976">
+      <c r="B976" s="7"/>
+      <c r="E976" s="7"/>
+    </row>
+    <row r="977">
+      <c r="B977" s="7"/>
+      <c r="E977" s="7"/>
+    </row>
+    <row r="978">
+      <c r="B978" s="7"/>
+      <c r="E978" s="7"/>
+    </row>
+    <row r="979">
+      <c r="B979" s="7"/>
+      <c r="E979" s="7"/>
+    </row>
+    <row r="980">
+      <c r="B980" s="7"/>
+      <c r="E980" s="7"/>
+    </row>
+    <row r="981">
+      <c r="B981" s="7"/>
+      <c r="E981" s="7"/>
+    </row>
+    <row r="982">
+      <c r="B982" s="7"/>
+      <c r="E982" s="7"/>
+    </row>
+    <row r="983">
+      <c r="B983" s="7"/>
+      <c r="E983" s="7"/>
+    </row>
+    <row r="984">
+      <c r="B984" s="7"/>
+      <c r="E984" s="7"/>
+    </row>
+    <row r="985">
+      <c r="B985" s="7"/>
+      <c r="E985" s="7"/>
+    </row>
+    <row r="986">
+      <c r="B986" s="7"/>
+      <c r="E986" s="7"/>
+    </row>
+    <row r="987">
+      <c r="B987" s="7"/>
+      <c r="E987" s="7"/>
+    </row>
+    <row r="988">
+      <c r="B988" s="7"/>
+      <c r="E988" s="7"/>
+    </row>
+    <row r="989">
+      <c r="B989" s="7"/>
+      <c r="E989" s="7"/>
+    </row>
+    <row r="990">
+      <c r="B990" s="7"/>
+      <c r="E990" s="7"/>
+    </row>
+    <row r="991">
+      <c r="B991" s="7"/>
+      <c r="E991" s="7"/>
+    </row>
+    <row r="992">
+      <c r="B992" s="7"/>
+      <c r="E992" s="7"/>
+    </row>
+    <row r="993">
+      <c r="B993" s="7"/>
+      <c r="E993" s="7"/>
+    </row>
+    <row r="994">
+      <c r="B994" s="7"/>
+      <c r="E994" s="7"/>
+    </row>
+    <row r="995">
+      <c r="B995" s="7"/>
+      <c r="E995" s="7"/>
+    </row>
+    <row r="996">
+      <c r="B996" s="7"/>
+      <c r="E996" s="7"/>
+    </row>
+    <row r="997">
+      <c r="B997" s="7"/>
+      <c r="E997" s="7"/>
+    </row>
+    <row r="998">
+      <c r="B998" s="7"/>
+      <c r="E998" s="7"/>
+    </row>
+    <row r="999">
+      <c r="B999" s="7"/>
+      <c r="E999" s="7"/>
+    </row>
+    <row r="1000">
+      <c r="B1000" s="7"/>
+      <c r="E1000" s="7"/>
+    </row>
+  </sheetData>
+  <dataValidations>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B19">
+      <formula1>"鎳系,輕系,各系,氰系,鉻系,通用"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B20:B1000">
+      <formula1>"鎳系,輕系,各系,氰系,鉻系,通用"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showDropDown="1" showErrorMessage="1" sqref="M2:M19">
+      <formula1>"D-1101 有害,,D-2299"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E19">
+      <formula1>"應加,禁加,可加"</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showDropDown="1" sqref="F2:K19">
+      <formula1>AND(ISNUMBER(F2),(NOT(OR(NOT(ISERROR(DATEVALUE(F2))), AND(ISNUMBER(F2), LEFT(CELL("format", F2))="D")))))</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E20:E1000">
+      <formula1>"應加,禁加,可加"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId3"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="2" max="2" width="16.25"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22.5" customHeight="1">
+      <c r="A1" s="14" t="s">
+        <v>2117</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>2118</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>2119</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="2" ht="22.5" customHeight="1">
+      <c r="A2" s="15" t="s">
+        <v>2120</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>2121</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>2122</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" ht="22.5" customHeight="1">
+      <c r="A3" s="15" t="s">
+        <v>2123</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>2124</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>2122</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" ht="22.5" customHeight="1">
+      <c r="A4" s="15" t="s">
+        <v>2125</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>2126</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>2122</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" ht="22.5" customHeight="1">
+      <c r="A5" s="15" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>2128</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>2122</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" ht="22.5" customHeight="1">
+      <c r="A6" s="15" t="s">
+        <v>2129</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>2130</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>2122</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" ht="22.5" customHeight="1">
+      <c r="A7" s="15" t="s">
+        <v>2131</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>2132</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>2122</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" ht="22.5" customHeight="1">
+      <c r="A8" s="15" t="s">
+        <v>2133</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>2134</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>2122</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" ht="22.5" customHeight="1">
+      <c r="A9" s="15" t="s">
+        <v>2135</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>2136</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>2122</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" ht="22.5" customHeight="1">
+      <c r="A10" s="15" t="s">
+        <v>2137</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>2138</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>2122</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" ht="22.5" customHeight="1">
+      <c r="A11" s="15" t="s">
+        <v>2139</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>2140</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>2122</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" ht="22.5" customHeight="1">
+      <c r="A12" s="15" t="s">
+        <v>2141</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>2142</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>2122</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" ht="22.5" customHeight="1">
+      <c r="A13" s="15" t="s">
+        <v>2143</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>2144</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>2122</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" ht="22.5" customHeight="1">
+      <c r="A14" s="15" t="s">
+        <v>2145</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>2146</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>2122</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" ht="22.5" customHeight="1">
+      <c r="A15" s="15" t="s">
+        <v>2147</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>2148</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>2122</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" ht="22.5" customHeight="1">
+      <c r="A16" s="15" t="s">
+        <v>2149</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>2150</v>
+      </c>
+      <c r="C16" s="12" t="s">
+        <v>2122</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" ht="22.5" customHeight="1">
+      <c r="A17" s="15" t="s">
+        <v>2151</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>2152</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>2122</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" ht="22.5" customHeight="1">
+      <c r="A18" s="15" t="s">
+        <v>2153</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>2154</v>
+      </c>
+      <c r="C18" s="12" t="s">
+        <v>2122</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" ht="22.5" customHeight="1">
+      <c r="A19" s="15" t="s">
+        <v>2155</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>2156</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>2122</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" ht="22.5" customHeight="1">
+      <c r="A20" s="15" t="s">
+        <v>2157</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>2158</v>
+      </c>
+      <c r="C20" s="12" t="s">
+        <v>2122</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" ht="22.5" customHeight="1">
+      <c r="A21" s="15" t="s">
+        <v>2159</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>2160</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>2122</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" ht="22.5" customHeight="1">
+      <c r="A22" s="15" t="s">
+        <v>2161</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>2162</v>
+      </c>
+      <c r="C22" s="12" t="s">
+        <v>2122</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" ht="22.5" customHeight="1">
+      <c r="A23" s="15" t="s">
+        <v>2163</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>2164</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>2122</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" ht="22.5" customHeight="1">
+      <c r="A24" s="15" t="s">
+        <v>2165</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>2166</v>
+      </c>
+      <c r="C24" s="12" t="s">
+        <v>2122</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" ht="22.5" customHeight="1">
+      <c r="A25" s="15" t="s">
+        <v>2167</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>2168</v>
+      </c>
+      <c r="C25" s="12" t="s">
+        <v>2122</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" ht="22.5" customHeight="1">
+      <c r="A26" s="15" t="s">
+        <v>2169</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>2170</v>
+      </c>
+      <c r="C26" s="12" t="s">
+        <v>2122</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" ht="22.5" customHeight="1">
+      <c r="A27" s="15" t="s">
+        <v>2171</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>2172</v>
+      </c>
+      <c r="C27" s="12" t="s">
+        <v>2122</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" ht="22.5" customHeight="1">
+      <c r="A28" s="15" t="s">
+        <v>2173</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>2174</v>
+      </c>
+      <c r="C28" s="12" t="s">
+        <v>2122</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" ht="22.5" customHeight="1">
+      <c r="A29" s="15" t="s">
+        <v>2175</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>2176</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>2122</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" ht="22.5" customHeight="1">
+      <c r="A30" s="15" t="s">
+        <v>2177</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>2178</v>
+      </c>
+      <c r="C30" s="12" t="s">
+        <v>2122</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" ht="22.5" customHeight="1">
+      <c r="A31" s="15" t="s">
+        <v>2179</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>2180</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" ht="22.5" customHeight="1">
+      <c r="A32" s="15" t="s">
+        <v>2182</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>2183</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" ht="22.5" customHeight="1">
+      <c r="A33" s="15" t="s">
+        <v>2184</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>2185</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" ht="22.5" customHeight="1">
+      <c r="A34" s="15" t="s">
+        <v>2186</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>2187</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" ht="22.5" customHeight="1">
+      <c r="A35" s="15" t="s">
+        <v>2188</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>2189</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" ht="22.5" customHeight="1">
+      <c r="A36" s="15" t="s">
+        <v>2190</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>2191</v>
+      </c>
+      <c r="C36" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" ht="22.5" customHeight="1">
+      <c r="A37" s="15" t="s">
+        <v>2192</v>
+      </c>
+      <c r="B37" s="11" t="s">
+        <v>2193</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" ht="22.5" customHeight="1">
+      <c r="A38" s="15" t="s">
+        <v>2194</v>
+      </c>
+      <c r="B38" s="11" t="s">
+        <v>2195</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" ht="22.5" customHeight="1">
+      <c r="A39" s="15" t="s">
+        <v>2196</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>2197</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" ht="22.5" customHeight="1">
+      <c r="A40" s="15" t="s">
+        <v>2198</v>
+      </c>
+      <c r="B40" s="11" t="s">
+        <v>2199</v>
+      </c>
+      <c r="C40" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" ht="22.5" customHeight="1">
+      <c r="A41" s="15" t="s">
+        <v>2200</v>
+      </c>
+      <c r="B41" s="11" t="s">
+        <v>2201</v>
+      </c>
+      <c r="C41" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="D41" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" ht="22.5" customHeight="1">
+      <c r="A42" s="15" t="s">
+        <v>2202</v>
+      </c>
+      <c r="B42" s="11" t="s">
+        <v>2203</v>
+      </c>
+      <c r="C42" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="D42" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" ht="22.5" customHeight="1">
+      <c r="A43" s="15" t="s">
+        <v>2204</v>
+      </c>
+      <c r="B43" s="11" t="s">
+        <v>2205</v>
+      </c>
+      <c r="C43" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="D43" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" ht="22.5" customHeight="1">
+      <c r="A44" s="15" t="s">
+        <v>2206</v>
+      </c>
+      <c r="B44" s="11" t="s">
+        <v>2207</v>
+      </c>
+      <c r="C44" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="D44" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" ht="22.5" customHeight="1">
+      <c r="A45" s="15" t="s">
+        <v>2208</v>
+      </c>
+      <c r="B45" s="11" t="s">
+        <v>2209</v>
+      </c>
+      <c r="C45" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="D45" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" ht="22.5" customHeight="1">
+      <c r="A46" s="15" t="s">
+        <v>2210</v>
+      </c>
+      <c r="B46" s="11" t="s">
+        <v>2211</v>
+      </c>
+      <c r="C46" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="D46" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" ht="22.5" customHeight="1">
+      <c r="A47" s="15" t="s">
+        <v>2212</v>
+      </c>
+      <c r="B47" s="11" t="s">
+        <v>2213</v>
+      </c>
+      <c r="C47" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="D47" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" ht="22.5" customHeight="1">
+      <c r="A48" s="15" t="s">
+        <v>2214</v>
+      </c>
+      <c r="B48" s="11" t="s">
+        <v>2215</v>
+      </c>
+      <c r="C48" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="D48" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" ht="22.5" customHeight="1">
+      <c r="A49" s="15" t="s">
+        <v>2216</v>
+      </c>
+      <c r="B49" s="11" t="s">
+        <v>2217</v>
+      </c>
+      <c r="C49" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="D49" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" ht="22.5" customHeight="1">
+      <c r="A50" s="15" t="s">
+        <v>2218</v>
+      </c>
+      <c r="B50" s="11" t="s">
+        <v>2219</v>
+      </c>
+      <c r="C50" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="D50" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" ht="22.5" customHeight="1">
+      <c r="A51" s="15" t="s">
+        <v>2220</v>
+      </c>
+      <c r="B51" s="11" t="s">
+        <v>2221</v>
+      </c>
+      <c r="C51" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="D51" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" ht="22.5" customHeight="1">
+      <c r="A52" s="15" t="s">
+        <v>2222</v>
+      </c>
+      <c r="B52" s="11" t="s">
+        <v>2223</v>
+      </c>
+      <c r="C52" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="D52" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" ht="22.5" customHeight="1">
+      <c r="A53" s="15" t="s">
+        <v>2224</v>
+      </c>
+      <c r="B53" s="11" t="s">
+        <v>2225</v>
+      </c>
+      <c r="C53" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="D53" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" ht="22.5" customHeight="1">
+      <c r="A54" s="15" t="s">
+        <v>2226</v>
+      </c>
+      <c r="B54" s="11" t="s">
+        <v>2227</v>
+      </c>
+      <c r="C54" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="D54" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" ht="22.5" customHeight="1">
+      <c r="A55" s="15" t="s">
+        <v>2228</v>
+      </c>
+      <c r="B55" s="11" t="s">
+        <v>2229</v>
+      </c>
+      <c r="C55" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="D55" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" ht="22.5" customHeight="1">
+      <c r="A56" s="15" t="s">
+        <v>2230</v>
+      </c>
+      <c r="B56" s="11" t="s">
+        <v>2231</v>
+      </c>
+      <c r="C56" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="D56" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" ht="22.5" customHeight="1">
+      <c r="A57" s="15" t="s">
+        <v>2232</v>
+      </c>
+      <c r="B57" s="11" t="s">
+        <v>2233</v>
+      </c>
+      <c r="C57" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="D57" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" ht="22.5" customHeight="1">
+      <c r="A58" s="15" t="s">
+        <v>2234</v>
+      </c>
+      <c r="B58" s="11" t="s">
+        <v>2235</v>
+      </c>
+      <c r="C58" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="D58" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" ht="22.5" customHeight="1">
+      <c r="A59" s="15" t="s">
+        <v>2236</v>
+      </c>
+      <c r="B59" s="11" t="s">
+        <v>2237</v>
+      </c>
+      <c r="C59" s="12" t="s">
+        <v>2238</v>
+      </c>
+      <c r="D59" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" ht="22.5" customHeight="1">
+      <c r="A60" s="15" t="s">
+        <v>2239</v>
+      </c>
+      <c r="B60" s="11" t="s">
+        <v>2240</v>
+      </c>
+      <c r="C60" s="12" t="s">
+        <v>2238</v>
+      </c>
+      <c r="D60" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" ht="22.5" customHeight="1">
+      <c r="A61" s="15" t="s">
+        <v>2241</v>
+      </c>
+      <c r="B61" s="11" t="s">
+        <v>2242</v>
+      </c>
+      <c r="C61" s="12" t="s">
+        <v>2243</v>
+      </c>
+      <c r="D61" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" ht="22.5" customHeight="1">
+      <c r="A62" s="15" t="s">
+        <v>2244</v>
+      </c>
+      <c r="B62" s="11" t="s">
+        <v>2245</v>
+      </c>
+      <c r="C62" s="12" t="s">
+        <v>2238</v>
+      </c>
+      <c r="D62" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" ht="22.5" customHeight="1">
+      <c r="A63" s="15" t="s">
+        <v>2246</v>
+      </c>
+      <c r="B63" s="11" t="s">
+        <v>2247</v>
+      </c>
+      <c r="C63" s="12" t="s">
+        <v>2243</v>
+      </c>
+      <c r="D63" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" ht="22.5" customHeight="1">
+      <c r="A64" s="15" t="s">
+        <v>2248</v>
+      </c>
+      <c r="B64" s="11" t="s">
+        <v>2249</v>
+      </c>
+      <c r="C64" s="12" t="s">
+        <v>2250</v>
+      </c>
+      <c r="D64" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" ht="22.5" customHeight="1">
+      <c r="A65" s="15" t="s">
+        <v>2251</v>
+      </c>
+      <c r="B65" s="11" t="s">
+        <v>2252</v>
+      </c>
+      <c r="C65" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="D65" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" ht="22.5" customHeight="1">
+      <c r="A66" s="15" t="s">
+        <v>2253</v>
+      </c>
+      <c r="B66" s="11" t="s">
+        <v>2254</v>
+      </c>
+      <c r="C66" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="D66" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" ht="22.5" customHeight="1">
+      <c r="A67" s="15" t="s">
+        <v>2255</v>
+      </c>
+      <c r="B67" s="11" t="s">
+        <v>2256</v>
+      </c>
+      <c r="C67" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="D67" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" ht="22.5" customHeight="1">
+      <c r="A68" s="15" t="s">
+        <v>2257</v>
+      </c>
+      <c r="B68" s="11" t="s">
+        <v>2258</v>
+      </c>
+      <c r="C68" s="12" t="s">
+        <v>2238</v>
+      </c>
+      <c r="D68" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" ht="22.5" customHeight="1">
+      <c r="A69" s="15" t="s">
+        <v>2259</v>
+      </c>
+      <c r="B69" s="11" t="s">
+        <v>2260</v>
+      </c>
+      <c r="C69" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="D69" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" ht="22.5" customHeight="1">
+      <c r="A70" s="15" t="s">
+        <v>2261</v>
+      </c>
+      <c r="B70" s="11" t="s">
+        <v>2262</v>
+      </c>
+      <c r="C70" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="D70" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" ht="22.5" customHeight="1">
+      <c r="A71" s="15" t="s">
+        <v>2263</v>
+      </c>
+      <c r="B71" s="11" t="s">
+        <v>2264</v>
+      </c>
+      <c r="C71" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="D71" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" ht="22.5" customHeight="1">
+      <c r="A72" s="15" t="s">
+        <v>2265</v>
+      </c>
+      <c r="B72" s="11" t="s">
+        <v>2266</v>
+      </c>
+      <c r="C72" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="D72" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" ht="22.5" customHeight="1">
+      <c r="A73" s="15" t="s">
+        <v>2267</v>
+      </c>
+      <c r="B73" s="11" t="s">
+        <v>2268</v>
+      </c>
+      <c r="C73" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="D73" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" ht="22.5" customHeight="1">
+      <c r="A74" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="B74" s="11" t="s">
+        <v>2269</v>
+      </c>
+      <c r="C74" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="D74" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" ht="22.5" customHeight="1">
+      <c r="A75" s="15" t="s">
+        <v>2270</v>
+      </c>
+      <c r="B75" s="11" t="s">
+        <v>2271</v>
+      </c>
+      <c r="C75" s="12" t="s">
+        <v>2272</v>
+      </c>
+      <c r="D75" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" ht="22.5" customHeight="1">
+      <c r="A76" s="15" t="s">
+        <v>2273</v>
+      </c>
+      <c r="B76" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C76" s="12" t="s">
+        <v>2272</v>
+      </c>
+      <c r="D76" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" ht="22.5" customHeight="1">
+      <c r="A77" s="15" t="s">
+        <v>2274</v>
+      </c>
+      <c r="B77" s="11" t="s">
+        <v>2275</v>
+      </c>
+      <c r="C77" s="12" t="s">
+        <v>2272</v>
+      </c>
+      <c r="D77" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" ht="22.5" customHeight="1">
+      <c r="A78" s="15" t="s">
+        <v>2276</v>
+      </c>
+      <c r="B78" s="11" t="s">
+        <v>2277</v>
+      </c>
+      <c r="C78" s="12" t="s">
+        <v>2272</v>
+      </c>
+      <c r="D78" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" ht="22.5" customHeight="1">
+      <c r="A79" s="15" t="s">
+        <v>2278</v>
+      </c>
+      <c r="B79" s="11" t="s">
+        <v>2279</v>
+      </c>
+      <c r="C79" s="12" t="s">
+        <v>2272</v>
+      </c>
+      <c r="D79" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" ht="22.5" customHeight="1">
+      <c r="A80" s="15" t="s">
+        <v>2280</v>
+      </c>
+      <c r="B80" s="11" t="s">
+        <v>2281</v>
+      </c>
+      <c r="C80" s="12" t="s">
+        <v>2272</v>
+      </c>
+      <c r="D80" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" ht="22.5" customHeight="1">
+      <c r="A81" s="15" t="s">
+        <v>2282</v>
+      </c>
+      <c r="B81" s="11" t="s">
+        <v>2283</v>
+      </c>
+      <c r="C81" s="12" t="s">
+        <v>2272</v>
+      </c>
+      <c r="D81" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" ht="22.5" customHeight="1">
+      <c r="A82" s="15" t="s">
+        <v>2284</v>
+      </c>
+      <c r="B82" s="11" t="s">
+        <v>2285</v>
+      </c>
+      <c r="C82" s="12" t="s">
+        <v>2272</v>
+      </c>
+      <c r="D82" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" ht="22.5" customHeight="1">
+      <c r="A83" s="15" t="s">
+        <v>2286</v>
+      </c>
+      <c r="B83" s="11" t="s">
+        <v>2287</v>
+      </c>
+      <c r="C83" s="12" t="s">
+        <v>2272</v>
+      </c>
+      <c r="D83" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="84" ht="22.5" customHeight="1">
+      <c r="A84" s="15" t="s">
+        <v>2288</v>
+      </c>
+      <c r="B84" s="11" t="s">
+        <v>2289</v>
+      </c>
+      <c r="C84" s="12" t="s">
+        <v>2272</v>
+      </c>
+      <c r="D84" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="85" ht="22.5" customHeight="1">
+      <c r="A85" s="15" t="s">
+        <v>2290</v>
+      </c>
+      <c r="B85" s="11" t="s">
+        <v>2291</v>
+      </c>
+      <c r="C85" s="12" t="s">
+        <v>2272</v>
+      </c>
+      <c r="D85" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" ht="22.5" customHeight="1">
+      <c r="A86" s="15" t="s">
+        <v>2292</v>
+      </c>
+      <c r="B86" s="11" t="s">
+        <v>2293</v>
+      </c>
+      <c r="C86" s="12" t="s">
+        <v>2272</v>
+      </c>
+      <c r="D86" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" ht="22.5" customHeight="1">
+      <c r="A87" s="15" t="s">
+        <v>2294</v>
+      </c>
+      <c r="B87" s="11" t="s">
+        <v>2295</v>
+      </c>
+      <c r="C87" s="12" t="s">
+        <v>2272</v>
+      </c>
+      <c r="D87" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" ht="22.5" customHeight="1">
+      <c r="A88" s="15" t="s">
+        <v>2296</v>
+      </c>
+      <c r="B88" s="11" t="s">
+        <v>2297</v>
+      </c>
+      <c r="C88" s="12" t="s">
+        <v>2272</v>
+      </c>
+      <c r="D88" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" ht="22.5" customHeight="1">
+      <c r="A89" s="15" t="s">
+        <v>2298</v>
+      </c>
+      <c r="B89" s="11" t="s">
+        <v>2299</v>
+      </c>
+      <c r="C89" s="12" t="s">
+        <v>2272</v>
+      </c>
+      <c r="D89" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" ht="22.5" customHeight="1">
+      <c r="A90" s="15" t="s">
+        <v>2300</v>
+      </c>
+      <c r="B90" s="11" t="s">
+        <v>2301</v>
+      </c>
+      <c r="C90" s="12" t="s">
+        <v>2272</v>
+      </c>
+      <c r="D90" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" ht="22.5" customHeight="1">
+      <c r="A91" s="15" t="s">
+        <v>2302</v>
+      </c>
+      <c r="B91" s="11" t="s">
+        <v>2303</v>
+      </c>
+      <c r="C91" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="D91" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" ht="22.5" customHeight="1">
+      <c r="A92" s="15" t="s">
+        <v>2304</v>
+      </c>
+      <c r="B92" s="11" t="s">
+        <v>2305</v>
+      </c>
+      <c r="C92" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="D92" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" ht="22.5" customHeight="1">
+      <c r="A93" s="15" t="s">
+        <v>2306</v>
+      </c>
+      <c r="B93" s="11" t="s">
+        <v>2307</v>
+      </c>
+      <c r="C93" s="12" t="s">
+        <v>2308</v>
+      </c>
+      <c r="D93" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" ht="22.5" customHeight="1">
+      <c r="A94" s="15" t="s">
+        <v>2309</v>
+      </c>
+      <c r="B94" s="11" t="s">
+        <v>2310</v>
+      </c>
+      <c r="C94" s="12" t="s">
+        <v>2308</v>
+      </c>
+      <c r="D94" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" ht="22.5" customHeight="1">
+      <c r="A95" s="15" t="s">
+        <v>2311</v>
+      </c>
+      <c r="B95" s="11" t="s">
+        <v>2312</v>
+      </c>
+      <c r="C95" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="D95" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" ht="22.5" customHeight="1">
+      <c r="A96" s="15" t="s">
+        <v>2313</v>
+      </c>
+      <c r="B96" s="11" t="s">
+        <v>2314</v>
+      </c>
+      <c r="C96" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="D96" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" ht="22.5" customHeight="1">
+      <c r="A97" s="15" t="s">
+        <v>2315</v>
+      </c>
+      <c r="B97" s="11" t="s">
+        <v>2316</v>
+      </c>
+      <c r="C97" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="D97" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" ht="22.5" customHeight="1">
+      <c r="A98" s="15" t="s">
+        <v>2317</v>
+      </c>
+      <c r="B98" s="11" t="s">
+        <v>2318</v>
+      </c>
+      <c r="C98" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="D98" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="99" ht="22.5" customHeight="1">
+      <c r="A99" s="15" t="s">
+        <v>2319</v>
+      </c>
+      <c r="B99" s="11" t="s">
+        <v>2320</v>
+      </c>
+      <c r="C99" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="D99" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" ht="22.5" customHeight="1">
+      <c r="A100" s="15" t="s">
+        <v>2321</v>
+      </c>
+      <c r="B100" s="11" t="s">
+        <v>2322</v>
+      </c>
+      <c r="C100" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="D100" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" ht="22.5" customHeight="1">
+      <c r="A101" s="15" t="s">
+        <v>2323</v>
+      </c>
+      <c r="B101" s="11" t="s">
+        <v>2324</v>
+      </c>
+      <c r="C101" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="D101" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" ht="22.5" customHeight="1">
+      <c r="A102" s="15" t="s">
+        <v>2325</v>
+      </c>
+      <c r="B102" s="11" t="s">
+        <v>2326</v>
+      </c>
+      <c r="C102" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="D102" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" ht="22.5" customHeight="1">
+      <c r="A103" s="15" t="s">
+        <v>2327</v>
+      </c>
+      <c r="B103" s="11" t="s">
+        <v>2328</v>
+      </c>
+      <c r="C103" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="D103" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" ht="22.5" customHeight="1">
+      <c r="A104" s="15" t="s">
+        <v>2329</v>
+      </c>
+      <c r="B104" s="11" t="s">
+        <v>2330</v>
+      </c>
+      <c r="C104" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="D104" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" ht="22.5" customHeight="1">
+      <c r="A105" s="15" t="s">
+        <v>2331</v>
+      </c>
+      <c r="B105" s="11" t="s">
+        <v>2332</v>
+      </c>
+      <c r="C105" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="D105" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" ht="22.5" customHeight="1">
+      <c r="A106" s="15" t="s">
+        <v>2333</v>
+      </c>
+      <c r="B106" s="11" t="s">
+        <v>2334</v>
+      </c>
+      <c r="C106" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="D106" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" ht="22.5" customHeight="1">
+      <c r="A107" s="15" t="s">
+        <v>2335</v>
+      </c>
+      <c r="B107" s="11" t="s">
+        <v>2336</v>
+      </c>
+      <c r="C107" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="D107" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="108" ht="22.5" customHeight="1">
+      <c r="A108" s="15" t="s">
+        <v>2337</v>
+      </c>
+      <c r="B108" s="11" t="s">
+        <v>2338</v>
+      </c>
+      <c r="C108" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="D108" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="109" ht="22.5" customHeight="1">
+      <c r="A109" s="15" t="s">
+        <v>2339</v>
+      </c>
+      <c r="B109" s="11" t="s">
+        <v>2340</v>
+      </c>
+      <c r="C109" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="D109" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" ht="22.5" customHeight="1">
+      <c r="A110" s="15" t="s">
+        <v>2341</v>
+      </c>
+      <c r="B110" s="11" t="s">
+        <v>2342</v>
+      </c>
+      <c r="C110" s="12" t="s">
+        <v>311</v>
+      </c>
+      <c r="D110" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" ht="22.5" customHeight="1">
+      <c r="A111" s="15" t="s">
+        <v>2343</v>
+      </c>
+      <c r="B111" s="11" t="s">
+        <v>2344</v>
+      </c>
+      <c r="C111" s="12" t="s">
+        <v>2345</v>
+      </c>
+      <c r="D111" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112" ht="22.5" customHeight="1">
+      <c r="A112" s="15" t="s">
+        <v>2346</v>
+      </c>
+      <c r="B112" s="11" t="s">
+        <v>2347</v>
+      </c>
+      <c r="C112" s="12" t="s">
+        <v>2345</v>
+      </c>
+      <c r="D112" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" ht="22.5" customHeight="1">
+      <c r="A113" s="15" t="s">
+        <v>2348</v>
+      </c>
+      <c r="B113" s="11" t="s">
+        <v>2349</v>
+      </c>
+      <c r="C113" s="12" t="s">
+        <v>2345</v>
+      </c>
+      <c r="D113" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" ht="22.5" customHeight="1">
+      <c r="A114" s="15" t="s">
+        <v>2350</v>
+      </c>
+      <c r="B114" s="11" t="s">
+        <v>2351</v>
+      </c>
+      <c r="C114" s="12" t="s">
+        <v>2345</v>
+      </c>
+      <c r="D114" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" ht="22.5" customHeight="1">
+      <c r="A115" s="15" t="s">
+        <v>2352</v>
+      </c>
+      <c r="B115" s="11" t="s">
+        <v>2353</v>
+      </c>
+      <c r="C115" s="12" t="s">
+        <v>2345</v>
+      </c>
+      <c r="D115" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" ht="22.5" customHeight="1">
+      <c r="A116" s="15" t="s">
+        <v>2354</v>
+      </c>
+      <c r="B116" s="11" t="s">
+        <v>2355</v>
+      </c>
+      <c r="C116" s="12" t="s">
+        <v>2345</v>
+      </c>
+      <c r="D116" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" ht="22.5" customHeight="1">
+      <c r="A117" s="15" t="s">
+        <v>2356</v>
+      </c>
+      <c r="B117" s="11" t="s">
+        <v>2357</v>
+      </c>
+      <c r="C117" s="12" t="s">
+        <v>2345</v>
+      </c>
+      <c r="D117" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="118" ht="22.5" customHeight="1">
+      <c r="A118" s="15" t="s">
+        <v>2358</v>
+      </c>
+      <c r="B118" s="11" t="s">
+        <v>2359</v>
+      </c>
+      <c r="C118" s="12" t="s">
+        <v>2345</v>
+      </c>
+      <c r="D118" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="119" ht="22.5" customHeight="1">
+      <c r="A119" s="15" t="s">
+        <v>2360</v>
+      </c>
+      <c r="B119" s="11" t="s">
+        <v>2361</v>
+      </c>
+      <c r="C119" s="12" t="s">
+        <v>2345</v>
+      </c>
+      <c r="D119" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="120" ht="22.5" customHeight="1">
+      <c r="A120" s="15" t="s">
+        <v>2362</v>
+      </c>
+      <c r="B120" s="11" t="s">
+        <v>2363</v>
+      </c>
+      <c r="C120" s="12" t="s">
+        <v>2345</v>
+      </c>
+      <c r="D120" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" ht="22.5" customHeight="1">
+      <c r="A121" s="15" t="s">
+        <v>2364</v>
+      </c>
+      <c r="B121" s="11" t="s">
+        <v>2365</v>
+      </c>
+      <c r="C121" s="12" t="s">
+        <v>2345</v>
+      </c>
+      <c r="D121" s="11" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations>
+    <dataValidation type="list" allowBlank="1" showDropDown="1" showErrorMessage="1" sqref="C2:C121">
+      <formula1>"一級,二級,二級_氰系,二級_鉻系,二級_鎳系,三級,其他,其他_污泥,污泥"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId3"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="2" max="2" width="16.38"/>
+    <col customWidth="1" min="3" max="3" width="21.38"/>
+    <col customWidth="1" min="4" max="4" width="27.75"/>
+    <col customWidth="1" min="5" max="5" width="20.25"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22.5" customHeight="1">
+      <c r="A1" s="14" t="s">
+        <v>2119</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>2118</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>910</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>2366</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>2367</v>
+      </c>
+    </row>
+    <row r="2" ht="22.5" customHeight="1">
+      <c r="A2" s="12" t="s">
+        <v>2122</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>2121</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>2368</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>2369</v>
+      </c>
+      <c r="E2" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="3" ht="22.5" customHeight="1">
+      <c r="A3" s="12" t="s">
+        <v>2122</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>2154</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>2371</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>2372</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="4" ht="22.5" customHeight="1">
+      <c r="A4" s="12" t="s">
+        <v>2122</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>2156</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>2371</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>2373</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="5" ht="22.5" customHeight="1">
+      <c r="A5" s="12" t="s">
+        <v>2122</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>2132</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>2374</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>2375</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="6" ht="22.5" customHeight="1">
+      <c r="A6" s="12" t="s">
+        <v>2122</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>2138</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>2371</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>2372</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="7" ht="22.5" customHeight="1">
+      <c r="A7" s="12" t="s">
+        <v>2122</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>2138</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>2376</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>2377</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="8" ht="22.5" customHeight="1">
+      <c r="A8" s="12" t="s">
+        <v>2122</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>2138</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>2378</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="9" ht="22.5" customHeight="1">
+      <c r="A9" s="12" t="s">
+        <v>2122</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>2138</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>2381</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="10" ht="22.5" customHeight="1">
+      <c r="A10" s="12" t="s">
+        <v>2122</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>1981</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>2382</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>2383</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="11" ht="22.5" customHeight="1">
+      <c r="A11" s="12" t="s">
+        <v>2122</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>1981</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>2371</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>2372</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="12" ht="22.5" customHeight="1">
+      <c r="A12" s="12" t="s">
+        <v>2122</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>1981</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>2384</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>2385</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="13" ht="22.5" customHeight="1">
+      <c r="A13" s="12" t="s">
+        <v>2122</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>1981</v>
+      </c>
+      <c r="C13" s="11" t="s">
+        <v>2386</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="14" ht="22.5" customHeight="1">
+      <c r="A14" s="12" t="s">
+        <v>2122</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>1981</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>2387</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="15" ht="22.5" customHeight="1">
+      <c r="A15" s="12" t="s">
+        <v>2122</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>1981</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>2388</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="16" ht="22.5" customHeight="1">
+      <c r="A16" s="12" t="s">
+        <v>2122</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>2289</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>2371</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="17" ht="22.5" customHeight="1">
+      <c r="A17" s="12" t="s">
+        <v>2122</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>2289</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>2389</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="18" ht="22.5" customHeight="1">
+      <c r="A18" s="12" t="s">
+        <v>2122</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>2289</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>2390</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="19" ht="22.5" customHeight="1">
+      <c r="A19" s="12" t="s">
+        <v>2122</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>2289</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>2391</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="20" ht="22.5" customHeight="1">
+      <c r="A20" s="12" t="s">
+        <v>2122</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>1955</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>2374</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>2375</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="21" ht="22.5" customHeight="1">
+      <c r="A21" s="12" t="s">
+        <v>2122</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>1955</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>2386</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="22" ht="22.5" customHeight="1">
+      <c r="A22" s="12" t="s">
+        <v>2122</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>1955</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>2389</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E22" s="12" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="23" ht="22.5" customHeight="1">
+      <c r="A23" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>2195</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>2392</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>2393</v>
+      </c>
+      <c r="E23" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="24" ht="22.5" customHeight="1">
+      <c r="A24" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>2195</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>2374</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>2375</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="25" ht="22.5" customHeight="1">
+      <c r="A25" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>2195</v>
+      </c>
+      <c r="C25" s="11" t="s">
+        <v>2394</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>2395</v>
+      </c>
+      <c r="E25" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="26" ht="22.5" customHeight="1">
+      <c r="A26" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>2195</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>2396</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>2397</v>
+      </c>
+      <c r="E26" s="12" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="27" ht="22.5" customHeight="1">
+      <c r="A27" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>2195</v>
+      </c>
+      <c r="C27" s="11" t="s">
+        <v>2398</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E27" s="12" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="28" ht="22.5" customHeight="1">
+      <c r="A28" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>2195</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>2399</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E28" s="12" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="29" ht="22.5" customHeight="1">
+      <c r="A29" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>2195</v>
+      </c>
+      <c r="C29" s="11" t="s">
+        <v>2400</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>2401</v>
+      </c>
+      <c r="E29" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="30" ht="22.5" customHeight="1">
+      <c r="A30" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>2195</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>1858</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E30" s="12" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="31" ht="22.5" customHeight="1">
+      <c r="A31" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>2195</v>
+      </c>
+      <c r="C31" s="11" t="s">
+        <v>2402</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E31" s="12" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="32" ht="22.5" customHeight="1">
+      <c r="A32" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>2195</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>2403</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>2404</v>
+      </c>
+      <c r="E32" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="33" ht="22.5" customHeight="1">
+      <c r="A33" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>2187</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>2394</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>2405</v>
+      </c>
+      <c r="E33" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="34" ht="22.5" customHeight="1">
+      <c r="A34" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>2187</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>2406</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>2407</v>
+      </c>
+      <c r="E34" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="35" ht="22.5" customHeight="1">
+      <c r="A35" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>2187</v>
+      </c>
+      <c r="C35" s="11" t="s">
+        <v>1858</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E35" s="12" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="36" ht="22.5" customHeight="1">
+      <c r="A36" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>2187</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>2408</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E36" s="12" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="37" ht="22.5" customHeight="1">
+      <c r="A37" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B37" s="11" t="s">
+        <v>2409</v>
+      </c>
+      <c r="C37" s="11" t="s">
+        <v>2410</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>2405</v>
+      </c>
+      <c r="E37" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="38" ht="22.5" customHeight="1">
+      <c r="A38" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B38" s="11" t="s">
+        <v>2409</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>2411</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>2372</v>
+      </c>
+      <c r="E38" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="39" ht="22.5" customHeight="1">
+      <c r="A39" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>2409</v>
+      </c>
+      <c r="C39" s="11" t="s">
+        <v>2398</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E39" s="12" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="40" ht="22.5" customHeight="1">
+      <c r="A40" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B40" s="11" t="s">
+        <v>2409</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>2389</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E40" s="12" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="41" ht="22.5" customHeight="1">
+      <c r="A41" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B41" s="11" t="s">
+        <v>2412</v>
+      </c>
+      <c r="C41" s="11" t="s">
+        <v>2413</v>
+      </c>
+      <c r="D41" s="11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E41" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="42" ht="22.5" customHeight="1">
+      <c r="A42" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B42" s="11" t="s">
+        <v>2412</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>2414</v>
+      </c>
+      <c r="D42" s="11" t="s">
+        <v>2415</v>
+      </c>
+      <c r="E42" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="43" ht="22.5" customHeight="1">
+      <c r="A43" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B43" s="11" t="s">
+        <v>2412</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>1858</v>
+      </c>
+      <c r="D43" s="11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E43" s="12" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="44" ht="22.5" customHeight="1">
+      <c r="A44" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B44" s="11" t="s">
+        <v>2412</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>2408</v>
+      </c>
+      <c r="D44" s="11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E44" s="12" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="45" ht="22.5" customHeight="1">
+      <c r="A45" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B45" s="11" t="s">
+        <v>2264</v>
+      </c>
+      <c r="C45" s="11" t="s">
+        <v>2392</v>
+      </c>
+      <c r="D45" s="11" t="s">
+        <v>2416</v>
+      </c>
+      <c r="E45" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="46" ht="22.5" customHeight="1">
+      <c r="A46" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B46" s="11" t="s">
+        <v>2264</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>2374</v>
+      </c>
+      <c r="D46" s="11" t="s">
+        <v>2375</v>
+      </c>
+      <c r="E46" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="47" ht="22.5" customHeight="1">
+      <c r="A47" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B47" s="11" t="s">
+        <v>2264</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>2394</v>
+      </c>
+      <c r="D47" s="11" t="s">
+        <v>2395</v>
+      </c>
+      <c r="E47" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="48" ht="22.5" customHeight="1">
+      <c r="A48" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B48" s="11" t="s">
+        <v>2264</v>
+      </c>
+      <c r="C48" s="11" t="s">
+        <v>2396</v>
+      </c>
+      <c r="D48" s="11" t="s">
+        <v>2397</v>
+      </c>
+      <c r="E48" s="12" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="49" ht="22.5" customHeight="1">
+      <c r="A49" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B49" s="11" t="s">
+        <v>2264</v>
+      </c>
+      <c r="C49" s="11" t="s">
+        <v>2398</v>
+      </c>
+      <c r="D49" s="11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E49" s="12" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="50" ht="22.5" customHeight="1">
+      <c r="A50" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B50" s="11" t="s">
+        <v>2264</v>
+      </c>
+      <c r="C50" s="11" t="s">
+        <v>2417</v>
+      </c>
+      <c r="D50" s="11" t="s">
+        <v>2418</v>
+      </c>
+      <c r="E50" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="51" ht="22.5" customHeight="1">
+      <c r="A51" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B51" s="11" t="s">
+        <v>2264</v>
+      </c>
+      <c r="C51" s="11" t="s">
+        <v>2419</v>
+      </c>
+      <c r="D51" s="11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E51" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="52" ht="22.5" customHeight="1">
+      <c r="A52" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B52" s="11" t="s">
+        <v>2264</v>
+      </c>
+      <c r="C52" s="11" t="s">
+        <v>2399</v>
+      </c>
+      <c r="D52" s="11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E52" s="12" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="53" ht="22.5" customHeight="1">
+      <c r="A53" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B53" s="11" t="s">
+        <v>2264</v>
+      </c>
+      <c r="C53" s="11" t="s">
+        <v>2420</v>
+      </c>
+      <c r="D53" s="11" t="s">
+        <v>2421</v>
+      </c>
+      <c r="E53" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="54" ht="22.5" customHeight="1">
+      <c r="A54" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B54" s="11" t="s">
+        <v>2264</v>
+      </c>
+      <c r="C54" s="11" t="s">
+        <v>2408</v>
+      </c>
+      <c r="D54" s="11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E54" s="12" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="55" ht="22.5" customHeight="1">
+      <c r="A55" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B55" s="11" t="s">
+        <v>2264</v>
+      </c>
+      <c r="C55" s="11" t="s">
+        <v>2403</v>
+      </c>
+      <c r="D55" s="11" t="s">
+        <v>2422</v>
+      </c>
+      <c r="E55" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="56" ht="22.5" customHeight="1">
+      <c r="A56" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B56" s="11" t="s">
+        <v>2266</v>
+      </c>
+      <c r="C56" s="11" t="s">
+        <v>2423</v>
+      </c>
+      <c r="D56" s="11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E56" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="57" ht="22.5" customHeight="1">
+      <c r="A57" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B57" s="11" t="s">
+        <v>2266</v>
+      </c>
+      <c r="C57" s="11" t="s">
+        <v>2374</v>
+      </c>
+      <c r="D57" s="11" t="s">
+        <v>2375</v>
+      </c>
+      <c r="E57" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="58" ht="22.5" customHeight="1">
+      <c r="A58" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B58" s="11" t="s">
+        <v>2266</v>
+      </c>
+      <c r="C58" s="11" t="s">
+        <v>405</v>
+      </c>
+      <c r="D58" s="11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E58" s="12" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="59" ht="22.5" customHeight="1">
+      <c r="A59" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B59" s="11" t="s">
+        <v>2266</v>
+      </c>
+      <c r="C59" s="11" t="s">
+        <v>2398</v>
+      </c>
+      <c r="D59" s="11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E59" s="12" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="60" ht="22.5" customHeight="1">
+      <c r="A60" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B60" s="11" t="s">
+        <v>2266</v>
+      </c>
+      <c r="C60" s="11" t="s">
+        <v>2424</v>
+      </c>
+      <c r="D60" s="11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E60" s="12" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="61" ht="22.5" customHeight="1">
+      <c r="A61" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B61" s="11" t="s">
+        <v>2266</v>
+      </c>
+      <c r="C61" s="11" t="s">
+        <v>2425</v>
+      </c>
+      <c r="D61" s="11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E61" s="12" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="62" ht="22.5" customHeight="1">
+      <c r="A62" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B62" s="11" t="s">
+        <v>2268</v>
+      </c>
+      <c r="C62" s="11" t="s">
+        <v>2371</v>
+      </c>
+      <c r="D62" s="11" t="s">
+        <v>2372</v>
+      </c>
+      <c r="E62" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="63" ht="22.5" customHeight="1">
+      <c r="A63" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B63" s="11" t="s">
+        <v>2268</v>
+      </c>
+      <c r="C63" s="11" t="s">
+        <v>2376</v>
+      </c>
+      <c r="D63" s="11" t="s">
+        <v>2377</v>
+      </c>
+      <c r="E63" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="64" ht="22.5" customHeight="1">
+      <c r="A64" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B64" s="11" t="s">
+        <v>2268</v>
+      </c>
+      <c r="C64" s="11" t="s">
+        <v>2378</v>
+      </c>
+      <c r="D64" s="11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E64" s="12" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="65" ht="22.5" customHeight="1">
+      <c r="A65" s="12" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B65" s="11" t="s">
+        <v>2268</v>
+      </c>
+      <c r="C65" s="11" t="s">
+        <v>2381</v>
+      </c>
+      <c r="D65" s="11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E65" s="12" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="66" ht="22.5" customHeight="1">
+      <c r="A66" s="12" t="s">
+        <v>2272</v>
+      </c>
+      <c r="B66" s="11" t="s">
+        <v>2164</v>
+      </c>
+      <c r="C66" s="11" t="s">
+        <v>2374</v>
+      </c>
+      <c r="D66" s="11" t="s">
+        <v>2375</v>
+      </c>
+      <c r="E66" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="67" ht="22.5" customHeight="1">
+      <c r="A67" s="12" t="s">
+        <v>2272</v>
+      </c>
+      <c r="B67" s="11" t="s">
+        <v>2164</v>
+      </c>
+      <c r="C67" s="11" t="s">
+        <v>2426</v>
+      </c>
+      <c r="D67" s="11" t="s">
+        <v>2427</v>
+      </c>
+      <c r="E67" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="68" ht="22.5" customHeight="1">
+      <c r="A68" s="12" t="s">
+        <v>2272</v>
+      </c>
+      <c r="B68" s="11" t="s">
+        <v>2164</v>
+      </c>
+      <c r="C68" s="11" t="s">
+        <v>2386</v>
+      </c>
+      <c r="D68" s="11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E68" s="12" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="69" ht="22.5" customHeight="1">
+      <c r="A69" s="12" t="s">
+        <v>2272</v>
+      </c>
+      <c r="B69" s="11" t="s">
+        <v>2164</v>
+      </c>
+      <c r="C69" s="11" t="s">
+        <v>2428</v>
+      </c>
+      <c r="D69" s="11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E69" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="70" ht="22.5" customHeight="1">
+      <c r="A70" s="12" t="s">
+        <v>2272</v>
+      </c>
+      <c r="B70" s="11" t="s">
+        <v>2295</v>
+      </c>
+      <c r="C70" s="11" t="s">
+        <v>2371</v>
+      </c>
+      <c r="D70" s="11" t="s">
+        <v>2372</v>
+      </c>
+      <c r="E70" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="71" ht="22.5" customHeight="1">
+      <c r="A71" s="12" t="s">
+        <v>2272</v>
+      </c>
+      <c r="B71" s="11" t="s">
+        <v>2295</v>
+      </c>
+      <c r="C71" s="11" t="s">
+        <v>2376</v>
+      </c>
+      <c r="D71" s="11" t="s">
+        <v>2377</v>
+      </c>
+      <c r="E71" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="72" ht="22.5" customHeight="1">
+      <c r="A72" s="12" t="s">
+        <v>2272</v>
+      </c>
+      <c r="B72" s="11" t="s">
+        <v>2295</v>
+      </c>
+      <c r="C72" s="11" t="s">
+        <v>2378</v>
+      </c>
+      <c r="D72" s="11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E72" s="12" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="73" ht="22.5" customHeight="1">
+      <c r="A73" s="12" t="s">
+        <v>2272</v>
+      </c>
+      <c r="B73" s="11" t="s">
+        <v>2295</v>
+      </c>
+      <c r="C73" s="11" t="s">
+        <v>2381</v>
+      </c>
+      <c r="D73" s="11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E73" s="12" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="74" ht="22.5" customHeight="1">
+      <c r="A74" s="12" t="s">
+        <v>2272</v>
+      </c>
+      <c r="B74" s="11" t="s">
+        <v>2277</v>
+      </c>
+      <c r="C74" s="11" t="s">
+        <v>2429</v>
+      </c>
+      <c r="D74" s="11" t="s">
+        <v>2430</v>
+      </c>
+      <c r="E74" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="75" ht="22.5" customHeight="1">
+      <c r="A75" s="12" t="s">
+        <v>2272</v>
+      </c>
+      <c r="B75" s="11" t="s">
+        <v>2277</v>
+      </c>
+      <c r="C75" s="11" t="s">
+        <v>2431</v>
+      </c>
+      <c r="D75" s="11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E75" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="76" ht="22.5" customHeight="1">
+      <c r="A76" s="12" t="s">
+        <v>2272</v>
+      </c>
+      <c r="B76" s="11" t="s">
+        <v>2297</v>
+      </c>
+      <c r="C76" s="11" t="s">
+        <v>2429</v>
+      </c>
+      <c r="D76" s="11" t="s">
+        <v>2430</v>
+      </c>
+      <c r="E76" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="77" ht="22.5" customHeight="1">
+      <c r="A77" s="12" t="s">
+        <v>2272</v>
+      </c>
+      <c r="B77" s="11" t="s">
+        <v>2297</v>
+      </c>
+      <c r="C77" s="11" t="s">
+        <v>2431</v>
+      </c>
+      <c r="D77" s="11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E77" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="78" ht="22.5" customHeight="1">
+      <c r="A78" s="12" t="s">
+        <v>2272</v>
+      </c>
+      <c r="B78" s="11" t="s">
+        <v>2299</v>
+      </c>
+      <c r="C78" s="11" t="s">
+        <v>2429</v>
+      </c>
+      <c r="D78" s="11" t="s">
+        <v>2430</v>
+      </c>
+      <c r="E78" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="79" ht="22.5" customHeight="1">
+      <c r="A79" s="12" t="s">
+        <v>2272</v>
+      </c>
+      <c r="B79" s="11" t="s">
+        <v>2299</v>
+      </c>
+      <c r="C79" s="11" t="s">
+        <v>2431</v>
+      </c>
+      <c r="D79" s="11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E79" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="80" ht="22.5" customHeight="1">
+      <c r="A80" s="12" t="s">
+        <v>2272</v>
+      </c>
+      <c r="B80" s="11" t="s">
+        <v>2287</v>
+      </c>
+      <c r="C80" s="11" t="s">
+        <v>2429</v>
+      </c>
+      <c r="D80" s="11" t="s">
+        <v>2430</v>
+      </c>
+      <c r="E80" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="81" ht="22.5" customHeight="1">
+      <c r="A81" s="12" t="s">
+        <v>2272</v>
+      </c>
+      <c r="B81" s="11" t="s">
+        <v>2287</v>
+      </c>
+      <c r="C81" s="11" t="s">
+        <v>2431</v>
+      </c>
+      <c r="D81" s="11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E81" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="82" ht="22.5" customHeight="1">
+      <c r="A82" s="12" t="s">
+        <v>2272</v>
+      </c>
+      <c r="B82" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C82" s="11" t="s">
+        <v>2429</v>
+      </c>
+      <c r="D82" s="11" t="s">
+        <v>2430</v>
+      </c>
+      <c r="E82" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="83" ht="22.5" customHeight="1">
+      <c r="A83" s="12" t="s">
+        <v>2272</v>
+      </c>
+      <c r="B83" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C83" s="11" t="s">
+        <v>2432</v>
+      </c>
+      <c r="D83" s="11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E83" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="84" ht="22.5" customHeight="1">
+      <c r="A84" s="12" t="s">
+        <v>2272</v>
+      </c>
+      <c r="B84" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="C84" s="11" t="s">
+        <v>2433</v>
+      </c>
+      <c r="D84" s="11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E84" s="12" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="85" ht="22.5" customHeight="1">
+      <c r="A85" s="12" t="s">
+        <v>2345</v>
+      </c>
+      <c r="B85" s="11" t="s">
+        <v>2363</v>
+      </c>
+      <c r="C85" s="11" t="s">
+        <v>2371</v>
+      </c>
+      <c r="D85" s="11" t="s">
+        <v>2430</v>
+      </c>
+      <c r="E85" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="86" ht="22.5" customHeight="1">
+      <c r="A86" s="12" t="s">
+        <v>2345</v>
+      </c>
+      <c r="B86" s="11" t="s">
+        <v>2363</v>
+      </c>
+      <c r="C86" s="11" t="s">
+        <v>2384</v>
+      </c>
+      <c r="D86" s="11" t="s">
+        <v>2434</v>
+      </c>
+      <c r="E86" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="87" ht="22.5" customHeight="1">
+      <c r="A87" s="12" t="s">
+        <v>2345</v>
+      </c>
+      <c r="B87" s="11" t="s">
+        <v>2363</v>
+      </c>
+      <c r="C87" s="11" t="s">
+        <v>2381</v>
+      </c>
+      <c r="D87" s="11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E87" s="12" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="88" ht="22.5" customHeight="1">
+      <c r="A88" s="12" t="s">
+        <v>2345</v>
+      </c>
+      <c r="B88" s="11" t="s">
+        <v>2363</v>
+      </c>
+      <c r="C88" s="11" t="s">
+        <v>2435</v>
+      </c>
+      <c r="D88" s="11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E88" s="12" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="89" ht="22.5" customHeight="1">
+      <c r="A89" s="12" t="s">
+        <v>2345</v>
+      </c>
+      <c r="B89" s="11" t="s">
+        <v>2307</v>
+      </c>
+      <c r="C89" s="11" t="s">
+        <v>2374</v>
+      </c>
+      <c r="D89" s="11" t="s">
+        <v>2436</v>
+      </c>
+      <c r="E89" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="90" ht="22.5" customHeight="1">
+      <c r="A90" s="12" t="s">
+        <v>2345</v>
+      </c>
+      <c r="B90" s="11" t="s">
+        <v>2307</v>
+      </c>
+      <c r="C90" s="11" t="s">
+        <v>2437</v>
+      </c>
+      <c r="D90" s="11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E90" s="12" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="91" ht="22.5" customHeight="1">
+      <c r="A91" s="12" t="s">
+        <v>2345</v>
+      </c>
+      <c r="B91" s="11" t="s">
+        <v>2307</v>
+      </c>
+      <c r="C91" s="11" t="s">
+        <v>2438</v>
+      </c>
+      <c r="D91" s="11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E91" s="12" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="92" ht="22.5" customHeight="1">
+      <c r="A92" s="12" t="s">
+        <v>2345</v>
+      </c>
+      <c r="B92" s="11" t="s">
+        <v>2307</v>
+      </c>
+      <c r="C92" s="11" t="s">
+        <v>2439</v>
+      </c>
+      <c r="D92" s="11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E92" s="12" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="93" ht="22.5" customHeight="1">
+      <c r="A93" s="12" t="s">
+        <v>2345</v>
+      </c>
+      <c r="B93" s="11" t="s">
+        <v>2307</v>
+      </c>
+      <c r="C93" s="11" t="s">
+        <v>2408</v>
+      </c>
+      <c r="D93" s="11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E93" s="12" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="94" ht="22.5" customHeight="1">
+      <c r="A94" s="12" t="s">
+        <v>2345</v>
+      </c>
+      <c r="B94" s="11" t="s">
+        <v>2310</v>
+      </c>
+      <c r="C94" s="11" t="s">
+        <v>2374</v>
+      </c>
+      <c r="D94" s="11" t="s">
+        <v>2436</v>
+      </c>
+      <c r="E94" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="95" ht="22.5" customHeight="1">
+      <c r="A95" s="12" t="s">
+        <v>2345</v>
+      </c>
+      <c r="B95" s="11" t="s">
+        <v>2310</v>
+      </c>
+      <c r="C95" s="11" t="s">
+        <v>2410</v>
+      </c>
+      <c r="D95" s="11" t="s">
+        <v>2405</v>
+      </c>
+      <c r="E95" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="96" ht="22.5" customHeight="1">
+      <c r="A96" s="12" t="s">
+        <v>2345</v>
+      </c>
+      <c r="B96" s="11" t="s">
+        <v>2310</v>
+      </c>
+      <c r="C96" s="11" t="s">
+        <v>2389</v>
+      </c>
+      <c r="D96" s="11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E96" s="12" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="97" ht="22.5" customHeight="1">
+      <c r="A97" s="12" t="s">
+        <v>2345</v>
+      </c>
+      <c r="B97" s="11" t="s">
+        <v>2310</v>
+      </c>
+      <c r="C97" s="11" t="s">
+        <v>2438</v>
+      </c>
+      <c r="D97" s="11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E97" s="12" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="98" ht="22.5" customHeight="1">
+      <c r="A98" s="12" t="s">
+        <v>2345</v>
+      </c>
+      <c r="B98" s="11" t="s">
+        <v>2310</v>
+      </c>
+      <c r="C98" s="11" t="s">
+        <v>2439</v>
+      </c>
+      <c r="D98" s="11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E98" s="12" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="99" ht="22.5" customHeight="1">
+      <c r="A99" s="12" t="s">
+        <v>2345</v>
+      </c>
+      <c r="B99" s="11" t="s">
+        <v>2310</v>
+      </c>
+      <c r="C99" s="11" t="s">
+        <v>2440</v>
+      </c>
+      <c r="D99" s="11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E99" s="12" t="s">
+        <v>2380</v>
+      </c>
+    </row>
+    <row r="100" ht="22.5" customHeight="1">
+      <c r="A100" s="12" t="s">
+        <v>2345</v>
+      </c>
+      <c r="B100" s="11" t="s">
+        <v>2355</v>
+      </c>
+      <c r="C100" s="11" t="s">
+        <v>1626</v>
+      </c>
+      <c r="D100" s="11" t="s">
+        <v>2441</v>
+      </c>
+      <c r="E100" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="101" ht="22.5" customHeight="1">
+      <c r="A101" s="12" t="s">
+        <v>2345</v>
+      </c>
+      <c r="B101" s="11" t="s">
+        <v>2353</v>
+      </c>
+      <c r="C101" s="11" t="s">
+        <v>1626</v>
+      </c>
+      <c r="D101" s="11" t="s">
+        <v>2442</v>
+      </c>
+      <c r="E101" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="102" ht="22.5" customHeight="1">
+      <c r="A102" s="12" t="s">
+        <v>2345</v>
+      </c>
+      <c r="B102" s="11" t="s">
+        <v>2443</v>
+      </c>
+      <c r="C102" s="11" t="s">
+        <v>2444</v>
+      </c>
+      <c r="D102" s="11" t="s">
+        <v>2379</v>
+      </c>
+      <c r="E102" s="12" t="s">
+        <v>2370</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="E103" s="7"/>
+    </row>
+    <row r="104">
+      <c r="E104" s="7"/>
+    </row>
+    <row r="105">
+      <c r="E105" s="7"/>
+    </row>
+    <row r="106">
+      <c r="E106" s="7"/>
+    </row>
+  </sheetData>
+  <dataValidations>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E102">
+      <formula1>"設計,量測"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E103:E106">
+      <formula1>"設計,量測"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showDropDown="1" showErrorMessage="1" sqref="A2:A102">
+      <formula1>"一級,二級,三級,污泥"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId3"/>
+  </tableParts>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
@@ -30476,6 +40172,35 @@
       </c>
       <c r="J28" s="5">
         <v>46183.48611111111</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B29" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="D29" s="4">
+        <v>46183.58226851852</v>
+      </c>
+      <c r="E29" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>23.0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>12.0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>225.0</v>
+      </c>
+      <c r="J29" s="5">
+        <v>46183.57847222222</v>
       </c>
     </row>
   </sheetData>

--- a/規則庫.xlsx
+++ b/規則庫.xlsx
@@ -44,21 +44,11 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision">
   <authors>
-    <author>tc={5aaed787-bfd2-4c77-9119-dfe99fb76b81}</author>
-    <author>tc={d91dee48-4ad6-4c1f-9fc0-9da73d9045b3}</author>
+    <author>tc={97b27b7f-eb38-4817-96ed-38d00d1e2f51}</author>
+    <author>tc={c85f3a2b-0517-4e84-9312-8d76d1c7f935}</author>
   </authors>
   <commentList>
-    <comment authorId="0" xr:uid="{5aaed787-bfd2-4c77-9119-dfe99fb76b81}" ref="C10">
-      <text>
-        <t xml:space="preserve">[Threaded comment]
- Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-	公式為：G=(P/ (μ*V))^1/2     計算是直接把馬達功率 P(ex. P= 370 W、槽體有效容積 V = 1.17 m³、水的粘滯係數 μ = 0.001 N⋅s/m² 直接代入。
-學理標準範圍10~50S^-1
-</t>
-      </text>
-    </comment>
-    <comment authorId="1" xr:uid="{d91dee48-4ad6-4c1f-9fc0-9da73d9045b3}" ref="C2">
+    <comment authorId="0" xr:uid="{97b27b7f-eb38-4817-96ed-38d00d1e2f51}" ref="C2">
       <text>
         <t xml:space="preserve">[Threaded comment]
  Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -75,12 +65,22 @@
 </t>
       </text>
     </comment>
+    <comment authorId="1" xr:uid="{c85f3a2b-0517-4e84-9312-8d76d1c7f935}" ref="C10">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+ Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+	公式為：G=(P/ (μ*V))^1/2     計算是直接把馬達功率 P(ex. P= 370 W、槽體有效容積 V = 1.17 m³、水的粘滯係數 μ = 0.001 N⋅s/m² 直接代入。
+學理標準範圍10~50S^-1
+</t>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6530" uniqueCount="2445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6782" uniqueCount="2492">
   <si>
     <t>水措審查系統 — 規則庫 使用說明 (v2)</t>
   </si>
@@ -6076,6 +6076,24 @@
     <t>系統下次同步時自動更新</t>
   </si>
   <si>
+    <t>預處理池</t>
+  </si>
+  <si>
+    <t>前處理槽 / 前處理池 / 預處理槽 / 預處理 / 前處理</t>
+  </si>
+  <si>
+    <t>預處理階段, 含匯流分離功能 (代碼 119)</t>
+  </si>
+  <si>
+    <t>鎳系</t>
+  </si>
+  <si>
+    <t>聶系 / 鎳水洗 / 化學鎳 / 鍍鎳 / 化銅 / 鎳系廢水</t>
+  </si>
+  <si>
+    <t>鎳系廢水分流 (聶 vs 鎳 同音字)</t>
+  </si>
+  <si>
     <t>標準槽體</t>
   </si>
   <si>
@@ -6115,6 +6133,24 @@
     <t>類型</t>
   </si>
   <si>
+    <t>體積負荷_max (kg BOD/m³·d)</t>
+  </si>
+  <si>
+    <t>F/M_min</t>
+  </si>
+  <si>
+    <t>F/M_max</t>
+  </si>
+  <si>
+    <t>SRT_min (d)</t>
+  </si>
+  <si>
+    <t>SRT_max (d)</t>
+  </si>
+  <si>
+    <t>含水率_max (%)</t>
+  </si>
+  <si>
     <t>酸/鹼</t>
   </si>
   <si>
@@ -6364,6 +6400,138 @@
     <t>放流前的暫存, 水質應與前端處理出流完全一致</t>
   </si>
   <si>
+    <t>接觸氧化池</t>
+  </si>
+  <si>
+    <t>無</t>
+  </si>
+  <si>
+    <t>COD, BOD, 氨氮</t>
+  </si>
+  <si>
+    <t>SS, 重金屬</t>
+  </si>
+  <si>
+    <t>生物處理單元, COD/BOD/氨氮應大幅下降; SS/重金屬不應變動 (沒固液分離)</t>
+  </si>
+  <si>
+    <t>MBR</t>
+  </si>
+  <si>
+    <t>COD, BOD, 氨氮, SS</t>
+  </si>
+  <si>
+    <t>重金屬</t>
+  </si>
+  <si>
+    <t>MBR 整合曝氣 + 過濾, COD/BOD/氨氮/SS 同時去除; 重金屬不應變動</t>
+  </si>
+  <si>
+    <t>氰系氧化槽</t>
+  </si>
+  <si>
+    <t>氧化劑 (NaOCl/H2O2)</t>
+  </si>
+  <si>
+    <t>氰化物, pH</t>
+  </si>
+  <si>
+    <t>兩段式鹼氯法: pH 10~11 鹼性氧化 CN⁻ → CNO⁻</t>
+  </si>
+  <si>
+    <t>鉻系還原槽</t>
+  </si>
+  <si>
+    <t>還原劑 (NaHSO3/Na2S)</t>
+  </si>
+  <si>
+    <t>六價鉻, pH</t>
+  </si>
+  <si>
+    <t>SS, 其他重金屬</t>
+  </si>
+  <si>
+    <t>酸性還原: pH 2~3 將 Cr⁶⁺ → Cr³⁺</t>
+  </si>
+  <si>
+    <t>混凝膠凝池</t>
+  </si>
+  <si>
+    <t>混凝劑 + 助凝劑</t>
+  </si>
+  <si>
+    <t>混凝 + 膠凝合一; G 值需控制 30~80 形成大絮羽</t>
+  </si>
+  <si>
+    <t>污泥離心式脫水機</t>
+  </si>
+  <si>
+    <t>助凝劑 (PAM)</t>
+  </si>
+  <si>
+    <t>進泥 95~98% → 出泥 75~85% (餅) + 濾液</t>
+  </si>
+  <si>
+    <t>污泥</t>
+  </si>
+  <si>
+    <t>污泥帶濾式脫水機</t>
+  </si>
+  <si>
+    <t>進泥 95~98% → 出泥 80~88% (餅) + 濾液</t>
+  </si>
+  <si>
+    <t>污泥濃縮設施</t>
+  </si>
+  <si>
+    <t>進泥 99.5% → 出泥 95~98% (重力濃縮)</t>
+  </si>
+  <si>
+    <t>再生劑 (酸/鹼)</t>
+  </si>
+  <si>
+    <t>特定離子 (Na+/Ca2+/重金屬)</t>
+  </si>
+  <si>
+    <t>SS, pH</t>
+  </si>
+  <si>
+    <t>離子交換, 接觸時間應 ≥ 15 min, 更換頻率視穿透曲線</t>
+  </si>
+  <si>
+    <t>砂濾器</t>
+  </si>
+  <si>
+    <t>溶解性物質</t>
+  </si>
+  <si>
+    <t>砂濾去除 SS; 濾速 5~15 m³/m²·d, 反洗週期視壓降</t>
+  </si>
+  <si>
+    <t>混凝劑 + 加壓空氣</t>
+  </si>
+  <si>
+    <t>DAF; 氣固比 0.005~0.02, 表面溢流率 &lt; 8 m³/m²·hr</t>
+  </si>
+  <si>
+    <t>油脂分離槽</t>
+  </si>
+  <si>
+    <t>無 (重力分離)</t>
+  </si>
+  <si>
+    <t>油脂</t>
+  </si>
+  <si>
+    <t>重力油水分離; 表面溢流率 &lt; 2 m³/m²·hr</t>
+  </si>
+  <si>
+    <t>SS, 重金屬, 油脂, 水溫</t>
+  </si>
+  <si>
+    <t>匯流分離: 收前段副流 + 加藥沉澱 + 污泥獨立排出。100% 去除常見但需確認污泥側是否實際排出</t>
+  </si>
+  <si>
     <t>編號</t>
   </si>
   <si>
@@ -6409,9 +6577,6 @@
     <t>D-DOSE-001</t>
   </si>
   <si>
-    <t>鎳系</t>
-  </si>
-  <si>
     <t>NaOH</t>
   </si>
   <si>
@@ -6736,15 +6901,9 @@
     <t>118</t>
   </si>
   <si>
-    <t>油脂分離槽</t>
-  </si>
-  <si>
     <t>119</t>
   </si>
   <si>
-    <t>預處理池</t>
-  </si>
-  <si>
     <t>120</t>
   </si>
   <si>
@@ -6994,9 +7153,6 @@
     <t>231</t>
   </si>
   <si>
-    <t>鉻系還原槽</t>
-  </si>
-  <si>
     <t>二級_鉻系</t>
   </si>
   <si>
@@ -7099,9 +7255,6 @@
     <t>304</t>
   </si>
   <si>
-    <t>砂濾器</t>
-  </si>
-  <si>
     <t>305</t>
   </si>
   <si>
@@ -7303,9 +7456,6 @@
     <t>污泥掏洗</t>
   </si>
   <si>
-    <t>污泥</t>
-  </si>
-  <si>
     <t>502</t>
   </si>
   <si>
@@ -7321,9 +7471,6 @@
     <t>504</t>
   </si>
   <si>
-    <t>污泥離心式脫水機</t>
-  </si>
-  <si>
     <t>505</t>
   </si>
   <si>
@@ -7333,9 +7480,6 @@
     <t>506</t>
   </si>
   <si>
-    <t>污泥帶濾式脫水機</t>
-  </si>
-  <si>
     <t>507</t>
   </si>
   <si>
@@ -7355,9 +7499,6 @@
   </si>
   <si>
     <t>510</t>
-  </si>
-  <si>
-    <t>污泥濃縮設施</t>
   </si>
   <si>
     <t>599</t>
@@ -7917,7 +8058,7 @@
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
-  <x18tc:person displayName="Faye Tsai" id="{dcafed0d-9573-4718-9329-e83cbb91b281}" providerId="google-sheets"/>
+  <x18tc:person displayName="Faye Tsai" id="{6161c5e8-0e2f-47f6-a450-b61a99797b8e}" providerId="google-sheets"/>
 </x18tc:personList>
 </file>
 
@@ -8164,11 +8305,11 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <x18tc:ThreadedComments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:xltc2="http://schemas.microsoft.com/office/spreadsheetml/2020/threadedcomments2" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <x18tc:threadedComment ref="C10" dT="2026-06-04T08:43:26.00" personId="{dcafed0d-9573-4718-9329-e83cbb91b281}" id="{5aaed787-bfd2-4c77-9119-dfe99fb76b81}" done="1">
+  <x18tc:threadedComment ref="C10" dT="2026-06-04T08:43:26.00" personId="{6161c5e8-0e2f-47f6-a450-b61a99797b8e}" id="{c85f3a2b-0517-4e84-9312-8d76d1c7f935}" done="1">
     <x18tc:text xml:space="preserve">公式為：G=(P/ (μ*V))^1/2     計算是直接把馬達功率 P(ex. P= 370 W、槽體有效容積 V = 1.17 m³、水的粘滯係數 μ = 0.001 N⋅s/m² 直接代入。
 學理標準範圍10~50S^-1</x18tc:text>
   </x18tc:threadedComment>
-  <x18tc:threadedComment ref="C2" dT="2026-06-04T07:39:16.00" personId="{dcafed0d-9573-4718-9329-e83cbb91b281}" id="{d91dee48-4ad6-4c1f-9fc0-9da73d9045b3}" done="0">
+  <x18tc:threadedComment ref="C2" dT="2026-06-04T07:39:16.00" personId="{6161c5e8-0e2f-47f6-a450-b61a99797b8e}" id="{97b27b7f-eb38-4817-96ed-38d00d1e2f51}" done="0">
     <x18tc:text xml:space="preserve">項目	常見設計去除率
 SS	80~95%
 銅(Cu)	90~99%
@@ -27717,6 +27858,28 @@
         <v>1</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="1" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>1937</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>1938</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="s">
+        <v>1939</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>1940</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>1941</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -27735,46 +27898,64 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>1936</v>
+        <v>1942</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1937</v>
+        <v>1943</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1938</v>
+        <v>1944</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1939</v>
+        <v>1945</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1940</v>
+        <v>1946</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1941</v>
+        <v>1947</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1942</v>
+        <v>1948</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>33</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>1943</v>
+        <v>1949</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>1944</v>
+        <v>1950</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>1945</v>
+        <v>1951</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>1946</v>
+        <v>1952</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>1947</v>
+        <v>1953</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>1948</v>
+        <v>1954</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>1955</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>1956</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>1957</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>1958</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>1959</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>1960</v>
       </c>
     </row>
     <row r="2">
@@ -27782,22 +27963,22 @@
         <v>116</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1949</v>
+        <v>1961</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>1950</v>
+        <v>1962</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>1951</v>
+        <v>1963</v>
       </c>
       <c r="E2" s="3">
         <v>5.0</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>1952</v>
+        <v>1964</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>1953</v>
+        <v>1965</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>44</v>
@@ -27818,30 +27999,36 @@
         <v>1</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>1954</v>
-      </c>
+        <v>1966</v>
+      </c>
+      <c r="O2" s="1"/>
+      <c r="P2" s="1"/>
+      <c r="Q2" s="1"/>
+      <c r="R2" s="1"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="1"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>1955</v>
+        <v>1967</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1949</v>
+        <v>1961</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1950</v>
+        <v>1962</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>1951</v>
+        <v>1963</v>
       </c>
       <c r="E3" s="3">
         <v>5.0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>1952</v>
+        <v>1964</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>1956</v>
+        <v>1968</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>44</v>
@@ -27862,30 +28049,36 @@
         <v>1</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>1957</v>
-      </c>
+        <v>1969</v>
+      </c>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
+      <c r="R3" s="1"/>
+      <c r="S3" s="1"/>
+      <c r="T3" s="1"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
         <v>125</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1949</v>
+        <v>1961</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>1950</v>
+        <v>1962</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>1951</v>
+        <v>1963</v>
       </c>
       <c r="E4" s="3">
         <v>5.0</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>1952</v>
+        <v>1964</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>1958</v>
+        <v>1970</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>44</v>
@@ -27906,30 +28099,36 @@
         <v>1</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>1954</v>
-      </c>
+        <v>1966</v>
+      </c>
+      <c r="O4" s="1"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
+      <c r="R4" s="1"/>
+      <c r="S4" s="1"/>
+      <c r="T4" s="1"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>1959</v>
+        <v>1971</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1960</v>
+        <v>1972</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>1961</v>
+        <v>1973</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>1951</v>
+        <v>1963</v>
       </c>
       <c r="E5" s="3">
         <v>5.0</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>1952</v>
+        <v>1964</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>1962</v>
+        <v>1974</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>44</v>
@@ -27950,30 +28149,36 @@
         <v>1000.0</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>1954</v>
-      </c>
+        <v>1966</v>
+      </c>
+      <c r="O5" s="1"/>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
+      <c r="R5" s="1"/>
+      <c r="S5" s="1"/>
+      <c r="T5" s="1"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
+        <v>1975</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>1972</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>1973</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>1963</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>1960</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>1961</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>1951</v>
       </c>
       <c r="E6" s="3">
         <v>5.0</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>1952</v>
+        <v>1964</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>1964</v>
+        <v>1976</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>44</v>
@@ -27994,30 +28199,36 @@
         <v>1000.0</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>1957</v>
-      </c>
+        <v>1969</v>
+      </c>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="1"/>
+      <c r="S6" s="1"/>
+      <c r="T6" s="1"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
         <v>149</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1965</v>
+        <v>1977</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>1966</v>
+        <v>1978</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>1951</v>
+        <v>1963</v>
       </c>
       <c r="E7" s="3">
         <v>5.0</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>1952</v>
+        <v>1964</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>1967</v>
+        <v>1979</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>44</v>
@@ -28038,30 +28249,36 @@
         <v>1000.0</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>1954</v>
-      </c>
+        <v>1966</v>
+      </c>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="1"/>
+      <c r="S7" s="1"/>
+      <c r="T7" s="1"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
-        <v>1968</v>
+        <v>1980</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>1965</v>
+        <v>1977</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>1966</v>
+        <v>1978</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>1951</v>
+        <v>1963</v>
       </c>
       <c r="E8" s="3">
         <v>5.0</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>1952</v>
+        <v>1964</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>1969</v>
+        <v>1981</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>44</v>
@@ -28082,30 +28299,36 @@
         <v>1000.0</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>1954</v>
-      </c>
+        <v>1966</v>
+      </c>
+      <c r="O8" s="1"/>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
+      <c r="R8" s="1"/>
+      <c r="S8" s="1"/>
+      <c r="T8" s="1"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
         <v>163</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1970</v>
+        <v>1982</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>1966</v>
+        <v>1978</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>1951</v>
+        <v>1963</v>
       </c>
       <c r="E9" s="1">
         <v>0.0</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>1952</v>
+        <v>1964</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>1971</v>
+        <v>1983</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>44</v>
@@ -28126,30 +28349,36 @@
         <v>50.0</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>1954</v>
-      </c>
+        <v>1966</v>
+      </c>
+      <c r="O9" s="1"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
+      <c r="R9" s="1"/>
+      <c r="S9" s="1"/>
+      <c r="T9" s="1"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
-        <v>1972</v>
+        <v>1984</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>1970</v>
+        <v>1982</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>1966</v>
+        <v>1978</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>1951</v>
+        <v>1963</v>
       </c>
       <c r="E10" s="1">
         <v>0.0</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>1952</v>
+        <v>1964</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>1973</v>
+        <v>1985</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>44</v>
@@ -28170,30 +28399,36 @@
         <v>50.0</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>1954</v>
-      </c>
+        <v>1966</v>
+      </c>
+      <c r="O10" s="1"/>
+      <c r="P10" s="1"/>
+      <c r="Q10" s="1"/>
+      <c r="R10" s="1"/>
+      <c r="S10" s="1"/>
+      <c r="T10" s="1"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
         <v>152</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>1974</v>
+        <v>1986</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>1975</v>
+        <v>1987</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>1976</v>
+        <v>1988</v>
       </c>
       <c r="E11" s="3">
         <v>10.0</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>1952</v>
+        <v>1964</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>1977</v>
+        <v>1989</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>44</v>
@@ -28214,30 +28449,48 @@
         <v>1</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>1978</v>
+        <v>1990</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T11" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
-        <v>1979</v>
+        <v>1991</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>1974</v>
+        <v>1986</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>1975</v>
+        <v>1987</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>1976</v>
+        <v>1988</v>
       </c>
       <c r="E12" s="3">
         <v>10.0</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>1952</v>
+        <v>1964</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>1980</v>
+        <v>1992</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>44</v>
@@ -28258,30 +28511,36 @@
         <v>1</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>1978</v>
-      </c>
+        <v>1990</v>
+      </c>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1"/>
+      <c r="R12" s="1"/>
+      <c r="S12" s="1"/>
+      <c r="T12" s="1"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>1981</v>
+        <v>1993</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>1982</v>
+        <v>1994</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>1983</v>
+        <v>1995</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>1984</v>
+        <v>1996</v>
       </c>
       <c r="E13" s="3">
         <v>10.0</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>1952</v>
+        <v>1964</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>1985</v>
+        <v>1997</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>44</v>
@@ -28302,30 +28561,36 @@
         <v>1</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>1978</v>
-      </c>
+        <v>1990</v>
+      </c>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+      <c r="Q13" s="1"/>
+      <c r="R13" s="1"/>
+      <c r="S13" s="1"/>
+      <c r="T13" s="1"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
         <v>154</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>1986</v>
+        <v>1998</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>1903</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>1987</v>
+        <v>1999</v>
       </c>
       <c r="E14" s="3">
         <v>10.0</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>1952</v>
+        <v>1964</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>1988</v>
+        <v>2000</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>44</v>
@@ -28346,30 +28611,36 @@
         <v>1</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>1978</v>
-      </c>
+        <v>1990</v>
+      </c>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1"/>
+      <c r="R14" s="1"/>
+      <c r="S14" s="1"/>
+      <c r="T14" s="1"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
         <v>237</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>1989</v>
+        <v>2001</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>1990</v>
+        <v>2002</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>1991</v>
+        <v>2003</v>
       </c>
       <c r="E15" s="3">
         <v>15.0</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>1952</v>
+        <v>1964</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>1992</v>
+        <v>2004</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>44</v>
@@ -28390,30 +28661,36 @@
         <v>1</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>1978</v>
-      </c>
+        <v>1990</v>
+      </c>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1"/>
+      <c r="S15" s="1"/>
+      <c r="T15" s="1"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
         <v>145</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>1989</v>
+        <v>2001</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>1990</v>
+        <v>2002</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>1991</v>
+        <v>2003</v>
       </c>
       <c r="E16" s="3">
         <v>15.0</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>1952</v>
+        <v>1964</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>1993</v>
+        <v>2005</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>44</v>
@@ -28434,21 +28711,27 @@
         <v>1</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>1978</v>
-      </c>
+        <v>1990</v>
+      </c>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1"/>
+      <c r="Q16" s="1"/>
+      <c r="R16" s="1"/>
+      <c r="S16" s="1"/>
+      <c r="T16" s="1"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>1994</v>
+        <v>2006</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>1995</v>
+        <v>2007</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>1996</v>
+        <v>2008</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>1997</v>
+        <v>2009</v>
       </c>
       <c r="E17" s="3">
         <v>20.0</v>
@@ -28457,7 +28740,7 @@
         <v>263</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>1998</v>
+        <v>2010</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>44</v>
@@ -28478,30 +28761,36 @@
         <v>1</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>1978</v>
-      </c>
+        <v>1990</v>
+      </c>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1"/>
+      <c r="Q17" s="1"/>
+      <c r="R17" s="1"/>
+      <c r="S17" s="1"/>
+      <c r="T17" s="1"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="s">
         <v>200</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>1999</v>
+        <v>2011</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>2000</v>
+        <v>2012</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>2001</v>
+        <v>2013</v>
       </c>
       <c r="E18" s="3">
         <v>15.0</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>1952</v>
+        <v>1964</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>2002</v>
+        <v>2014</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>44</v>
@@ -28522,7 +28811,25 @@
         <v>1</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>2003</v>
+        <v>2015</v>
+      </c>
+      <c r="O18" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="P18" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="R18" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="S18" s="1">
+        <v>15.0</v>
+      </c>
+      <c r="T18" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -28530,22 +28837,22 @@
         <v>229</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>2004</v>
+        <v>2016</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>2005</v>
+        <v>2017</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>1984</v>
+        <v>1996</v>
       </c>
       <c r="E19" s="3">
         <v>15.0</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>1952</v>
+        <v>1964</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>2006</v>
+        <v>2018</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>44</v>
@@ -28566,30 +28873,36 @@
         <v>1</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>1954</v>
-      </c>
+        <v>1966</v>
+      </c>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1"/>
+      <c r="R19" s="1"/>
+      <c r="S19" s="1"/>
+      <c r="T19" s="1"/>
     </row>
     <row r="20">
       <c r="A20" s="1" t="s">
-        <v>2007</v>
+        <v>2019</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>2008</v>
+        <v>2020</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>2009</v>
+        <v>2021</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>1984</v>
+        <v>1996</v>
       </c>
       <c r="E20" s="3">
         <v>15.0</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>1952</v>
+        <v>1964</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>2010</v>
+        <v>2022</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>44</v>
@@ -28610,7 +28923,25 @@
         <v>1</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>2003</v>
+        <v>2015</v>
+      </c>
+      <c r="O20" s="1">
+        <v>5.0</v>
+      </c>
+      <c r="P20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T20" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -28618,13 +28949,13 @@
         <v>147</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>2011</v>
+        <v>2023</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>2012</v>
+        <v>2024</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>1951</v>
+        <v>1963</v>
       </c>
       <c r="E21" s="3">
         <v>10.0</v>
@@ -28633,7 +28964,7 @@
         <v>263</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>2013</v>
+        <v>2025</v>
       </c>
       <c r="H21" s="1" t="s">
         <v>44</v>
@@ -28654,7 +28985,25 @@
         <v>1</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>1978</v>
+        <v>1990</v>
+      </c>
+      <c r="O21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T21" s="1">
+        <v>85.0</v>
       </c>
     </row>
     <row r="22">
@@ -28662,13 +29011,13 @@
         <v>242</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>2014</v>
+        <v>2026</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>2012</v>
+        <v>2024</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>1951</v>
+        <v>1963</v>
       </c>
       <c r="E22" s="3">
         <v>10.0</v>
@@ -28677,7 +29026,7 @@
         <v>263</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>2015</v>
+        <v>2027</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>44</v>
@@ -28698,21 +29047,39 @@
         <v>1</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>1978</v>
+        <v>1990</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T22" s="1">
+        <v>99.0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>2016</v>
+        <v>2028</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>2017</v>
+        <v>2029</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>2012</v>
+        <v>2024</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>1951</v>
+        <v>1963</v>
       </c>
       <c r="E23" s="3">
         <v>15.0</v>
@@ -28721,7 +29088,7 @@
         <v>263</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>2018</v>
+        <v>2030</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>44</v>
@@ -28742,21 +29109,27 @@
         <v>1</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>1957</v>
-      </c>
+        <v>1969</v>
+      </c>
+      <c r="O23" s="1"/>
+      <c r="P23" s="1"/>
+      <c r="Q23" s="1"/>
+      <c r="R23" s="1"/>
+      <c r="S23" s="1"/>
+      <c r="T23" s="1"/>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
         <v>194</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>2019</v>
+        <v>2031</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>1951</v>
+        <v>1963</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>2020</v>
+        <v>2032</v>
       </c>
       <c r="E24" s="3">
         <v>30.0</v>
@@ -28765,7 +29138,7 @@
         <v>263</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>2021</v>
+        <v>2033</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>44</v>
@@ -28786,21 +29159,27 @@
         <v>1</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>1957</v>
-      </c>
+        <v>1969</v>
+      </c>
+      <c r="O24" s="1"/>
+      <c r="P24" s="1"/>
+      <c r="Q24" s="1"/>
+      <c r="R24" s="1"/>
+      <c r="S24" s="1"/>
+      <c r="T24" s="1"/>
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>2022</v>
+        <v>2034</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>2019</v>
+        <v>2031</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>1951</v>
+        <v>1963</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>2020</v>
+        <v>2032</v>
       </c>
       <c r="E25" s="3">
         <v>30.0</v>
@@ -28809,7 +29188,7 @@
         <v>263</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>2023</v>
+        <v>2035</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>44</v>
@@ -28830,21 +29209,27 @@
         <v>1</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>1957</v>
-      </c>
+        <v>1969</v>
+      </c>
+      <c r="O25" s="1"/>
+      <c r="P25" s="1"/>
+      <c r="Q25" s="1"/>
+      <c r="R25" s="1"/>
+      <c r="S25" s="1"/>
+      <c r="T25" s="1"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
         <v>216</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>2019</v>
+        <v>2031</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>1951</v>
+        <v>1963</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>1951</v>
+        <v>1963</v>
       </c>
       <c r="E26" s="3">
         <v>30.0</v>
@@ -28853,7 +29238,7 @@
         <v>263</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>2023</v>
+        <v>2035</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>44</v>
@@ -28874,21 +29259,27 @@
         <v>1</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>1957</v>
-      </c>
+        <v>1969</v>
+      </c>
+      <c r="O26" s="1"/>
+      <c r="P26" s="1"/>
+      <c r="Q26" s="1"/>
+      <c r="R26" s="1"/>
+      <c r="S26" s="1"/>
+      <c r="T26" s="1"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
         <v>121</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>2019</v>
+        <v>2031</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>1951</v>
+        <v>1963</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>2020</v>
+        <v>2032</v>
       </c>
       <c r="E27" s="3">
         <v>30.0</v>
@@ -28897,7 +29288,7 @@
         <v>263</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>2024</v>
+        <v>2036</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>44</v>
@@ -28918,21 +29309,27 @@
         <v>1</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>1957</v>
-      </c>
+        <v>1969</v>
+      </c>
+      <c r="O27" s="1"/>
+      <c r="P27" s="1"/>
+      <c r="Q27" s="1"/>
+      <c r="R27" s="1"/>
+      <c r="S27" s="1"/>
+      <c r="T27" s="1"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>2025</v>
+        <v>2037</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>2019</v>
+        <v>2031</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>1951</v>
+        <v>1963</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>2020</v>
+        <v>2032</v>
       </c>
       <c r="E28" s="3">
         <v>30.0</v>
@@ -28941,7 +29338,7 @@
         <v>263</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>2026</v>
+        <v>2038</v>
       </c>
       <c r="H28" s="1" t="s">
         <v>44</v>
@@ -28962,21 +29359,27 @@
         <v>1</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>1957</v>
-      </c>
+        <v>1969</v>
+      </c>
+      <c r="O28" s="1"/>
+      <c r="P28" s="1"/>
+      <c r="Q28" s="1"/>
+      <c r="R28" s="1"/>
+      <c r="S28" s="1"/>
+      <c r="T28" s="1"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
         <v>141</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>2027</v>
+        <v>2039</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>2028</v>
+        <v>2040</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>2028</v>
+        <v>2040</v>
       </c>
       <c r="E29" s="3">
         <v>20.0</v>
@@ -28985,7 +29388,7 @@
         <v>263</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>2029</v>
+        <v>2041</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>44</v>
@@ -29006,30 +29409,36 @@
         <v>1</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>1954</v>
-      </c>
+        <v>1966</v>
+      </c>
+      <c r="O29" s="1"/>
+      <c r="P29" s="1"/>
+      <c r="Q29" s="1"/>
+      <c r="R29" s="1"/>
+      <c r="S29" s="1"/>
+      <c r="T29" s="1"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
         <v>128</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>2017</v>
+        <v>2029</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>2030</v>
+        <v>2042</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>1951</v>
+        <v>1963</v>
       </c>
       <c r="E30" s="3">
         <v>5.0</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>1952</v>
+        <v>1964</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>2031</v>
+        <v>2043</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>44</v>
@@ -29050,47 +29459,820 @@
         <v>1</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>1957</v>
-      </c>
+        <v>1969</v>
+      </c>
+      <c r="O30" s="1"/>
+      <c r="P30" s="1"/>
+      <c r="Q30" s="1"/>
+      <c r="R30" s="1"/>
+      <c r="S30" s="1"/>
+      <c r="T30" s="1"/>
     </row>
     <row r="31">
-      <c r="N31" s="7"/>
+      <c r="A31" s="1" t="s">
+        <v>2044</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>2046</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E31" s="3">
+        <v>15.0</v>
+      </c>
+      <c r="F31" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>2048</v>
+      </c>
+      <c r="H31" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I31" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="J31" s="3">
+        <v>24.0</v>
+      </c>
+      <c r="K31" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L31" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M31" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N31" s="1" t="s">
+        <v>2015</v>
+      </c>
+      <c r="O31" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="P31" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q31" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R31" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S31" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T31" s="1" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="32">
-      <c r="N32" s="7"/>
+      <c r="A32" s="1" t="s">
+        <v>2049</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>2050</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>2051</v>
+      </c>
+      <c r="E32" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>2052</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I32" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="J32" s="3">
+        <v>24.0</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N32" s="1" t="s">
+        <v>2015</v>
+      </c>
+      <c r="O32" s="3">
+        <v>1.5</v>
+      </c>
+      <c r="P32" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>0.3</v>
+      </c>
+      <c r="R32" s="3">
+        <v>15.0</v>
+      </c>
+      <c r="S32" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="T32" s="1" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="33">
-      <c r="N33" s="7"/>
+      <c r="A33" s="1" t="s">
+        <v>2053</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>2054</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>2055</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>2047</v>
+      </c>
+      <c r="E33" s="3">
+        <v>15.0</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>1964</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>2056</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I33" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="J33" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="K33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N33" s="1" t="s">
+        <v>1966</v>
+      </c>
+      <c r="O33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S33" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T33" s="1" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="34">
-      <c r="N34" s="7"/>
+      <c r="A34" s="1" t="s">
+        <v>2057</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>2058</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>2059</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>2060</v>
+      </c>
+      <c r="E34" s="3">
+        <v>15.0</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>1964</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>2061</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I34" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="J34" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N34" s="1" t="s">
+        <v>1966</v>
+      </c>
+      <c r="O34" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P34" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q34" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R34" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S34" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T34" s="1" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="35">
-      <c r="N35" s="7"/>
+      <c r="A35" s="1" t="s">
+        <v>2062</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>2063</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>1978</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>1963</v>
+      </c>
+      <c r="E35" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="F35" s="1" t="s">
+        <v>1964</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>2064</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I35" s="3">
+        <v>0.083</v>
+      </c>
+      <c r="J35" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L35" s="3">
+        <v>30.0</v>
+      </c>
+      <c r="M35" s="3">
+        <v>80.0</v>
+      </c>
+      <c r="N35" s="1" t="s">
+        <v>1966</v>
+      </c>
+      <c r="O35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S35" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T35" s="1" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="36">
-      <c r="N36" s="7"/>
+      <c r="A36" s="1" t="s">
+        <v>2065</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>2066</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>2024</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>1963</v>
+      </c>
+      <c r="E36" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>2067</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L36" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M36" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N36" s="1" t="s">
+        <v>2068</v>
+      </c>
+      <c r="O36" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P36" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q36" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R36" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S36" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T36" s="3">
+        <v>85.0</v>
+      </c>
     </row>
     <row r="37">
-      <c r="N37" s="7"/>
+      <c r="A37" s="1" t="s">
+        <v>2069</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>2066</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>2024</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>1963</v>
+      </c>
+      <c r="E37" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>2070</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L37" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M37" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N37" s="1" t="s">
+        <v>2068</v>
+      </c>
+      <c r="O37" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P37" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q37" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R37" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S37" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T37" s="3">
+        <v>88.0</v>
+      </c>
     </row>
     <row r="38">
-      <c r="N38" s="7"/>
+      <c r="A38" s="1" t="s">
+        <v>2071</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>2026</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>2024</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>1963</v>
+      </c>
+      <c r="E38" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>2072</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K38" s="3">
+        <v>24.0</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M38" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N38" s="1" t="s">
+        <v>2068</v>
+      </c>
+      <c r="O38" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P38" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q38" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R38" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S38" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T38" s="3">
+        <v>98.0</v>
+      </c>
     </row>
     <row r="39">
-      <c r="N39" s="7"/>
+      <c r="A39" s="1" t="s">
+        <v>2006</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>2073</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>2074</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>2075</v>
+      </c>
+      <c r="E39" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>2076</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I39" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="J39" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K39" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L39" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M39" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N39" s="1" t="s">
+        <v>1990</v>
+      </c>
+      <c r="O39" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P39" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q39" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R39" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S39" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T39" s="1" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="40">
-      <c r="N40" s="7"/>
+      <c r="A40" s="1" t="s">
+        <v>2077</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>2045</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>1903</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>2078</v>
+      </c>
+      <c r="E40" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>1964</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>2079</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I40" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J40" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K40" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L40" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M40" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N40" s="1" t="s">
+        <v>1990</v>
+      </c>
+      <c r="O40" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P40" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q40" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R40" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S40" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T40" s="1" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="41">
-      <c r="N41" s="7"/>
+      <c r="A41" s="1" t="s">
+        <v>1993</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>2080</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>1995</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>2078</v>
+      </c>
+      <c r="E41" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>1964</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>2081</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I41" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="J41" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="K41" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="L41" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M41" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N41" s="1" t="s">
+        <v>1990</v>
+      </c>
+      <c r="O41" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P41" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q41" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R41" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S41" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T41" s="1" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="42">
-      <c r="N42" s="7"/>
+      <c r="A42" s="1" t="s">
+        <v>2082</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>2083</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>2084</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>2078</v>
+      </c>
+      <c r="E42" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>2085</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I42" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="K42" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M42" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N42" s="1" t="s">
+        <v>1990</v>
+      </c>
+      <c r="O42" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P42" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q42" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R42" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S42" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T42" s="1" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="43">
-      <c r="N43" s="7"/>
+      <c r="A43" s="1" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>2063</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>2086</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>1963</v>
+      </c>
+      <c r="E43" s="3">
+        <v>20.0</v>
+      </c>
+      <c r="F43" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>2087</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K43" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="L43" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="M43" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N43" s="1" t="s">
+        <v>1990</v>
+      </c>
+      <c r="O43" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="P43" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q43" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="R43" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="S43" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T43" s="1" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="44">
       <c r="N44" s="7"/>
@@ -31071,63 +32253,63 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="10" t="s">
-        <v>2032</v>
+        <v>2088</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>2033</v>
+        <v>2089</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>2034</v>
+        <v>2090</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>2035</v>
+        <v>2091</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>2036</v>
+        <v>2092</v>
       </c>
       <c r="F1" s="10" t="s">
-        <v>2037</v>
+        <v>2093</v>
       </c>
       <c r="G1" s="10" t="s">
-        <v>2038</v>
+        <v>2094</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>2039</v>
+        <v>2095</v>
       </c>
       <c r="I1" s="10" t="s">
-        <v>2040</v>
+        <v>2096</v>
       </c>
       <c r="J1" s="10" t="s">
-        <v>2041</v>
+        <v>2097</v>
       </c>
       <c r="K1" s="10" t="s">
-        <v>2042</v>
+        <v>2098</v>
       </c>
       <c r="L1" s="10" t="s">
-        <v>2043</v>
+        <v>2099</v>
       </c>
       <c r="M1" s="10" t="s">
-        <v>2044</v>
+        <v>2100</v>
       </c>
       <c r="N1" s="10" t="s">
-        <v>2045</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="11" t="s">
-        <v>2046</v>
+        <v>2102</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>2047</v>
+        <v>1939</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>1955</v>
+        <v>1967</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>2048</v>
+        <v>2103</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>2049</v>
+        <v>2104</v>
       </c>
       <c r="F2" s="13">
         <v>1.0</v>
@@ -31148,30 +32330,30 @@
         <v>11.0</v>
       </c>
       <c r="L2" s="11" t="s">
-        <v>2050</v>
+        <v>2105</v>
       </c>
       <c r="M2" s="12" t="s">
-        <v>2051</v>
+        <v>2106</v>
       </c>
       <c r="N2" s="11" t="s">
-        <v>2052</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="11" t="s">
-        <v>2053</v>
+        <v>2108</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>2047</v>
+        <v>1939</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>1955</v>
+        <v>1967</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>2054</v>
+        <v>2109</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>2049</v>
+        <v>2104</v>
       </c>
       <c r="F3" s="13">
         <v>2.0</v>
@@ -31192,30 +32374,30 @@
         <v>11.0</v>
       </c>
       <c r="L3" s="11" t="s">
-        <v>2050</v>
+        <v>2105</v>
       </c>
       <c r="M3" s="12" t="s">
-        <v>2051</v>
+        <v>2106</v>
       </c>
       <c r="N3" s="11" t="s">
-        <v>2055</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="11" t="s">
-        <v>2056</v>
+        <v>2111</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>2047</v>
+        <v>1939</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>1955</v>
+        <v>1967</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>440</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>2057</v>
+        <v>2112</v>
       </c>
       <c r="F4" s="11" t="s">
         <v>1</v>
@@ -31242,24 +32424,24 @@
         <v>1</v>
       </c>
       <c r="N4" s="11" t="s">
-        <v>2058</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="11" t="s">
-        <v>2059</v>
+        <v>2114</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>2047</v>
+        <v>1939</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>1955</v>
+        <v>1967</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>2060</v>
+        <v>2115</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>2057</v>
+        <v>2112</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>1</v>
@@ -31286,24 +32468,24 @@
         <v>1</v>
       </c>
       <c r="N5" s="11" t="s">
-        <v>2061</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="11" t="s">
-        <v>2062</v>
+        <v>2117</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>2063</v>
+        <v>2118</v>
       </c>
       <c r="C6" s="11" t="s">
         <v>125</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>2048</v>
+        <v>2103</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>2049</v>
+        <v>2104</v>
       </c>
       <c r="F6" s="13">
         <v>0.1</v>
@@ -31324,30 +32506,30 @@
         <v>8.0</v>
       </c>
       <c r="L6" s="11" t="s">
-        <v>2064</v>
+        <v>2119</v>
       </c>
       <c r="M6" s="12" t="s">
-        <v>2065</v>
+        <v>2120</v>
       </c>
       <c r="N6" s="11" t="s">
-        <v>2066</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="11" t="s">
-        <v>2067</v>
+        <v>2122</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>2063</v>
+        <v>2118</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>125</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>2068</v>
+        <v>2123</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>2049</v>
+        <v>2104</v>
       </c>
       <c r="F7" s="13">
         <v>0.1</v>
@@ -31368,30 +32550,30 @@
         <v>8.0</v>
       </c>
       <c r="L7" s="11" t="s">
-        <v>2069</v>
+        <v>2124</v>
       </c>
       <c r="M7" s="12" t="s">
-        <v>2065</v>
+        <v>2120</v>
       </c>
       <c r="N7" s="11" t="s">
-        <v>2070</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="11" t="s">
-        <v>2071</v>
+        <v>2126</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>2063</v>
+        <v>2118</v>
       </c>
       <c r="C8" s="11" t="s">
         <v>125</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>2072</v>
+        <v>2127</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>2049</v>
+        <v>2104</v>
       </c>
       <c r="F8" s="13">
         <v>0.1</v>
@@ -31412,21 +32594,21 @@
         <v>8.0</v>
       </c>
       <c r="L8" s="11" t="s">
-        <v>2069</v>
+        <v>2124</v>
       </c>
       <c r="M8" s="12" t="s">
-        <v>2065</v>
+        <v>2120</v>
       </c>
       <c r="N8" s="11" t="s">
-        <v>2070</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="11" t="s">
-        <v>2073</v>
+        <v>2128</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>2063</v>
+        <v>2118</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>125</v>
@@ -31435,7 +32617,7 @@
         <v>440</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>2057</v>
+        <v>2112</v>
       </c>
       <c r="F9" s="11" t="s">
         <v>1</v>
@@ -31462,24 +32644,24 @@
         <v>1</v>
       </c>
       <c r="N9" s="11" t="s">
-        <v>2074</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="11" t="s">
-        <v>2075</v>
+        <v>2130</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>439</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>1968</v>
+        <v>1980</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>440</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>2049</v>
+        <v>2104</v>
       </c>
       <c r="F10" s="13">
         <v>0.05</v>
@@ -31500,18 +32682,18 @@
         <v>1</v>
       </c>
       <c r="L10" s="11" t="s">
-        <v>2076</v>
+        <v>2131</v>
       </c>
       <c r="M10" s="12" t="s">
-        <v>2065</v>
+        <v>2120</v>
       </c>
       <c r="N10" s="11" t="s">
-        <v>2077</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="11" t="s">
-        <v>2078</v>
+        <v>2133</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>439</v>
@@ -31520,10 +32702,10 @@
         <v>163</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>2079</v>
+        <v>2134</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>2049</v>
+        <v>2104</v>
       </c>
       <c r="F11" s="13">
         <v>5.0E-4</v>
@@ -31544,30 +32726,30 @@
         <v>1</v>
       </c>
       <c r="L11" s="11" t="s">
-        <v>2080</v>
+        <v>2135</v>
       </c>
       <c r="M11" s="12" t="s">
-        <v>2065</v>
+        <v>2120</v>
       </c>
       <c r="N11" s="11" t="s">
-        <v>2081</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="11" t="s">
-        <v>2082</v>
+        <v>2137</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>439</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>2083</v>
+        <v>2138</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>2084</v>
+        <v>2139</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>2049</v>
+        <v>2104</v>
       </c>
       <c r="F12" s="13">
         <v>0.05</v>
@@ -31588,30 +32770,30 @@
         <v>1</v>
       </c>
       <c r="L12" s="11" t="s">
-        <v>2085</v>
+        <v>2140</v>
       </c>
       <c r="M12" s="12" t="s">
-        <v>2065</v>
+        <v>2120</v>
       </c>
       <c r="N12" s="11" t="s">
-        <v>2086</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="11" t="s">
-        <v>2087</v>
+        <v>2142</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>2088</v>
+        <v>2143</v>
       </c>
       <c r="C13" s="11" t="s">
         <v>229</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>2089</v>
+        <v>2144</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>2049</v>
+        <v>2104</v>
       </c>
       <c r="F13" s="13">
         <v>1.0</v>
@@ -31632,30 +32814,30 @@
         <v>11.0</v>
       </c>
       <c r="L13" s="11" t="s">
-        <v>2090</v>
+        <v>2145</v>
       </c>
       <c r="M13" s="12" t="s">
-        <v>2065</v>
+        <v>2120</v>
       </c>
       <c r="N13" s="11" t="s">
-        <v>2091</v>
+        <v>2146</v>
       </c>
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="11" t="s">
-        <v>2092</v>
+        <v>2147</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>2088</v>
+        <v>2143</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>229</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>2093</v>
+        <v>2148</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>2049</v>
+        <v>2104</v>
       </c>
       <c r="F14" s="13">
         <v>0.5</v>
@@ -31676,30 +32858,30 @@
         <v>11.0</v>
       </c>
       <c r="L14" s="11" t="s">
-        <v>2094</v>
+        <v>2149</v>
       </c>
       <c r="M14" s="12" t="s">
-        <v>2065</v>
+        <v>2120</v>
       </c>
       <c r="N14" s="11" t="s">
-        <v>2095</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="11" t="s">
-        <v>2096</v>
+        <v>2151</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>2097</v>
+        <v>2152</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>2098</v>
+        <v>2153</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>2099</v>
+        <v>2154</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>2049</v>
+        <v>2104</v>
       </c>
       <c r="F15" s="13">
         <v>1.0</v>
@@ -31720,30 +32902,30 @@
         <v>3.0</v>
       </c>
       <c r="L15" s="11" t="s">
-        <v>2100</v>
+        <v>2155</v>
       </c>
       <c r="M15" s="12" t="s">
-        <v>2065</v>
+        <v>2120</v>
       </c>
       <c r="N15" s="11" t="s">
-        <v>2101</v>
+        <v>2156</v>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="11" t="s">
-        <v>2102</v>
+        <v>2157</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>2097</v>
+        <v>2152</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>2098</v>
+        <v>2153</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>2103</v>
+        <v>2158</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>2049</v>
+        <v>2104</v>
       </c>
       <c r="F16" s="13">
         <v>1.0</v>
@@ -31764,30 +32946,30 @@
         <v>3.0</v>
       </c>
       <c r="L16" s="11" t="s">
-        <v>2100</v>
+        <v>2155</v>
       </c>
       <c r="M16" s="12" t="s">
-        <v>2065</v>
+        <v>2120</v>
       </c>
       <c r="N16" s="11" t="s">
-        <v>2104</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="11" t="s">
-        <v>2105</v>
+        <v>2160</v>
       </c>
       <c r="B17" s="12" t="s">
-        <v>2106</v>
+        <v>2161</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>2107</v>
+        <v>2162</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>2103</v>
+        <v>2158</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>2049</v>
+        <v>2104</v>
       </c>
       <c r="F17" s="13">
         <v>0.5</v>
@@ -31808,30 +32990,30 @@
         <v>10.0</v>
       </c>
       <c r="L17" s="11" t="s">
-        <v>2108</v>
+        <v>2163</v>
       </c>
       <c r="M17" s="12" t="s">
-        <v>2051</v>
+        <v>2106</v>
       </c>
       <c r="N17" s="11" t="s">
-        <v>2109</v>
+        <v>2164</v>
       </c>
     </row>
     <row r="18" ht="22.5" customHeight="1">
       <c r="A18" s="11" t="s">
-        <v>2110</v>
+        <v>2165</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>2106</v>
+        <v>2161</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>2111</v>
+        <v>2166</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>2089</v>
+        <v>2144</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>2049</v>
+        <v>2104</v>
       </c>
       <c r="F18" s="13">
         <v>0.01</v>
@@ -31852,30 +33034,30 @@
         <v>8.0</v>
       </c>
       <c r="L18" s="11" t="s">
-        <v>2112</v>
+        <v>2167</v>
       </c>
       <c r="M18" s="12" t="s">
-        <v>2065</v>
+        <v>2120</v>
       </c>
       <c r="N18" s="11" t="s">
-        <v>2113</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1">
       <c r="A19" s="11" t="s">
-        <v>2114</v>
+        <v>2169</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>2106</v>
+        <v>2161</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>1955</v>
+        <v>1967</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>2048</v>
+        <v>2103</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>2049</v>
+        <v>2104</v>
       </c>
       <c r="F19" s="13">
         <v>0.5</v>
@@ -31896,13 +33078,13 @@
         <v>8.0</v>
       </c>
       <c r="L19" s="11" t="s">
-        <v>2115</v>
+        <v>2170</v>
       </c>
       <c r="M19" s="12" t="s">
-        <v>2065</v>
+        <v>2120</v>
       </c>
       <c r="N19" s="11" t="s">
-        <v>2116</v>
+        <v>2171</v>
       </c>
     </row>
     <row r="20">
@@ -35869,13 +37051,13 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="14" t="s">
-        <v>2117</v>
+        <v>2172</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>2118</v>
+        <v>2173</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>2119</v>
+        <v>2174</v>
       </c>
       <c r="D1" s="14" t="s">
         <v>95</v>
@@ -35883,13 +37065,13 @@
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="15" t="s">
-        <v>2120</v>
+        <v>2175</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>2121</v>
+        <v>2176</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>2122</v>
+        <v>2177</v>
       </c>
       <c r="D2" s="11" t="s">
         <v>1</v>
@@ -35897,13 +37079,13 @@
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="15" t="s">
-        <v>2123</v>
+        <v>2178</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>2124</v>
+        <v>2179</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>2122</v>
+        <v>2177</v>
       </c>
       <c r="D3" s="11" t="s">
         <v>1</v>
@@ -35911,13 +37093,13 @@
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="15" t="s">
-        <v>2125</v>
+        <v>2180</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>2126</v>
+        <v>2181</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>2122</v>
+        <v>2177</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>1</v>
@@ -35925,13 +37107,13 @@
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="15" t="s">
-        <v>2127</v>
+        <v>2182</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>2128</v>
+        <v>2183</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>2122</v>
+        <v>2177</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>1</v>
@@ -35939,13 +37121,13 @@
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="15" t="s">
-        <v>2129</v>
+        <v>2184</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>2130</v>
+        <v>2185</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>2122</v>
+        <v>2177</v>
       </c>
       <c r="D6" s="11" t="s">
         <v>1</v>
@@ -35953,13 +37135,13 @@
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="15" t="s">
-        <v>2131</v>
+        <v>2186</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>2132</v>
+        <v>2187</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>2122</v>
+        <v>2177</v>
       </c>
       <c r="D7" s="11" t="s">
         <v>1</v>
@@ -35967,13 +37149,13 @@
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="15" t="s">
-        <v>2133</v>
+        <v>2188</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>2134</v>
+        <v>2189</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>2122</v>
+        <v>2177</v>
       </c>
       <c r="D8" s="11" t="s">
         <v>1</v>
@@ -35981,13 +37163,13 @@
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="15" t="s">
-        <v>2135</v>
+        <v>2190</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>2136</v>
+        <v>2191</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>2122</v>
+        <v>2177</v>
       </c>
       <c r="D9" s="11" t="s">
         <v>1</v>
@@ -35995,13 +37177,13 @@
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="15" t="s">
-        <v>2137</v>
+        <v>2192</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>2138</v>
+        <v>2193</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>2122</v>
+        <v>2177</v>
       </c>
       <c r="D10" s="11" t="s">
         <v>1</v>
@@ -36009,13 +37191,13 @@
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="15" t="s">
-        <v>2139</v>
+        <v>2194</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>2140</v>
+        <v>2195</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>2122</v>
+        <v>2177</v>
       </c>
       <c r="D11" s="11" t="s">
         <v>1</v>
@@ -36023,13 +37205,13 @@
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="15" t="s">
-        <v>2141</v>
+        <v>2196</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>2142</v>
+        <v>2197</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>2122</v>
+        <v>2177</v>
       </c>
       <c r="D12" s="11" t="s">
         <v>1</v>
@@ -36037,13 +37219,13 @@
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="15" t="s">
-        <v>2143</v>
+        <v>2198</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>2144</v>
+        <v>2199</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>2122</v>
+        <v>2177</v>
       </c>
       <c r="D13" s="11" t="s">
         <v>1</v>
@@ -36051,13 +37233,13 @@
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="15" t="s">
-        <v>2145</v>
+        <v>2200</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>2146</v>
+        <v>2201</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>2122</v>
+        <v>2177</v>
       </c>
       <c r="D14" s="11" t="s">
         <v>1</v>
@@ -36065,13 +37247,13 @@
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="15" t="s">
-        <v>2147</v>
+        <v>2202</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>2148</v>
+        <v>2203</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>2122</v>
+        <v>2177</v>
       </c>
       <c r="D15" s="11" t="s">
         <v>1</v>
@@ -36079,13 +37261,13 @@
     </row>
     <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="15" t="s">
-        <v>2149</v>
+        <v>2204</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>2150</v>
+        <v>2205</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>2122</v>
+        <v>2177</v>
       </c>
       <c r="D16" s="11" t="s">
         <v>1</v>
@@ -36093,13 +37275,13 @@
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="15" t="s">
-        <v>2151</v>
+        <v>2206</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>2152</v>
+        <v>2207</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>2122</v>
+        <v>2177</v>
       </c>
       <c r="D17" s="11" t="s">
         <v>1</v>
@@ -36107,13 +37289,13 @@
     </row>
     <row r="18" ht="22.5" customHeight="1">
       <c r="A18" s="15" t="s">
-        <v>2153</v>
+        <v>2208</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>2154</v>
+        <v>2209</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>2122</v>
+        <v>2177</v>
       </c>
       <c r="D18" s="11" t="s">
         <v>1</v>
@@ -36121,13 +37303,13 @@
     </row>
     <row r="19" ht="22.5" customHeight="1">
       <c r="A19" s="15" t="s">
-        <v>2155</v>
+        <v>2210</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>2156</v>
+        <v>2082</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>2122</v>
+        <v>2177</v>
       </c>
       <c r="D19" s="11" t="s">
         <v>1</v>
@@ -36135,13 +37317,13 @@
     </row>
     <row r="20" ht="22.5" customHeight="1">
       <c r="A20" s="15" t="s">
-        <v>2157</v>
+        <v>2211</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>2158</v>
+        <v>1936</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>2122</v>
+        <v>2177</v>
       </c>
       <c r="D20" s="11" t="s">
         <v>1</v>
@@ -36149,13 +37331,13 @@
     </row>
     <row r="21" ht="22.5" customHeight="1">
       <c r="A21" s="15" t="s">
-        <v>2159</v>
+        <v>2212</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>2160</v>
+        <v>2213</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>2122</v>
+        <v>2177</v>
       </c>
       <c r="D21" s="11" t="s">
         <v>1</v>
@@ -36163,13 +37345,13 @@
     </row>
     <row r="22" ht="22.5" customHeight="1">
       <c r="A22" s="15" t="s">
-        <v>2161</v>
+        <v>2214</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>2162</v>
+        <v>2215</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>2122</v>
+        <v>2177</v>
       </c>
       <c r="D22" s="11" t="s">
         <v>1</v>
@@ -36177,13 +37359,13 @@
     </row>
     <row r="23" ht="22.5" customHeight="1">
       <c r="A23" s="15" t="s">
-        <v>2163</v>
+        <v>2216</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>2164</v>
+        <v>2217</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>2122</v>
+        <v>2177</v>
       </c>
       <c r="D23" s="11" t="s">
         <v>1</v>
@@ -36191,13 +37373,13 @@
     </row>
     <row r="24" ht="22.5" customHeight="1">
       <c r="A24" s="15" t="s">
-        <v>2165</v>
+        <v>2218</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>2166</v>
+        <v>2219</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>2122</v>
+        <v>2177</v>
       </c>
       <c r="D24" s="11" t="s">
         <v>1</v>
@@ -36205,13 +37387,13 @@
     </row>
     <row r="25" ht="22.5" customHeight="1">
       <c r="A25" s="15" t="s">
-        <v>2167</v>
+        <v>2220</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>2168</v>
+        <v>2221</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>2122</v>
+        <v>2177</v>
       </c>
       <c r="D25" s="11" t="s">
         <v>1</v>
@@ -36219,13 +37401,13 @@
     </row>
     <row r="26" ht="22.5" customHeight="1">
       <c r="A26" s="15" t="s">
-        <v>2169</v>
+        <v>2222</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>2170</v>
+        <v>2223</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>2122</v>
+        <v>2177</v>
       </c>
       <c r="D26" s="11" t="s">
         <v>1</v>
@@ -36233,13 +37415,13 @@
     </row>
     <row r="27" ht="22.5" customHeight="1">
       <c r="A27" s="15" t="s">
-        <v>2171</v>
+        <v>2224</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>2172</v>
+        <v>2225</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>2122</v>
+        <v>2177</v>
       </c>
       <c r="D27" s="11" t="s">
         <v>1</v>
@@ -36247,13 +37429,13 @@
     </row>
     <row r="28" ht="22.5" customHeight="1">
       <c r="A28" s="15" t="s">
-        <v>2173</v>
+        <v>2226</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>2174</v>
+        <v>2227</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>2122</v>
+        <v>2177</v>
       </c>
       <c r="D28" s="11" t="s">
         <v>1</v>
@@ -36261,13 +37443,13 @@
     </row>
     <row r="29" ht="22.5" customHeight="1">
       <c r="A29" s="15" t="s">
-        <v>2175</v>
+        <v>2228</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>2176</v>
+        <v>2229</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>2122</v>
+        <v>2177</v>
       </c>
       <c r="D29" s="11" t="s">
         <v>1</v>
@@ -36275,13 +37457,13 @@
     </row>
     <row r="30" ht="22.5" customHeight="1">
       <c r="A30" s="15" t="s">
+        <v>2230</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>2231</v>
+      </c>
+      <c r="C30" s="12" t="s">
         <v>2177</v>
-      </c>
-      <c r="B30" s="11" t="s">
-        <v>2178</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>2122</v>
       </c>
       <c r="D30" s="11" t="s">
         <v>1</v>
@@ -36289,13 +37471,13 @@
     </row>
     <row r="31" ht="22.5" customHeight="1">
       <c r="A31" s="15" t="s">
-        <v>2179</v>
+        <v>2232</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>2180</v>
+        <v>2233</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="D31" s="11" t="s">
         <v>1</v>
@@ -36303,13 +37485,13 @@
     </row>
     <row r="32" ht="22.5" customHeight="1">
       <c r="A32" s="15" t="s">
-        <v>2182</v>
+        <v>2235</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>2183</v>
+        <v>2236</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="D32" s="11" t="s">
         <v>1</v>
@@ -36317,13 +37499,13 @@
     </row>
     <row r="33" ht="22.5" customHeight="1">
       <c r="A33" s="15" t="s">
-        <v>2184</v>
+        <v>2237</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>2185</v>
+        <v>2238</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="D33" s="11" t="s">
         <v>1</v>
@@ -36331,13 +37513,13 @@
     </row>
     <row r="34" ht="22.5" customHeight="1">
       <c r="A34" s="15" t="s">
-        <v>2186</v>
+        <v>2239</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>2187</v>
+        <v>2240</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="D34" s="11" t="s">
         <v>1</v>
@@ -36345,13 +37527,13 @@
     </row>
     <row r="35" ht="22.5" customHeight="1">
       <c r="A35" s="15" t="s">
-        <v>2188</v>
+        <v>2241</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>2189</v>
+        <v>2242</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="D35" s="11" t="s">
         <v>1</v>
@@ -36359,13 +37541,13 @@
     </row>
     <row r="36" ht="22.5" customHeight="1">
       <c r="A36" s="15" t="s">
-        <v>2190</v>
+        <v>2243</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>2191</v>
+        <v>2244</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="D36" s="11" t="s">
         <v>1</v>
@@ -36373,13 +37555,13 @@
     </row>
     <row r="37" ht="22.5" customHeight="1">
       <c r="A37" s="15" t="s">
-        <v>2192</v>
+        <v>2245</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>2193</v>
+        <v>2246</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="D37" s="11" t="s">
         <v>1</v>
@@ -36387,13 +37569,13 @@
     </row>
     <row r="38" ht="22.5" customHeight="1">
       <c r="A38" s="15" t="s">
-        <v>2194</v>
+        <v>2247</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>2195</v>
+        <v>2248</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="D38" s="11" t="s">
         <v>1</v>
@@ -36401,13 +37583,13 @@
     </row>
     <row r="39" ht="22.5" customHeight="1">
       <c r="A39" s="15" t="s">
-        <v>2196</v>
+        <v>2249</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>2197</v>
+        <v>2250</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="D39" s="11" t="s">
         <v>1</v>
@@ -36415,13 +37597,13 @@
     </row>
     <row r="40" ht="22.5" customHeight="1">
       <c r="A40" s="15" t="s">
-        <v>2198</v>
+        <v>2251</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>2199</v>
+        <v>2252</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="D40" s="11" t="s">
         <v>1</v>
@@ -36429,13 +37611,13 @@
     </row>
     <row r="41" ht="22.5" customHeight="1">
       <c r="A41" s="15" t="s">
-        <v>2200</v>
+        <v>2253</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>2201</v>
+        <v>2254</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="D41" s="11" t="s">
         <v>1</v>
@@ -36443,13 +37625,13 @@
     </row>
     <row r="42" ht="22.5" customHeight="1">
       <c r="A42" s="15" t="s">
-        <v>2202</v>
+        <v>2255</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>2203</v>
+        <v>2256</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="D42" s="11" t="s">
         <v>1</v>
@@ -36457,13 +37639,13 @@
     </row>
     <row r="43" ht="22.5" customHeight="1">
       <c r="A43" s="15" t="s">
-        <v>2204</v>
+        <v>2257</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>2205</v>
+        <v>2258</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="D43" s="11" t="s">
         <v>1</v>
@@ -36471,13 +37653,13 @@
     </row>
     <row r="44" ht="22.5" customHeight="1">
       <c r="A44" s="15" t="s">
-        <v>2206</v>
+        <v>2259</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>2207</v>
+        <v>2260</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="D44" s="11" t="s">
         <v>1</v>
@@ -36485,13 +37667,13 @@
     </row>
     <row r="45" ht="22.5" customHeight="1">
       <c r="A45" s="15" t="s">
-        <v>2208</v>
+        <v>2261</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>2209</v>
+        <v>2262</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="D45" s="11" t="s">
         <v>1</v>
@@ -36499,13 +37681,13 @@
     </row>
     <row r="46" ht="22.5" customHeight="1">
       <c r="A46" s="15" t="s">
-        <v>2210</v>
+        <v>2263</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>2211</v>
+        <v>2264</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="D46" s="11" t="s">
         <v>1</v>
@@ -36513,13 +37695,13 @@
     </row>
     <row r="47" ht="22.5" customHeight="1">
       <c r="A47" s="15" t="s">
-        <v>2212</v>
+        <v>2265</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>2213</v>
+        <v>2266</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="D47" s="11" t="s">
         <v>1</v>
@@ -36527,13 +37709,13 @@
     </row>
     <row r="48" ht="22.5" customHeight="1">
       <c r="A48" s="15" t="s">
-        <v>2214</v>
+        <v>2267</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>2215</v>
+        <v>2268</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="D48" s="11" t="s">
         <v>1</v>
@@ -36541,13 +37723,13 @@
     </row>
     <row r="49" ht="22.5" customHeight="1">
       <c r="A49" s="15" t="s">
-        <v>2216</v>
+        <v>2269</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>2217</v>
+        <v>2270</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="D49" s="11" t="s">
         <v>1</v>
@@ -36555,13 +37737,13 @@
     </row>
     <row r="50" ht="22.5" customHeight="1">
       <c r="A50" s="15" t="s">
-        <v>2218</v>
+        <v>2271</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>2219</v>
+        <v>2272</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="D50" s="11" t="s">
         <v>1</v>
@@ -36569,13 +37751,13 @@
     </row>
     <row r="51" ht="22.5" customHeight="1">
       <c r="A51" s="15" t="s">
-        <v>2220</v>
+        <v>2273</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>2221</v>
+        <v>2274</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="D51" s="11" t="s">
         <v>1</v>
@@ -36583,13 +37765,13 @@
     </row>
     <row r="52" ht="22.5" customHeight="1">
       <c r="A52" s="15" t="s">
-        <v>2222</v>
+        <v>2275</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>2223</v>
+        <v>2276</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="D52" s="11" t="s">
         <v>1</v>
@@ -36597,13 +37779,13 @@
     </row>
     <row r="53" ht="22.5" customHeight="1">
       <c r="A53" s="15" t="s">
-        <v>2224</v>
+        <v>2277</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>2225</v>
+        <v>2278</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="D53" s="11" t="s">
         <v>1</v>
@@ -36611,13 +37793,13 @@
     </row>
     <row r="54" ht="22.5" customHeight="1">
       <c r="A54" s="15" t="s">
-        <v>2226</v>
+        <v>2279</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>2227</v>
+        <v>2280</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="D54" s="11" t="s">
         <v>1</v>
@@ -36625,13 +37807,13 @@
     </row>
     <row r="55" ht="22.5" customHeight="1">
       <c r="A55" s="15" t="s">
-        <v>2228</v>
+        <v>2281</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>2229</v>
+        <v>2282</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="D55" s="11" t="s">
         <v>1</v>
@@ -36639,13 +37821,13 @@
     </row>
     <row r="56" ht="22.5" customHeight="1">
       <c r="A56" s="15" t="s">
-        <v>2230</v>
+        <v>2283</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>2231</v>
+        <v>2284</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="D56" s="11" t="s">
         <v>1</v>
@@ -36653,13 +37835,13 @@
     </row>
     <row r="57" ht="22.5" customHeight="1">
       <c r="A57" s="15" t="s">
-        <v>2232</v>
+        <v>2285</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>2233</v>
+        <v>2286</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="D57" s="11" t="s">
         <v>1</v>
@@ -36667,13 +37849,13 @@
     </row>
     <row r="58" ht="22.5" customHeight="1">
       <c r="A58" s="15" t="s">
+        <v>2287</v>
+      </c>
+      <c r="B58" s="11" t="s">
+        <v>2288</v>
+      </c>
+      <c r="C58" s="12" t="s">
         <v>2234</v>
-      </c>
-      <c r="B58" s="11" t="s">
-        <v>2235</v>
-      </c>
-      <c r="C58" s="12" t="s">
-        <v>2181</v>
       </c>
       <c r="D58" s="11" t="s">
         <v>1</v>
@@ -36681,13 +37863,13 @@
     </row>
     <row r="59" ht="22.5" customHeight="1">
       <c r="A59" s="15" t="s">
-        <v>2236</v>
+        <v>2289</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>2237</v>
+        <v>2290</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>2238</v>
+        <v>2291</v>
       </c>
       <c r="D59" s="11" t="s">
         <v>1</v>
@@ -36695,13 +37877,13 @@
     </row>
     <row r="60" ht="22.5" customHeight="1">
       <c r="A60" s="15" t="s">
-        <v>2239</v>
+        <v>2292</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>2240</v>
+        <v>2293</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>2238</v>
+        <v>2291</v>
       </c>
       <c r="D60" s="11" t="s">
         <v>1</v>
@@ -36709,13 +37891,13 @@
     </row>
     <row r="61" ht="22.5" customHeight="1">
       <c r="A61" s="15" t="s">
-        <v>2241</v>
+        <v>2294</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>2242</v>
+        <v>2057</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>2243</v>
+        <v>2295</v>
       </c>
       <c r="D61" s="11" t="s">
         <v>1</v>
@@ -36723,13 +37905,13 @@
     </row>
     <row r="62" ht="22.5" customHeight="1">
       <c r="A62" s="15" t="s">
-        <v>2244</v>
+        <v>2296</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>2245</v>
+        <v>2297</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>2238</v>
+        <v>2291</v>
       </c>
       <c r="D62" s="11" t="s">
         <v>1</v>
@@ -36737,13 +37919,13 @@
     </row>
     <row r="63" ht="22.5" customHeight="1">
       <c r="A63" s="15" t="s">
-        <v>2246</v>
+        <v>2298</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>2247</v>
+        <v>2299</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>2243</v>
+        <v>2295</v>
       </c>
       <c r="D63" s="11" t="s">
         <v>1</v>
@@ -36751,13 +37933,13 @@
     </row>
     <row r="64" ht="22.5" customHeight="1">
       <c r="A64" s="15" t="s">
-        <v>2248</v>
+        <v>2300</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>2249</v>
+        <v>2301</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>2250</v>
+        <v>2302</v>
       </c>
       <c r="D64" s="11" t="s">
         <v>1</v>
@@ -36765,13 +37947,13 @@
     </row>
     <row r="65" ht="22.5" customHeight="1">
       <c r="A65" s="15" t="s">
-        <v>2251</v>
+        <v>2303</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>2252</v>
+        <v>2304</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="D65" s="11" t="s">
         <v>1</v>
@@ -36779,13 +37961,13 @@
     </row>
     <row r="66" ht="22.5" customHeight="1">
       <c r="A66" s="15" t="s">
-        <v>2253</v>
+        <v>2305</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>2254</v>
+        <v>2306</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="D66" s="11" t="s">
         <v>1</v>
@@ -36793,13 +37975,13 @@
     </row>
     <row r="67" ht="22.5" customHeight="1">
       <c r="A67" s="15" t="s">
-        <v>2255</v>
+        <v>2307</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>2256</v>
+        <v>2308</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="D67" s="11" t="s">
         <v>1</v>
@@ -36807,13 +37989,13 @@
     </row>
     <row r="68" ht="22.5" customHeight="1">
       <c r="A68" s="15" t="s">
-        <v>2257</v>
+        <v>2309</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>2258</v>
+        <v>2310</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>2238</v>
+        <v>2291</v>
       </c>
       <c r="D68" s="11" t="s">
         <v>1</v>
@@ -36821,13 +38003,13 @@
     </row>
     <row r="69" ht="22.5" customHeight="1">
       <c r="A69" s="15" t="s">
-        <v>2259</v>
+        <v>2311</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>2260</v>
+        <v>2312</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="D69" s="11" t="s">
         <v>1</v>
@@ -36835,13 +38017,13 @@
     </row>
     <row r="70" ht="22.5" customHeight="1">
       <c r="A70" s="15" t="s">
-        <v>2261</v>
+        <v>2313</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>2262</v>
+        <v>2314</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="D70" s="11" t="s">
         <v>1</v>
@@ -36849,13 +38031,13 @@
     </row>
     <row r="71" ht="22.5" customHeight="1">
       <c r="A71" s="15" t="s">
-        <v>2263</v>
+        <v>2315</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>2264</v>
+        <v>2316</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="D71" s="11" t="s">
         <v>1</v>
@@ -36863,13 +38045,13 @@
     </row>
     <row r="72" ht="22.5" customHeight="1">
       <c r="A72" s="15" t="s">
-        <v>2265</v>
+        <v>2317</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>2266</v>
+        <v>2318</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="D72" s="11" t="s">
         <v>1</v>
@@ -36877,13 +38059,13 @@
     </row>
     <row r="73" ht="22.5" customHeight="1">
       <c r="A73" s="15" t="s">
-        <v>2267</v>
+        <v>2319</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>2268</v>
+        <v>2320</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="D73" s="11" t="s">
         <v>1</v>
@@ -36894,10 +38076,10 @@
         <v>107</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>2269</v>
+        <v>2321</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="D74" s="11" t="s">
         <v>1</v>
@@ -36905,13 +38087,13 @@
     </row>
     <row r="75" ht="22.5" customHeight="1">
       <c r="A75" s="15" t="s">
-        <v>2270</v>
+        <v>2322</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>2271</v>
+        <v>2323</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>2272</v>
+        <v>2324</v>
       </c>
       <c r="D75" s="11" t="s">
         <v>1</v>
@@ -36919,13 +38101,13 @@
     </row>
     <row r="76" ht="22.5" customHeight="1">
       <c r="A76" s="15" t="s">
-        <v>2273</v>
+        <v>2325</v>
       </c>
       <c r="B76" s="11" t="s">
         <v>145</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>2272</v>
+        <v>2324</v>
       </c>
       <c r="D76" s="11" t="s">
         <v>1</v>
@@ -36933,13 +38115,13 @@
     </row>
     <row r="77" ht="22.5" customHeight="1">
       <c r="A77" s="15" t="s">
-        <v>2274</v>
+        <v>2326</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>2275</v>
+        <v>2327</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>2272</v>
+        <v>2324</v>
       </c>
       <c r="D77" s="11" t="s">
         <v>1</v>
@@ -36947,13 +38129,13 @@
     </row>
     <row r="78" ht="22.5" customHeight="1">
       <c r="A78" s="15" t="s">
-        <v>2276</v>
+        <v>2328</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>2277</v>
+        <v>2077</v>
       </c>
       <c r="C78" s="12" t="s">
-        <v>2272</v>
+        <v>2324</v>
       </c>
       <c r="D78" s="11" t="s">
         <v>1</v>
@@ -36961,13 +38143,13 @@
     </row>
     <row r="79" ht="22.5" customHeight="1">
       <c r="A79" s="15" t="s">
-        <v>2278</v>
+        <v>2329</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>2279</v>
+        <v>2330</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>2272</v>
+        <v>2324</v>
       </c>
       <c r="D79" s="11" t="s">
         <v>1</v>
@@ -36975,13 +38157,13 @@
     </row>
     <row r="80" ht="22.5" customHeight="1">
       <c r="A80" s="15" t="s">
-        <v>2280</v>
+        <v>2331</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>2281</v>
+        <v>2332</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>2272</v>
+        <v>2324</v>
       </c>
       <c r="D80" s="11" t="s">
         <v>1</v>
@@ -36989,13 +38171,13 @@
     </row>
     <row r="81" ht="22.5" customHeight="1">
       <c r="A81" s="15" t="s">
-        <v>2282</v>
+        <v>2333</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>2283</v>
+        <v>2334</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>2272</v>
+        <v>2324</v>
       </c>
       <c r="D81" s="11" t="s">
         <v>1</v>
@@ -37003,13 +38185,13 @@
     </row>
     <row r="82" ht="22.5" customHeight="1">
       <c r="A82" s="15" t="s">
-        <v>2284</v>
+        <v>2335</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>2285</v>
+        <v>2336</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>2272</v>
+        <v>2324</v>
       </c>
       <c r="D82" s="11" t="s">
         <v>1</v>
@@ -37017,13 +38199,13 @@
     </row>
     <row r="83" ht="22.5" customHeight="1">
       <c r="A83" s="15" t="s">
-        <v>2286</v>
+        <v>2337</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>2287</v>
+        <v>2338</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>2272</v>
+        <v>2324</v>
       </c>
       <c r="D83" s="11" t="s">
         <v>1</v>
@@ -37031,13 +38213,13 @@
     </row>
     <row r="84" ht="22.5" customHeight="1">
       <c r="A84" s="15" t="s">
-        <v>2288</v>
+        <v>2339</v>
       </c>
       <c r="B84" s="11" t="s">
-        <v>2289</v>
+        <v>2340</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>2272</v>
+        <v>2324</v>
       </c>
       <c r="D84" s="11" t="s">
         <v>1</v>
@@ -37045,13 +38227,13 @@
     </row>
     <row r="85" ht="22.5" customHeight="1">
       <c r="A85" s="15" t="s">
-        <v>2290</v>
+        <v>2341</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>2291</v>
+        <v>2342</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>2272</v>
+        <v>2324</v>
       </c>
       <c r="D85" s="11" t="s">
         <v>1</v>
@@ -37059,13 +38241,13 @@
     </row>
     <row r="86" ht="22.5" customHeight="1">
       <c r="A86" s="15" t="s">
-        <v>2292</v>
+        <v>2343</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>2293</v>
+        <v>2344</v>
       </c>
       <c r="C86" s="12" t="s">
-        <v>2272</v>
+        <v>2324</v>
       </c>
       <c r="D86" s="11" t="s">
         <v>1</v>
@@ -37073,13 +38255,13 @@
     </row>
     <row r="87" ht="22.5" customHeight="1">
       <c r="A87" s="15" t="s">
-        <v>2294</v>
+        <v>2345</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>2295</v>
+        <v>2346</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>2272</v>
+        <v>2324</v>
       </c>
       <c r="D87" s="11" t="s">
         <v>1</v>
@@ -37087,13 +38269,13 @@
     </row>
     <row r="88" ht="22.5" customHeight="1">
       <c r="A88" s="15" t="s">
-        <v>2296</v>
+        <v>2347</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>2297</v>
+        <v>2348</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>2272</v>
+        <v>2324</v>
       </c>
       <c r="D88" s="11" t="s">
         <v>1</v>
@@ -37101,13 +38283,13 @@
     </row>
     <row r="89" ht="22.5" customHeight="1">
       <c r="A89" s="15" t="s">
-        <v>2298</v>
+        <v>2349</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>2299</v>
+        <v>2350</v>
       </c>
       <c r="C89" s="12" t="s">
-        <v>2272</v>
+        <v>2324</v>
       </c>
       <c r="D89" s="11" t="s">
         <v>1</v>
@@ -37115,13 +38297,13 @@
     </row>
     <row r="90" ht="22.5" customHeight="1">
       <c r="A90" s="15" t="s">
-        <v>2300</v>
+        <v>2351</v>
       </c>
       <c r="B90" s="11" t="s">
-        <v>2301</v>
+        <v>2352</v>
       </c>
       <c r="C90" s="12" t="s">
-        <v>2272</v>
+        <v>2324</v>
       </c>
       <c r="D90" s="11" t="s">
         <v>1</v>
@@ -37129,10 +38311,10 @@
     </row>
     <row r="91" ht="22.5" customHeight="1">
       <c r="A91" s="15" t="s">
-        <v>2302</v>
+        <v>2353</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>2303</v>
+        <v>2354</v>
       </c>
       <c r="C91" s="12" t="s">
         <v>311</v>
@@ -37143,10 +38325,10 @@
     </row>
     <row r="92" ht="22.5" customHeight="1">
       <c r="A92" s="15" t="s">
-        <v>2304</v>
+        <v>2355</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>2305</v>
+        <v>2356</v>
       </c>
       <c r="C92" s="12" t="s">
         <v>311</v>
@@ -37157,13 +38339,13 @@
     </row>
     <row r="93" ht="22.5" customHeight="1">
       <c r="A93" s="15" t="s">
-        <v>2306</v>
+        <v>2357</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>2307</v>
+        <v>2358</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>2308</v>
+        <v>2359</v>
       </c>
       <c r="D93" s="11" t="s">
         <v>1</v>
@@ -37171,13 +38353,13 @@
     </row>
     <row r="94" ht="22.5" customHeight="1">
       <c r="A94" s="15" t="s">
-        <v>2309</v>
+        <v>2360</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>2310</v>
+        <v>2361</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>2308</v>
+        <v>2359</v>
       </c>
       <c r="D94" s="11" t="s">
         <v>1</v>
@@ -37185,10 +38367,10 @@
     </row>
     <row r="95" ht="22.5" customHeight="1">
       <c r="A95" s="15" t="s">
-        <v>2311</v>
+        <v>2362</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>2312</v>
+        <v>2363</v>
       </c>
       <c r="C95" s="12" t="s">
         <v>311</v>
@@ -37199,10 +38381,10 @@
     </row>
     <row r="96" ht="22.5" customHeight="1">
       <c r="A96" s="15" t="s">
-        <v>2313</v>
+        <v>2364</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>2314</v>
+        <v>2365</v>
       </c>
       <c r="C96" s="12" t="s">
         <v>311</v>
@@ -37213,10 +38395,10 @@
     </row>
     <row r="97" ht="22.5" customHeight="1">
       <c r="A97" s="15" t="s">
-        <v>2315</v>
+        <v>2366</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>2316</v>
+        <v>2367</v>
       </c>
       <c r="C97" s="12" t="s">
         <v>311</v>
@@ -37227,10 +38409,10 @@
     </row>
     <row r="98" ht="22.5" customHeight="1">
       <c r="A98" s="15" t="s">
-        <v>2317</v>
+        <v>2368</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>2318</v>
+        <v>2369</v>
       </c>
       <c r="C98" s="12" t="s">
         <v>311</v>
@@ -37241,10 +38423,10 @@
     </row>
     <row r="99" ht="22.5" customHeight="1">
       <c r="A99" s="15" t="s">
-        <v>2319</v>
+        <v>2370</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>2320</v>
+        <v>2371</v>
       </c>
       <c r="C99" s="12" t="s">
         <v>311</v>
@@ -37255,10 +38437,10 @@
     </row>
     <row r="100" ht="22.5" customHeight="1">
       <c r="A100" s="15" t="s">
-        <v>2321</v>
+        <v>2372</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>2322</v>
+        <v>2373</v>
       </c>
       <c r="C100" s="12" t="s">
         <v>311</v>
@@ -37269,10 +38451,10 @@
     </row>
     <row r="101" ht="22.5" customHeight="1">
       <c r="A101" s="15" t="s">
-        <v>2323</v>
+        <v>2374</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>2324</v>
+        <v>2375</v>
       </c>
       <c r="C101" s="12" t="s">
         <v>311</v>
@@ -37283,10 +38465,10 @@
     </row>
     <row r="102" ht="22.5" customHeight="1">
       <c r="A102" s="15" t="s">
-        <v>2325</v>
+        <v>2376</v>
       </c>
       <c r="B102" s="11" t="s">
-        <v>2326</v>
+        <v>2377</v>
       </c>
       <c r="C102" s="12" t="s">
         <v>311</v>
@@ -37297,10 +38479,10 @@
     </row>
     <row r="103" ht="22.5" customHeight="1">
       <c r="A103" s="15" t="s">
-        <v>2327</v>
+        <v>2378</v>
       </c>
       <c r="B103" s="11" t="s">
-        <v>2328</v>
+        <v>2379</v>
       </c>
       <c r="C103" s="12" t="s">
         <v>311</v>
@@ -37311,10 +38493,10 @@
     </row>
     <row r="104" ht="22.5" customHeight="1">
       <c r="A104" s="15" t="s">
-        <v>2329</v>
+        <v>2380</v>
       </c>
       <c r="B104" s="11" t="s">
-        <v>2330</v>
+        <v>2381</v>
       </c>
       <c r="C104" s="12" t="s">
         <v>311</v>
@@ -37325,10 +38507,10 @@
     </row>
     <row r="105" ht="22.5" customHeight="1">
       <c r="A105" s="15" t="s">
-        <v>2331</v>
+        <v>2382</v>
       </c>
       <c r="B105" s="11" t="s">
-        <v>2332</v>
+        <v>2383</v>
       </c>
       <c r="C105" s="12" t="s">
         <v>311</v>
@@ -37339,10 +38521,10 @@
     </row>
     <row r="106" ht="22.5" customHeight="1">
       <c r="A106" s="15" t="s">
-        <v>2333</v>
+        <v>2384</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>2334</v>
+        <v>2385</v>
       </c>
       <c r="C106" s="12" t="s">
         <v>311</v>
@@ -37353,10 +38535,10 @@
     </row>
     <row r="107" ht="22.5" customHeight="1">
       <c r="A107" s="15" t="s">
-        <v>2335</v>
+        <v>2386</v>
       </c>
       <c r="B107" s="11" t="s">
-        <v>2336</v>
+        <v>2387</v>
       </c>
       <c r="C107" s="12" t="s">
         <v>311</v>
@@ -37367,10 +38549,10 @@
     </row>
     <row r="108" ht="22.5" customHeight="1">
       <c r="A108" s="15" t="s">
-        <v>2337</v>
+        <v>2388</v>
       </c>
       <c r="B108" s="11" t="s">
-        <v>2338</v>
+        <v>2389</v>
       </c>
       <c r="C108" s="12" t="s">
         <v>311</v>
@@ -37381,10 +38563,10 @@
     </row>
     <row r="109" ht="22.5" customHeight="1">
       <c r="A109" s="15" t="s">
-        <v>2339</v>
+        <v>2390</v>
       </c>
       <c r="B109" s="11" t="s">
-        <v>2340</v>
+        <v>2391</v>
       </c>
       <c r="C109" s="12" t="s">
         <v>311</v>
@@ -37395,10 +38577,10 @@
     </row>
     <row r="110" ht="22.5" customHeight="1">
       <c r="A110" s="15" t="s">
-        <v>2341</v>
+        <v>2392</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>2342</v>
+        <v>2393</v>
       </c>
       <c r="C110" s="12" t="s">
         <v>311</v>
@@ -37409,13 +38591,13 @@
     </row>
     <row r="111" ht="22.5" customHeight="1">
       <c r="A111" s="15" t="s">
-        <v>2343</v>
+        <v>2394</v>
       </c>
       <c r="B111" s="11" t="s">
-        <v>2344</v>
+        <v>2395</v>
       </c>
       <c r="C111" s="12" t="s">
-        <v>2345</v>
+        <v>2068</v>
       </c>
       <c r="D111" s="11" t="s">
         <v>1</v>
@@ -37423,13 +38605,13 @@
     </row>
     <row r="112" ht="22.5" customHeight="1">
       <c r="A112" s="15" t="s">
-        <v>2346</v>
+        <v>2396</v>
       </c>
       <c r="B112" s="11" t="s">
-        <v>2347</v>
+        <v>2397</v>
       </c>
       <c r="C112" s="12" t="s">
-        <v>2345</v>
+        <v>2068</v>
       </c>
       <c r="D112" s="11" t="s">
         <v>1</v>
@@ -37437,13 +38619,13 @@
     </row>
     <row r="113" ht="22.5" customHeight="1">
       <c r="A113" s="15" t="s">
-        <v>2348</v>
+        <v>2398</v>
       </c>
       <c r="B113" s="11" t="s">
-        <v>2349</v>
+        <v>2399</v>
       </c>
       <c r="C113" s="12" t="s">
-        <v>2345</v>
+        <v>2068</v>
       </c>
       <c r="D113" s="11" t="s">
         <v>1</v>
@@ -37451,13 +38633,13 @@
     </row>
     <row r="114" ht="22.5" customHeight="1">
       <c r="A114" s="15" t="s">
-        <v>2350</v>
+        <v>2400</v>
       </c>
       <c r="B114" s="11" t="s">
-        <v>2351</v>
+        <v>2065</v>
       </c>
       <c r="C114" s="12" t="s">
-        <v>2345</v>
+        <v>2068</v>
       </c>
       <c r="D114" s="11" t="s">
         <v>1</v>
@@ -37465,13 +38647,13 @@
     </row>
     <row r="115" ht="22.5" customHeight="1">
       <c r="A115" s="15" t="s">
-        <v>2352</v>
+        <v>2401</v>
       </c>
       <c r="B115" s="11" t="s">
-        <v>2353</v>
+        <v>2402</v>
       </c>
       <c r="C115" s="12" t="s">
-        <v>2345</v>
+        <v>2068</v>
       </c>
       <c r="D115" s="11" t="s">
         <v>1</v>
@@ -37479,13 +38661,13 @@
     </row>
     <row r="116" ht="22.5" customHeight="1">
       <c r="A116" s="15" t="s">
-        <v>2354</v>
+        <v>2403</v>
       </c>
       <c r="B116" s="11" t="s">
-        <v>2355</v>
+        <v>2069</v>
       </c>
       <c r="C116" s="12" t="s">
-        <v>2345</v>
+        <v>2068</v>
       </c>
       <c r="D116" s="11" t="s">
         <v>1</v>
@@ -37493,13 +38675,13 @@
     </row>
     <row r="117" ht="22.5" customHeight="1">
       <c r="A117" s="15" t="s">
-        <v>2356</v>
+        <v>2404</v>
       </c>
       <c r="B117" s="11" t="s">
-        <v>2357</v>
+        <v>2405</v>
       </c>
       <c r="C117" s="12" t="s">
-        <v>2345</v>
+        <v>2068</v>
       </c>
       <c r="D117" s="11" t="s">
         <v>1</v>
@@ -37507,13 +38689,13 @@
     </row>
     <row r="118" ht="22.5" customHeight="1">
       <c r="A118" s="15" t="s">
-        <v>2358</v>
+        <v>2406</v>
       </c>
       <c r="B118" s="11" t="s">
-        <v>2359</v>
+        <v>2407</v>
       </c>
       <c r="C118" s="12" t="s">
-        <v>2345</v>
+        <v>2068</v>
       </c>
       <c r="D118" s="11" t="s">
         <v>1</v>
@@ -37521,13 +38703,13 @@
     </row>
     <row r="119" ht="22.5" customHeight="1">
       <c r="A119" s="15" t="s">
-        <v>2360</v>
+        <v>2408</v>
       </c>
       <c r="B119" s="11" t="s">
-        <v>2361</v>
+        <v>2409</v>
       </c>
       <c r="C119" s="12" t="s">
-        <v>2345</v>
+        <v>2068</v>
       </c>
       <c r="D119" s="11" t="s">
         <v>1</v>
@@ -37535,13 +38717,13 @@
     </row>
     <row r="120" ht="22.5" customHeight="1">
       <c r="A120" s="15" t="s">
-        <v>2362</v>
+        <v>2410</v>
       </c>
       <c r="B120" s="11" t="s">
-        <v>2363</v>
+        <v>2071</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>2345</v>
+        <v>2068</v>
       </c>
       <c r="D120" s="11" t="s">
         <v>1</v>
@@ -37549,13 +38731,13 @@
     </row>
     <row r="121" ht="22.5" customHeight="1">
       <c r="A121" s="15" t="s">
-        <v>2364</v>
+        <v>2411</v>
       </c>
       <c r="B121" s="11" t="s">
-        <v>2365</v>
+        <v>2412</v>
       </c>
       <c r="C121" s="12" t="s">
-        <v>2345</v>
+        <v>2068</v>
       </c>
       <c r="D121" s="11" t="s">
         <v>1</v>
@@ -37589,1736 +38771,1736 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="14" t="s">
-        <v>2119</v>
+        <v>2174</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>2118</v>
+        <v>2173</v>
       </c>
       <c r="C1" s="14" t="s">
         <v>910</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>2366</v>
+        <v>2413</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>2367</v>
+        <v>2414</v>
       </c>
     </row>
     <row r="2" ht="22.5" customHeight="1">
       <c r="A2" s="12" t="s">
-        <v>2122</v>
+        <v>2177</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>2121</v>
+        <v>2176</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>2368</v>
+        <v>2415</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>2369</v>
+        <v>2416</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>2370</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="3" ht="22.5" customHeight="1">
       <c r="A3" s="12" t="s">
-        <v>2122</v>
+        <v>2177</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>2154</v>
+        <v>2209</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>2371</v>
+        <v>2418</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>2372</v>
+        <v>2419</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>2370</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1">
       <c r="A4" s="12" t="s">
-        <v>2122</v>
+        <v>2177</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>2156</v>
+        <v>2082</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>2371</v>
+        <v>2418</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>2373</v>
+        <v>2420</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>2370</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="5" ht="22.5" customHeight="1">
       <c r="A5" s="12" t="s">
-        <v>2122</v>
+        <v>2177</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>2132</v>
+        <v>2187</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>2374</v>
+        <v>2421</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>2375</v>
+        <v>2422</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>2370</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="6" ht="22.5" customHeight="1">
       <c r="A6" s="12" t="s">
-        <v>2122</v>
+        <v>2177</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>2138</v>
+        <v>2193</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>2371</v>
+        <v>2418</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>2372</v>
+        <v>2419</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>2370</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="7" ht="22.5" customHeight="1">
       <c r="A7" s="12" t="s">
-        <v>2122</v>
+        <v>2177</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>2138</v>
+        <v>2193</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>2376</v>
+        <v>2423</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>2377</v>
+        <v>2424</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>2370</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="8" ht="22.5" customHeight="1">
       <c r="A8" s="12" t="s">
-        <v>2122</v>
+        <v>2177</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>2138</v>
+        <v>2193</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>2378</v>
+        <v>2425</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>2379</v>
+        <v>2426</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>2380</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="9" ht="22.5" customHeight="1">
       <c r="A9" s="12" t="s">
-        <v>2122</v>
+        <v>2177</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>2138</v>
+        <v>2193</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>2381</v>
+        <v>2428</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>2379</v>
+        <v>2426</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>2380</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="10" ht="22.5" customHeight="1">
       <c r="A10" s="12" t="s">
-        <v>2122</v>
+        <v>2177</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>1981</v>
+        <v>1993</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>2382</v>
+        <v>2429</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>2383</v>
+        <v>2430</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>2370</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="11" ht="22.5" customHeight="1">
       <c r="A11" s="12" t="s">
-        <v>2122</v>
+        <v>2177</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>1981</v>
+        <v>1993</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>2371</v>
+        <v>2418</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>2372</v>
+        <v>2419</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>2370</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="12" ht="22.5" customHeight="1">
       <c r="A12" s="12" t="s">
-        <v>2122</v>
+        <v>2177</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>1981</v>
+        <v>1993</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>2384</v>
+        <v>2431</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>2385</v>
+        <v>2432</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>2370</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="13" ht="22.5" customHeight="1">
       <c r="A13" s="12" t="s">
-        <v>2122</v>
+        <v>2177</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>1981</v>
+        <v>1993</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>2386</v>
+        <v>2433</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>2379</v>
+        <v>2426</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>2380</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="14" ht="22.5" customHeight="1">
       <c r="A14" s="12" t="s">
-        <v>2122</v>
+        <v>2177</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>1981</v>
+        <v>1993</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>2387</v>
+        <v>2434</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>2379</v>
+        <v>2426</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>2380</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="15" ht="22.5" customHeight="1">
       <c r="A15" s="12" t="s">
-        <v>2122</v>
+        <v>2177</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>1981</v>
+        <v>1993</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>2388</v>
+        <v>2435</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>2379</v>
+        <v>2426</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>2380</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="16" ht="22.5" customHeight="1">
       <c r="A16" s="12" t="s">
-        <v>2122</v>
+        <v>2177</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>2289</v>
+        <v>2340</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>2371</v>
+        <v>2418</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>2379</v>
+        <v>2426</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>2370</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="17" ht="22.5" customHeight="1">
       <c r="A17" s="12" t="s">
-        <v>2122</v>
+        <v>2177</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>2289</v>
+        <v>2340</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>2389</v>
+        <v>2436</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>2379</v>
+        <v>2426</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>2380</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="18" ht="22.5" customHeight="1">
       <c r="A18" s="12" t="s">
-        <v>2122</v>
+        <v>2177</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>2289</v>
+        <v>2340</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>2390</v>
+        <v>2437</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>2379</v>
+        <v>2426</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>2370</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="19" ht="22.5" customHeight="1">
       <c r="A19" s="12" t="s">
-        <v>2122</v>
+        <v>2177</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>2289</v>
+        <v>2340</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>2391</v>
+        <v>2438</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>2379</v>
+        <v>2426</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>2380</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="20" ht="22.5" customHeight="1">
       <c r="A20" s="12" t="s">
-        <v>2122</v>
+        <v>2177</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>1955</v>
+        <v>1967</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>2374</v>
+        <v>2421</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>2375</v>
+        <v>2422</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>2370</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="21" ht="22.5" customHeight="1">
       <c r="A21" s="12" t="s">
-        <v>2122</v>
+        <v>2177</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>1955</v>
+        <v>1967</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>2386</v>
+        <v>2433</v>
       </c>
       <c r="D21" s="11" t="s">
-        <v>2379</v>
+        <v>2426</v>
       </c>
       <c r="E21" s="12" t="s">
-        <v>2380</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="22" ht="22.5" customHeight="1">
       <c r="A22" s="12" t="s">
-        <v>2122</v>
+        <v>2177</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>1955</v>
+        <v>1967</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>2389</v>
+        <v>2436</v>
       </c>
       <c r="D22" s="11" t="s">
-        <v>2379</v>
+        <v>2426</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>2380</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="23" ht="22.5" customHeight="1">
       <c r="A23" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>2195</v>
+        <v>2248</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>2392</v>
+        <v>2439</v>
       </c>
       <c r="D23" s="11" t="s">
-        <v>2393</v>
+        <v>2440</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>2370</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="24" ht="22.5" customHeight="1">
       <c r="A24" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>2195</v>
+        <v>2248</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>2374</v>
+        <v>2421</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>2375</v>
+        <v>2422</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>2370</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="25" ht="22.5" customHeight="1">
       <c r="A25" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>2195</v>
+        <v>2248</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>2394</v>
+        <v>2441</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>2395</v>
+        <v>2442</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>2370</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="26" ht="22.5" customHeight="1">
       <c r="A26" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>2195</v>
+        <v>2248</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>2396</v>
+        <v>2443</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>2397</v>
+        <v>2444</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>2380</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="27" ht="22.5" customHeight="1">
       <c r="A27" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>2195</v>
+        <v>2248</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>2398</v>
+        <v>2445</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>2379</v>
+        <v>2426</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>2380</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="28" ht="22.5" customHeight="1">
       <c r="A28" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>2195</v>
+        <v>2248</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>2399</v>
+        <v>2446</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>2379</v>
+        <v>2426</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>2380</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="29" ht="22.5" customHeight="1">
       <c r="A29" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>2195</v>
+        <v>2248</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>2400</v>
+        <v>2447</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>2401</v>
+        <v>2448</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>2370</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="30" ht="22.5" customHeight="1">
       <c r="A30" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>2195</v>
+        <v>2248</v>
       </c>
       <c r="C30" s="11" t="s">
         <v>1858</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>2379</v>
+        <v>2426</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>2380</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="31" ht="22.5" customHeight="1">
       <c r="A31" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>2195</v>
+        <v>2248</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>2402</v>
+        <v>2449</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>2379</v>
+        <v>2426</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>2380</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="32" ht="22.5" customHeight="1">
       <c r="A32" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>2195</v>
+        <v>2248</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>2403</v>
+        <v>2450</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>2404</v>
+        <v>2451</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>2370</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="33" ht="22.5" customHeight="1">
       <c r="A33" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>2187</v>
+        <v>2240</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>2394</v>
+        <v>2441</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>2405</v>
+        <v>2452</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>2370</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="34" ht="22.5" customHeight="1">
       <c r="A34" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>2187</v>
+        <v>2240</v>
       </c>
       <c r="C34" s="11" t="s">
-        <v>2406</v>
+        <v>2453</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>2407</v>
+        <v>2454</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>2370</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="35" ht="22.5" customHeight="1">
       <c r="A35" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>2187</v>
+        <v>2240</v>
       </c>
       <c r="C35" s="11" t="s">
         <v>1858</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>2379</v>
+        <v>2426</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>2380</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="36" ht="22.5" customHeight="1">
       <c r="A36" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>2187</v>
+        <v>2240</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>2408</v>
+        <v>2455</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>2379</v>
+        <v>2426</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>2380</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="37" ht="22.5" customHeight="1">
       <c r="A37" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>2409</v>
+        <v>2456</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>2410</v>
+        <v>2457</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>2405</v>
+        <v>2452</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>2370</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="38" ht="22.5" customHeight="1">
       <c r="A38" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>2409</v>
+        <v>2456</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>2411</v>
+        <v>2458</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>2372</v>
+        <v>2419</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>2370</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="39" ht="22.5" customHeight="1">
       <c r="A39" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="B39" s="11" t="s">
-        <v>2409</v>
+        <v>2456</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>2398</v>
+        <v>2445</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>2379</v>
+        <v>2426</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>2380</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="40" ht="22.5" customHeight="1">
       <c r="A40" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>2409</v>
+        <v>2456</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>2389</v>
+        <v>2436</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>2379</v>
+        <v>2426</v>
       </c>
       <c r="E40" s="12" t="s">
-        <v>2380</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="41" ht="22.5" customHeight="1">
       <c r="A41" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>2412</v>
+        <v>2459</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>2413</v>
+        <v>2460</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>2379</v>
+        <v>2426</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>2370</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="42" ht="22.5" customHeight="1">
       <c r="A42" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>2412</v>
+        <v>2459</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>2414</v>
+        <v>2461</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>2415</v>
+        <v>2462</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>2370</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="43" ht="22.5" customHeight="1">
       <c r="A43" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>2412</v>
+        <v>2459</v>
       </c>
       <c r="C43" s="11" t="s">
         <v>1858</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>2379</v>
+        <v>2426</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>2380</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="44" ht="22.5" customHeight="1">
       <c r="A44" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>2412</v>
+        <v>2459</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>2408</v>
+        <v>2455</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>2379</v>
+        <v>2426</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>2380</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="45" ht="22.5" customHeight="1">
       <c r="A45" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>2264</v>
+        <v>2316</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>2392</v>
+        <v>2439</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>2416</v>
+        <v>2463</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>2370</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="46" ht="22.5" customHeight="1">
       <c r="A46" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>2264</v>
+        <v>2316</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>2374</v>
+        <v>2421</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>2375</v>
+        <v>2422</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>2370</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="47" ht="22.5" customHeight="1">
       <c r="A47" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>2264</v>
+        <v>2316</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>2394</v>
+        <v>2441</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>2395</v>
+        <v>2442</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>2370</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="48" ht="22.5" customHeight="1">
       <c r="A48" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>2264</v>
+        <v>2316</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>2396</v>
+        <v>2443</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>2397</v>
+        <v>2444</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>2380</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="49" ht="22.5" customHeight="1">
       <c r="A49" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="B49" s="11" t="s">
-        <v>2264</v>
+        <v>2316</v>
       </c>
       <c r="C49" s="11" t="s">
-        <v>2398</v>
+        <v>2445</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>2379</v>
+        <v>2426</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>2380</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="50" ht="22.5" customHeight="1">
       <c r="A50" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>2264</v>
+        <v>2316</v>
       </c>
       <c r="C50" s="11" t="s">
+        <v>2464</v>
+      </c>
+      <c r="D50" s="11" t="s">
+        <v>2465</v>
+      </c>
+      <c r="E50" s="12" t="s">
         <v>2417</v>
-      </c>
-      <c r="D50" s="11" t="s">
-        <v>2418</v>
-      </c>
-      <c r="E50" s="12" t="s">
-        <v>2370</v>
       </c>
     </row>
     <row r="51" ht="22.5" customHeight="1">
       <c r="A51" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>2264</v>
+        <v>2316</v>
       </c>
       <c r="C51" s="11" t="s">
-        <v>2419</v>
+        <v>2466</v>
       </c>
       <c r="D51" s="11" t="s">
-        <v>2379</v>
+        <v>2426</v>
       </c>
       <c r="E51" s="12" t="s">
-        <v>2370</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="52" ht="22.5" customHeight="1">
       <c r="A52" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>2264</v>
+        <v>2316</v>
       </c>
       <c r="C52" s="11" t="s">
-        <v>2399</v>
+        <v>2446</v>
       </c>
       <c r="D52" s="11" t="s">
-        <v>2379</v>
+        <v>2426</v>
       </c>
       <c r="E52" s="12" t="s">
-        <v>2380</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="53" ht="22.5" customHeight="1">
       <c r="A53" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>2264</v>
+        <v>2316</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>2420</v>
+        <v>2467</v>
       </c>
       <c r="D53" s="11" t="s">
-        <v>2421</v>
+        <v>2468</v>
       </c>
       <c r="E53" s="12" t="s">
-        <v>2370</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="54" ht="22.5" customHeight="1">
       <c r="A54" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>2264</v>
+        <v>2316</v>
       </c>
       <c r="C54" s="11" t="s">
-        <v>2408</v>
+        <v>2455</v>
       </c>
       <c r="D54" s="11" t="s">
-        <v>2379</v>
+        <v>2426</v>
       </c>
       <c r="E54" s="12" t="s">
-        <v>2380</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="55" ht="22.5" customHeight="1">
       <c r="A55" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="B55" s="11" t="s">
-        <v>2264</v>
+        <v>2316</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>2403</v>
+        <v>2450</v>
       </c>
       <c r="D55" s="11" t="s">
-        <v>2422</v>
+        <v>2469</v>
       </c>
       <c r="E55" s="12" t="s">
-        <v>2370</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="56" ht="22.5" customHeight="1">
       <c r="A56" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>2266</v>
+        <v>2318</v>
       </c>
       <c r="C56" s="11" t="s">
-        <v>2423</v>
+        <v>2470</v>
       </c>
       <c r="D56" s="11" t="s">
-        <v>2379</v>
+        <v>2426</v>
       </c>
       <c r="E56" s="12" t="s">
-        <v>2370</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="57" ht="22.5" customHeight="1">
       <c r="A57" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="B57" s="11" t="s">
-        <v>2266</v>
+        <v>2318</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>2374</v>
+        <v>2421</v>
       </c>
       <c r="D57" s="11" t="s">
-        <v>2375</v>
+        <v>2422</v>
       </c>
       <c r="E57" s="12" t="s">
-        <v>2370</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="58" ht="22.5" customHeight="1">
       <c r="A58" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="B58" s="11" t="s">
-        <v>2266</v>
+        <v>2318</v>
       </c>
       <c r="C58" s="11" t="s">
         <v>405</v>
       </c>
       <c r="D58" s="11" t="s">
-        <v>2379</v>
+        <v>2426</v>
       </c>
       <c r="E58" s="12" t="s">
-        <v>2380</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="59" ht="22.5" customHeight="1">
       <c r="A59" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="B59" s="11" t="s">
-        <v>2266</v>
+        <v>2318</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>2398</v>
+        <v>2445</v>
       </c>
       <c r="D59" s="11" t="s">
-        <v>2379</v>
+        <v>2426</v>
       </c>
       <c r="E59" s="12" t="s">
-        <v>2380</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="60" ht="22.5" customHeight="1">
       <c r="A60" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>2266</v>
+        <v>2318</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>2424</v>
+        <v>2471</v>
       </c>
       <c r="D60" s="11" t="s">
-        <v>2379</v>
+        <v>2426</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>2380</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="61" ht="22.5" customHeight="1">
       <c r="A61" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="B61" s="11" t="s">
-        <v>2266</v>
+        <v>2318</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>2425</v>
+        <v>2472</v>
       </c>
       <c r="D61" s="11" t="s">
-        <v>2379</v>
+        <v>2426</v>
       </c>
       <c r="E61" s="12" t="s">
-        <v>2380</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="62" ht="22.5" customHeight="1">
       <c r="A62" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="B62" s="11" t="s">
-        <v>2268</v>
+        <v>2320</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>2371</v>
+        <v>2418</v>
       </c>
       <c r="D62" s="11" t="s">
-        <v>2372</v>
+        <v>2419</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>2370</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="63" ht="22.5" customHeight="1">
       <c r="A63" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>2268</v>
+        <v>2320</v>
       </c>
       <c r="C63" s="11" t="s">
-        <v>2376</v>
+        <v>2423</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>2377</v>
+        <v>2424</v>
       </c>
       <c r="E63" s="12" t="s">
-        <v>2370</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="64" ht="22.5" customHeight="1">
       <c r="A64" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>2268</v>
+        <v>2320</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>2378</v>
+        <v>2425</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>2379</v>
+        <v>2426</v>
       </c>
       <c r="E64" s="12" t="s">
-        <v>2380</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="65" ht="22.5" customHeight="1">
       <c r="A65" s="12" t="s">
-        <v>2181</v>
+        <v>2234</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>2268</v>
+        <v>2320</v>
       </c>
       <c r="C65" s="11" t="s">
-        <v>2381</v>
+        <v>2428</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>2379</v>
+        <v>2426</v>
       </c>
       <c r="E65" s="12" t="s">
-        <v>2380</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="66" ht="22.5" customHeight="1">
       <c r="A66" s="12" t="s">
-        <v>2272</v>
+        <v>2324</v>
       </c>
       <c r="B66" s="11" t="s">
-        <v>2164</v>
+        <v>2217</v>
       </c>
       <c r="C66" s="11" t="s">
-        <v>2374</v>
+        <v>2421</v>
       </c>
       <c r="D66" s="11" t="s">
-        <v>2375</v>
+        <v>2422</v>
       </c>
       <c r="E66" s="12" t="s">
-        <v>2370</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="67" ht="22.5" customHeight="1">
       <c r="A67" s="12" t="s">
-        <v>2272</v>
+        <v>2324</v>
       </c>
       <c r="B67" s="11" t="s">
-        <v>2164</v>
+        <v>2217</v>
       </c>
       <c r="C67" s="11" t="s">
-        <v>2426</v>
+        <v>2473</v>
       </c>
       <c r="D67" s="11" t="s">
-        <v>2427</v>
+        <v>2474</v>
       </c>
       <c r="E67" s="12" t="s">
-        <v>2370</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="68" ht="22.5" customHeight="1">
       <c r="A68" s="12" t="s">
-        <v>2272</v>
+        <v>2324</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>2164</v>
+        <v>2217</v>
       </c>
       <c r="C68" s="11" t="s">
-        <v>2386</v>
+        <v>2433</v>
       </c>
       <c r="D68" s="11" t="s">
-        <v>2379</v>
+        <v>2426</v>
       </c>
       <c r="E68" s="12" t="s">
-        <v>2380</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="69" ht="22.5" customHeight="1">
       <c r="A69" s="12" t="s">
-        <v>2272</v>
+        <v>2324</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>2164</v>
+        <v>2217</v>
       </c>
       <c r="C69" s="11" t="s">
-        <v>2428</v>
+        <v>2475</v>
       </c>
       <c r="D69" s="11" t="s">
-        <v>2379</v>
+        <v>2426</v>
       </c>
       <c r="E69" s="12" t="s">
-        <v>2370</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="70" ht="22.5" customHeight="1">
       <c r="A70" s="12" t="s">
-        <v>2272</v>
+        <v>2324</v>
       </c>
       <c r="B70" s="11" t="s">
-        <v>2295</v>
+        <v>2346</v>
       </c>
       <c r="C70" s="11" t="s">
-        <v>2371</v>
+        <v>2418</v>
       </c>
       <c r="D70" s="11" t="s">
-        <v>2372</v>
+        <v>2419</v>
       </c>
       <c r="E70" s="12" t="s">
-        <v>2370</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="71" ht="22.5" customHeight="1">
       <c r="A71" s="12" t="s">
-        <v>2272</v>
+        <v>2324</v>
       </c>
       <c r="B71" s="11" t="s">
-        <v>2295</v>
+        <v>2346</v>
       </c>
       <c r="C71" s="11" t="s">
-        <v>2376</v>
+        <v>2423</v>
       </c>
       <c r="D71" s="11" t="s">
-        <v>2377</v>
+        <v>2424</v>
       </c>
       <c r="E71" s="12" t="s">
-        <v>2370</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="72" ht="22.5" customHeight="1">
       <c r="A72" s="12" t="s">
-        <v>2272</v>
+        <v>2324</v>
       </c>
       <c r="B72" s="11" t="s">
-        <v>2295</v>
+        <v>2346</v>
       </c>
       <c r="C72" s="11" t="s">
-        <v>2378</v>
+        <v>2425</v>
       </c>
       <c r="D72" s="11" t="s">
-        <v>2379</v>
+        <v>2426</v>
       </c>
       <c r="E72" s="12" t="s">
-        <v>2380</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="73" ht="22.5" customHeight="1">
       <c r="A73" s="12" t="s">
-        <v>2272</v>
+        <v>2324</v>
       </c>
       <c r="B73" s="11" t="s">
-        <v>2295</v>
+        <v>2346</v>
       </c>
       <c r="C73" s="11" t="s">
-        <v>2381</v>
+        <v>2428</v>
       </c>
       <c r="D73" s="11" t="s">
-        <v>2379</v>
+        <v>2426</v>
       </c>
       <c r="E73" s="12" t="s">
-        <v>2380</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="74" ht="22.5" customHeight="1">
       <c r="A74" s="12" t="s">
-        <v>2272</v>
+        <v>2324</v>
       </c>
       <c r="B74" s="11" t="s">
-        <v>2277</v>
+        <v>2077</v>
       </c>
       <c r="C74" s="11" t="s">
-        <v>2429</v>
+        <v>2476</v>
       </c>
       <c r="D74" s="11" t="s">
-        <v>2430</v>
+        <v>2477</v>
       </c>
       <c r="E74" s="12" t="s">
-        <v>2370</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="75" ht="22.5" customHeight="1">
       <c r="A75" s="12" t="s">
-        <v>2272</v>
+        <v>2324</v>
       </c>
       <c r="B75" s="11" t="s">
-        <v>2277</v>
+        <v>2077</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>2431</v>
+        <v>2478</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>2379</v>
+        <v>2426</v>
       </c>
       <c r="E75" s="12" t="s">
-        <v>2370</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="76" ht="22.5" customHeight="1">
       <c r="A76" s="12" t="s">
-        <v>2272</v>
+        <v>2324</v>
       </c>
       <c r="B76" s="11" t="s">
-        <v>2297</v>
+        <v>2348</v>
       </c>
       <c r="C76" s="11" t="s">
-        <v>2429</v>
+        <v>2476</v>
       </c>
       <c r="D76" s="11" t="s">
-        <v>2430</v>
+        <v>2477</v>
       </c>
       <c r="E76" s="12" t="s">
-        <v>2370</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="77" ht="22.5" customHeight="1">
       <c r="A77" s="12" t="s">
-        <v>2272</v>
+        <v>2324</v>
       </c>
       <c r="B77" s="11" t="s">
-        <v>2297</v>
+        <v>2348</v>
       </c>
       <c r="C77" s="11" t="s">
-        <v>2431</v>
+        <v>2478</v>
       </c>
       <c r="D77" s="11" t="s">
-        <v>2379</v>
+        <v>2426</v>
       </c>
       <c r="E77" s="12" t="s">
-        <v>2370</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="78" ht="22.5" customHeight="1">
       <c r="A78" s="12" t="s">
-        <v>2272</v>
+        <v>2324</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>2299</v>
+        <v>2350</v>
       </c>
       <c r="C78" s="11" t="s">
-        <v>2429</v>
+        <v>2476</v>
       </c>
       <c r="D78" s="11" t="s">
-        <v>2430</v>
+        <v>2477</v>
       </c>
       <c r="E78" s="12" t="s">
-        <v>2370</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="79" ht="22.5" customHeight="1">
       <c r="A79" s="12" t="s">
-        <v>2272</v>
+        <v>2324</v>
       </c>
       <c r="B79" s="11" t="s">
-        <v>2299</v>
+        <v>2350</v>
       </c>
       <c r="C79" s="11" t="s">
-        <v>2431</v>
+        <v>2478</v>
       </c>
       <c r="D79" s="11" t="s">
-        <v>2379</v>
+        <v>2426</v>
       </c>
       <c r="E79" s="12" t="s">
-        <v>2370</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="80" ht="22.5" customHeight="1">
       <c r="A80" s="12" t="s">
-        <v>2272</v>
+        <v>2324</v>
       </c>
       <c r="B80" s="11" t="s">
-        <v>2287</v>
+        <v>2338</v>
       </c>
       <c r="C80" s="11" t="s">
-        <v>2429</v>
+        <v>2476</v>
       </c>
       <c r="D80" s="11" t="s">
-        <v>2430</v>
+        <v>2477</v>
       </c>
       <c r="E80" s="12" t="s">
-        <v>2370</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="81" ht="22.5" customHeight="1">
       <c r="A81" s="12" t="s">
-        <v>2272</v>
+        <v>2324</v>
       </c>
       <c r="B81" s="11" t="s">
-        <v>2287</v>
+        <v>2338</v>
       </c>
       <c r="C81" s="11" t="s">
-        <v>2431</v>
+        <v>2478</v>
       </c>
       <c r="D81" s="11" t="s">
-        <v>2379</v>
+        <v>2426</v>
       </c>
       <c r="E81" s="12" t="s">
-        <v>2370</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="82" ht="22.5" customHeight="1">
       <c r="A82" s="12" t="s">
-        <v>2272</v>
+        <v>2324</v>
       </c>
       <c r="B82" s="11" t="s">
         <v>145</v>
       </c>
       <c r="C82" s="11" t="s">
-        <v>2429</v>
+        <v>2476</v>
       </c>
       <c r="D82" s="11" t="s">
-        <v>2430</v>
+        <v>2477</v>
       </c>
       <c r="E82" s="12" t="s">
-        <v>2370</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="83" ht="22.5" customHeight="1">
       <c r="A83" s="12" t="s">
-        <v>2272</v>
+        <v>2324</v>
       </c>
       <c r="B83" s="11" t="s">
         <v>145</v>
       </c>
       <c r="C83" s="11" t="s">
-        <v>2432</v>
+        <v>2479</v>
       </c>
       <c r="D83" s="11" t="s">
-        <v>2379</v>
+        <v>2426</v>
       </c>
       <c r="E83" s="12" t="s">
-        <v>2370</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="84" ht="22.5" customHeight="1">
       <c r="A84" s="12" t="s">
-        <v>2272</v>
+        <v>2324</v>
       </c>
       <c r="B84" s="11" t="s">
         <v>145</v>
       </c>
       <c r="C84" s="11" t="s">
-        <v>2433</v>
+        <v>2480</v>
       </c>
       <c r="D84" s="11" t="s">
-        <v>2379</v>
+        <v>2426</v>
       </c>
       <c r="E84" s="12" t="s">
-        <v>2380</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="85" ht="22.5" customHeight="1">
       <c r="A85" s="12" t="s">
-        <v>2345</v>
+        <v>2068</v>
       </c>
       <c r="B85" s="11" t="s">
-        <v>2363</v>
+        <v>2071</v>
       </c>
       <c r="C85" s="11" t="s">
-        <v>2371</v>
+        <v>2418</v>
       </c>
       <c r="D85" s="11" t="s">
-        <v>2430</v>
+        <v>2477</v>
       </c>
       <c r="E85" s="12" t="s">
-        <v>2370</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="86" ht="22.5" customHeight="1">
       <c r="A86" s="12" t="s">
-        <v>2345</v>
+        <v>2068</v>
       </c>
       <c r="B86" s="11" t="s">
-        <v>2363</v>
+        <v>2071</v>
       </c>
       <c r="C86" s="11" t="s">
-        <v>2384</v>
+        <v>2431</v>
       </c>
       <c r="D86" s="11" t="s">
-        <v>2434</v>
+        <v>2481</v>
       </c>
       <c r="E86" s="12" t="s">
-        <v>2370</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="87" ht="22.5" customHeight="1">
       <c r="A87" s="12" t="s">
-        <v>2345</v>
+        <v>2068</v>
       </c>
       <c r="B87" s="11" t="s">
-        <v>2363</v>
+        <v>2071</v>
       </c>
       <c r="C87" s="11" t="s">
-        <v>2381</v>
+        <v>2428</v>
       </c>
       <c r="D87" s="11" t="s">
-        <v>2379</v>
+        <v>2426</v>
       </c>
       <c r="E87" s="12" t="s">
-        <v>2380</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="88" ht="22.5" customHeight="1">
       <c r="A88" s="12" t="s">
-        <v>2345</v>
+        <v>2068</v>
       </c>
       <c r="B88" s="11" t="s">
-        <v>2363</v>
+        <v>2071</v>
       </c>
       <c r="C88" s="11" t="s">
-        <v>2435</v>
+        <v>2482</v>
       </c>
       <c r="D88" s="11" t="s">
-        <v>2379</v>
+        <v>2426</v>
       </c>
       <c r="E88" s="12" t="s">
-        <v>2380</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="89" ht="22.5" customHeight="1">
       <c r="A89" s="12" t="s">
-        <v>2345</v>
+        <v>2068</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>2307</v>
+        <v>2358</v>
       </c>
       <c r="C89" s="11" t="s">
-        <v>2374</v>
+        <v>2421</v>
       </c>
       <c r="D89" s="11" t="s">
-        <v>2436</v>
+        <v>2483</v>
       </c>
       <c r="E89" s="12" t="s">
-        <v>2370</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="90" ht="22.5" customHeight="1">
       <c r="A90" s="12" t="s">
-        <v>2345</v>
+        <v>2068</v>
       </c>
       <c r="B90" s="11" t="s">
-        <v>2307</v>
+        <v>2358</v>
       </c>
       <c r="C90" s="11" t="s">
-        <v>2437</v>
+        <v>2484</v>
       </c>
       <c r="D90" s="11" t="s">
-        <v>2379</v>
+        <v>2426</v>
       </c>
       <c r="E90" s="12" t="s">
-        <v>2380</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="91" ht="22.5" customHeight="1">
       <c r="A91" s="12" t="s">
-        <v>2345</v>
+        <v>2068</v>
       </c>
       <c r="B91" s="11" t="s">
-        <v>2307</v>
+        <v>2358</v>
       </c>
       <c r="C91" s="11" t="s">
-        <v>2438</v>
+        <v>2485</v>
       </c>
       <c r="D91" s="11" t="s">
-        <v>2379</v>
+        <v>2426</v>
       </c>
       <c r="E91" s="12" t="s">
-        <v>2380</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="92" ht="22.5" customHeight="1">
       <c r="A92" s="12" t="s">
-        <v>2345</v>
+        <v>2068</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>2307</v>
+        <v>2358</v>
       </c>
       <c r="C92" s="11" t="s">
-        <v>2439</v>
+        <v>2486</v>
       </c>
       <c r="D92" s="11" t="s">
-        <v>2379</v>
+        <v>2426</v>
       </c>
       <c r="E92" s="12" t="s">
-        <v>2380</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="93" ht="22.5" customHeight="1">
       <c r="A93" s="12" t="s">
-        <v>2345</v>
+        <v>2068</v>
       </c>
       <c r="B93" s="11" t="s">
-        <v>2307</v>
+        <v>2358</v>
       </c>
       <c r="C93" s="11" t="s">
-        <v>2408</v>
+        <v>2455</v>
       </c>
       <c r="D93" s="11" t="s">
-        <v>2379</v>
+        <v>2426</v>
       </c>
       <c r="E93" s="12" t="s">
-        <v>2380</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="94" ht="22.5" customHeight="1">
       <c r="A94" s="12" t="s">
-        <v>2345</v>
+        <v>2068</v>
       </c>
       <c r="B94" s="11" t="s">
-        <v>2310</v>
+        <v>2361</v>
       </c>
       <c r="C94" s="11" t="s">
-        <v>2374</v>
+        <v>2421</v>
       </c>
       <c r="D94" s="11" t="s">
-        <v>2436</v>
+        <v>2483</v>
       </c>
       <c r="E94" s="12" t="s">
-        <v>2370</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="95" ht="22.5" customHeight="1">
       <c r="A95" s="12" t="s">
-        <v>2345</v>
+        <v>2068</v>
       </c>
       <c r="B95" s="11" t="s">
-        <v>2310</v>
+        <v>2361</v>
       </c>
       <c r="C95" s="11" t="s">
-        <v>2410</v>
+        <v>2457</v>
       </c>
       <c r="D95" s="11" t="s">
-        <v>2405</v>
+        <v>2452</v>
       </c>
       <c r="E95" s="12" t="s">
-        <v>2370</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="96" ht="22.5" customHeight="1">
       <c r="A96" s="12" t="s">
-        <v>2345</v>
+        <v>2068</v>
       </c>
       <c r="B96" s="11" t="s">
-        <v>2310</v>
+        <v>2361</v>
       </c>
       <c r="C96" s="11" t="s">
-        <v>2389</v>
+        <v>2436</v>
       </c>
       <c r="D96" s="11" t="s">
-        <v>2379</v>
+        <v>2426</v>
       </c>
       <c r="E96" s="12" t="s">
-        <v>2380</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="97" ht="22.5" customHeight="1">
       <c r="A97" s="12" t="s">
-        <v>2345</v>
+        <v>2068</v>
       </c>
       <c r="B97" s="11" t="s">
-        <v>2310</v>
+        <v>2361</v>
       </c>
       <c r="C97" s="11" t="s">
-        <v>2438</v>
+        <v>2485</v>
       </c>
       <c r="D97" s="11" t="s">
-        <v>2379</v>
+        <v>2426</v>
       </c>
       <c r="E97" s="12" t="s">
-        <v>2380</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="98" ht="22.5" customHeight="1">
       <c r="A98" s="12" t="s">
-        <v>2345</v>
+        <v>2068</v>
       </c>
       <c r="B98" s="11" t="s">
-        <v>2310</v>
+        <v>2361</v>
       </c>
       <c r="C98" s="11" t="s">
-        <v>2439</v>
+        <v>2486</v>
       </c>
       <c r="D98" s="11" t="s">
-        <v>2379</v>
+        <v>2426</v>
       </c>
       <c r="E98" s="12" t="s">
-        <v>2380</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="99" ht="22.5" customHeight="1">
       <c r="A99" s="12" t="s">
-        <v>2345</v>
+        <v>2068</v>
       </c>
       <c r="B99" s="11" t="s">
-        <v>2310</v>
+        <v>2361</v>
       </c>
       <c r="C99" s="11" t="s">
-        <v>2440</v>
+        <v>2487</v>
       </c>
       <c r="D99" s="11" t="s">
-        <v>2379</v>
+        <v>2426</v>
       </c>
       <c r="E99" s="12" t="s">
-        <v>2380</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="100" ht="22.5" customHeight="1">
       <c r="A100" s="12" t="s">
-        <v>2345</v>
+        <v>2068</v>
       </c>
       <c r="B100" s="11" t="s">
-        <v>2355</v>
+        <v>2069</v>
       </c>
       <c r="C100" s="11" t="s">
         <v>1626</v>
       </c>
       <c r="D100" s="11" t="s">
-        <v>2441</v>
+        <v>2488</v>
       </c>
       <c r="E100" s="12" t="s">
-        <v>2370</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="101" ht="22.5" customHeight="1">
       <c r="A101" s="12" t="s">
-        <v>2345</v>
+        <v>2068</v>
       </c>
       <c r="B101" s="11" t="s">
-        <v>2353</v>
+        <v>2402</v>
       </c>
       <c r="C101" s="11" t="s">
         <v>1626</v>
       </c>
       <c r="D101" s="11" t="s">
-        <v>2442</v>
+        <v>2489</v>
       </c>
       <c r="E101" s="12" t="s">
-        <v>2370</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="102" ht="22.5" customHeight="1">
       <c r="A102" s="12" t="s">
-        <v>2345</v>
+        <v>2068</v>
       </c>
       <c r="B102" s="11" t="s">
-        <v>2443</v>
+        <v>2490</v>
       </c>
       <c r="C102" s="11" t="s">
-        <v>2444</v>
+        <v>2491</v>
       </c>
       <c r="D102" s="11" t="s">
-        <v>2379</v>
+        <v>2426</v>
       </c>
       <c r="E102" s="12" t="s">
-        <v>2370</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="103">

--- a/規則庫.xlsx
+++ b/規則庫.xlsx
@@ -35,6 +35,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_加藥規則" sheetId="30" state="visible" r:id="rId30"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_官方代碼表" sheetId="31" state="visible" r:id="rId31"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_官方參數規範" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_放流標準_附表五" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_放流標準_附表十六" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_放流標準_附表四" sheetId="35" state="visible" r:id="rId35"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25483,7 +25486,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U100"/>
+  <dimension ref="A1:X100"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="21.13" customWidth="1" style="19" min="7" max="7"/>
@@ -25596,6 +25599,21 @@
           <t>應變動方向備註</t>
         </is>
       </c>
+      <c r="V1" s="0" t="inlineStr">
+        <is>
+          <t>RPM_min (轉/分)</t>
+        </is>
+      </c>
+      <c r="W1" s="0" t="inlineStr">
+        <is>
+          <t>RPM_max (轉/分)</t>
+        </is>
+      </c>
+      <c r="X1" s="0" t="inlineStr">
+        <is>
+          <t>RPM 備註</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
@@ -25661,6 +25679,17 @@
           <t>pH:↕(加酸鹼); 水溫:⇉</t>
         </is>
       </c>
+      <c r="V2" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="W2" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="X2" s="0" t="inlineStr">
+        <is>
+          <t>中低速混合加藥點</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
@@ -25726,6 +25755,17 @@
           <t>pH:↕; 水溫:⇉</t>
         </is>
       </c>
+      <c r="V3" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="W3" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="X3" s="0" t="inlineStr">
+        <is>
+          <t>中低速混合加藥點</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
@@ -25791,6 +25831,17 @@
           <t>pH:↕(中和至中性); 水溫:⇉</t>
         </is>
       </c>
+      <c r="V4" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="W4" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="X4" s="0" t="inlineStr">
+        <is>
+          <t>中低速中和反應</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -25860,6 +25911,17 @@
           <t>pH:↕; SS:↑(加PAC形成新固體); 水溫:⇉</t>
         </is>
       </c>
+      <c r="V5" s="0" t="n">
+        <v>120</v>
+      </c>
+      <c r="W5" s="0" t="n">
+        <v>250</v>
+      </c>
+      <c r="X5" s="0" t="inlineStr">
+        <is>
+          <t>兼具 pH 調整+快混</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -25929,6 +25991,17 @@
           <t>pH:↕; SS:↑; 水溫:⇉</t>
         </is>
       </c>
+      <c r="V6" s="0" t="n">
+        <v>120</v>
+      </c>
+      <c r="W6" s="0" t="n">
+        <v>250</v>
+      </c>
+      <c r="X6" s="0" t="inlineStr">
+        <is>
+          <t>兼具 pH 調整+快混</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -25998,6 +26071,17 @@
           <t>SS:↑(加PAC/絮凝劑); 水溫:⇉</t>
         </is>
       </c>
+      <c r="V7" s="0" t="n">
+        <v>150</v>
+      </c>
+      <c r="W7" s="0" t="n">
+        <v>300</v>
+      </c>
+      <c r="X7" s="0" t="inlineStr">
+        <is>
+          <t>高速分散凝集劑</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -26067,6 +26151,17 @@
           <t>SS:↑; 水溫:⇉</t>
         </is>
       </c>
+      <c r="V8" s="0" t="n">
+        <v>150</v>
+      </c>
+      <c r="W8" s="0" t="n">
+        <v>300</v>
+      </c>
+      <c r="X8" s="0" t="inlineStr">
+        <is>
+          <t>高速分散凝集劑</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -26136,6 +26231,17 @@
           <t>SS:↑(加PAM絮凝, 顆粒變大但質量略增); 水溫:⇉</t>
         </is>
       </c>
+      <c r="V9" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="W9" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="X9" s="0" t="inlineStr">
+        <is>
+          <t>低速不打散絮體</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -26205,6 +26311,17 @@
           <t>SS:↑; 水溫:⇉</t>
         </is>
       </c>
+      <c r="V10" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="W10" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="X10" s="0" t="inlineStr">
+        <is>
+          <t>低速不打散絮體</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -26272,6 +26389,17 @@
           <t>SS:↓↓(主流出口); SS:↑(污泥支線); 重金屬:↓(隨絮體沉降); COD/BOD:↓(伴隨SS)</t>
         </is>
       </c>
+      <c r="V11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="X11" s="0" t="inlineStr">
+        <is>
+          <t>0=不攪, 5~15=刮泥機</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -26339,6 +26467,17 @@
           <t>SS:↓↓; SS污泥支線:↑; 重金屬:↓; COD/BOD:↓</t>
         </is>
       </c>
+      <c r="V12" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="X12" s="0" t="inlineStr">
+        <is>
+          <t>0=不攪, 5~15=刮泥機</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -26404,6 +26543,17 @@
           <t>SS:↓↓; 油脂:↓↓(主流出口); 浮渣支線:↑</t>
         </is>
       </c>
+      <c r="V13" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="X13" s="0" t="inlineStr">
+        <is>
+          <t>靠氣泡, 一般不攪</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -26465,6 +26615,11 @@
           <t>SS:↓↓(過濾); 濁度:↓↓; 反洗水支線:SS↑</t>
         </is>
       </c>
+      <c r="X14" s="0" t="inlineStr">
+        <is>
+          <t>無攪拌 (過濾)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -26526,6 +26681,11 @@
           <t>COD:↓; BOD:↓; 色度:↓↓; 異味:↓↓; 游離氯:↓↓; 微量有機物:↓↓</t>
         </is>
       </c>
+      <c r="X15" s="0" t="inlineStr">
+        <is>
+          <t>無攪拌 (吸附)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
@@ -26587,6 +26747,11 @@
           <t>COD:↓; BOD:↓; 色度:↓↓; 異味:↓↓; 游離氯:↓↓; 微量有機物:↓↓</t>
         </is>
       </c>
+      <c r="X16" s="0" t="inlineStr">
+        <is>
+          <t>無攪拌 (吸附)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
@@ -26648,6 +26813,11 @@
           <t>重金屬離子:↓↓(Cu/Ni/Zn/Cr/Cd); 硬度離子(Ca/Mg):↓; 反洗液支線:↑</t>
         </is>
       </c>
+      <c r="X17" s="0" t="inlineStr">
+        <is>
+          <t>無攪拌 (離子交換)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
@@ -26721,6 +26891,17 @@
       <c r="U18" s="0" t="inlineStr">
         <is>
           <t>BOD:↓↓; COD:↓; 氨氮:↓(硝化); DO:↑(鼓風); MLSS:↑(微生物增生)</t>
+        </is>
+      </c>
+      <c r="V18" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="W18" s="0" t="n">
+        <v>150</v>
+      </c>
+      <c r="X18" s="0" t="inlineStr">
+        <is>
+          <t>機械式; 鼓風式無此參數</t>
         </is>
       </c>
     </row>
@@ -26788,6 +26969,17 @@
           <t>COD:↓↓; BOD:↓↓; 真色色度:↓; pH:↕(加氧化劑改變)</t>
         </is>
       </c>
+      <c r="V19" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="W19" s="0" t="n">
+        <v>150</v>
+      </c>
+      <c r="X19" s="0" t="inlineStr">
+        <is>
+          <t>中速讓氧化劑接觸</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
@@ -26853,6 +27045,17 @@
       <c r="U20" s="0" t="inlineStr">
         <is>
           <t>BOD:↓↓; COD:↓↓; 沼氣:↑; pH:↕(可能酸化)</t>
+        </is>
+      </c>
+      <c r="V20" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="W20" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="X20" s="0" t="inlineStr">
+        <is>
+          <t>保持微生物懸浮</t>
         </is>
       </c>
     </row>
@@ -26918,6 +27121,11 @@
           <t>含水率:↓↓(脫水至70~85%); 濾液:含水率↑</t>
         </is>
       </c>
+      <c r="X21" s="0" t="inlineStr">
+        <is>
+          <t>視機型: 帶濾 5~30, 離心 1000~3000</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -26983,6 +27191,17 @@
           <t>含水率:↓(濃縮至95~97%); 上澄液:↑</t>
         </is>
       </c>
+      <c r="V22" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="X22" s="0" t="inlineStr">
+        <is>
+          <t>0=重力, 20=有刮泥</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
@@ -27044,6 +27263,17 @@
           <t>含水率:可能↓(沉降進一步濃縮); 一般⇉</t>
         </is>
       </c>
+      <c r="V23" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="W23" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="X23" s="0" t="inlineStr">
+        <is>
+          <t>低速防結塊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
@@ -27109,6 +27339,17 @@
           <t>⇉ (應守恆, 僅暫存)</t>
         </is>
       </c>
+      <c r="V24" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="X24" s="0" t="inlineStr">
+        <is>
+          <t>通常不攪或低速</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
@@ -27174,6 +27415,17 @@
           <t>⇉ (應守恆)</t>
         </is>
       </c>
+      <c r="V25" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="X25" s="0" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
@@ -27239,6 +27491,17 @@
           <t>pH:↕; 水質波動:↓(均勻化); 質量⇉</t>
         </is>
       </c>
+      <c r="V26" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="W26" s="0" t="n">
+        <v>80</v>
+      </c>
+      <c r="X26" s="0" t="inlineStr">
+        <is>
+          <t>均勻化 + 水質波動吸收</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
@@ -27304,6 +27567,17 @@
           <t>pH:↕(均勻化); 其他⇉</t>
         </is>
       </c>
+      <c r="V27" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="W27" s="0" t="n">
+        <v>80</v>
+      </c>
+      <c r="X27" s="0" t="inlineStr">
+        <is>
+          <t>均勻化用</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
@@ -27367,6 +27641,17 @@
           <t>⇉ (僅收集匯流)</t>
         </is>
       </c>
+      <c r="V28" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="X28" s="0" t="inlineStr">
+        <is>
+          <t>通常不攪</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
@@ -27428,6 +27713,17 @@
           <t>視批次操作而定 (酸/鹼/氧化/還原皆可能)</t>
         </is>
       </c>
+      <c r="V29" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="W29" s="0" t="n">
+        <v>200</v>
+      </c>
+      <c r="X29" s="0" t="inlineStr">
+        <is>
+          <t>變頻: 反應期高沉降期停</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
@@ -27489,6 +27785,11 @@
           <t>⇉ (放流前緩衝)</t>
         </is>
       </c>
+      <c r="X30" s="0" t="inlineStr">
+        <is>
+          <t>無攪拌 (放流前緩衝)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
@@ -27556,6 +27857,17 @@
           <t>COD:↓; BOD:↓; 氨氮:↓</t>
         </is>
       </c>
+      <c r="V31" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="W31" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="X31" s="0" t="inlineStr">
+        <is>
+          <t>低速循環水流</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
@@ -27629,6 +27941,17 @@
       <c r="U32" s="0" t="inlineStr">
         <is>
           <t>COD:↓↓; BOD:↓↓; 氨氮:↓↓; SS:↓↓(膜過濾, 出水極低)</t>
+        </is>
+      </c>
+      <c r="V32" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="W32" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="X32" s="0" t="inlineStr">
+        <is>
+          <t>配合膜組件</t>
         </is>
       </c>
     </row>
@@ -27696,6 +28019,17 @@
           <t>氰化物:↓↓(NaClO破氰); pH:↑(鹼性條件)</t>
         </is>
       </c>
+      <c r="V33" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="W33" s="0" t="n">
+        <v>150</v>
+      </c>
+      <c r="X33" s="0" t="inlineStr">
+        <is>
+          <t>同氧化池, 需 ORP 儀</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
@@ -27761,6 +28095,17 @@
           <t>六價鉻:↓↓(還原成3價); pH:↓(酸性條件)</t>
         </is>
       </c>
+      <c r="V34" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="W34" s="0" t="n">
+        <v>150</v>
+      </c>
+      <c r="X34" s="0" t="inlineStr">
+        <is>
+          <t>同氧化池, 需 ORP 儀</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
@@ -27830,6 +28175,17 @@
           <t>SS:↑(混凝形成絮體); 水溫:⇉</t>
         </is>
       </c>
+      <c r="V35" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="W35" s="0" t="n">
+        <v>120</v>
+      </c>
+      <c r="X35" s="0" t="inlineStr">
+        <is>
+          <t>多段: 進口高出口低</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
@@ -27893,6 +28249,17 @@
           <t>含水率:↓↓; 濾液:↑</t>
         </is>
       </c>
+      <c r="V36" s="0" t="n">
+        <v>1000</v>
+      </c>
+      <c r="W36" s="0" t="n">
+        <v>3500</v>
+      </c>
+      <c r="X36" s="0" t="inlineStr">
+        <is>
+          <t>離心式高速</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
@@ -27956,6 +28323,17 @@
           <t>含水率:↓↓; 濾液:↑</t>
         </is>
       </c>
+      <c r="V37" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="W37" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="X37" s="0" t="inlineStr">
+        <is>
+          <t>帶濾式低速</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
@@ -28021,6 +28399,17 @@
           <t>含水率:↓; 上澄液:↑</t>
         </is>
       </c>
+      <c r="V38" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="X38" s="0" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
@@ -28086,6 +28475,11 @@
           <t>重金屬離子:↓↓(Cu/Ni/Zn/Cr/Cd); 硬度離子(Ca/Mg):↓; 反洗液支線:↑</t>
         </is>
       </c>
+      <c r="X39" s="0" t="inlineStr">
+        <is>
+          <t>無攪拌 (離子交換)</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
@@ -28147,6 +28541,11 @@
           <t>SS:↓↓; 濁度:↓↓; 反洗水:SS↑</t>
         </is>
       </c>
+      <c r="X40" s="0" t="inlineStr">
+        <is>
+          <t>無攪拌 (過濾)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
@@ -28214,6 +28613,17 @@
           <t>SS:↓↓; 油脂:↓↓(主流出口); 浮渣支線:↑</t>
         </is>
       </c>
+      <c r="V41" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="X41" s="0" t="inlineStr">
+        <is>
+          <t>靠氣泡, 一般不攪</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
@@ -28281,6 +28691,17 @@
           <t>油脂:↓↓(主流); 油脂渣支線:↑</t>
         </is>
       </c>
+      <c r="V42" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="X42" s="0" t="inlineStr">
+        <is>
+          <t>靠浮力</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
@@ -28342,6 +28763,17 @@
           <t>SS:↓(粗篩); 重金屬:↓(初步去除); 油脂:↓; 水溫:↕</t>
         </is>
       </c>
+      <c r="V43" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="W43" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="X43" s="0" t="inlineStr">
+        <is>
+          <t>均勻化 + 部分沉降</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
@@ -28405,6 +28837,17 @@
       <c r="U44" s="0" t="inlineStr">
         <is>
           <t>SS:↕(濾液SS可能高於主流); 含水率:↑</t>
+        </is>
+      </c>
+      <c r="V44" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="X44" s="0" t="inlineStr">
+        <is>
+          <t>視是否加藥</t>
         </is>
       </c>
     </row>
@@ -30222,17 +30665,17 @@
           <t>ORP_max (mV)</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="0" t="inlineStr">
         <is>
           <t>典型劑量 (mg/L)</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="0" t="inlineStr">
         <is>
           <t>引入水質項目</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="0" t="inlineStr">
         <is>
           <t>轉換係數</t>
         </is>
@@ -30304,7 +30747,7 @@
       </c>
       <c r="P2" s="16" t="inlineStr"/>
       <c r="Q2" s="16" t="inlineStr"/>
-      <c r="R2" t="n">
+      <c r="R2" s="0" t="n">
         <v>80</v>
       </c>
     </row>
@@ -30374,15 +30817,15 @@
       </c>
       <c r="P3" s="16" t="inlineStr"/>
       <c r="Q3" s="16" t="inlineStr"/>
-      <c r="R3" t="n">
+      <c r="R3" s="0" t="n">
         <v>60</v>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S3" s="0" t="inlineStr">
         <is>
           <t>懸浮固體（mg/L）</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T3" s="0" t="inlineStr">
         <is>
           <t>0.50</t>
         </is>
@@ -30548,7 +30991,7 @@
       </c>
       <c r="P6" s="16" t="inlineStr"/>
       <c r="Q6" s="16" t="inlineStr"/>
-      <c r="R6" t="n">
+      <c r="R6" s="0" t="n">
         <v>50</v>
       </c>
     </row>
@@ -30618,15 +31061,15 @@
       </c>
       <c r="P7" s="16" t="inlineStr"/>
       <c r="Q7" s="16" t="inlineStr"/>
-      <c r="R7" t="n">
+      <c r="R7" s="0" t="n">
         <v>30</v>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="S7" s="0" t="inlineStr">
         <is>
           <t>硫酸根</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="T7" s="0" t="inlineStr">
         <is>
           <t>0.98</t>
         </is>
@@ -30698,15 +31141,15 @@
       </c>
       <c r="P8" s="16" t="inlineStr"/>
       <c r="Q8" s="16" t="inlineStr"/>
-      <c r="R8" t="n">
+      <c r="R8" s="0" t="n">
         <v>30</v>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="S8" s="0" t="inlineStr">
         <is>
           <t>氯離子</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="T8" s="0" t="inlineStr">
         <is>
           <t>0.97</t>
         </is>
@@ -30821,15 +31264,15 @@
       </c>
       <c r="P10" s="16" t="inlineStr"/>
       <c r="Q10" s="16" t="inlineStr"/>
-      <c r="R10" t="n">
+      <c r="R10" s="0" t="n">
         <v>100</v>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="S10" s="0" t="inlineStr">
         <is>
           <t>懸浮固體（mg/L）; 氯離子</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="T10" s="0" t="inlineStr">
         <is>
           <t>0.30; 0.05</t>
         </is>
@@ -30897,15 +31340,15 @@
       </c>
       <c r="P11" s="16" t="inlineStr"/>
       <c r="Q11" s="16" t="inlineStr"/>
-      <c r="R11" t="n">
+      <c r="R11" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="S11" s="0" t="inlineStr">
         <is>
           <t>懸浮固體（mg/L）</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="T11" s="0" t="inlineStr">
         <is>
           <t>1.00</t>
         </is>
@@ -30973,15 +31416,15 @@
       </c>
       <c r="P12" s="16" t="inlineStr"/>
       <c r="Q12" s="16" t="inlineStr"/>
-      <c r="R12" t="n">
+      <c r="R12" s="0" t="n">
         <v>80</v>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="S12" s="0" t="inlineStr">
         <is>
           <t>懸浮固體（mg/L）; 氯離子</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="T12" s="0" t="inlineStr">
         <is>
           <t>0.35; 0.65</t>
         </is>
@@ -31057,15 +31500,15 @@
       <c r="Q13" s="16" t="n">
         <v>450</v>
       </c>
-      <c r="R13" t="n">
+      <c r="R13" s="0" t="n">
         <v>300</v>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="S13" s="0" t="inlineStr">
         <is>
           <t>氯離子</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="T13" s="0" t="inlineStr">
         <is>
           <t>0.48</t>
         </is>
@@ -31141,7 +31584,7 @@
       <c r="Q14" s="16" t="n">
         <v>450</v>
       </c>
-      <c r="R14" t="n">
+      <c r="R14" s="0" t="n">
         <v>200</v>
       </c>
     </row>
@@ -31215,15 +31658,15 @@
       <c r="Q15" s="16" t="n">
         <v>300</v>
       </c>
-      <c r="R15" t="n">
+      <c r="R15" s="0" t="n">
         <v>200</v>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="S15" s="0" t="inlineStr">
         <is>
           <t>硫酸根</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="T15" s="0" t="inlineStr">
         <is>
           <t>0.92</t>
         </is>
@@ -31299,7 +31742,7 @@
       <c r="Q16" s="16" t="n">
         <v>300</v>
       </c>
-      <c r="R16" t="n">
+      <c r="R16" s="0" t="n">
         <v>50</v>
       </c>
     </row>
@@ -31369,7 +31812,7 @@
       </c>
       <c r="P17" s="16" t="inlineStr"/>
       <c r="Q17" s="16" t="inlineStr"/>
-      <c r="R17" t="n">
+      <c r="R17" s="0" t="n">
         <v>50</v>
       </c>
     </row>
@@ -31439,15 +31882,15 @@
       </c>
       <c r="P18" s="16" t="inlineStr"/>
       <c r="Q18" s="16" t="inlineStr"/>
-      <c r="R18" t="n">
+      <c r="R18" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="S18" s="0" t="inlineStr">
         <is>
           <t>氯離子</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="T18" s="0" t="inlineStr">
         <is>
           <t>0.48</t>
         </is>
@@ -31519,7 +31962,7 @@
       </c>
       <c r="P19" s="16" t="inlineStr"/>
       <c r="Q19" s="16" t="inlineStr"/>
-      <c r="R19" t="n">
+      <c r="R19" s="0" t="n">
         <v>50</v>
       </c>
     </row>
@@ -31589,7 +32032,7 @@
       </c>
       <c r="P20" s="16" t="inlineStr"/>
       <c r="Q20" s="16" t="inlineStr"/>
-      <c r="R20" t="n">
+      <c r="R20" s="0" t="n">
         <v>30</v>
       </c>
     </row>
@@ -31659,15 +32102,15 @@
       </c>
       <c r="P21" s="7" t="inlineStr"/>
       <c r="Q21" s="7" t="inlineStr"/>
-      <c r="R21" t="n">
+      <c r="R21" s="0" t="n">
         <v>50</v>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="S21" s="0" t="inlineStr">
         <is>
           <t>懸浮固體（mg/L）; 氯離子</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="T21" s="0" t="inlineStr">
         <is>
           <t>0.35; 0.65</t>
         </is>
@@ -40624,6 +41067,6257 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G67"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>業別</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>水質項目</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>限值</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>單位</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>適用條件</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>施行日期</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>備註/來源</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>水溫</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>℃</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>5-9月, 非海洋</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>水溫</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>℃</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>10-4月, 非海洋</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>水溫</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>℃</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>直接排放海洋 (放流口500m內表面溫差≤4℃)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>6.0~9.0</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>氟鹽</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>硝酸鹽氮</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>金屬基本/表面處理/電鍍/PCB</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>氨氮</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>排放於自來水水質水量保護區內</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>金屬表面處理/電鍍</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>氨氮</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>保護區外, 106/12/25 前完成</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>金屬表面處理/電鍍</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>氨氮</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>保護區外, 106/12/25 前完成</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>116/1/1 施行加嚴</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>金屬表面處理/電鍍</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>氨氮</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>保護區外, 106/12/25 前尚未招標</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>氨氮</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>保護區外, 113/12/18 前完成</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>116/1/1 施行</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>氨氮</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>保護區外, 113/12/18 前完成</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>118/1/1 施行</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>氨氮</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>保護區外, 113/12/18 前尚未招標</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>正磷酸鹽</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>mg/L as PO4</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>排放於自來水水質水量保護區內</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>酚類</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>陰離子界面活性劑</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>氰化物</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>油脂</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>正己烷抽出物</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>溶解性鐵</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>溶解性錳</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>電鍍/表面/基本 或 PCB</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>鎘</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>106/12/25 前完成</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>電鍍/表面/基本 (&gt;150CMD) 或 PCB (&gt;500CMD)</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>鎘</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>106/12/25 前完成</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>鎘</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>106/12/25 前尚未招標</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>電鍍/表面/基本 或 PCB</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>鉛</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>106/12/25 前完成</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>電鍍/表面/基本 (&gt;150CMD) 或 PCB (&gt;500CMD)</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>鉛</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>106/12/25 前完成</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>鉛</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>106/12/25 前尚未招標</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>電鍍/表面/基本 或 PCB</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>總鉻</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>106/12/25 前完成</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>電鍍/表面/基本 (&gt;150CMD) 或 PCB (&gt;500CMD)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>總鉻</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>106/12/25 前完成</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>總鉻</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>106/12/25 前尚未招標</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>電鍍/表面/基本 或 PCB</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>六價鉻</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>106/12/25 前完成</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>電鍍/表面/基本 (&gt;150CMD) 或 PCB (&gt;500CMD)</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>六價鉻</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>106/12/25 前完成</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>六價鉻</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>106/12/25 前尚未招標</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>電鍍/表面/基本 (≤150CMD) 或 PCB (≤500CMD)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>銅</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>106/12/25 前完成</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>銅</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>116/1/1 施行</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>電鍍/表面/基本 (≤150CMD) 或 PCB (≤500CMD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>銅</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>106/12/25 前尚未招標</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>電鍍/表面/基本 (&gt;150CMD) 或 PCB (&gt;500CMD)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>銅</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>113/12/18 前完成</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>銅</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>116/1/1 施行</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>電鍍/表面/基本 (&gt;150CMD) 或 PCB (&gt;500CMD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>銅</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>113/12/18 前尚未招標</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>鋅</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>106/12/25 前完成</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>電鍍/表面/基本 (&gt;150CMD) 或 PCB (&gt;500CMD)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>鋅</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>106/12/25 前完成</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>鋅</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>106/12/25 前尚未招標</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>鎳</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>106/12/25 前完成</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>電鍍/表面/基本 (&gt;150CMD) 或 PCB (&gt;500CMD)</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>鎳</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>106/12/25 前完成</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>鎳</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>106/12/25 前尚未招標</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>硒</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>106/12/25 前完成</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>電鍍/表面/基本 (&gt;150CMD) 或 PCB (&gt;500CMD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>硒</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>106/12/25 前完成</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>硒</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>106/12/25 前尚未招標</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>砷</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>106/12/25 前完成</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>電鍍/表面/基本 (&gt;150CMD) 或 PCB (&gt;500CMD)</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>砷</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>106/12/25 前完成</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>砷</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>106/12/25 前尚未招標</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>電鍍/表面/基本 (&gt;150CMD) 或 PCB (&gt;500CMD)</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>錫</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>106/12/25 前完成</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>錫</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>106/12/25 前尚未招標</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>總汞</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>0.005</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>銀</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>金屬基本/PCB</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>硼</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>排放於自來水水質水量保護區內</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>金屬基本/PCB</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>硼</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>排放於自來水水質水量保護區外</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>金屬表面處理/電鍍</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>硼</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>排放於自來水水質水量保護區內</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>金屬表面處理/電鍍</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>硼</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>排放於自來水水質水量保護區外</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>硼</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>116/1/1 施行</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>鉬</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>全</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>硫化物</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>金屬基本/表面處理/電鍍</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>化學需氧量</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>化學需氧量</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>金屬基本/表面處理/電鍍</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>懸浮固體</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>懸浮固體</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>PCB</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>生化需氧量</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G37"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>業別</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>水質項目</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>限值</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>單位</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>適用條件</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>施行日期</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>備註/來源</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>第一級-新設</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>鎘</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>&lt;0.005</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>第一級, 新設事業或工業區, 公告前尚未招標</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>公告日起</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>第一級-新設</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>總鉻</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>&lt;0.01</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>公告日起</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>第一級-新設</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>六價鉻</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>&lt;0.02</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>公告日起</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>第一級-新設</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>銅</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>&lt;0.01</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>公告日起</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>第一級-新設</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>鋅</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>&lt;0.01</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>公告日起</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>第一級-新設</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>鎳</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>&lt;0.02</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>公告日起</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>第一級-既設事業</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>鎘</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>第一級, 既設事業, 公告前完成</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>公告後 2 年</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>第一級-既設事業</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>總鉻</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>公告後 2 年</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>第一級-既設事業</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>六價鉻</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>公告後 2 年</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>第一級-既設事業</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>銅</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>公告後 2 年</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>第一級-既設事業</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>鋅</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>公告後 2 年</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>第一級-既設事業</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>鎳</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>公告後 2 年</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>第一級-既設工業區</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>鎘</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0.015</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>第一級, 既設工業區污水下水道</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>公告後 2 年</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>第一級-既設工業區</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>總鉻</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>公告後 2 年</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>第一級-既設工業區</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>六價鉻</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>公告後 2 年</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>第一級-既設工業區</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>銅</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>公告後 2 年</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>第一級-既設工業區</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>鋅</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>公告後 2 年</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>第一級-既設工業區</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>鎳</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>公告後 2 年</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>第二級-新設事業</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>鎘</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>第二級, 新設事業</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>公告日起</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>第二級-新設事業</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>總鉻</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>公告日起</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>第二級-新設事業</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>六價鉻</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>公告日起</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>第二級-新設事業</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>銅</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>公告日起</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>第二級-新設事業</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>鋅</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>公告日起</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>第二級-新設事業</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>鎳</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>公告日起</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>第二級-新設工業區</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>鎘</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>0.015</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>第二級, 新設工業區污水下水道</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>公告日起</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>第二級-新設工業區</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>總鉻</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>公告日起</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>第二級-新設工業區</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>六價鉻</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>公告日起</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>第二級-新設工業區</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>銅</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>公告日起</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>第二級-新設工業區</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>鋅</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>公告日起</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>第二級-新設工業區</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>鎳</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>公告日起</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>第二級-既設</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>鎘</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>0.015</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>第二級, 既設事業及工業區</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>公告後 2 年</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>第二級-既設</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>總鉻</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>公告後 2 年</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>第二級-既設</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>六價鉻</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>公告後 2 年</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>第二級-既設</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>銅</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>公告後 2 年</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>第二級-既設</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>鋅</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>公告後 2 年</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>第二級-既設</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>鎳</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>公告後 2 年</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G85"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>業別</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>水質項目</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>限值</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>單位</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>適用條件</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>施行日期</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>備註/來源</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>化工業</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>水溫</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>℃</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>5-9月, 非海洋</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>化工業</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>水溫</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>℃</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>10-4月, 非海洋</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>化工業</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>水溫</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>℃</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>直接排放海洋</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>化工業</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>pH</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>6.0~9.0</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>化工業</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>氟鹽</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>化工業</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>硝酸鹽氮</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>化工業</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>氨氮</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>排放於自來水水質水量保護區內</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>化工業-非高含氮</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>氨氮</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>保護區外, 103/1/22 前完成</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>化工業-高含氮</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>氨氮</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>保護區外, 103/1/22 前完成</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>化工業</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>氨氮</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>保護區外, 103/1/22 前尚未招標</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>化工業</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>正磷酸鹽</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>4.0</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>mg/L as PO4</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>排放於自來水水質水量保護區內</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>化工業</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>酚類</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>化工業</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>陰離子界面活性劑</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>化工業</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>氰化物</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>化工業</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>油脂</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>正己烷抽出物</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>化工業</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>溶解性鐵</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>化工業</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>溶解性錳</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>化工業</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>鎘</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>106/12/25 前完成</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>化工業-大於500CMD</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>鎘</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>106/12/25 前完成</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>化工業</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>鎘</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>106/12/25 前尚未招標</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>化工業</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>鉛</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>106/12/25 前完成</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>化工業-大於500CMD</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>鉛</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>106/12/25 前完成</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>化工業</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>鉛</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>106/12/25 前尚未招標</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>化工業</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>總鉻</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>106/12/25 前完成</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>化工業-大於500CMD</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>總鉻</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>106/12/25 前完成</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>化工業</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>總鉻</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>106/12/25 前尚未招標</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>化工業</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>六價鉻</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>106/12/25 前完成</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>化工業-大於500CMD</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>六價鉻</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>106/12/25 前完成</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>化工業</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>六價鉻</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>106/12/25 前尚未招標</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>化工業-≤500CMD</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>銅</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>106/12/25 前完成</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>銅</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>116/1/1 施行</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>化工業-≤500CMD</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>銅</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>106/12/25 前尚未招標</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>化工業-大於500CMD</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>銅</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>113/12/18 前完成</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>銅</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>116/1/1 施行</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>化工業-大於500CMD</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>銅</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>113/12/18 前尚未招標</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>化工業</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>鋅</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>106/12/25 前完成</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>化工業-大於500CMD</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>鋅</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>106/12/25 前完成</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>化工業</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>鋅</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>106/12/25 前尚未招標</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>化工業</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>鎳</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>106/12/25 前完成</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>化工業-大於500CMD</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>鎳</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>106/12/25 前完成</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>化工業</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>鎳</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>0.7</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>106/12/25 前尚未招標</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>化工業</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>硒</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>106/12/25 前完成</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>化工業-大於500CMD</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>硒</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>106/12/25 前完成</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>化工業</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>硒</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>106/12/25 前尚未招標</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>化工業</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>砷</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>106/12/25 前完成</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>化工業-大於500CMD</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>砷</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>106/12/25 前完成</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>化工業</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>砷</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>106/12/25 前尚未招標</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>化工業-大於500CMD</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>錫</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>106/12/25 前完成</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>化工業</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>錫</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>106/12/25 前尚未招標</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>化工業</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>甲基汞</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.0000002</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>化工業</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>總汞</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.005</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>化工業</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>銀</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>化工業</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>硼</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>排放於自來水水質水量保護區內</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>化工業</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>硼</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>排放於自來水水質水量保護區外</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>化工業</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>鉬</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>化工業</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>硫化物</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>化工業</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>甲醛</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>3.0</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>化工業</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>多氯聯苯</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>0.00005</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>化工業-氯乙烯製造</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>戴奧辛</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>pg-TEQ/L</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>101/10/12 前完成</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>化工業-氯乙烯製造</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>戴奧辛</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>pg-TEQ/L</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>101/10/12 前尚未招標</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>化工業</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>生化需氧量</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>化工業</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>化學需氧量</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>化工業</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>懸浮固體</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>化工業</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>真色色度</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>106/12/25 前完成</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>化工業</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>真色色度</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>106/12/25 前尚未招標</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>化工業</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>自由有效餘氯</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>化工業-基本化學/其他化學材料/塗料染料顏料/其他化學製品/電池</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>鈷</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>化工業-基本化學/人造纖維/合成樹脂塑膠橡膠/其他化學材料/塗料染料顏料/清潔用品/化妝品/其他化學製品/電池</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>鋇</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>化工業</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>二氯甲烷</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>化工業</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>三氯甲烷</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>化工業-基本化學/合成樹脂塑膠橡膠/其他化學材料/塗料染料顏料/化妝品/其他化學製品</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>苯</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>0.05</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>乙苯</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>1,2-二氯乙烷</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>0.10</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>氯乙烯</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>0.10</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>鄰苯二甲酸二甲酯DMP</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>鄰苯二甲酸二乙酯DEP</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>鄰苯二甲酸二丁酯DBP</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>鄰苯二甲酸丁基苯甲酯BBP</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>鄰苯二甲酸二辛酯DNOP</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>鄰苯二甲酸二(2-乙基己基)酯DEHP</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>硝基苯</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>0.4</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>三氯乙烯</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>化工業-≥10000CMD (除肥料/石灰/煤製品外)</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>丙烯腈</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>0.2</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>1,3-丁二烯</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>0.1</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>mg/L</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/規則庫.xlsx
+++ b/規則庫.xlsx
@@ -25486,7 +25486,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X100"/>
+  <dimension ref="A1:AA100"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="21.13" customWidth="1" style="19" min="7" max="7"/>
@@ -25614,6 +25614,21 @@
           <t>RPM 備註</t>
         </is>
       </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>主要削減項目</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>削減率範圍(%)</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>削減率學理依據</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
@@ -25690,6 +25705,11 @@
           <t>中低速混合加藥點</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>純調 pH, 不去除任何項目</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
@@ -25766,6 +25786,11 @@
           <t>中低速混合加藥點</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>純調 pH, 不去除任何項目</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
@@ -25842,6 +25867,11 @@
           <t>中低速中和反應</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>純中和, 不去除任何項目</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -25922,6 +25952,21 @@
           <t>兼具 pH 調整+快混</t>
         </is>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0~5 (加PAC反而略升)</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>調pH + 快混, 加PAC後 SS 略升, 未沉澱不去除重金屬</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -26002,6 +26047,21 @@
           <t>兼具 pH 調整+快混</t>
         </is>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0~5 (加PAC反而略升)</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>同上</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -26082,6 +26142,21 @@
           <t>高速分散凝集劑</t>
         </is>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>0~5 (加PAC反而略升)</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>D054 學理: 快混無沉澱功能, 不應表現重金屬去除</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -26162,6 +26237,21 @@
           <t>高速分散凝集劑</t>
         </is>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>0~5 (加PAC反而略升)</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>同快混槽</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -26242,6 +26332,21 @@
           <t>低速不打散絮體</t>
         </is>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0~5 (加PAM 顆粒變大但未沉澱)</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>絮凝但未分離, 質量守恆</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -26322,6 +26427,21 @@
           <t>低速不打散絮體</t>
         </is>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0~5</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>同慢混池</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -26400,6 +26520,21 @@
           <t>0=不攪, 5~15=刮泥機</t>
         </is>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>SS;銅;鎳;鋅;鉛;總鉻;COD;BOD</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>80~95;60~90;50~90;70~95;60~90;60~90;20~50;20~40</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>重力沉降 + 絮體氫氧化物沉澱, COD/BOD 隨 SS 略降</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -26478,6 +26613,21 @@
           <t>0=不攪, 5~15=刮泥機</t>
         </is>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>SS;銅;鎳;鋅;鉛;總鉻;COD;BOD</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>80~95;60~90;50~90;70~95;60~90;60~90;20~50;20~40</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>同沉澱池</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -26554,6 +26704,21 @@
           <t>靠氣泡, 一般不攪</t>
         </is>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>油脂;SS;COD</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>80~98;60~90;20~50</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>加壓浮除, 油脂主力, SS 伴隨</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -26620,6 +26785,21 @@
           <t>無攪拌 (過濾)</t>
         </is>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>SS;濁度</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>70~95;70~95</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>顆粒物理過濾, 溶解性物質不去除, 反洗水 SS↑↑</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -26686,6 +26866,21 @@
           <t>無攪拌 (吸附)</t>
         </is>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>COD;BOD;色度;異味;游離氯</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>30~80;30~70;70~95;80~98;90~99</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>吸附有機物/色度/餘氯, SS 不應去除 (會堵塞)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
@@ -26752,6 +26947,21 @@
           <t>無攪拌 (吸附)</t>
         </is>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>COD;BOD;色度;異味;游離氯</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>30~80;30~70;70~95;80~98;90~99</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>同活性碳吸附塔</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
@@ -26818,6 +27028,21 @@
           <t>無攪拌 (離子交換)</t>
         </is>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>銅;鎳;鋅;鉻;鎘;硬度離子</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>90~99;90~99;90~99;90~99;90~99;50~90</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>離子交換, 對特定金屬去除極高</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
@@ -26902,6 +27127,21 @@
       <c r="X18" s="0" t="inlineStr">
         <is>
           <t>機械式; 鼓風式無此參數</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>BOD;COD;氨氮</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>85~98;60~85;70~95</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>活性污泥好氧分解, 氨氮硝化, MLSS 微生物自增</t>
         </is>
       </c>
     </row>
@@ -26980,6 +27220,21 @@
           <t>中速讓氧化劑接觸</t>
         </is>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>COD;BOD;真色色度</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>30~70;30~70;30~60</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>化學氧化分解有機物</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
@@ -27056,6 +27311,21 @@
       <c r="X20" s="0" t="inlineStr">
         <is>
           <t>保持微生物懸浮</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>BOD;COD</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>70~90;60~85</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>厭氧分解產沼氣, pH 可能酸化</t>
         </is>
       </c>
     </row>
@@ -27126,6 +27396,21 @@
           <t>視機型: 帶濾 5~30, 離心 1000~3000</t>
         </is>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>含水率</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>8~15 (從 97% → 82~89%)</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>機械脫水</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -27202,6 +27487,21 @@
           <t>0=重力, 20=有刮泥</t>
         </is>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>含水率</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>1~3 (從 97% → 94~96%)</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>重力濃縮</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
@@ -27274,6 +27574,11 @@
           <t>低速防結塊</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>儲存, 質量守恆; 略沉降可能微降含水率</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
@@ -27350,6 +27655,11 @@
           <t>通常不攪或低速</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>應守恆</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
@@ -27426,6 +27736,11 @@
           <t>同上</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>應守恆</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
@@ -27502,6 +27817,11 @@
           <t>均勻化 + 水質波動吸收</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>均勻化水質波動, 質量守恆</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
@@ -27578,6 +27898,11 @@
           <t>均勻化用</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>同調勻池</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
@@ -27652,6 +27977,11 @@
           <t>通常不攪</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>僅匯流</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
@@ -27724,6 +28054,11 @@
           <t>變頻: 反應期高沉降期停</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>視批次配方而定, 無固定去除率</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
@@ -27790,6 +28125,11 @@
           <t>無攪拌 (放流前緩衝)</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>放流前緩衝, 應守恆</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
@@ -27868,6 +28208,21 @@
           <t>低速循環水流</t>
         </is>
       </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>BOD;COD;氨氮</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>60~90;50~80;50~90</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>生物膜好氧分解</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
@@ -27952,6 +28307,21 @@
       <c r="X32" s="0" t="inlineStr">
         <is>
           <t>配合膜組件</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>BOD;COD;氨氮;SS</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>85~99;70~95;80~99;95~99</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>生物 + 膜過濾, SS 極低</t>
         </is>
       </c>
     </row>
@@ -28030,6 +28400,21 @@
           <t>同氧化池, 需 ORP 儀</t>
         </is>
       </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>氰化物;COD</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>90~99;20~50</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>NaClO 破氰: CN⁻ → CNO⁻ → N₂↑</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
@@ -28106,6 +28491,21 @@
           <t>同氧化池, 需 ORP 儀</t>
         </is>
       </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>六價鉻</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>95~99</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>NaHSO₃ 還原 Cr⁶⁺ → Cr³⁺ (總鉻不去除, 只變價)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
@@ -28186,6 +28586,21 @@
           <t>多段: 進口高出口低</t>
         </is>
       </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>SS</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>0~5 (絮體形成但未沉澱)</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>只形成絮體, 未分離</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
@@ -28260,6 +28675,21 @@
           <t>離心式高速</t>
         </is>
       </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>含水率</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>12~22 (從 97% → 75~85%)</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>離心高速脫水</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
@@ -28334,6 +28764,21 @@
           <t>帶濾式低速</t>
         </is>
       </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>含水率</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>8~17 (從 97% → 80~89%)</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>帶濾中速脫水</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
@@ -28410,6 +28855,21 @@
           <t>同上</t>
         </is>
       </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>含水率</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>1~3 (從 97% → 94~96%)</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>同濃縮槽</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
@@ -28480,6 +28940,21 @@
           <t>無攪拌 (離子交換)</t>
         </is>
       </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>銅;鎳;鋅;鉻;鎘;硬度離子</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>90~99;90~99;90~99;90~99;90~99;50~90</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>離子交換, 對特定金屬去除極高</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
@@ -28546,6 +29021,21 @@
           <t>無攪拌 (過濾)</t>
         </is>
       </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>SS;濁度</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>70~95;70~95</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>同砂濾塔</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
@@ -28624,6 +29114,21 @@
           <t>靠氣泡, 一般不攪</t>
         </is>
       </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>油脂;SS;COD</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>80~98;60~90;20~50</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>加壓浮除, 油脂主力, SS 伴隨</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
@@ -28702,6 +29207,21 @@
           <t>靠浮力</t>
         </is>
       </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>油脂</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>70~95</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>重力分離, 只降油脂</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
@@ -28774,6 +29294,21 @@
           <t>均勻化 + 部分沉降</t>
         </is>
       </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>SS;油脂</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>20~60;30~70</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>粗篩/沉砂, 重金屬未沉澱不去除</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
@@ -28848,6 +29383,11 @@
       <c r="X44" s="0" t="inlineStr">
         <is>
           <t>視是否加藥</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>回收濾液, 質量守恆但含水率高</t>
         </is>
       </c>
     </row>
@@ -41077,2171 +41617,2171 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="0" t="inlineStr">
         <is>
           <t>業別</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="0" t="inlineStr">
         <is>
           <t>水質項目</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="0" t="inlineStr">
         <is>
           <t>限值</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="0" t="inlineStr">
         <is>
           <t>單位</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="0" t="inlineStr">
         <is>
           <t>適用條件</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="0" t="inlineStr">
         <is>
           <t>施行日期</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="0" t="inlineStr">
         <is>
           <t>備註/來源</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
         <is>
           <t>全</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="0" t="inlineStr">
         <is>
           <t>水溫</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="0" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="0" t="inlineStr">
         <is>
           <t>℃</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="0" t="inlineStr">
         <is>
           <t>5-9月, 非海洋</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
+      <c r="F2" s="0" t="inlineStr"/>
+      <c r="G2" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
         <is>
           <t>全</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="0" t="inlineStr">
         <is>
           <t>水溫</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="0" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="0" t="inlineStr">
         <is>
           <t>℃</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="0" t="inlineStr">
         <is>
           <t>10-4月, 非海洋</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
+      <c r="F3" s="0" t="inlineStr"/>
+      <c r="G3" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
         <is>
           <t>全</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>水溫</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="0" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="0" t="inlineStr">
         <is>
           <t>℃</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="0" t="inlineStr">
         <is>
           <t>直接排放海洋 (放流口500m內表面溫差≤4℃)</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
+      <c r="F4" s="0" t="inlineStr"/>
+      <c r="G4" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="0" t="inlineStr">
         <is>
           <t>全</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>pH</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>6.0~9.0</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="0" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
+      <c r="E5" s="0" t="inlineStr"/>
+      <c r="F5" s="0" t="inlineStr"/>
+      <c r="G5" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="0" t="inlineStr">
         <is>
           <t>全</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="0" t="inlineStr">
         <is>
           <t>氟鹽</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="0" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
+      <c r="E6" s="0" t="inlineStr"/>
+      <c r="F6" s="0" t="inlineStr"/>
+      <c r="G6" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="0" t="inlineStr">
         <is>
           <t>全</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="0" t="inlineStr">
         <is>
           <t>硝酸鹽氮</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="0" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
+      <c r="E7" s="0" t="inlineStr"/>
+      <c r="F7" s="0" t="inlineStr"/>
+      <c r="G7" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="0" t="inlineStr">
         <is>
           <t>金屬基本/表面處理/電鍍/PCB</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="0" t="inlineStr">
         <is>
           <t>氨氮</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="0" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="0" t="inlineStr">
         <is>
           <t>排放於自來水水質水量保護區內</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
+      <c r="F8" s="0" t="inlineStr"/>
+      <c r="G8" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="0" t="inlineStr">
         <is>
           <t>金屬表面處理/電鍍</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="0" t="inlineStr">
         <is>
           <t>氨氮</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="0" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="0" t="inlineStr">
         <is>
           <t>保護區外, 106/12/25 前完成</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
+      <c r="F9" s="0" t="inlineStr"/>
+      <c r="G9" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="0" t="inlineStr">
         <is>
           <t>金屬表面處理/電鍍</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="0" t="inlineStr">
         <is>
           <t>氨氮</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="0" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="0" t="inlineStr">
         <is>
           <t>保護區外, 106/12/25 前完成</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="0" t="inlineStr">
         <is>
           <t>116/1/1 施行加嚴</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="0" t="inlineStr">
         <is>
           <t>金屬表面處理/電鍍</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="0" t="inlineStr">
         <is>
           <t>氨氮</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="0" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="0" t="inlineStr">
         <is>
           <t>保護區外, 106/12/25 前尚未招標</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
+      <c r="F11" s="0" t="inlineStr"/>
+      <c r="G11" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="0" t="inlineStr">
         <is>
           <t>PCB</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="0" t="inlineStr">
         <is>
           <t>氨氮</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="0" t="inlineStr">
         <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="0" t="inlineStr">
         <is>
           <t>保護區外, 113/12/18 前完成</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="0" t="inlineStr">
         <is>
           <t>116/1/1 施行</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="0" t="inlineStr">
         <is>
           <t>PCB</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="0" t="inlineStr">
         <is>
           <t>氨氮</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="0" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="0" t="inlineStr">
         <is>
           <t>保護區外, 113/12/18 前完成</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="0" t="inlineStr">
         <is>
           <t>118/1/1 施行</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="0" t="inlineStr">
         <is>
           <t>PCB</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="0" t="inlineStr">
         <is>
           <t>氨氮</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="0" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="0" t="inlineStr">
         <is>
           <t>保護區外, 113/12/18 前尚未招標</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
+      <c r="F14" s="0" t="inlineStr"/>
+      <c r="G14" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="0" t="inlineStr">
         <is>
           <t>全</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="0" t="inlineStr">
         <is>
           <t>正磷酸鹽</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="0" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="0" t="inlineStr">
         <is>
           <t>mg/L as PO4</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="0" t="inlineStr">
         <is>
           <t>排放於自來水水質水量保護區內</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
+      <c r="F15" s="0" t="inlineStr"/>
+      <c r="G15" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="0" t="inlineStr">
         <is>
           <t>全</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="0" t="inlineStr">
         <is>
           <t>酚類</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="0" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
+      <c r="E16" s="0" t="inlineStr"/>
+      <c r="F16" s="0" t="inlineStr"/>
+      <c r="G16" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="0" t="inlineStr">
         <is>
           <t>全</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="0" t="inlineStr">
         <is>
           <t>陰離子界面活性劑</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="0" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
+      <c r="E17" s="0" t="inlineStr"/>
+      <c r="F17" s="0" t="inlineStr"/>
+      <c r="G17" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="0" t="inlineStr">
         <is>
           <t>全</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="0" t="inlineStr">
         <is>
           <t>氰化物</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="0" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
+      <c r="E18" s="0" t="inlineStr"/>
+      <c r="F18" s="0" t="inlineStr"/>
+      <c r="G18" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="0" t="inlineStr">
         <is>
           <t>全</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="0" t="inlineStr">
         <is>
           <t>油脂</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="0" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="0" t="inlineStr">
         <is>
           <t>正己烷抽出物</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
+      <c r="F19" s="0" t="inlineStr"/>
+      <c r="G19" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="0" t="inlineStr">
         <is>
           <t>全</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="0" t="inlineStr">
         <is>
           <t>溶解性鐵</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="0" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
+      <c r="E20" s="0" t="inlineStr"/>
+      <c r="F20" s="0" t="inlineStr"/>
+      <c r="G20" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="0" t="inlineStr">
         <is>
           <t>全</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="0" t="inlineStr">
         <is>
           <t>溶解性錳</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="0" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
+      <c r="E21" s="0" t="inlineStr"/>
+      <c r="F21" s="0" t="inlineStr"/>
+      <c r="G21" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="0" t="inlineStr">
         <is>
           <t>電鍍/表面/基本 或 PCB</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="0" t="inlineStr">
         <is>
           <t>鎘</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="0" t="inlineStr">
         <is>
           <t>0.03</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前完成</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr">
+      <c r="F22" s="0" t="inlineStr"/>
+      <c r="G22" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="0" t="inlineStr">
         <is>
           <t>電鍍/表面/基本 (&gt;150CMD) 或 PCB (&gt;500CMD)</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="0" t="inlineStr">
         <is>
           <t>鎘</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="0" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前完成</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr">
+      <c r="F23" s="0" t="inlineStr"/>
+      <c r="G23" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="0" t="inlineStr">
         <is>
           <t>全</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="0" t="inlineStr">
         <is>
           <t>鎘</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="0" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前尚未招標</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr">
+      <c r="F24" s="0" t="inlineStr"/>
+      <c r="G24" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="0" t="inlineStr">
         <is>
           <t>電鍍/表面/基本 或 PCB</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="0" t="inlineStr">
         <is>
           <t>鉛</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="0" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前完成</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr">
+      <c r="F25" s="0" t="inlineStr"/>
+      <c r="G25" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="0" t="inlineStr">
         <is>
           <t>電鍍/表面/基本 (&gt;150CMD) 或 PCB (&gt;500CMD)</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="0" t="inlineStr">
         <is>
           <t>鉛</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="0" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前完成</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr">
+      <c r="F26" s="0" t="inlineStr"/>
+      <c r="G26" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="0" t="inlineStr">
         <is>
           <t>全</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="0" t="inlineStr">
         <is>
           <t>鉛</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="0" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前尚未招標</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr">
+      <c r="F27" s="0" t="inlineStr"/>
+      <c r="G27" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="0" t="inlineStr">
         <is>
           <t>電鍍/表面/基本 或 PCB</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="0" t="inlineStr">
         <is>
           <t>總鉻</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="0" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前完成</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr">
+      <c r="F28" s="0" t="inlineStr"/>
+      <c r="G28" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="0" t="inlineStr">
         <is>
           <t>電鍍/表面/基本 (&gt;150CMD) 或 PCB (&gt;500CMD)</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="0" t="inlineStr">
         <is>
           <t>總鉻</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="0" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前完成</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr">
+      <c r="F29" s="0" t="inlineStr"/>
+      <c r="G29" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="0" t="inlineStr">
         <is>
           <t>全</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="0" t="inlineStr">
         <is>
           <t>總鉻</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="0" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E30" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前尚未招標</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr">
+      <c r="F30" s="0" t="inlineStr"/>
+      <c r="G30" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="0" t="inlineStr">
         <is>
           <t>電鍍/表面/基本 或 PCB</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="0" t="inlineStr">
         <is>
           <t>六價鉻</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="0" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前完成</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr">
+      <c r="F31" s="0" t="inlineStr"/>
+      <c r="G31" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="0" t="inlineStr">
         <is>
           <t>電鍍/表面/基本 (&gt;150CMD) 或 PCB (&gt;500CMD)</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="0" t="inlineStr">
         <is>
           <t>六價鉻</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="0" t="inlineStr">
         <is>
           <t>0.35</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前完成</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr">
+      <c r="F32" s="0" t="inlineStr"/>
+      <c r="G32" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="0" t="inlineStr">
         <is>
           <t>全</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="0" t="inlineStr">
         <is>
           <t>六價鉻</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="0" t="inlineStr">
         <is>
           <t>0.35</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前尚未招標</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr">
+      <c r="F33" s="0" t="inlineStr"/>
+      <c r="G33" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="0" t="inlineStr">
         <is>
           <t>電鍍/表面/基本 (≤150CMD) 或 PCB (≤500CMD)</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="0" t="inlineStr">
         <is>
           <t>銅</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="0" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前完成</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr">
+      <c r="F34" s="0" t="inlineStr"/>
+      <c r="G34" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="0" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="0" t="inlineStr">
         <is>
           <t>銅</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="0" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" s="0" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" s="0" t="inlineStr">
         <is>
           <t>116/1/1 施行</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G35" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="0" t="inlineStr">
         <is>
           <t>電鍍/表面/基本 (≤150CMD) 或 PCB (≤500CMD)</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="0" t="inlineStr">
         <is>
           <t>銅</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="0" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E36" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前尚未招標</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr">
+      <c r="F36" s="0" t="inlineStr"/>
+      <c r="G36" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="0" t="inlineStr">
         <is>
           <t>電鍍/表面/基本 (&gt;150CMD) 或 PCB (&gt;500CMD)</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="0" t="inlineStr">
         <is>
           <t>銅</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="0" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E37" s="0" t="inlineStr">
         <is>
           <t>113/12/18 前完成</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
+      <c r="F37" s="0" t="inlineStr"/>
+      <c r="G37" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="0" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="0" t="inlineStr">
         <is>
           <t>銅</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="0" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E38" s="0" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" s="0" t="inlineStr">
         <is>
           <t>116/1/1 施行</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="G38" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="0" t="inlineStr">
         <is>
           <t>電鍍/表面/基本 (&gt;150CMD) 或 PCB (&gt;500CMD)</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="0" t="inlineStr">
         <is>
           <t>銅</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="0" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E39" s="0" t="inlineStr">
         <is>
           <t>113/12/18 前尚未招標</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr">
+      <c r="F39" s="0" t="inlineStr"/>
+      <c r="G39" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="0" t="inlineStr">
         <is>
           <t>全</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="0" t="inlineStr">
         <is>
           <t>鋅</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="0" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D40" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E40" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前完成</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr">
+      <c r="F40" s="0" t="inlineStr"/>
+      <c r="G40" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="0" t="inlineStr">
         <is>
           <t>電鍍/表面/基本 (&gt;150CMD) 或 PCB (&gt;500CMD)</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="0" t="inlineStr">
         <is>
           <t>鋅</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="0" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E41" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前完成</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr">
+      <c r="F41" s="0" t="inlineStr"/>
+      <c r="G41" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="0" t="inlineStr">
         <is>
           <t>全</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="0" t="inlineStr">
         <is>
           <t>鋅</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="0" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D42" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E42" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前尚未招標</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr">
+      <c r="F42" s="0" t="inlineStr"/>
+      <c r="G42" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="0" t="inlineStr">
         <is>
           <t>全</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="0" t="inlineStr">
         <is>
           <t>鎳</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="0" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E43" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前完成</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr">
+      <c r="F43" s="0" t="inlineStr"/>
+      <c r="G43" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="0" t="inlineStr">
         <is>
           <t>電鍍/表面/基本 (&gt;150CMD) 或 PCB (&gt;500CMD)</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="0" t="inlineStr">
         <is>
           <t>鎳</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="0" t="inlineStr">
         <is>
           <t>0.7</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D44" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E44" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前完成</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr">
+      <c r="F44" s="0" t="inlineStr"/>
+      <c r="G44" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="0" t="inlineStr">
         <is>
           <t>全</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="0" t="inlineStr">
         <is>
           <t>鎳</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="0" t="inlineStr">
         <is>
           <t>0.7</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E45" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前尚未招標</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr">
+      <c r="F45" s="0" t="inlineStr"/>
+      <c r="G45" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="0" t="inlineStr">
         <is>
           <t>全</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="0" t="inlineStr">
         <is>
           <t>硒</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="0" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E46" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前完成</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr">
+      <c r="F46" s="0" t="inlineStr"/>
+      <c r="G46" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="0" t="inlineStr">
         <is>
           <t>電鍍/表面/基本 (&gt;150CMD) 或 PCB (&gt;500CMD)</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="0" t="inlineStr">
         <is>
           <t>硒</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="0" t="inlineStr">
         <is>
           <t>0.35</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E47" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前完成</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr">
+      <c r="F47" s="0" t="inlineStr"/>
+      <c r="G47" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="0" t="inlineStr">
         <is>
           <t>全</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="0" t="inlineStr">
         <is>
           <t>硒</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="0" t="inlineStr">
         <is>
           <t>0.35</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D48" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E48" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前尚未招標</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr">
+      <c r="F48" s="0" t="inlineStr"/>
+      <c r="G48" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="0" t="inlineStr">
         <is>
           <t>全</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="0" t="inlineStr">
         <is>
           <t>砷</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="0" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E49" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前完成</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr">
+      <c r="F49" s="0" t="inlineStr"/>
+      <c r="G49" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="0" t="inlineStr">
         <is>
           <t>電鍍/表面/基本 (&gt;150CMD) 或 PCB (&gt;500CMD)</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="0" t="inlineStr">
         <is>
           <t>砷</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="0" t="inlineStr">
         <is>
           <t>0.35</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D50" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E50" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前完成</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr">
+      <c r="F50" s="0" t="inlineStr"/>
+      <c r="G50" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="0" t="inlineStr">
         <is>
           <t>全</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="0" t="inlineStr">
         <is>
           <t>砷</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="0" t="inlineStr">
         <is>
           <t>0.35</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E51" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前尚未招標</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr">
+      <c r="F51" s="0" t="inlineStr"/>
+      <c r="G51" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="0" t="inlineStr">
         <is>
           <t>電鍍/表面/基本 (&gt;150CMD) 或 PCB (&gt;500CMD)</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="0" t="inlineStr">
         <is>
           <t>錫</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="0" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D52" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E52" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前完成</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr">
+      <c r="F52" s="0" t="inlineStr"/>
+      <c r="G52" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="0" t="inlineStr">
         <is>
           <t>全</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="0" t="inlineStr">
         <is>
           <t>錫</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="0" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D53" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E53" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前尚未招標</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr">
+      <c r="F53" s="0" t="inlineStr"/>
+      <c r="G53" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="0" t="inlineStr">
         <is>
           <t>全</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="0" t="inlineStr">
         <is>
           <t>總汞</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="0" t="inlineStr">
         <is>
           <t>0.005</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D54" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr">
+      <c r="E54" s="0" t="inlineStr"/>
+      <c r="F54" s="0" t="inlineStr"/>
+      <c r="G54" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="0" t="inlineStr">
         <is>
           <t>全</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="0" t="inlineStr">
         <is>
           <t>銀</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="0" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D55" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr">
+      <c r="E55" s="0" t="inlineStr"/>
+      <c r="F55" s="0" t="inlineStr"/>
+      <c r="G55" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="0" t="inlineStr">
         <is>
           <t>金屬基本/PCB</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="0" t="inlineStr">
         <is>
           <t>硼</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="0" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D56" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E56" s="0" t="inlineStr">
         <is>
           <t>排放於自來水水質水量保護區內</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr">
+      <c r="F56" s="0" t="inlineStr"/>
+      <c r="G56" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="0" t="inlineStr">
         <is>
           <t>金屬基本/PCB</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="0" t="inlineStr">
         <is>
           <t>硼</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="0" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D57" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E57" s="0" t="inlineStr">
         <is>
           <t>排放於自來水水質水量保護區外</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr">
+      <c r="F57" s="0" t="inlineStr"/>
+      <c r="G57" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="0" t="inlineStr">
         <is>
           <t>金屬表面處理/電鍍</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="0" t="inlineStr">
         <is>
           <t>硼</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="0" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D58" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E58" s="0" t="inlineStr">
         <is>
           <t>排放於自來水水質水量保護區內</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr">
+      <c r="F58" s="0" t="inlineStr"/>
+      <c r="G58" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="0" t="inlineStr">
         <is>
           <t>金屬表面處理/電鍍</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="0" t="inlineStr">
         <is>
           <t>硼</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="0" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D59" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="E59" s="0" t="inlineStr">
         <is>
           <t>排放於自來水水質水量保護區外</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr">
+      <c r="F59" s="0" t="inlineStr"/>
+      <c r="G59" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="0" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="0" t="inlineStr">
         <is>
           <t>硼</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="0" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D60" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E60" s="0" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F60" s="0" t="inlineStr">
         <is>
           <t>116/1/1 施行</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="G60" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="0" t="inlineStr">
         <is>
           <t>全</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="0" t="inlineStr">
         <is>
           <t>鉬</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="0" t="inlineStr">
         <is>
           <t>0.6</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D61" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr">
+      <c r="E61" s="0" t="inlineStr"/>
+      <c r="F61" s="0" t="inlineStr"/>
+      <c r="G61" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="0" t="inlineStr">
         <is>
           <t>全</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="0" t="inlineStr">
         <is>
           <t>硫化物</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C62" s="0" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D62" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr">
+      <c r="E62" s="0" t="inlineStr"/>
+      <c r="F62" s="0" t="inlineStr"/>
+      <c r="G62" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="0" t="inlineStr">
         <is>
           <t>金屬基本/表面處理/電鍍</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="0" t="inlineStr">
         <is>
           <t>化學需氧量</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="0" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D63" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr">
+      <c r="E63" s="0" t="inlineStr"/>
+      <c r="F63" s="0" t="inlineStr"/>
+      <c r="G63" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="0" t="inlineStr">
         <is>
           <t>PCB</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="0" t="inlineStr">
         <is>
           <t>化學需氧量</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="0" t="inlineStr">
         <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D64" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr">
+      <c r="E64" s="0" t="inlineStr"/>
+      <c r="F64" s="0" t="inlineStr"/>
+      <c r="G64" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="0" t="inlineStr">
         <is>
           <t>金屬基本/表面處理/電鍍</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="0" t="inlineStr">
         <is>
           <t>懸浮固體</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="0" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D65" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr">
+      <c r="E65" s="0" t="inlineStr"/>
+      <c r="F65" s="0" t="inlineStr"/>
+      <c r="G65" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="0" t="inlineStr">
         <is>
           <t>PCB</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="0" t="inlineStr">
         <is>
           <t>懸浮固體</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="0" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D66" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr">
+      <c r="E66" s="0" t="inlineStr"/>
+      <c r="F66" s="0" t="inlineStr"/>
+      <c r="G66" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="0" t="inlineStr">
         <is>
           <t>PCB</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="0" t="inlineStr">
         <is>
           <t>生化需氧量</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="0" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D67" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr">
+      <c r="E67" s="0" t="inlineStr"/>
+      <c r="F67" s="0" t="inlineStr"/>
+      <c r="G67" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表五 (113/12/18 修正)</t>
         </is>
@@ -43262,1369 +43802,1369 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="0" t="inlineStr">
         <is>
           <t>業別</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="0" t="inlineStr">
         <is>
           <t>水質項目</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="0" t="inlineStr">
         <is>
           <t>限值</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="0" t="inlineStr">
         <is>
           <t>單位</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="0" t="inlineStr">
         <is>
           <t>適用條件</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="0" t="inlineStr">
         <is>
           <t>施行日期</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="0" t="inlineStr">
         <is>
           <t>備註/來源</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
         <is>
           <t>第一級-新設</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="0" t="inlineStr">
         <is>
           <t>鎘</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="0" t="inlineStr">
         <is>
           <t>&lt;0.005</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="0" t="inlineStr">
         <is>
           <t>第一級, 新設事業或工業區, 公告前尚未招標</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="0" t="inlineStr">
         <is>
           <t>公告日起</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G2" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
         <is>
           <t>第一級-新設</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="0" t="inlineStr">
         <is>
           <t>總鉻</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="0" t="inlineStr">
         <is>
           <t>&lt;0.01</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="0" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="0" t="inlineStr">
         <is>
           <t>公告日起</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
         <is>
           <t>第一級-新設</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>六價鉻</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="0" t="inlineStr">
         <is>
           <t>&lt;0.02</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="0" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="0" t="inlineStr">
         <is>
           <t>公告日起</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="0" t="inlineStr">
         <is>
           <t>第一級-新設</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>銅</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>&lt;0.01</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="0" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="0" t="inlineStr">
         <is>
           <t>公告日起</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="0" t="inlineStr">
         <is>
           <t>第一級-新設</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="0" t="inlineStr">
         <is>
           <t>鋅</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="0" t="inlineStr">
         <is>
           <t>&lt;0.01</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="0" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="0" t="inlineStr">
         <is>
           <t>公告日起</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="0" t="inlineStr">
         <is>
           <t>第一級-新設</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="0" t="inlineStr">
         <is>
           <t>鎳</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="0" t="inlineStr">
         <is>
           <t>&lt;0.02</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="0" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="0" t="inlineStr">
         <is>
           <t>公告日起</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="0" t="inlineStr">
         <is>
           <t>第一級-既設事業</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="0" t="inlineStr">
         <is>
           <t>鎘</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="0" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="0" t="inlineStr">
         <is>
           <t>第一級, 既設事業, 公告前完成</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="0" t="inlineStr">
         <is>
           <t>公告後 2 年</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="0" t="inlineStr">
         <is>
           <t>第一級-既設事業</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="0" t="inlineStr">
         <is>
           <t>總鉻</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="0" t="inlineStr">
         <is>
           <t>0.1</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="0" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="0" t="inlineStr">
         <is>
           <t>公告後 2 年</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="G9" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="0" t="inlineStr">
         <is>
           <t>第一級-既設事業</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="0" t="inlineStr">
         <is>
           <t>六價鉻</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="0" t="inlineStr">
         <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="0" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="0" t="inlineStr">
         <is>
           <t>公告後 2 年</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G10" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="0" t="inlineStr">
         <is>
           <t>第一級-既設事業</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="0" t="inlineStr">
         <is>
           <t>銅</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="0" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="0" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="0" t="inlineStr">
         <is>
           <t>公告後 2 年</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="0" t="inlineStr">
         <is>
           <t>第一級-既設事業</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="0" t="inlineStr">
         <is>
           <t>鋅</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="0" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="0" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="0" t="inlineStr">
         <is>
           <t>公告後 2 年</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="0" t="inlineStr">
         <is>
           <t>第一級-既設事業</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="0" t="inlineStr">
         <is>
           <t>鎳</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="0" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E13" s="0" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="0" t="inlineStr">
         <is>
           <t>公告後 2 年</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="0" t="inlineStr">
         <is>
           <t>第一級-既設工業區</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="0" t="inlineStr">
         <is>
           <t>鎘</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="0" t="inlineStr">
         <is>
           <t>0.015</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E14" s="0" t="inlineStr">
         <is>
           <t>第一級, 既設工業區污水下水道</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="0" t="inlineStr">
         <is>
           <t>公告後 2 年</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="G14" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="0" t="inlineStr">
         <is>
           <t>第一級-既設工業區</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="0" t="inlineStr">
         <is>
           <t>總鉻</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="0" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E15" s="0" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="0" t="inlineStr">
         <is>
           <t>公告後 2 年</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="G15" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="0" t="inlineStr">
         <is>
           <t>第一級-既設工業區</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="0" t="inlineStr">
         <is>
           <t>六價鉻</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="0" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="0" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="0" t="inlineStr">
         <is>
           <t>公告後 2 年</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="G16" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="0" t="inlineStr">
         <is>
           <t>第一級-既設工業區</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="0" t="inlineStr">
         <is>
           <t>銅</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="0" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E17" s="0" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="0" t="inlineStr">
         <is>
           <t>公告後 2 年</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="G17" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="0" t="inlineStr">
         <is>
           <t>第一級-既設工業區</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="0" t="inlineStr">
         <is>
           <t>鋅</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="0" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E18" s="0" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="0" t="inlineStr">
         <is>
           <t>公告後 2 年</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="G18" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="0" t="inlineStr">
         <is>
           <t>第一級-既設工業區</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="0" t="inlineStr">
         <is>
           <t>鎳</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="0" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="0" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="0" t="inlineStr">
         <is>
           <t>公告後 2 年</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="G19" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="0" t="inlineStr">
         <is>
           <t>第二級-新設事業</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="0" t="inlineStr">
         <is>
           <t>鎘</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="0" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="0" t="inlineStr">
         <is>
           <t>第二級, 新設事業</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="0" t="inlineStr">
         <is>
           <t>公告日起</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="G20" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="0" t="inlineStr">
         <is>
           <t>第二級-新設事業</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="0" t="inlineStr">
         <is>
           <t>總鉻</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="0" t="inlineStr">
         <is>
           <t>0.1</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="0" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="0" t="inlineStr">
         <is>
           <t>公告日起</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G21" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="0" t="inlineStr">
         <is>
           <t>第二級-新設事業</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="0" t="inlineStr">
         <is>
           <t>六價鉻</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="0" t="inlineStr">
         <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="0" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="0" t="inlineStr">
         <is>
           <t>公告日起</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="G22" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="0" t="inlineStr">
         <is>
           <t>第二級-新設事業</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="0" t="inlineStr">
         <is>
           <t>銅</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="0" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="0" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" s="0" t="inlineStr">
         <is>
           <t>公告日起</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="0" t="inlineStr">
         <is>
           <t>第二級-新設事業</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="0" t="inlineStr">
         <is>
           <t>鋅</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="0" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="0" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="0" t="inlineStr">
         <is>
           <t>公告日起</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="G24" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="0" t="inlineStr">
         <is>
           <t>第二級-新設事業</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="0" t="inlineStr">
         <is>
           <t>鎳</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="0" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" s="0" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" s="0" t="inlineStr">
         <is>
           <t>公告日起</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G25" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="0" t="inlineStr">
         <is>
           <t>第二級-新設工業區</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="0" t="inlineStr">
         <is>
           <t>鎘</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="0" t="inlineStr">
         <is>
           <t>0.015</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" s="0" t="inlineStr">
         <is>
           <t>第二級, 新設工業區污水下水道</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" s="0" t="inlineStr">
         <is>
           <t>公告日起</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="G26" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="0" t="inlineStr">
         <is>
           <t>第二級-新設工業區</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="0" t="inlineStr">
         <is>
           <t>總鉻</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="0" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" s="0" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" s="0" t="inlineStr">
         <is>
           <t>公告日起</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="G27" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="0" t="inlineStr">
         <is>
           <t>第二級-新設工業區</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="0" t="inlineStr">
         <is>
           <t>六價鉻</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="0" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" s="0" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" s="0" t="inlineStr">
         <is>
           <t>公告日起</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G28" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="0" t="inlineStr">
         <is>
           <t>第二級-新設工業區</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="0" t="inlineStr">
         <is>
           <t>銅</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="0" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" s="0" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" s="0" t="inlineStr">
         <is>
           <t>公告日起</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="G29" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="0" t="inlineStr">
         <is>
           <t>第二級-新設工業區</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="0" t="inlineStr">
         <is>
           <t>鋅</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="0" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E30" s="0" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" s="0" t="inlineStr">
         <is>
           <t>公告日起</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G30" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="0" t="inlineStr">
         <is>
           <t>第二級-新設工業區</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="0" t="inlineStr">
         <is>
           <t>鎳</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="0" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" s="0" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F31" s="0" t="inlineStr">
         <is>
           <t>公告日起</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G31" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="0" t="inlineStr">
         <is>
           <t>第二級-既設</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="0" t="inlineStr">
         <is>
           <t>鎘</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="0" t="inlineStr">
         <is>
           <t>0.015</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" s="0" t="inlineStr">
         <is>
           <t>第二級, 既設事業及工業區</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" s="0" t="inlineStr">
         <is>
           <t>公告後 2 年</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G32" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="0" t="inlineStr">
         <is>
           <t>第二級-既設</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="0" t="inlineStr">
         <is>
           <t>總鉻</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="0" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" s="0" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" s="0" t="inlineStr">
         <is>
           <t>公告後 2 年</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G33" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="0" t="inlineStr">
         <is>
           <t>第二級-既設</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="0" t="inlineStr">
         <is>
           <t>六價鉻</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="0" t="inlineStr">
         <is>
           <t>0.25</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" s="0" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" s="0" t="inlineStr">
         <is>
           <t>公告後 2 年</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="G34" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="0" t="inlineStr">
         <is>
           <t>第二級-既設</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="0" t="inlineStr">
         <is>
           <t>銅</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="0" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" s="0" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" s="0" t="inlineStr">
         <is>
           <t>公告後 2 年</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G35" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="0" t="inlineStr">
         <is>
           <t>第二級-既設</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="0" t="inlineStr">
         <is>
           <t>鋅</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="0" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E36" s="0" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F36" s="0" t="inlineStr">
         <is>
           <t>公告後 2 年</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="G36" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="0" t="inlineStr">
         <is>
           <t>第二級-既設</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="0" t="inlineStr">
         <is>
           <t>鎳</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="0" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E37" s="0" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" s="0" t="inlineStr">
         <is>
           <t>公告後 2 年</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="G37" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表十六 保護農地水體加嚴 (113/12/18)</t>
         </is>
@@ -44645,2669 +45185,2669 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="0" t="inlineStr">
         <is>
           <t>業別</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="0" t="inlineStr">
         <is>
           <t>水質項目</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="0" t="inlineStr">
         <is>
           <t>限值</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="0" t="inlineStr">
         <is>
           <t>單位</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="0" t="inlineStr">
         <is>
           <t>適用條件</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="0" t="inlineStr">
         <is>
           <t>施行日期</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="0" t="inlineStr">
         <is>
           <t>備註/來源</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="0" t="inlineStr">
         <is>
           <t>化工業</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="0" t="inlineStr">
         <is>
           <t>水溫</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="0" t="inlineStr">
         <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="0" t="inlineStr">
         <is>
           <t>℃</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E2" s="0" t="inlineStr">
         <is>
           <t>5-9月, 非海洋</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
+      <c r="F2" s="0" t="inlineStr"/>
+      <c r="G2" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="0" t="inlineStr">
         <is>
           <t>化工業</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="0" t="inlineStr">
         <is>
           <t>水溫</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="0" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D3" s="0" t="inlineStr">
         <is>
           <t>℃</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E3" s="0" t="inlineStr">
         <is>
           <t>10-4月, 非海洋</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
+      <c r="F3" s="0" t="inlineStr"/>
+      <c r="G3" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="0" t="inlineStr">
         <is>
           <t>化工業</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>水溫</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="0" t="inlineStr">
         <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D4" s="0" t="inlineStr">
         <is>
           <t>℃</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="0" t="inlineStr">
         <is>
           <t>直接排放海洋</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
+      <c r="F4" s="0" t="inlineStr"/>
+      <c r="G4" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="0" t="inlineStr">
         <is>
           <t>化工業</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>pH</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>6.0~9.0</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D5" s="0" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
+      <c r="E5" s="0" t="inlineStr"/>
+      <c r="F5" s="0" t="inlineStr"/>
+      <c r="G5" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="0" t="inlineStr">
         <is>
           <t>化工業</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="0" t="inlineStr">
         <is>
           <t>氟鹽</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="0" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D6" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
+      <c r="E6" s="0" t="inlineStr"/>
+      <c r="F6" s="0" t="inlineStr"/>
+      <c r="G6" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="0" t="inlineStr">
         <is>
           <t>化工業</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="0" t="inlineStr">
         <is>
           <t>硝酸鹽氮</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="0" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D7" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
+      <c r="E7" s="0" t="inlineStr"/>
+      <c r="F7" s="0" t="inlineStr"/>
+      <c r="G7" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="0" t="inlineStr">
         <is>
           <t>化工業</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="0" t="inlineStr">
         <is>
           <t>氨氮</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="0" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D8" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="0" t="inlineStr">
         <is>
           <t>排放於自來水水質水量保護區內</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
+      <c r="F8" s="0" t="inlineStr"/>
+      <c r="G8" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="0" t="inlineStr">
         <is>
           <t>化工業-非高含氮</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="0" t="inlineStr">
         <is>
           <t>氨氮</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="0" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D9" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E9" s="0" t="inlineStr">
         <is>
           <t>保護區外, 103/1/22 前完成</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
+      <c r="F9" s="0" t="inlineStr"/>
+      <c r="G9" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="0" t="inlineStr">
         <is>
           <t>化工業-高含氮</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="0" t="inlineStr">
         <is>
           <t>氨氮</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="0" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D10" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" s="0" t="inlineStr">
         <is>
           <t>保護區外, 103/1/22 前完成</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
+      <c r="F10" s="0" t="inlineStr"/>
+      <c r="G10" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="0" t="inlineStr">
         <is>
           <t>化工業</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="0" t="inlineStr">
         <is>
           <t>氨氮</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="0" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D11" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="0" t="inlineStr">
         <is>
           <t>保護區外, 103/1/22 前尚未招標</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
+      <c r="F11" s="0" t="inlineStr"/>
+      <c r="G11" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="0" t="inlineStr">
         <is>
           <t>化工業</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="0" t="inlineStr">
         <is>
           <t>正磷酸鹽</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="0" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D12" s="0" t="inlineStr">
         <is>
           <t>mg/L as PO4</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="0" t="inlineStr">
         <is>
           <t>排放於自來水水質水量保護區內</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
+      <c r="F12" s="0" t="inlineStr"/>
+      <c r="G12" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="0" t="inlineStr">
         <is>
           <t>化工業</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="0" t="inlineStr">
         <is>
           <t>酚類</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="0" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D13" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
+      <c r="E13" s="0" t="inlineStr"/>
+      <c r="F13" s="0" t="inlineStr"/>
+      <c r="G13" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="0" t="inlineStr">
         <is>
           <t>化工業</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="0" t="inlineStr">
         <is>
           <t>陰離子界面活性劑</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="0" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D14" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
+      <c r="E14" s="0" t="inlineStr"/>
+      <c r="F14" s="0" t="inlineStr"/>
+      <c r="G14" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="0" t="inlineStr">
         <is>
           <t>化工業</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="0" t="inlineStr">
         <is>
           <t>氰化物</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="0" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D15" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
+      <c r="E15" s="0" t="inlineStr"/>
+      <c r="F15" s="0" t="inlineStr"/>
+      <c r="G15" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="0" t="inlineStr">
         <is>
           <t>化工業</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="0" t="inlineStr">
         <is>
           <t>油脂</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="0" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E16" s="0" t="inlineStr">
         <is>
           <t>正己烷抽出物</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
+      <c r="F16" s="0" t="inlineStr"/>
+      <c r="G16" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="0" t="inlineStr">
         <is>
           <t>化工業</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="0" t="inlineStr">
         <is>
           <t>溶解性鐵</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="0" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D17" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
+      <c r="E17" s="0" t="inlineStr"/>
+      <c r="F17" s="0" t="inlineStr"/>
+      <c r="G17" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="0" t="inlineStr">
         <is>
           <t>化工業</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="0" t="inlineStr">
         <is>
           <t>溶解性錳</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="0" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D18" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
+      <c r="E18" s="0" t="inlineStr"/>
+      <c r="F18" s="0" t="inlineStr"/>
+      <c r="G18" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="0" t="inlineStr">
         <is>
           <t>化工業</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="0" t="inlineStr">
         <is>
           <t>鎘</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="0" t="inlineStr">
         <is>
           <t>0.03</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E19" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前完成</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
+      <c r="F19" s="0" t="inlineStr"/>
+      <c r="G19" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="0" t="inlineStr">
         <is>
           <t>化工業-大於500CMD</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="0" t="inlineStr">
         <is>
           <t>鎘</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="0" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D20" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E20" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前完成</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
+      <c r="F20" s="0" t="inlineStr"/>
+      <c r="G20" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="0" t="inlineStr">
         <is>
           <t>化工業</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="0" t="inlineStr">
         <is>
           <t>鎘</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="0" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D21" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E21" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前尚未招標</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
+      <c r="F21" s="0" t="inlineStr"/>
+      <c r="G21" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="0" t="inlineStr">
         <is>
           <t>化工業</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="0" t="inlineStr">
         <is>
           <t>鉛</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="0" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E22" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前完成</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr">
+      <c r="F22" s="0" t="inlineStr"/>
+      <c r="G22" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="0" t="inlineStr">
         <is>
           <t>化工業-大於500CMD</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="0" t="inlineStr">
         <is>
           <t>鉛</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="0" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
+      <c r="D23" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E23" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前完成</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr">
+      <c r="F23" s="0" t="inlineStr"/>
+      <c r="G23" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="0" t="inlineStr">
         <is>
           <t>化工業</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="0" t="inlineStr">
         <is>
           <t>鉛</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="0" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
+      <c r="D24" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E24" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前尚未招標</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr">
+      <c r="F24" s="0" t="inlineStr"/>
+      <c r="G24" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="0" t="inlineStr">
         <is>
           <t>化工業</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="0" t="inlineStr">
         <is>
           <t>總鉻</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="0" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
+      <c r="D25" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E25" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前完成</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr">
+      <c r="F25" s="0" t="inlineStr"/>
+      <c r="G25" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="0" t="inlineStr">
         <is>
           <t>化工業-大於500CMD</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="0" t="inlineStr">
         <is>
           <t>總鉻</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="0" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D26" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E26" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前完成</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr">
+      <c r="F26" s="0" t="inlineStr"/>
+      <c r="G26" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="0" t="inlineStr">
         <is>
           <t>化工業</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="0" t="inlineStr">
         <is>
           <t>總鉻</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="0" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E27" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前尚未招標</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr">
+      <c r="F27" s="0" t="inlineStr"/>
+      <c r="G27" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="0" t="inlineStr">
         <is>
           <t>化工業</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="0" t="inlineStr">
         <is>
           <t>六價鉻</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="0" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D28" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E28" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前完成</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr">
+      <c r="F28" s="0" t="inlineStr"/>
+      <c r="G28" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="0" t="inlineStr">
         <is>
           <t>化工業-大於500CMD</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="0" t="inlineStr">
         <is>
           <t>六價鉻</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="0" t="inlineStr">
         <is>
           <t>0.35</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D29" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E29" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前完成</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr">
+      <c r="F29" s="0" t="inlineStr"/>
+      <c r="G29" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="0" t="inlineStr">
         <is>
           <t>化工業</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="0" t="inlineStr">
         <is>
           <t>六價鉻</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="0" t="inlineStr">
         <is>
           <t>0.35</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D30" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E30" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前尚未招標</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr">
+      <c r="F30" s="0" t="inlineStr"/>
+      <c r="G30" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="0" t="inlineStr">
         <is>
           <t>化工業-≤500CMD</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="0" t="inlineStr">
         <is>
           <t>銅</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="0" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D31" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E31" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前完成</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr">
+      <c r="F31" s="0" t="inlineStr"/>
+      <c r="G31" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="0" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="0" t="inlineStr">
         <is>
           <t>銅</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="0" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
+      <c r="D32" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E32" s="0" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" s="0" t="inlineStr">
         <is>
           <t>116/1/1 施行</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="G32" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="0" t="inlineStr">
         <is>
           <t>化工業-≤500CMD</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="0" t="inlineStr">
         <is>
           <t>銅</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="0" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D33" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E33" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前尚未招標</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr">
+      <c r="F33" s="0" t="inlineStr"/>
+      <c r="G33" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="0" t="inlineStr">
         <is>
           <t>化工業-大於500CMD</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="0" t="inlineStr">
         <is>
           <t>銅</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="0" t="inlineStr">
         <is>
           <t>1.5</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
+      <c r="D34" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E34" s="0" t="inlineStr">
         <is>
           <t>113/12/18 前完成</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr">
+      <c r="F34" s="0" t="inlineStr"/>
+      <c r="G34" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="0" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="0" t="inlineStr">
         <is>
           <t>銅</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="0" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
+      <c r="D35" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E35" s="0" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" s="0" t="inlineStr">
         <is>
           <t>116/1/1 施行</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="G35" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="0" t="inlineStr">
         <is>
           <t>化工業-大於500CMD</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="0" t="inlineStr">
         <is>
           <t>銅</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="0" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
+      <c r="D36" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E36" s="0" t="inlineStr">
         <is>
           <t>113/12/18 前尚未招標</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr">
+      <c r="F36" s="0" t="inlineStr"/>
+      <c r="G36" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="0" t="inlineStr">
         <is>
           <t>化工業</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="0" t="inlineStr">
         <is>
           <t>鋅</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="0" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D37" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E37" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前完成</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
+      <c r="F37" s="0" t="inlineStr"/>
+      <c r="G37" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="0" t="inlineStr">
         <is>
           <t>化工業-大於500CMD</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="0" t="inlineStr">
         <is>
           <t>鋅</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="0" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
+      <c r="D38" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E38" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前完成</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr">
+      <c r="F38" s="0" t="inlineStr"/>
+      <c r="G38" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="0" t="inlineStr">
         <is>
           <t>化工業</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="0" t="inlineStr">
         <is>
           <t>鋅</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="0" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
+      <c r="D39" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E39" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前尚未招標</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr">
+      <c r="F39" s="0" t="inlineStr"/>
+      <c r="G39" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="0" t="inlineStr">
         <is>
           <t>化工業</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="0" t="inlineStr">
         <is>
           <t>鎳</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="0" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D40" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E40" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前完成</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr">
+      <c r="F40" s="0" t="inlineStr"/>
+      <c r="G40" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="0" t="inlineStr">
         <is>
           <t>化工業-大於500CMD</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="0" t="inlineStr">
         <is>
           <t>鎳</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="0" t="inlineStr">
         <is>
           <t>0.7</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
+      <c r="D41" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E41" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前完成</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr">
+      <c r="F41" s="0" t="inlineStr"/>
+      <c r="G41" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="0" t="inlineStr">
         <is>
           <t>化工業</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="0" t="inlineStr">
         <is>
           <t>鎳</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="0" t="inlineStr">
         <is>
           <t>0.7</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D42" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E42" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前尚未招標</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr">
+      <c r="F42" s="0" t="inlineStr"/>
+      <c r="G42" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="0" t="inlineStr">
         <is>
           <t>化工業</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="0" t="inlineStr">
         <is>
           <t>硒</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="0" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D43" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E43" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前完成</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr">
+      <c r="F43" s="0" t="inlineStr"/>
+      <c r="G43" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="0" t="inlineStr">
         <is>
           <t>化工業-大於500CMD</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="0" t="inlineStr">
         <is>
           <t>硒</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="0" t="inlineStr">
         <is>
           <t>0.35</t>
         </is>
       </c>
-      <c r="D44" t="inlineStr">
+      <c r="D44" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="E44" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前完成</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr">
+      <c r="F44" s="0" t="inlineStr"/>
+      <c r="G44" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="0" t="inlineStr">
         <is>
           <t>化工業</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="0" t="inlineStr">
         <is>
           <t>硒</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="0" t="inlineStr">
         <is>
           <t>0.35</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D45" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E45" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前尚未招標</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr">
+      <c r="F45" s="0" t="inlineStr"/>
+      <c r="G45" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="0" t="inlineStr">
         <is>
           <t>化工業</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="0" t="inlineStr">
         <is>
           <t>砷</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="0" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
+      <c r="D46" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E46" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前完成</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr">
+      <c r="F46" s="0" t="inlineStr"/>
+      <c r="G46" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="0" t="inlineStr">
         <is>
           <t>化工業-大於500CMD</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="0" t="inlineStr">
         <is>
           <t>砷</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="0" t="inlineStr">
         <is>
           <t>0.35</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
+      <c r="D47" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E47" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前完成</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr">
+      <c r="F47" s="0" t="inlineStr"/>
+      <c r="G47" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="0" t="inlineStr">
         <is>
           <t>化工業</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="0" t="inlineStr">
         <is>
           <t>砷</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="0" t="inlineStr">
         <is>
           <t>0.35</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D48" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E48" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前尚未招標</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr">
+      <c r="F48" s="0" t="inlineStr"/>
+      <c r="G48" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
+      <c r="A49" s="0" t="inlineStr">
         <is>
           <t>化工業-大於500CMD</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="0" t="inlineStr">
         <is>
           <t>錫</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C49" s="0" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D49" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E49" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前完成</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr">
+      <c r="F49" s="0" t="inlineStr"/>
+      <c r="G49" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
+      <c r="A50" s="0" t="inlineStr">
         <is>
           <t>化工業</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="0" t="inlineStr">
         <is>
           <t>錫</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C50" s="0" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D50" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E50" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前尚未招標</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr">
+      <c r="F50" s="0" t="inlineStr"/>
+      <c r="G50" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
+      <c r="A51" s="0" t="inlineStr">
         <is>
           <t>化工業</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="0" t="inlineStr">
         <is>
           <t>甲基汞</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C51" s="0" t="inlineStr">
         <is>
           <t>0.0000002</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D51" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr">
+      <c r="E51" s="0" t="inlineStr"/>
+      <c r="F51" s="0" t="inlineStr"/>
+      <c r="G51" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
+      <c r="A52" s="0" t="inlineStr">
         <is>
           <t>化工業</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="0" t="inlineStr">
         <is>
           <t>總汞</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C52" s="0" t="inlineStr">
         <is>
           <t>0.005</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D52" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr">
+      <c r="E52" s="0" t="inlineStr"/>
+      <c r="F52" s="0" t="inlineStr"/>
+      <c r="G52" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
+      <c r="A53" s="0" t="inlineStr">
         <is>
           <t>化工業</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="0" t="inlineStr">
         <is>
           <t>銀</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C53" s="0" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D53" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr">
+      <c r="E53" s="0" t="inlineStr"/>
+      <c r="F53" s="0" t="inlineStr"/>
+      <c r="G53" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
+      <c r="A54" s="0" t="inlineStr">
         <is>
           <t>化工業</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
+      <c r="B54" s="0" t="inlineStr">
         <is>
           <t>硼</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C54" s="0" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D54" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E54" s="0" t="inlineStr">
         <is>
           <t>排放於自來水水質水量保護區內</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr">
+      <c r="F54" s="0" t="inlineStr"/>
+      <c r="G54" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
+      <c r="A55" s="0" t="inlineStr">
         <is>
           <t>化工業</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
+      <c r="B55" s="0" t="inlineStr">
         <is>
           <t>硼</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C55" s="0" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D55" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E55" s="0" t="inlineStr">
         <is>
           <t>排放於自來水水質水量保護區外</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr">
+      <c r="F55" s="0" t="inlineStr"/>
+      <c r="G55" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
+      <c r="A56" s="0" t="inlineStr">
         <is>
           <t>化工業</t>
         </is>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="0" t="inlineStr">
         <is>
           <t>鉬</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
+      <c r="C56" s="0" t="inlineStr">
         <is>
           <t>0.6</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
+      <c r="D56" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr">
+      <c r="E56" s="0" t="inlineStr"/>
+      <c r="F56" s="0" t="inlineStr"/>
+      <c r="G56" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
+      <c r="A57" s="0" t="inlineStr">
         <is>
           <t>化工業</t>
         </is>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="0" t="inlineStr">
         <is>
           <t>硫化物</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
+      <c r="C57" s="0" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
+      <c r="D57" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr">
+      <c r="E57" s="0" t="inlineStr"/>
+      <c r="F57" s="0" t="inlineStr"/>
+      <c r="G57" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
+      <c r="A58" s="0" t="inlineStr">
         <is>
           <t>化工業</t>
         </is>
       </c>
-      <c r="B58" t="inlineStr">
+      <c r="B58" s="0" t="inlineStr">
         <is>
           <t>甲醛</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr">
+      <c r="C58" s="0" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr">
+      <c r="D58" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr">
+      <c r="E58" s="0" t="inlineStr"/>
+      <c r="F58" s="0" t="inlineStr"/>
+      <c r="G58" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
+      <c r="A59" s="0" t="inlineStr">
         <is>
           <t>化工業</t>
         </is>
       </c>
-      <c r="B59" t="inlineStr">
+      <c r="B59" s="0" t="inlineStr">
         <is>
           <t>多氯聯苯</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C59" s="0" t="inlineStr">
         <is>
           <t>0.00005</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
+      <c r="D59" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr">
+      <c r="E59" s="0" t="inlineStr"/>
+      <c r="F59" s="0" t="inlineStr"/>
+      <c r="G59" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
+      <c r="A60" s="0" t="inlineStr">
         <is>
           <t>化工業-氯乙烯製造</t>
         </is>
       </c>
-      <c r="B60" t="inlineStr">
+      <c r="B60" s="0" t="inlineStr">
         <is>
           <t>戴奧辛</t>
         </is>
       </c>
-      <c r="C60" t="inlineStr">
+      <c r="C60" s="0" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
+      <c r="D60" s="0" t="inlineStr">
         <is>
           <t>pg-TEQ/L</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E60" s="0" t="inlineStr">
         <is>
           <t>101/10/12 前完成</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr">
+      <c r="F60" s="0" t="inlineStr"/>
+      <c r="G60" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
+      <c r="A61" s="0" t="inlineStr">
         <is>
           <t>化工業-氯乙烯製造</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B61" s="0" t="inlineStr">
         <is>
           <t>戴奧辛</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C61" s="0" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D61" s="0" t="inlineStr">
         <is>
           <t>pg-TEQ/L</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E61" s="0" t="inlineStr">
         <is>
           <t>101/10/12 前尚未招標</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr">
+      <c r="F61" s="0" t="inlineStr"/>
+      <c r="G61" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
+      <c r="A62" s="0" t="inlineStr">
         <is>
           <t>化工業</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B62" s="0" t="inlineStr">
         <is>
           <t>生化需氧量</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C62" s="0" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D62" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr">
+      <c r="E62" s="0" t="inlineStr"/>
+      <c r="F62" s="0" t="inlineStr"/>
+      <c r="G62" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
+      <c r="A63" s="0" t="inlineStr">
         <is>
           <t>化工業</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="0" t="inlineStr">
         <is>
           <t>化學需氧量</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C63" s="0" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D63" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr">
+      <c r="E63" s="0" t="inlineStr"/>
+      <c r="F63" s="0" t="inlineStr"/>
+      <c r="G63" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
+      <c r="A64" s="0" t="inlineStr">
         <is>
           <t>化工業</t>
         </is>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="0" t="inlineStr">
         <is>
           <t>懸浮固體</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C64" s="0" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D64" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr">
+      <c r="E64" s="0" t="inlineStr"/>
+      <c r="F64" s="0" t="inlineStr"/>
+      <c r="G64" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="0" t="inlineStr">
         <is>
           <t>化工業</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="0" t="inlineStr">
         <is>
           <t>真色色度</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="0" t="inlineStr">
         <is>
           <t>400</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D65" s="0" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E65" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前完成</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr">
+      <c r="F65" s="0" t="inlineStr"/>
+      <c r="G65" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="0" t="inlineStr">
         <is>
           <t>化工業</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="0" t="inlineStr">
         <is>
           <t>真色色度</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="0" t="inlineStr">
         <is>
           <t>300</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D66" s="0" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E66" s="0" t="inlineStr">
         <is>
           <t>106/12/25 前尚未招標</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr">
+      <c r="F66" s="0" t="inlineStr"/>
+      <c r="G66" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="A67" s="0" t="inlineStr">
         <is>
           <t>化工業</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B67" s="0" t="inlineStr">
         <is>
           <t>自由有效餘氯</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C67" s="0" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D67" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr">
+      <c r="E67" s="0" t="inlineStr"/>
+      <c r="F67" s="0" t="inlineStr"/>
+      <c r="G67" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
+      <c r="A68" s="0" t="inlineStr">
         <is>
           <t>化工業-基本化學/其他化學材料/塗料染料顏料/其他化學製品/電池</t>
         </is>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="0" t="inlineStr">
         <is>
           <t>鈷</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
+      <c r="C68" s="0" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
+      <c r="D68" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr">
+      <c r="E68" s="0" t="inlineStr"/>
+      <c r="F68" s="0" t="inlineStr"/>
+      <c r="G68" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
+      <c r="A69" s="0" t="inlineStr">
         <is>
           <t>化工業-基本化學/人造纖維/合成樹脂塑膠橡膠/其他化學材料/塗料染料顏料/清潔用品/化妝品/其他化學製品/電池</t>
         </is>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="0" t="inlineStr">
         <is>
           <t>鋇</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
+      <c r="C69" s="0" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
+      <c r="D69" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr">
+      <c r="E69" s="0" t="inlineStr"/>
+      <c r="F69" s="0" t="inlineStr"/>
+      <c r="G69" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
+      <c r="A70" s="0" t="inlineStr">
         <is>
           <t>化工業</t>
         </is>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="0" t="inlineStr">
         <is>
           <t>二氯甲烷</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
+      <c r="C70" s="0" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
+      <c r="D70" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr">
+      <c r="E70" s="0" t="inlineStr"/>
+      <c r="F70" s="0" t="inlineStr"/>
+      <c r="G70" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="0" t="inlineStr">
         <is>
           <t>化工業</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B71" s="0" t="inlineStr">
         <is>
           <t>三氯甲烷</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C71" s="0" t="inlineStr">
         <is>
           <t>0.6</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D71" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr">
+      <c r="E71" s="0" t="inlineStr"/>
+      <c r="F71" s="0" t="inlineStr"/>
+      <c r="G71" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
+      <c r="A72" s="0" t="inlineStr">
         <is>
           <t>化工業-基本化學/合成樹脂塑膠橡膠/其他化學材料/塗料染料顏料/化妝品/其他化學製品</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="0" t="inlineStr">
         <is>
           <t>苯</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C72" s="0" t="inlineStr">
         <is>
           <t>0.05</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D72" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr">
+      <c r="E72" s="0" t="inlineStr"/>
+      <c r="F72" s="0" t="inlineStr"/>
+      <c r="G72" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
+      <c r="A73" s="0" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="0" t="inlineStr">
         <is>
           <t>乙苯</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C73" s="0" t="inlineStr">
         <is>
           <t>0.4</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
+      <c r="D73" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr">
+      <c r="E73" s="0" t="inlineStr"/>
+      <c r="F73" s="0" t="inlineStr"/>
+      <c r="G73" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A74" s="0" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="0" t="inlineStr">
         <is>
           <t>1,2-二氯乙烷</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
+      <c r="C74" s="0" t="inlineStr">
         <is>
           <t>0.10</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
+      <c r="D74" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr">
+      <c r="E74" s="0" t="inlineStr"/>
+      <c r="F74" s="0" t="inlineStr"/>
+      <c r="G74" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
+      <c r="A75" s="0" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="0" t="inlineStr">
         <is>
           <t>氯乙烯</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" s="0" t="inlineStr">
         <is>
           <t>0.10</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
+      <c r="D75" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr"/>
-      <c r="F75" t="inlineStr"/>
-      <c r="G75" t="inlineStr">
+      <c r="E75" s="0" t="inlineStr"/>
+      <c r="F75" s="0" t="inlineStr"/>
+      <c r="G75" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
+      <c r="A76" s="0" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B76" s="0" t="inlineStr">
         <is>
           <t>鄰苯二甲酸二甲酯DMP</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C76" s="0" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="D76" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr"/>
-      <c r="G76" t="inlineStr">
+      <c r="E76" s="0" t="inlineStr"/>
+      <c r="F76" s="0" t="inlineStr"/>
+      <c r="G76" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
+      <c r="A77" s="0" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B77" s="0" t="inlineStr">
         <is>
           <t>鄰苯二甲酸二乙酯DEP</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C77" s="0" t="inlineStr">
         <is>
           <t>0.4</t>
         </is>
       </c>
-      <c r="D77" t="inlineStr">
+      <c r="D77" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr"/>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="inlineStr">
+      <c r="E77" s="0" t="inlineStr"/>
+      <c r="F77" s="0" t="inlineStr"/>
+      <c r="G77" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="A78" s="0" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
-      <c r="B78" t="inlineStr">
+      <c r="B78" s="0" t="inlineStr">
         <is>
           <t>鄰苯二甲酸二丁酯DBP</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr">
+      <c r="C78" s="0" t="inlineStr">
         <is>
           <t>0.4</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr">
+      <c r="D78" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr"/>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr">
+      <c r="E78" s="0" t="inlineStr"/>
+      <c r="F78" s="0" t="inlineStr"/>
+      <c r="G78" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="A79" s="0" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B79" s="0" t="inlineStr">
         <is>
           <t>鄰苯二甲酸丁基苯甲酯BBP</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C79" s="0" t="inlineStr">
         <is>
           <t>0.4</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D79" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr">
+      <c r="E79" s="0" t="inlineStr"/>
+      <c r="F79" s="0" t="inlineStr"/>
+      <c r="G79" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
+      <c r="A80" s="0" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B80" s="0" t="inlineStr">
         <is>
           <t>鄰苯二甲酸二辛酯DNOP</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C80" s="0" t="inlineStr">
         <is>
           <t>0.6</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
+      <c r="D80" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr"/>
-      <c r="F80" t="inlineStr"/>
-      <c r="G80" t="inlineStr">
+      <c r="E80" s="0" t="inlineStr"/>
+      <c r="F80" s="0" t="inlineStr"/>
+      <c r="G80" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
+      <c r="A81" s="0" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B81" s="0" t="inlineStr">
         <is>
           <t>鄰苯二甲酸二(2-乙基己基)酯DEHP</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr">
+      <c r="C81" s="0" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
+      <c r="D81" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr">
+      <c r="E81" s="0" t="inlineStr"/>
+      <c r="F81" s="0" t="inlineStr"/>
+      <c r="G81" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
+      <c r="A82" s="0" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B82" s="0" t="inlineStr">
         <is>
           <t>硝基苯</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C82" s="0" t="inlineStr">
         <is>
           <t>0.4</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="D82" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr">
+      <c r="E82" s="0" t="inlineStr"/>
+      <c r="F82" s="0" t="inlineStr"/>
+      <c r="G82" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="A83" s="0" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B83" s="0" t="inlineStr">
         <is>
           <t>三氯乙烯</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C83" s="0" t="inlineStr">
         <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="D83" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
-      <c r="G83" t="inlineStr">
+      <c r="E83" s="0" t="inlineStr"/>
+      <c r="F83" s="0" t="inlineStr"/>
+      <c r="G83" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
+      <c r="A84" s="0" t="inlineStr">
         <is>
           <t>化工業-≥10000CMD (除肥料/石灰/煤製品外)</t>
         </is>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B84" s="0" t="inlineStr">
         <is>
           <t>丙烯腈</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C84" s="0" t="inlineStr">
         <is>
           <t>0.2</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
+      <c r="D84" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
-      <c r="G84" t="inlineStr">
+      <c r="E84" s="0" t="inlineStr"/>
+      <c r="F84" s="0" t="inlineStr"/>
+      <c r="G84" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
+      <c r="A85" s="0" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B85" s="0" t="inlineStr">
         <is>
           <t>1,3-丁二烯</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C85" s="0" t="inlineStr">
         <is>
           <t>0.1</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D85" s="0" t="inlineStr">
         <is>
           <t>mg/L</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr"/>
-      <c r="F85" t="inlineStr"/>
-      <c r="G85" t="inlineStr">
+      <c r="E85" s="0" t="inlineStr"/>
+      <c r="F85" s="0" t="inlineStr"/>
+      <c r="G85" s="0" t="inlineStr">
         <is>
           <t>環境部放流水標準 附表四 化工業 (113/12/18 修正)</t>
         </is>

--- a/規則庫.xlsx
+++ b/規則庫.xlsx
@@ -25614,17 +25614,17 @@
           <t>RPM 備註</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Y1" s="0" t="inlineStr">
         <is>
           <t>主要削減項目</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="Z1" s="0" t="inlineStr">
         <is>
           <t>削減率範圍(%)</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AA1" s="0" t="inlineStr">
         <is>
           <t>削減率學理依據</t>
         </is>
@@ -25705,7 +25705,7 @@
           <t>中低速混合加藥點</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AA2" s="0" t="inlineStr">
         <is>
           <t>純調 pH, 不去除任何項目</t>
         </is>
@@ -25786,7 +25786,7 @@
           <t>中低速混合加藥點</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA3" s="0" t="inlineStr">
         <is>
           <t>純調 pH, 不去除任何項目</t>
         </is>
@@ -25867,7 +25867,7 @@
           <t>中低速中和反應</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AA4" s="0" t="inlineStr">
         <is>
           <t>純中和, 不去除任何項目</t>
         </is>
@@ -25952,17 +25952,17 @@
           <t>兼具 pH 調整+快混</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Y5" s="0" t="inlineStr">
         <is>
           <t>SS</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="Z5" s="0" t="inlineStr">
         <is>
           <t>0~5 (加PAC反而略升)</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AA5" s="0" t="inlineStr">
         <is>
           <t>調pH + 快混, 加PAC後 SS 略升, 未沉澱不去除重金屬</t>
         </is>
@@ -26047,17 +26047,17 @@
           <t>兼具 pH 調整+快混</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="Y6" s="0" t="inlineStr">
         <is>
           <t>SS</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="Z6" s="0" t="inlineStr">
         <is>
           <t>0~5 (加PAC反而略升)</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AA6" s="0" t="inlineStr">
         <is>
           <t>同上</t>
         </is>
@@ -26142,17 +26142,17 @@
           <t>高速分散凝集劑</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
+      <c r="Y7" s="0" t="inlineStr">
         <is>
           <t>SS</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="Z7" s="0" t="inlineStr">
         <is>
           <t>0~5 (加PAC反而略升)</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AA7" s="0" t="inlineStr">
         <is>
           <t>D054 學理: 快混無沉澱功能, 不應表現重金屬去除</t>
         </is>
@@ -26237,17 +26237,17 @@
           <t>高速分散凝集劑</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="Y8" s="0" t="inlineStr">
         <is>
           <t>SS</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="Z8" s="0" t="inlineStr">
         <is>
           <t>0~5 (加PAC反而略升)</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AA8" s="0" t="inlineStr">
         <is>
           <t>同快混槽</t>
         </is>
@@ -26332,17 +26332,17 @@
           <t>低速不打散絮體</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
+      <c r="Y9" s="0" t="inlineStr">
         <is>
           <t>SS</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="Z9" s="0" t="inlineStr">
         <is>
           <t>0~5 (加PAM 顆粒變大但未沉澱)</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AA9" s="0" t="inlineStr">
         <is>
           <t>絮凝但未分離, 質量守恆</t>
         </is>
@@ -26427,17 +26427,17 @@
           <t>低速不打散絮體</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
+      <c r="Y10" s="0" t="inlineStr">
         <is>
           <t>SS</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="Z10" s="0" t="inlineStr">
         <is>
           <t>0~5</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AA10" s="0" t="inlineStr">
         <is>
           <t>同慢混池</t>
         </is>
@@ -26520,17 +26520,17 @@
           <t>0=不攪, 5~15=刮泥機</t>
         </is>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y11" s="0" t="inlineStr">
         <is>
           <t>SS;銅;鎳;鋅;鉛;總鉻;COD;BOD</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z11" s="0" t="inlineStr">
         <is>
           <t>80~95;60~90;50~90;70~95;60~90;60~90;20~50;20~40</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AA11" s="0" t="inlineStr">
         <is>
           <t>重力沉降 + 絮體氫氧化物沉澱, COD/BOD 隨 SS 略降</t>
         </is>
@@ -26613,17 +26613,17 @@
           <t>0=不攪, 5~15=刮泥機</t>
         </is>
       </c>
-      <c r="Y12" t="inlineStr">
+      <c r="Y12" s="0" t="inlineStr">
         <is>
           <t>SS;銅;鎳;鋅;鉛;總鉻;COD;BOD</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="Z12" s="0" t="inlineStr">
         <is>
           <t>80~95;60~90;50~90;70~95;60~90;60~90;20~50;20~40</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AA12" s="0" t="inlineStr">
         <is>
           <t>同沉澱池</t>
         </is>
@@ -26704,17 +26704,17 @@
           <t>靠氣泡, 一般不攪</t>
         </is>
       </c>
-      <c r="Y13" t="inlineStr">
+      <c r="Y13" s="0" t="inlineStr">
         <is>
           <t>油脂;SS;COD</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
+      <c r="Z13" s="0" t="inlineStr">
         <is>
           <t>80~98;60~90;20~50</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr">
+      <c r="AA13" s="0" t="inlineStr">
         <is>
           <t>加壓浮除, 油脂主力, SS 伴隨</t>
         </is>
@@ -26785,17 +26785,17 @@
           <t>無攪拌 (過濾)</t>
         </is>
       </c>
-      <c r="Y14" t="inlineStr">
+      <c r="Y14" s="0" t="inlineStr">
         <is>
           <t>SS;濁度</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
+      <c r="Z14" s="0" t="inlineStr">
         <is>
           <t>70~95;70~95</t>
         </is>
       </c>
-      <c r="AA14" t="inlineStr">
+      <c r="AA14" s="0" t="inlineStr">
         <is>
           <t>顆粒物理過濾, 溶解性物質不去除, 反洗水 SS↑↑</t>
         </is>
@@ -26866,17 +26866,17 @@
           <t>無攪拌 (吸附)</t>
         </is>
       </c>
-      <c r="Y15" t="inlineStr">
+      <c r="Y15" s="0" t="inlineStr">
         <is>
           <t>COD;BOD;色度;異味;游離氯</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
+      <c r="Z15" s="0" t="inlineStr">
         <is>
           <t>30~80;30~70;70~95;80~98;90~99</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AA15" s="0" t="inlineStr">
         <is>
           <t>吸附有機物/色度/餘氯, SS 不應去除 (會堵塞)</t>
         </is>
@@ -26947,17 +26947,17 @@
           <t>無攪拌 (吸附)</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Y16" s="0" t="inlineStr">
         <is>
           <t>COD;BOD;色度;異味;游離氯</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="Z16" s="0" t="inlineStr">
         <is>
           <t>30~80;30~70;70~95;80~98;90~99</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AA16" s="0" t="inlineStr">
         <is>
           <t>同活性碳吸附塔</t>
         </is>
@@ -27028,17 +27028,17 @@
           <t>無攪拌 (離子交換)</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Y17" s="0" t="inlineStr">
         <is>
           <t>銅;鎳;鋅;鉻;鎘;硬度離子</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="Z17" s="0" t="inlineStr">
         <is>
           <t>90~99;90~99;90~99;90~99;90~99;50~90</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AA17" s="0" t="inlineStr">
         <is>
           <t>離子交換, 對特定金屬去除極高</t>
         </is>
@@ -27129,17 +27129,17 @@
           <t>機械式; 鼓風式無此參數</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Y18" s="0" t="inlineStr">
         <is>
           <t>BOD;COD;氨氮</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="Z18" s="0" t="inlineStr">
         <is>
           <t>85~98;60~85;70~95</t>
         </is>
       </c>
-      <c r="AA18" t="inlineStr">
+      <c r="AA18" s="0" t="inlineStr">
         <is>
           <t>活性污泥好氧分解, 氨氮硝化, MLSS 微生物自增</t>
         </is>
@@ -27220,17 +27220,17 @@
           <t>中速讓氧化劑接觸</t>
         </is>
       </c>
-      <c r="Y19" t="inlineStr">
+      <c r="Y19" s="0" t="inlineStr">
         <is>
           <t>COD;BOD;真色色度</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
+      <c r="Z19" s="0" t="inlineStr">
         <is>
           <t>30~70;30~70;30~60</t>
         </is>
       </c>
-      <c r="AA19" t="inlineStr">
+      <c r="AA19" s="0" t="inlineStr">
         <is>
           <t>化學氧化分解有機物</t>
         </is>
@@ -27313,17 +27313,17 @@
           <t>保持微生物懸浮</t>
         </is>
       </c>
-      <c r="Y20" t="inlineStr">
+      <c r="Y20" s="0" t="inlineStr">
         <is>
           <t>BOD;COD</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
+      <c r="Z20" s="0" t="inlineStr">
         <is>
           <t>70~90;60~85</t>
         </is>
       </c>
-      <c r="AA20" t="inlineStr">
+      <c r="AA20" s="0" t="inlineStr">
         <is>
           <t>厭氧分解產沼氣, pH 可能酸化</t>
         </is>
@@ -27396,17 +27396,17 @@
           <t>視機型: 帶濾 5~30, 離心 1000~3000</t>
         </is>
       </c>
-      <c r="Y21" t="inlineStr">
+      <c r="Y21" s="0" t="inlineStr">
         <is>
           <t>含水率</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
+      <c r="Z21" s="0" t="inlineStr">
         <is>
           <t>8~15 (從 97% → 82~89%)</t>
         </is>
       </c>
-      <c r="AA21" t="inlineStr">
+      <c r="AA21" s="0" t="inlineStr">
         <is>
           <t>機械脫水</t>
         </is>
@@ -27487,17 +27487,17 @@
           <t>0=重力, 20=有刮泥</t>
         </is>
       </c>
-      <c r="Y22" t="inlineStr">
+      <c r="Y22" s="0" t="inlineStr">
         <is>
           <t>含水率</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
+      <c r="Z22" s="0" t="inlineStr">
         <is>
           <t>1~3 (從 97% → 94~96%)</t>
         </is>
       </c>
-      <c r="AA22" t="inlineStr">
+      <c r="AA22" s="0" t="inlineStr">
         <is>
           <t>重力濃縮</t>
         </is>
@@ -27574,7 +27574,7 @@
           <t>低速防結塊</t>
         </is>
       </c>
-      <c r="AA23" t="inlineStr">
+      <c r="AA23" s="0" t="inlineStr">
         <is>
           <t>儲存, 質量守恆; 略沉降可能微降含水率</t>
         </is>
@@ -27655,7 +27655,7 @@
           <t>通常不攪或低速</t>
         </is>
       </c>
-      <c r="AA24" t="inlineStr">
+      <c r="AA24" s="0" t="inlineStr">
         <is>
           <t>應守恆</t>
         </is>
@@ -27736,7 +27736,7 @@
           <t>同上</t>
         </is>
       </c>
-      <c r="AA25" t="inlineStr">
+      <c r="AA25" s="0" t="inlineStr">
         <is>
           <t>應守恆</t>
         </is>
@@ -27817,7 +27817,7 @@
           <t>均勻化 + 水質波動吸收</t>
         </is>
       </c>
-      <c r="AA26" t="inlineStr">
+      <c r="AA26" s="0" t="inlineStr">
         <is>
           <t>均勻化水質波動, 質量守恆</t>
         </is>
@@ -27898,7 +27898,7 @@
           <t>均勻化用</t>
         </is>
       </c>
-      <c r="AA27" t="inlineStr">
+      <c r="AA27" s="0" t="inlineStr">
         <is>
           <t>同調勻池</t>
         </is>
@@ -27977,7 +27977,7 @@
           <t>通常不攪</t>
         </is>
       </c>
-      <c r="AA28" t="inlineStr">
+      <c r="AA28" s="0" t="inlineStr">
         <is>
           <t>僅匯流</t>
         </is>
@@ -28054,7 +28054,7 @@
           <t>變頻: 反應期高沉降期停</t>
         </is>
       </c>
-      <c r="AA29" t="inlineStr">
+      <c r="AA29" s="0" t="inlineStr">
         <is>
           <t>視批次配方而定, 無固定去除率</t>
         </is>
@@ -28125,7 +28125,7 @@
           <t>無攪拌 (放流前緩衝)</t>
         </is>
       </c>
-      <c r="AA30" t="inlineStr">
+      <c r="AA30" s="0" t="inlineStr">
         <is>
           <t>放流前緩衝, 應守恆</t>
         </is>
@@ -28208,17 +28208,17 @@
           <t>低速循環水流</t>
         </is>
       </c>
-      <c r="Y31" t="inlineStr">
+      <c r="Y31" s="0" t="inlineStr">
         <is>
           <t>BOD;COD;氨氮</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
+      <c r="Z31" s="0" t="inlineStr">
         <is>
           <t>60~90;50~80;50~90</t>
         </is>
       </c>
-      <c r="AA31" t="inlineStr">
+      <c r="AA31" s="0" t="inlineStr">
         <is>
           <t>生物膜好氧分解</t>
         </is>
@@ -28309,17 +28309,17 @@
           <t>配合膜組件</t>
         </is>
       </c>
-      <c r="Y32" t="inlineStr">
+      <c r="Y32" s="0" t="inlineStr">
         <is>
           <t>BOD;COD;氨氮;SS</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
+      <c r="Z32" s="0" t="inlineStr">
         <is>
           <t>85~99;70~95;80~99;95~99</t>
         </is>
       </c>
-      <c r="AA32" t="inlineStr">
+      <c r="AA32" s="0" t="inlineStr">
         <is>
           <t>生物 + 膜過濾, SS 極低</t>
         </is>
@@ -28400,17 +28400,17 @@
           <t>同氧化池, 需 ORP 儀</t>
         </is>
       </c>
-      <c r="Y33" t="inlineStr">
+      <c r="Y33" s="0" t="inlineStr">
         <is>
           <t>氰化物;COD</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
+      <c r="Z33" s="0" t="inlineStr">
         <is>
           <t>90~99;20~50</t>
         </is>
       </c>
-      <c r="AA33" t="inlineStr">
+      <c r="AA33" s="0" t="inlineStr">
         <is>
           <t>NaClO 破氰: CN⁻ → CNO⁻ → N₂↑</t>
         </is>
@@ -28491,17 +28491,17 @@
           <t>同氧化池, 需 ORP 儀</t>
         </is>
       </c>
-      <c r="Y34" t="inlineStr">
+      <c r="Y34" s="0" t="inlineStr">
         <is>
           <t>六價鉻</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
+      <c r="Z34" s="0" t="inlineStr">
         <is>
           <t>95~99</t>
         </is>
       </c>
-      <c r="AA34" t="inlineStr">
+      <c r="AA34" s="0" t="inlineStr">
         <is>
           <t>NaHSO₃ 還原 Cr⁶⁺ → Cr³⁺ (總鉻不去除, 只變價)</t>
         </is>
@@ -28586,17 +28586,17 @@
           <t>多段: 進口高出口低</t>
         </is>
       </c>
-      <c r="Y35" t="inlineStr">
+      <c r="Y35" s="0" t="inlineStr">
         <is>
           <t>SS</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
+      <c r="Z35" s="0" t="inlineStr">
         <is>
           <t>0~5 (絮體形成但未沉澱)</t>
         </is>
       </c>
-      <c r="AA35" t="inlineStr">
+      <c r="AA35" s="0" t="inlineStr">
         <is>
           <t>只形成絮體, 未分離</t>
         </is>
@@ -28675,17 +28675,17 @@
           <t>離心式高速</t>
         </is>
       </c>
-      <c r="Y36" t="inlineStr">
+      <c r="Y36" s="0" t="inlineStr">
         <is>
           <t>含水率</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
+      <c r="Z36" s="0" t="inlineStr">
         <is>
           <t>12~22 (從 97% → 75~85%)</t>
         </is>
       </c>
-      <c r="AA36" t="inlineStr">
+      <c r="AA36" s="0" t="inlineStr">
         <is>
           <t>離心高速脫水</t>
         </is>
@@ -28764,17 +28764,17 @@
           <t>帶濾式低速</t>
         </is>
       </c>
-      <c r="Y37" t="inlineStr">
+      <c r="Y37" s="0" t="inlineStr">
         <is>
           <t>含水率</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
+      <c r="Z37" s="0" t="inlineStr">
         <is>
           <t>8~17 (從 97% → 80~89%)</t>
         </is>
       </c>
-      <c r="AA37" t="inlineStr">
+      <c r="AA37" s="0" t="inlineStr">
         <is>
           <t>帶濾中速脫水</t>
         </is>
@@ -28855,17 +28855,17 @@
           <t>同上</t>
         </is>
       </c>
-      <c r="Y38" t="inlineStr">
+      <c r="Y38" s="0" t="inlineStr">
         <is>
           <t>含水率</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
+      <c r="Z38" s="0" t="inlineStr">
         <is>
           <t>1~3 (從 97% → 94~96%)</t>
         </is>
       </c>
-      <c r="AA38" t="inlineStr">
+      <c r="AA38" s="0" t="inlineStr">
         <is>
           <t>同濃縮槽</t>
         </is>
@@ -28940,17 +28940,17 @@
           <t>無攪拌 (離子交換)</t>
         </is>
       </c>
-      <c r="Y39" t="inlineStr">
+      <c r="Y39" s="0" t="inlineStr">
         <is>
           <t>銅;鎳;鋅;鉻;鎘;硬度離子</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
+      <c r="Z39" s="0" t="inlineStr">
         <is>
           <t>90~99;90~99;90~99;90~99;90~99;50~90</t>
         </is>
       </c>
-      <c r="AA39" t="inlineStr">
+      <c r="AA39" s="0" t="inlineStr">
         <is>
           <t>離子交換, 對特定金屬去除極高</t>
         </is>
@@ -29021,17 +29021,17 @@
           <t>無攪拌 (過濾)</t>
         </is>
       </c>
-      <c r="Y40" t="inlineStr">
+      <c r="Y40" s="0" t="inlineStr">
         <is>
           <t>SS;濁度</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
+      <c r="Z40" s="0" t="inlineStr">
         <is>
           <t>70~95;70~95</t>
         </is>
       </c>
-      <c r="AA40" t="inlineStr">
+      <c r="AA40" s="0" t="inlineStr">
         <is>
           <t>同砂濾塔</t>
         </is>
@@ -29114,17 +29114,17 @@
           <t>靠氣泡, 一般不攪</t>
         </is>
       </c>
-      <c r="Y41" t="inlineStr">
+      <c r="Y41" s="0" t="inlineStr">
         <is>
           <t>油脂;SS;COD</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
+      <c r="Z41" s="0" t="inlineStr">
         <is>
           <t>80~98;60~90;20~50</t>
         </is>
       </c>
-      <c r="AA41" t="inlineStr">
+      <c r="AA41" s="0" t="inlineStr">
         <is>
           <t>加壓浮除, 油脂主力, SS 伴隨</t>
         </is>
@@ -29207,17 +29207,17 @@
           <t>靠浮力</t>
         </is>
       </c>
-      <c r="Y42" t="inlineStr">
+      <c r="Y42" s="0" t="inlineStr">
         <is>
           <t>油脂</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
+      <c r="Z42" s="0" t="inlineStr">
         <is>
           <t>70~95</t>
         </is>
       </c>
-      <c r="AA42" t="inlineStr">
+      <c r="AA42" s="0" t="inlineStr">
         <is>
           <t>重力分離, 只降油脂</t>
         </is>
@@ -29294,17 +29294,17 @@
           <t>均勻化 + 部分沉降</t>
         </is>
       </c>
-      <c r="Y43" t="inlineStr">
+      <c r="Y43" s="0" t="inlineStr">
         <is>
           <t>SS;油脂</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
+      <c r="Z43" s="0" t="inlineStr">
         <is>
           <t>20~60;30~70</t>
         </is>
       </c>
-      <c r="AA43" t="inlineStr">
+      <c r="AA43" s="0" t="inlineStr">
         <is>
           <t>粗篩/沉砂, 重金屬未沉澱不去除</t>
         </is>
@@ -29385,7 +29385,7 @@
           <t>視是否加藥</t>
         </is>
       </c>
-      <c r="AA44" t="inlineStr">
+      <c r="AA44" s="0" t="inlineStr">
         <is>
           <t>回收濾液, 質量守恆但含水率高</t>
         </is>
@@ -32657,16 +32657,187 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="7" t="n"/>
-      <c r="E22" s="7" t="n"/>
+      <c r="A22" s="0" t="inlineStr">
+        <is>
+          <t>D-DOSE-021</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="C22" s="0" t="inlineStr">
+        <is>
+          <t>pH調整池</t>
+        </is>
+      </c>
+      <c r="D22" s="0" t="inlineStr">
+        <is>
+          <t>活性碳</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>應加</t>
+        </is>
+      </c>
+      <c r="H22" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="I22" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="L22" s="0" t="inlineStr">
+        <is>
+          <t>COD/BOD/色度 吸附去除, 但活性碳粉本身是 SS</t>
+        </is>
+      </c>
+      <c r="N22" s="0" t="inlineStr">
+        <is>
+          <t>粉末活性碳作助濾/吸附劑, 引入 SS</t>
+        </is>
+      </c>
+      <c r="O22" s="0" t="inlineStr">
+        <is>
+          <t>後處理</t>
+        </is>
+      </c>
+      <c r="R22" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="S22" s="0" t="inlineStr">
+        <is>
+          <t>懸浮固體（mg/L）</t>
+        </is>
+      </c>
+      <c r="T22" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="23">
-      <c r="B23" s="7" t="n"/>
-      <c r="E23" s="7" t="n"/>
+      <c r="A23" s="0" t="inlineStr">
+        <is>
+          <t>D-DOSE-022</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>通用</t>
+        </is>
+      </c>
+      <c r="C23" s="0" t="inlineStr">
+        <is>
+          <t>快混池</t>
+        </is>
+      </c>
+      <c r="D23" s="0" t="inlineStr">
+        <is>
+          <t>活性碳</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>應加</t>
+        </is>
+      </c>
+      <c r="H23" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="I23" s="0" t="n">
+        <v>60</v>
+      </c>
+      <c r="L23" s="0" t="inlineStr">
+        <is>
+          <t>COD/BOD/色度 吸附去除, 但活性碳粉本身是 SS</t>
+        </is>
+      </c>
+      <c r="N23" s="0" t="inlineStr">
+        <is>
+          <t>混凝時加活性碳助沉</t>
+        </is>
+      </c>
+      <c r="O23" s="0" t="inlineStr">
+        <is>
+          <t>後處理</t>
+        </is>
+      </c>
+      <c r="R23" s="0" t="n">
+        <v>100</v>
+      </c>
+      <c r="S23" s="0" t="inlineStr">
+        <is>
+          <t>懸浮固體（mg/L）</t>
+        </is>
+      </c>
+      <c r="T23" s="0" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="24">
-      <c r="B24" s="7" t="n"/>
-      <c r="E24" s="7" t="n"/>
+      <c r="A24" s="0" t="inlineStr">
+        <is>
+          <t>D-DOSE-023</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>含氟系</t>
+        </is>
+      </c>
+      <c r="C24" s="0" t="inlineStr">
+        <is>
+          <t>pH調整池</t>
+        </is>
+      </c>
+      <c r="D24" s="0" t="inlineStr">
+        <is>
+          <t>CaCl2</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>應加</t>
+        </is>
+      </c>
+      <c r="H24" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="I24" s="0" t="n">
+        <v>90</v>
+      </c>
+      <c r="J24" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="K24" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="L24" s="0" t="inlineStr">
+        <is>
+          <t>F⁻ 沉澱為 CaF₂</t>
+        </is>
+      </c>
+      <c r="N24" s="0" t="inlineStr">
+        <is>
+          <t>含氟廢水加 CaCl₂ 沉氟</t>
+        </is>
+      </c>
+      <c r="O24" s="0" t="inlineStr">
+        <is>
+          <t>主處理</t>
+        </is>
+      </c>
+      <c r="R24" s="0" t="n">
+        <v>50</v>
+      </c>
+      <c r="S24" s="0" t="inlineStr">
+        <is>
+          <t>懸浮固體（mg/L）</t>
+        </is>
+      </c>
+      <c r="T24" s="0" t="n">
+        <v>1.11</v>
+      </c>
     </row>
     <row r="25">
       <c r="B25" s="7" t="n"/>

--- a/規則庫.xlsx
+++ b/規則庫.xlsx
@@ -25486,7 +25486,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA100"/>
+  <dimension ref="A1:AB100"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="21.13" customWidth="1" style="19" min="7" max="7"/>
@@ -25629,6 +25629,11 @@
           <t>削減率學理依據</t>
         </is>
       </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>必備機具</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="inlineStr">
@@ -25710,6 +25715,11 @@
           <t>純調 pH, 不去除任何項目</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>攪拌機,加藥機,pH計</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="7" t="inlineStr">
@@ -25791,6 +25801,11 @@
           <t>純調 pH, 不去除任何項目</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>攪拌機,加藥機,pH計</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
@@ -25872,6 +25887,11 @@
           <t>純中和, 不去除任何項目</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>攪拌機,加藥機,pH計</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="inlineStr">
@@ -25967,6 +25987,11 @@
           <t>調pH + 快混, 加PAC後 SS 略升, 未沉澱不去除重金屬</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>攪拌機,加藥機,pH計</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -26062,6 +26087,11 @@
           <t>同上</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>攪拌機,加藥機,pH計</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
@@ -26157,6 +26187,11 @@
           <t>D054 學理: 快混無沉澱功能, 不應表現重金屬去除</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>攪拌機,加藥機</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -26252,6 +26287,11 @@
           <t>同快混槽</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>攪拌機,加藥機</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="inlineStr">
@@ -26347,6 +26387,11 @@
           <t>絮凝但未分離, 質量守恆</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>攪拌機,加藥機</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -26442,6 +26487,11 @@
           <t>同慢混池</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>攪拌機,加藥機</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
@@ -26535,6 +26585,11 @@
           <t>重力沉降 + 絮體氫氧化物沉澱, COD/BOD 隨 SS 略降</t>
         </is>
       </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>排泥</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
@@ -26628,6 +26683,11 @@
           <t>同沉澱池</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>排泥</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="inlineStr">
@@ -26719,6 +26779,11 @@
           <t>加壓浮除, 油脂主力, SS 伴隨</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>加藥機,排泥</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
@@ -26800,6 +26865,11 @@
           <t>顆粒物理過濾, 溶解性物質不去除, 反洗水 SS↑↑</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>反洗</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="inlineStr">
@@ -26881,6 +26951,11 @@
           <t>吸附有機物/色度/餘氯, SS 不應去除 (會堵塞)</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>反洗</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
@@ -26962,6 +27037,11 @@
           <t>同活性碳吸附塔</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>反洗</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="inlineStr">
@@ -27043,6 +27123,11 @@
           <t>離子交換, 對特定金屬去除極高</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>再生系統</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="inlineStr">
@@ -27142,6 +27227,11 @@
       <c r="AA18" s="0" t="inlineStr">
         <is>
           <t>活性污泥好氧分解, 氨氮硝化, MLSS 微生物自增</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>鼓風機,液位計</t>
         </is>
       </c>
     </row>
@@ -27235,6 +27325,11 @@
           <t>化學氧化分解有機物</t>
         </is>
       </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>攪拌機,加藥機</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
@@ -27326,6 +27421,11 @@
       <c r="AA20" s="0" t="inlineStr">
         <is>
           <t>厭氧分解產沼氣, pH 可能酸化</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>液位計</t>
         </is>
       </c>
     </row>
@@ -27411,6 +27511,11 @@
           <t>機械脫水</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>加藥機</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
@@ -27502,6 +27607,11 @@
           <t>重力濃縮</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>排泥</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
@@ -27579,6 +27689,11 @@
           <t>儲存, 質量守恆; 略沉降可能微降含水率</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>液位計</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
@@ -27660,6 +27775,11 @@
           <t>應守恆</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>液位計</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="inlineStr">
@@ -27741,6 +27861,11 @@
           <t>應守恆</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>液位計</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="7" t="inlineStr">
@@ -27822,6 +27947,11 @@
           <t>均勻化水質波動, 質量守恆</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>液位計</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="inlineStr">
@@ -27903,6 +28033,11 @@
           <t>同調勻池</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>液位計</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
@@ -27982,6 +28117,11 @@
           <t>僅匯流</t>
         </is>
       </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>液位計</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="inlineStr">
@@ -28059,6 +28199,11 @@
           <t>視批次配方而定, 無固定去除率</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>攪拌機,加藥機</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
@@ -28130,6 +28275,11 @@
           <t>放流前緩衝, 應守恆</t>
         </is>
       </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>流量計</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="inlineStr">
@@ -28223,6 +28373,11 @@
           <t>生物膜好氧分解</t>
         </is>
       </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>鼓風機</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
@@ -28322,6 +28477,11 @@
       <c r="AA32" s="0" t="inlineStr">
         <is>
           <t>生物 + 膜過濾, SS 極低</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>鼓風機,液位計</t>
         </is>
       </c>
     </row>
@@ -28415,6 +28575,11 @@
           <t>NaClO 破氰: CN⁻ → CNO⁻ → N₂↑</t>
         </is>
       </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>攪拌機,加藥機,ORP計</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
@@ -28506,6 +28671,11 @@
           <t>NaHSO₃ 還原 Cr⁶⁺ → Cr³⁺ (總鉻不去除, 只變價)</t>
         </is>
       </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>攪拌機,加藥機,ORP計,pH計</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="inlineStr">
@@ -28601,6 +28771,11 @@
           <t>只形成絮體, 未分離</t>
         </is>
       </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>攪拌機,加藥機</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
@@ -28690,6 +28865,11 @@
           <t>離心高速脫水</t>
         </is>
       </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>加藥機</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
@@ -28779,6 +28959,11 @@
           <t>帶濾中速脫水</t>
         </is>
       </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>加藥機</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
@@ -28870,6 +29055,11 @@
           <t>同濃縮槽</t>
         </is>
       </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>排泥</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="inlineStr">
@@ -28955,6 +29145,11 @@
           <t>離子交換, 對特定金屬去除極高</t>
         </is>
       </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>再生系統</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
@@ -29036,6 +29231,11 @@
           <t>同砂濾塔</t>
         </is>
       </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>反洗</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="inlineStr">
@@ -29129,6 +29329,11 @@
           <t>加壓浮除, 油脂主力, SS 伴隨</t>
         </is>
       </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>加藥機,排泥</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
@@ -29222,6 +29427,11 @@
           <t>重力分離, 只降油脂</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>排泥</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="inlineStr">
@@ -29309,6 +29519,7 @@
           <t>粗篩/沉砂, 重金屬未沉澱不去除</t>
         </is>
       </c>
+      <c r="AB43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
@@ -29388,6 +29599,11 @@
       <c r="AA44" s="0" t="inlineStr">
         <is>
           <t>回收濾液, 質量守恆但含水率高</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>液位計</t>
         </is>
       </c>
     </row>

--- a/規則庫.xlsx
+++ b/規則庫.xlsx
@@ -25629,7 +25629,7 @@
           <t>削減率學理依據</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AB1" s="0" t="inlineStr">
         <is>
           <t>必備機具</t>
         </is>
@@ -25715,7 +25715,7 @@
           <t>純調 pH, 不去除任何項目</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB2" s="0" t="inlineStr">
         <is>
           <t>攪拌機,加藥機,pH計</t>
         </is>
@@ -25801,7 +25801,7 @@
           <t>純調 pH, 不去除任何項目</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB3" s="0" t="inlineStr">
         <is>
           <t>攪拌機,加藥機,pH計</t>
         </is>
@@ -25820,7 +25820,7 @@
       </c>
       <c r="C4" s="7" t="inlineStr">
         <is>
-          <t>pH, 水溫</t>
+          <t>pH, SS, 水溫</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
@@ -25887,7 +25887,7 @@
           <t>純中和, 不去除任何項目</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AB4" s="0" t="inlineStr">
         <is>
           <t>攪拌機,加藥機,pH計</t>
         </is>
@@ -25987,7 +25987,7 @@
           <t>調pH + 快混, 加PAC後 SS 略升, 未沉澱不去除重金屬</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AB5" s="0" t="inlineStr">
         <is>
           <t>攪拌機,加藥機,pH計</t>
         </is>
@@ -26087,7 +26087,7 @@
           <t>同上</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AB6" s="0" t="inlineStr">
         <is>
           <t>攪拌機,加藥機,pH計</t>
         </is>
@@ -26187,7 +26187,7 @@
           <t>D054 學理: 快混無沉澱功能, 不應表現重金屬去除</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AB7" s="0" t="inlineStr">
         <is>
           <t>攪拌機,加藥機</t>
         </is>
@@ -26287,7 +26287,7 @@
           <t>同快混槽</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AB8" s="0" t="inlineStr">
         <is>
           <t>攪拌機,加藥機</t>
         </is>
@@ -26387,7 +26387,7 @@
           <t>絮凝但未分離, 質量守恆</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AB9" s="0" t="inlineStr">
         <is>
           <t>攪拌機,加藥機</t>
         </is>
@@ -26487,7 +26487,7 @@
           <t>同慢混池</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AB10" s="0" t="inlineStr">
         <is>
           <t>攪拌機,加藥機</t>
         </is>
@@ -26585,7 +26585,7 @@
           <t>重力沉降 + 絮體氫氧化物沉澱, COD/BOD 隨 SS 略降</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AB11" s="0" t="inlineStr">
         <is>
           <t>排泥</t>
         </is>
@@ -26683,7 +26683,7 @@
           <t>同沉澱池</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AB12" s="0" t="inlineStr">
         <is>
           <t>排泥</t>
         </is>
@@ -26779,7 +26779,7 @@
           <t>加壓浮除, 油脂主力, SS 伴隨</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
+      <c r="AB13" s="0" t="inlineStr">
         <is>
           <t>加藥機,排泥</t>
         </is>
@@ -26865,7 +26865,7 @@
           <t>顆粒物理過濾, 溶解性物質不去除, 反洗水 SS↑↑</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
+      <c r="AB14" s="0" t="inlineStr">
         <is>
           <t>反洗</t>
         </is>
@@ -26951,7 +26951,7 @@
           <t>吸附有機物/色度/餘氯, SS 不應去除 (會堵塞)</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
+      <c r="AB15" s="0" t="inlineStr">
         <is>
           <t>反洗</t>
         </is>
@@ -27037,7 +27037,7 @@
           <t>同活性碳吸附塔</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
+      <c r="AB16" s="0" t="inlineStr">
         <is>
           <t>反洗</t>
         </is>
@@ -27123,7 +27123,7 @@
           <t>離子交換, 對特定金屬去除極高</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
+      <c r="AB17" s="0" t="inlineStr">
         <is>
           <t>再生系統</t>
         </is>
@@ -27229,7 +27229,7 @@
           <t>活性污泥好氧分解, 氨氮硝化, MLSS 微生物自增</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
+      <c r="AB18" s="0" t="inlineStr">
         <is>
           <t>鼓風機,液位計</t>
         </is>
@@ -27248,7 +27248,7 @@
       </c>
       <c r="C19" s="7" t="inlineStr">
         <is>
-          <t>COD, BOD, 真色色度</t>
+          <t>COD, BOD, 真色色度, pH, ORP</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
@@ -27325,7 +27325,7 @@
           <t>化學氧化分解有機物</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
+      <c r="AB19" s="0" t="inlineStr">
         <is>
           <t>攪拌機,加藥機</t>
         </is>
@@ -27423,7 +27423,7 @@
           <t>厭氧分解產沼氣, pH 可能酸化</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
+      <c r="AB20" s="0" t="inlineStr">
         <is>
           <t>液位計</t>
         </is>
@@ -27511,7 +27511,7 @@
           <t>機械脫水</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
+      <c r="AB21" s="0" t="inlineStr">
         <is>
           <t>加藥機</t>
         </is>
@@ -27607,7 +27607,7 @@
           <t>重力濃縮</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
+      <c r="AB22" s="0" t="inlineStr">
         <is>
           <t>排泥</t>
         </is>
@@ -27689,7 +27689,7 @@
           <t>儲存, 質量守恆; 略沉降可能微降含水率</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
+      <c r="AB23" s="0" t="inlineStr">
         <is>
           <t>液位計</t>
         </is>
@@ -27775,7 +27775,7 @@
           <t>應守恆</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
+      <c r="AB24" s="0" t="inlineStr">
         <is>
           <t>液位計</t>
         </is>
@@ -27861,7 +27861,7 @@
           <t>應守恆</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
+      <c r="AB25" s="0" t="inlineStr">
         <is>
           <t>液位計</t>
         </is>
@@ -27947,7 +27947,7 @@
           <t>均勻化水質波動, 質量守恆</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
+      <c r="AB26" s="0" t="inlineStr">
         <is>
           <t>液位計</t>
         </is>
@@ -28033,7 +28033,7 @@
           <t>同調勻池</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
+      <c r="AB27" s="0" t="inlineStr">
         <is>
           <t>液位計</t>
         </is>
@@ -28117,7 +28117,7 @@
           <t>僅匯流</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
+      <c r="AB28" s="0" t="inlineStr">
         <is>
           <t>液位計</t>
         </is>
@@ -28136,7 +28136,7 @@
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
-          <t>視批次而定</t>
+          <t>pH, SS, 水溫, 氟鹽</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
@@ -28199,7 +28199,7 @@
           <t>視批次配方而定, 無固定去除率</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
+      <c r="AB29" s="0" t="inlineStr">
         <is>
           <t>攪拌機,加藥機</t>
         </is>
@@ -28275,7 +28275,7 @@
           <t>放流前緩衝, 應守恆</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
+      <c r="AB30" s="0" t="inlineStr">
         <is>
           <t>流量計</t>
         </is>
@@ -28373,7 +28373,7 @@
           <t>生物膜好氧分解</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
+      <c r="AB31" s="0" t="inlineStr">
         <is>
           <t>鼓風機</t>
         </is>
@@ -28479,7 +28479,7 @@
           <t>生物 + 膜過濾, SS 極低</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
+      <c r="AB32" s="0" t="inlineStr">
         <is>
           <t>鼓風機,液位計</t>
         </is>
@@ -28575,7 +28575,7 @@
           <t>NaClO 破氰: CN⁻ → CNO⁻ → N₂↑</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
+      <c r="AB33" s="0" t="inlineStr">
         <is>
           <t>攪拌機,加藥機,ORP計</t>
         </is>
@@ -28671,7 +28671,7 @@
           <t>NaHSO₃ 還原 Cr⁶⁺ → Cr³⁺ (總鉻不去除, 只變價)</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
+      <c r="AB34" s="0" t="inlineStr">
         <is>
           <t>攪拌機,加藥機,ORP計,pH計</t>
         </is>
@@ -28771,7 +28771,7 @@
           <t>只形成絮體, 未分離</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
+      <c r="AB35" s="0" t="inlineStr">
         <is>
           <t>攪拌機,加藥機</t>
         </is>
@@ -28865,7 +28865,7 @@
           <t>離心高速脫水</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
+      <c r="AB36" s="0" t="inlineStr">
         <is>
           <t>加藥機</t>
         </is>
@@ -28959,7 +28959,7 @@
           <t>帶濾中速脫水</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
+      <c r="AB37" s="0" t="inlineStr">
         <is>
           <t>加藥機</t>
         </is>
@@ -29055,7 +29055,7 @@
           <t>同濃縮槽</t>
         </is>
       </c>
-      <c r="AB38" t="inlineStr">
+      <c r="AB38" s="0" t="inlineStr">
         <is>
           <t>排泥</t>
         </is>
@@ -29145,7 +29145,7 @@
           <t>離子交換, 對特定金屬去除極高</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
+      <c r="AB39" s="0" t="inlineStr">
         <is>
           <t>再生系統</t>
         </is>
@@ -29231,7 +29231,7 @@
           <t>同砂濾塔</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
+      <c r="AB40" s="0" t="inlineStr">
         <is>
           <t>反洗</t>
         </is>
@@ -29329,7 +29329,7 @@
           <t>加壓浮除, 油脂主力, SS 伴隨</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
+      <c r="AB41" s="0" t="inlineStr">
         <is>
           <t>加藥機,排泥</t>
         </is>
@@ -29427,7 +29427,7 @@
           <t>重力分離, 只降油脂</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
+      <c r="AB42" s="0" t="inlineStr">
         <is>
           <t>排泥</t>
         </is>
@@ -29519,7 +29519,7 @@
           <t>粗篩/沉砂, 重金屬未沉澱不去除</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr"/>
+      <c r="AB43" s="0" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
@@ -29601,7 +29601,7 @@
           <t>回收濾液, 質量守恆但含水率高</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
+      <c r="AB44" s="0" t="inlineStr">
         <is>
           <t>液位計</t>
         </is>
